--- a/data/Plan.xlsx
+++ b/data/Plan.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raman/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raman/Documents/GitHub/production-board/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25FE3562-2D46-E341-A8D5-6F7AB792E18B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F21B4E-42CE-7044-B603-52723091E731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="680" yWindow="660" windowWidth="28040" windowHeight="16560" xr2:uid="{7C08584A-5D47-2049-B143-911B93E5D6E0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="113">
   <si>
     <t>Date</t>
   </si>
@@ -158,12 +158,6 @@
     <t>Brightening Face Serum(10% VitaminC)30ml</t>
   </si>
   <si>
-    <t>CAP119</t>
-  </si>
-  <si>
-    <t>AHA Body Lotion - 473 ml</t>
-  </si>
-  <si>
     <t>BA98</t>
   </si>
   <si>
@@ -176,12 +170,6 @@
     <t>Anti-Frizz Leave-In Conditioner</t>
   </si>
   <si>
-    <t>CAP153</t>
-  </si>
-  <si>
-    <t>Exfoliating face wash 100 ml</t>
-  </si>
-  <si>
     <t>BA66</t>
   </si>
   <si>
@@ -200,12 +188,6 @@
     <t>Anti-Dandruff Conditioner 100 gm</t>
   </si>
   <si>
-    <t>USTTBA10</t>
-  </si>
-  <si>
-    <t>EXPERT | Ultra Smoothing Shampoo (250 ML) -  TikTok US</t>
-  </si>
-  <si>
     <t>BA50</t>
   </si>
   <si>
@@ -236,12 +218,6 @@
     <t>Exfoliating Body Wash-236ml</t>
   </si>
   <si>
-    <t>BA88</t>
-  </si>
-  <si>
-    <t>Gentle Cleansing Shampoo- 750ml</t>
-  </si>
-  <si>
     <t>BA109</t>
   </si>
   <si>
@@ -258,6 +234,150 @@
   </si>
   <si>
     <t>Curl Intensifying Leave in Conditioner USTT</t>
+  </si>
+  <si>
+    <t>CAP165</t>
+  </si>
+  <si>
+    <t>Epsom Body Wash - 236ml</t>
+  </si>
+  <si>
+    <t>CAP24</t>
+  </si>
+  <si>
+    <t>Exfoliating Body Wash (236 ml)</t>
+  </si>
+  <si>
+    <t>CAP146</t>
+  </si>
+  <si>
+    <t>Clarifying Face Serum - 10ml</t>
+  </si>
+  <si>
+    <t>BA11</t>
+  </si>
+  <si>
+    <t>EXPERT | Volumizing mask ( 250 gms )</t>
+  </si>
+  <si>
+    <t>BA87</t>
+  </si>
+  <si>
+    <t>Advanced Anti-Grey Hair Serum 50ml</t>
+  </si>
+  <si>
+    <t>CO358</t>
+  </si>
+  <si>
+    <t>Combo- Anti-Dandruff Shampoo (100ml) + Anti-Dandruff Conditioner (100g)</t>
+  </si>
+  <si>
+    <t>CAP144</t>
+  </si>
+  <si>
+    <t>Oil &amp; Acne Control Face Wash - Flipkart pack of 2</t>
+  </si>
+  <si>
+    <t>BA94</t>
+  </si>
+  <si>
+    <t>Damage Repair Hair Serum 100ml</t>
+  </si>
+  <si>
+    <t>BA47</t>
+  </si>
+  <si>
+    <t>Curl Defining Hair Gel 140 ml</t>
+  </si>
+  <si>
+    <t>CAP1</t>
+  </si>
+  <si>
+    <t>Acne Control Body Wash (236 ml)</t>
+  </si>
+  <si>
+    <t>CAP83</t>
+  </si>
+  <si>
+    <t>Brightening Boost Face Wash</t>
+  </si>
+  <si>
+    <t>CAP17</t>
+  </si>
+  <si>
+    <t>Brightening Body Wash (473 ml)</t>
+  </si>
+  <si>
+    <t>CAP77</t>
+  </si>
+  <si>
+    <t>Exfoliating Body Scrub - 75 gms</t>
+  </si>
+  <si>
+    <t>CAP34</t>
+  </si>
+  <si>
+    <t>Hydrating Body Wash (236 ml)</t>
+  </si>
+  <si>
+    <t>BA105</t>
+  </si>
+  <si>
+    <t>Ultra smoothing shampoo 100 ml</t>
+  </si>
+  <si>
+    <t>CAP16</t>
+  </si>
+  <si>
+    <t>Brightening Body Wash (236 ml)</t>
+  </si>
+  <si>
+    <t>CO357</t>
+  </si>
+  <si>
+    <t>Combo- Anti-Hairfall Shampoo (100ml) + Anti-Hairfall Conditioner (100g)</t>
+  </si>
+  <si>
+    <t>CO343</t>
+  </si>
+  <si>
+    <t>Ultra smoothing kit ( shampoo 40 ml + mask 40 gm)</t>
+  </si>
+  <si>
+    <t>CAP25</t>
+  </si>
+  <si>
+    <t>Exfoliating Body Wash (473 ml)</t>
+  </si>
+  <si>
+    <t>CAP126</t>
+  </si>
+  <si>
+    <t>Chemist at Play Underarm Roll On Aqua 75ml</t>
+  </si>
+  <si>
+    <t>USTTCAP70</t>
+  </si>
+  <si>
+    <t> Roll On -  White jasmine 40 ml- Tik Tok US</t>
+  </si>
+  <si>
+    <t>CAP145</t>
+  </si>
+  <si>
+    <t>Oil &amp; Acne Control Face Wash - Flipkart pack of 3</t>
+  </si>
+  <si>
+    <t>CAP173</t>
+  </si>
+  <si>
+    <t>Gentle Exfoliating Face Wash 75ml- Pack of 2</t>
+  </si>
+  <si>
+    <t>CAP137</t>
+  </si>
+  <si>
+    <t>Oil &amp; Acne Control Face Wash 100ml - Flipkart</t>
   </si>
 </sst>
 </file>
@@ -654,7 +774,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C578346-EE80-DF41-8099-4E3028D96EBE}">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -682,7 +802,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>65</v>
@@ -691,10 +811,10 @@
         <v>66</v>
       </c>
       <c r="D2" s="5">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="E2" s="5">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="4">
@@ -703,19 +823,19 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="D3" s="5">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="E3" s="5">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="4">
@@ -724,19 +844,19 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="D4" s="5">
-        <v>1500</v>
+        <v>6000</v>
       </c>
       <c r="E4" s="5">
-        <v>1500</v>
+        <v>6000</v>
       </c>
       <c r="F4" s="6"/>
       <c r="G4" s="4">
@@ -745,19 +865,19 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D5" s="5">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="E5" s="5">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="4">
@@ -766,19 +886,19 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="D6" s="5">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="E6" s="5">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="4">
@@ -787,19 +907,19 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="D7" s="5">
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="E7" s="5">
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="4">
@@ -808,19 +928,19 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D8" s="5">
-        <v>18000</v>
+        <v>12000</v>
       </c>
       <c r="E8" s="5">
-        <v>18000</v>
+        <v>12000</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="4">
@@ -829,19 +949,19 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="D9" s="5">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E9" s="5">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="4">
@@ -850,19 +970,19 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="D10" s="5">
-        <v>20000</v>
+        <v>12000</v>
       </c>
       <c r="E10" s="5">
-        <v>20000</v>
+        <v>12000</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="4">
@@ -871,19 +991,19 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D11" s="5">
-        <v>40000</v>
+        <v>15000</v>
       </c>
       <c r="E11" s="5">
-        <v>40000</v>
+        <v>15000</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="4">
@@ -892,19 +1012,19 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D12" s="5">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="E12" s="5">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="4">
@@ -916,16 +1036,16 @@
         <v>46252</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="D13" s="5">
-        <v>6000</v>
+        <v>24000</v>
       </c>
       <c r="E13" s="5">
-        <v>6000</v>
+        <v>24000</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="4">
@@ -937,16 +1057,16 @@
         <v>46252</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="D14" s="5">
-        <v>10000</v>
+        <v>28000</v>
       </c>
       <c r="E14" s="5">
-        <v>10000</v>
+        <v>28000</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="4">
@@ -958,16 +1078,16 @@
         <v>46252</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="D15" s="5">
-        <v>15000</v>
+        <v>45000</v>
       </c>
       <c r="E15" s="5">
-        <v>15000</v>
+        <v>45000</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="4">
@@ -976,19 +1096,19 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="D16" s="5">
-        <v>24000</v>
-      </c>
-      <c r="E16" s="5">
-        <v>24000</v>
+        <v>1500</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="4">
@@ -997,19 +1117,19 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="D17" s="5">
-        <v>28000</v>
+        <v>5000</v>
       </c>
       <c r="E17" s="5">
-        <v>28000</v>
+        <v>5000</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="4">
@@ -1018,19 +1138,19 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D18" s="5">
-        <v>20000</v>
+        <v>4500</v>
       </c>
       <c r="E18" s="5">
-        <v>20000</v>
+        <v>4500</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="4">
@@ -1039,19 +1159,19 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="D19" s="5">
-        <v>20000</v>
+        <v>6000</v>
       </c>
       <c r="E19" s="5">
-        <v>20000</v>
+        <v>6000</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="4">
@@ -1060,19 +1180,19 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="D20" s="5">
-        <v>45000</v>
+        <v>7000</v>
       </c>
       <c r="E20" s="5">
-        <v>45000</v>
+        <v>7000</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="4">
@@ -1084,16 +1204,16 @@
         <v>46253</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D21" s="5">
-        <v>1500</v>
-      </c>
-      <c r="E21" s="3">
-        <v>0</v>
+        <v>7000</v>
+      </c>
+      <c r="E21" s="5">
+        <v>7000</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="4">
@@ -1105,16 +1225,16 @@
         <v>46253</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="D22" s="5">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="E22" s="5">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="4">
@@ -1126,16 +1246,16 @@
         <v>46253</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D23" s="5">
-        <v>4500</v>
+        <v>20000</v>
       </c>
       <c r="E23" s="5">
-        <v>4500</v>
+        <v>20000</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="4">
@@ -1147,16 +1267,16 @@
         <v>46253</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D24" s="5">
-        <v>6000</v>
+        <v>20000</v>
       </c>
       <c r="E24" s="5">
-        <v>6000</v>
+        <v>20000</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="4">
@@ -1168,16 +1288,16 @@
         <v>46253</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D25" s="5">
-        <v>10000</v>
+        <v>35000</v>
       </c>
       <c r="E25" s="5">
-        <v>10000</v>
+        <v>35000</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="4">
@@ -1189,16 +1309,16 @@
         <v>46253</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D26" s="5">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="E26" s="5">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="4">
@@ -1207,19 +1327,19 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="D27" s="5">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="E27" s="5">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="4">
@@ -1228,19 +1348,19 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D28" s="5">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E28" s="5">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="4">
@@ -1249,19 +1369,19 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="D29" s="5">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E29" s="5">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="4">
@@ -1270,19 +1390,19 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>9</v>
+        <v>77</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="D30" s="5">
-        <v>20000</v>
+        <v>11000</v>
       </c>
       <c r="E30" s="5">
-        <v>20000</v>
+        <v>11000</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="4">
@@ -1291,19 +1411,19 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D31" s="5">
-        <v>40000</v>
+        <v>13000</v>
       </c>
       <c r="E31" s="5">
-        <v>40000</v>
+        <v>13000</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="4">
@@ -1315,16 +1435,16 @@
         <v>46254</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D32" s="5">
-        <v>11000</v>
+        <v>20000</v>
       </c>
       <c r="E32" s="5">
-        <v>11000</v>
+        <v>20000</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="4">
@@ -1336,16 +1456,16 @@
         <v>46254</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="D33" s="5">
-        <v>13000</v>
+        <v>20000</v>
       </c>
       <c r="E33" s="5">
-        <v>13000</v>
+        <v>20000</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="4">
@@ -1357,16 +1477,16 @@
         <v>46254</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="D34" s="5">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="E34" s="5">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="F34" s="6"/>
       <c r="G34" s="4">
@@ -1378,16 +1498,16 @@
         <v>46254</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D35" s="5">
-        <v>20000</v>
+        <v>45000</v>
       </c>
       <c r="E35" s="5">
-        <v>20000</v>
+        <v>45000</v>
       </c>
       <c r="F35" s="6"/>
       <c r="G35" s="4">
@@ -1396,19 +1516,19 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="D36" s="5">
-        <v>40000</v>
+        <v>5000</v>
       </c>
       <c r="E36" s="5">
-        <v>40000</v>
+        <v>5000</v>
       </c>
       <c r="F36" s="6"/>
       <c r="G36" s="4">
@@ -1417,19 +1537,19 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="D37" s="5">
-        <v>45000</v>
+        <v>3200</v>
       </c>
       <c r="E37" s="5">
-        <v>45000</v>
+        <v>3200</v>
       </c>
       <c r="F37" s="6"/>
       <c r="G37" s="4">
@@ -1437,11 +1557,21 @@
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" s="6"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
+      <c r="A38" s="2">
+        <v>46255</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D38" s="5">
+        <v>8000</v>
+      </c>
+      <c r="E38" s="5">
+        <v>8000</v>
+      </c>
       <c r="F38" s="6"/>
       <c r="G38" s="4">
         <v>0</v>
@@ -1452,10 +1582,10 @@
         <v>46255</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="D39" s="5">
         <v>10000</v>
@@ -1473,16 +1603,16 @@
         <v>46255</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="D40" s="5">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E40" s="5">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F40" s="6"/>
       <c r="G40" s="4">
@@ -1494,16 +1624,16 @@
         <v>46255</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D41" s="5">
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="E41" s="5">
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="F41" s="6"/>
       <c r="G41" s="4">
@@ -1515,16 +1645,16 @@
         <v>46255</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="D42" s="5">
-        <v>20000</v>
+        <v>11000</v>
       </c>
       <c r="E42" s="5">
-        <v>20000</v>
+        <v>11000</v>
       </c>
       <c r="F42" s="6"/>
       <c r="G42" s="4">
@@ -1536,16 +1666,16 @@
         <v>46255</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="D43" s="5">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="E43" s="5">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="F43" s="6"/>
       <c r="G43" s="4">
@@ -1557,10 +1687,10 @@
         <v>46255</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D44" s="5">
         <v>40000</v>
@@ -1574,11 +1704,21 @@
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A45" s="6"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
+      <c r="A45" s="2">
+        <v>46255</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D45" s="5">
+        <v>40000</v>
+      </c>
+      <c r="E45" s="5">
+        <v>40000</v>
+      </c>
       <c r="F45" s="6"/>
       <c r="G45" s="4">
         <v>0</v>
@@ -1589,16 +1729,16 @@
         <v>46256</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="D46" s="5">
-        <v>28000</v>
+        <v>2000</v>
       </c>
       <c r="E46" s="5">
-        <v>28000</v>
+        <v>2000</v>
       </c>
       <c r="F46" s="6"/>
       <c r="G46" s="4">
@@ -1610,16 +1750,16 @@
         <v>46256</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>7</v>
+        <v>89</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="D47" s="5">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="E47" s="5">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="F47" s="6"/>
       <c r="G47" s="4">
@@ -1631,10 +1771,10 @@
         <v>46256</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="D48" s="5">
         <v>8000</v>
@@ -1652,16 +1792,16 @@
         <v>46256</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="D49" s="5">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="E49" s="5">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="F49" s="6"/>
       <c r="G49" s="4">
@@ -1673,16 +1813,16 @@
         <v>46256</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>11</v>
+        <v>93</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>12</v>
+        <v>94</v>
       </c>
       <c r="D50" s="5">
-        <v>40000</v>
+        <v>10000</v>
       </c>
       <c r="E50" s="5">
-        <v>40000</v>
+        <v>10000</v>
       </c>
       <c r="F50" s="6"/>
       <c r="G50" s="4">
@@ -1694,21 +1834,704 @@
         <v>46256</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="D51" s="5">
-        <v>40000</v>
+        <v>15000</v>
       </c>
       <c r="E51" s="5">
-        <v>40000</v>
+        <v>15000</v>
       </c>
       <c r="F51" s="6"/>
       <c r="G51" s="4">
         <v>0</v>
       </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A52" s="2">
+        <v>46256</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D52" s="5">
+        <v>20000</v>
+      </c>
+      <c r="E52" s="5">
+        <v>20000</v>
+      </c>
+      <c r="F52" s="6"/>
+      <c r="G52" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A53" s="2">
+        <v>46256</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="5">
+        <v>20000</v>
+      </c>
+      <c r="E53" s="5">
+        <v>20000</v>
+      </c>
+      <c r="F53" s="6"/>
+      <c r="G53" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="2">
+        <v>46256</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D54" s="5">
+        <v>28000</v>
+      </c>
+      <c r="E54" s="5">
+        <v>28000</v>
+      </c>
+      <c r="F54" s="6"/>
+      <c r="G54" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="2">
+        <v>46256</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D55" s="5">
+        <v>40000</v>
+      </c>
+      <c r="E55" s="5">
+        <v>40000</v>
+      </c>
+      <c r="F55" s="6"/>
+      <c r="G55" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D56" s="5">
+        <v>8000</v>
+      </c>
+      <c r="E56" s="5">
+        <v>8000</v>
+      </c>
+      <c r="F56" s="6"/>
+      <c r="G56" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D57" s="5">
+        <v>10000</v>
+      </c>
+      <c r="E57" s="5">
+        <v>10000</v>
+      </c>
+      <c r="F57" s="6"/>
+      <c r="G57" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="5">
+        <v>10000</v>
+      </c>
+      <c r="E58" s="5">
+        <v>10000</v>
+      </c>
+      <c r="F58" s="6"/>
+      <c r="G58" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D59" s="5">
+        <v>10000</v>
+      </c>
+      <c r="E59" s="5">
+        <v>10000</v>
+      </c>
+      <c r="F59" s="6"/>
+      <c r="G59" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D60" s="5">
+        <v>15000</v>
+      </c>
+      <c r="E60" s="5">
+        <v>15000</v>
+      </c>
+      <c r="F60" s="6"/>
+      <c r="G60" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D61" s="5">
+        <v>20000</v>
+      </c>
+      <c r="E61" s="5">
+        <v>20000</v>
+      </c>
+      <c r="F61" s="6"/>
+      <c r="G61" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A62" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D62" s="5">
+        <v>20000</v>
+      </c>
+      <c r="E62" s="5">
+        <v>20000</v>
+      </c>
+      <c r="F62" s="6"/>
+      <c r="G62" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A63" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D63" s="5">
+        <v>20000</v>
+      </c>
+      <c r="E63" s="5">
+        <v>20000</v>
+      </c>
+      <c r="F63" s="6"/>
+      <c r="G63" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A64" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D64" s="5">
+        <v>40000</v>
+      </c>
+      <c r="E64" s="5">
+        <v>40000</v>
+      </c>
+      <c r="F64" s="6"/>
+      <c r="G64" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A65" s="2">
+        <v>46258</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D65" s="5">
+        <v>6000</v>
+      </c>
+      <c r="E65" s="5">
+        <v>6000</v>
+      </c>
+      <c r="F65" s="6"/>
+      <c r="G65" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A66" s="2">
+        <v>46258</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D66" s="5">
+        <v>11000</v>
+      </c>
+      <c r="E66" s="5">
+        <v>11000</v>
+      </c>
+      <c r="F66" s="6"/>
+      <c r="G66" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A67" s="2">
+        <v>46258</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D67" s="5">
+        <v>15000</v>
+      </c>
+      <c r="E67" s="5">
+        <v>15000</v>
+      </c>
+      <c r="F67" s="6"/>
+      <c r="G67" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A68" s="2">
+        <v>46258</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D68" s="5">
+        <v>20000</v>
+      </c>
+      <c r="E68" s="5">
+        <v>20000</v>
+      </c>
+      <c r="F68" s="6"/>
+      <c r="G68" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A69" s="2">
+        <v>46258</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D69" s="5">
+        <v>30000</v>
+      </c>
+      <c r="E69" s="5">
+        <v>30000</v>
+      </c>
+      <c r="F69" s="6"/>
+      <c r="G69" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A70" s="2">
+        <v>46258</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D70" s="5">
+        <v>40000</v>
+      </c>
+      <c r="E70" s="5">
+        <v>40000</v>
+      </c>
+      <c r="F70" s="6"/>
+      <c r="G70" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A71" s="2">
+        <v>46258</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D71" s="5">
+        <v>40000</v>
+      </c>
+      <c r="E71" s="5">
+        <v>40000</v>
+      </c>
+      <c r="F71" s="6"/>
+      <c r="G71" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A72" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D72" s="5">
+        <v>2300</v>
+      </c>
+      <c r="E72" s="5">
+        <v>2300</v>
+      </c>
+      <c r="F72" s="6"/>
+      <c r="G72" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A73" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D73" s="5">
+        <v>10000</v>
+      </c>
+      <c r="E73" s="5">
+        <v>10000</v>
+      </c>
+      <c r="F73" s="6"/>
+      <c r="G73" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A74" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D74" s="5">
+        <v>20000</v>
+      </c>
+      <c r="E74" s="5">
+        <v>20000</v>
+      </c>
+      <c r="F74" s="6"/>
+      <c r="G74" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A75" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D75" s="5">
+        <v>20000</v>
+      </c>
+      <c r="E75" s="5">
+        <v>20000</v>
+      </c>
+      <c r="F75" s="6"/>
+      <c r="G75" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A76" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D76" s="5">
+        <v>28000</v>
+      </c>
+      <c r="E76" s="5">
+        <v>28000</v>
+      </c>
+      <c r="F76" s="6"/>
+      <c r="G76" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A77" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D77" s="5">
+        <v>40000</v>
+      </c>
+      <c r="E77" s="5">
+        <v>40000</v>
+      </c>
+      <c r="F77" s="6"/>
+      <c r="G77" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A78" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D78" s="5">
+        <v>40000</v>
+      </c>
+      <c r="E78" s="5">
+        <v>40000</v>
+      </c>
+      <c r="F78" s="6"/>
+      <c r="G78" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A79" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D79" s="5">
+        <v>6000</v>
+      </c>
+      <c r="E79" s="5">
+        <v>6000</v>
+      </c>
+      <c r="F79" s="6"/>
+      <c r="G79" s="6"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A80" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D80" s="5">
+        <v>10000</v>
+      </c>
+      <c r="E80" s="5">
+        <v>10000</v>
+      </c>
+      <c r="F80" s="6"/>
+      <c r="G80" s="6"/>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A81" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D81" s="5">
+        <v>20000</v>
+      </c>
+      <c r="E81" s="5">
+        <v>20000</v>
+      </c>
+      <c r="F81" s="6"/>
+      <c r="G81" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A82" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D82" s="5">
+        <v>20000</v>
+      </c>
+      <c r="E82" s="5">
+        <v>20000</v>
+      </c>
+      <c r="F82" s="6"/>
+      <c r="G82" s="6"/>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A83" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D83" s="5">
+        <v>40000</v>
+      </c>
+      <c r="E83" s="5">
+        <v>40000</v>
+      </c>
+      <c r="F83" s="6"/>
+      <c r="G83" s="6"/>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A84" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D84" s="5">
+        <v>40000</v>
+      </c>
+      <c r="E84" s="5">
+        <v>40000</v>
+      </c>
+      <c r="F84" s="6"/>
+      <c r="G84" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Plan.xlsx
+++ b/data/Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raman/Documents/GitHub/production-board/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F21B4E-42CE-7044-B603-52723091E731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{663DCF84-71CF-DB40-8A81-AE171AE03F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="680" yWindow="660" windowWidth="28040" windowHeight="16560" xr2:uid="{7C08584A-5D47-2049-B143-911B93E5D6E0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="124">
   <si>
     <t>Date</t>
   </si>
@@ -378,6 +378,39 @@
   </si>
   <si>
     <t>Oil &amp; Acne Control Face Wash 100ml - Flipkart</t>
+  </si>
+  <si>
+    <t>CAP139</t>
+  </si>
+  <si>
+    <t>Cherry Lip Balm 4.5gm</t>
+  </si>
+  <si>
+    <t>CAP138</t>
+  </si>
+  <si>
+    <t>Natural Lip Balm 4.5gm</t>
+  </si>
+  <si>
+    <t>CAP157</t>
+  </si>
+  <si>
+    <t>Age Defence Night Cream-30gm</t>
+  </si>
+  <si>
+    <t>BA107</t>
+  </si>
+  <si>
+    <t>Advanced Hair Growth Serum Roll-On</t>
+  </si>
+  <si>
+    <t>Exfoliating Body Wash 236 ml</t>
+  </si>
+  <si>
+    <t>BA5</t>
+  </si>
+  <si>
+    <t>Anti Frizz Mask 250 g</t>
   </si>
 </sst>
 </file>
@@ -774,7 +807,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C578346-EE80-DF41-8099-4E3028D96EBE}">
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -2533,6 +2566,176 @@
       <c r="F84" s="6"/>
       <c r="G84" s="6"/>
     </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A85" s="2">
+        <v>46255</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D85" s="5">
+        <v>50000</v>
+      </c>
+      <c r="E85" s="5">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A86" s="2">
+        <v>46255</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D86" s="5">
+        <v>50000</v>
+      </c>
+      <c r="E86" s="5">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A87" s="2">
+        <v>46252</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D87" s="5">
+        <v>4000</v>
+      </c>
+      <c r="E87" s="5">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A88" s="2">
+        <v>46255</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D88" s="5">
+        <v>22000</v>
+      </c>
+      <c r="E88" s="5">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A89" s="2">
+        <v>46252</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D89" s="5">
+        <v>93480</v>
+      </c>
+      <c r="E89" s="5">
+        <v>93480</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A90" s="2">
+        <v>46255</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D90" s="5">
+        <v>64000</v>
+      </c>
+      <c r="E90" s="5">
+        <v>64000</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A91" s="2">
+        <v>46255</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D91" s="5">
+        <v>8000</v>
+      </c>
+      <c r="E91" s="5">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A92" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D92" s="5">
+        <v>50000</v>
+      </c>
+      <c r="E92" s="5">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A93" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D93" s="5">
+        <v>80000</v>
+      </c>
+      <c r="E93" s="5">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A94" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D94" s="5">
+        <v>80000</v>
+      </c>
+      <c r="E94" s="5">
+        <v>80000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Plan.xlsx
+++ b/data/Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raman/Documents/GitHub/production-board/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{663DCF84-71CF-DB40-8A81-AE171AE03F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81EC1C64-8CF6-B64A-B94F-1BFB1FFD2E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="680" yWindow="660" windowWidth="28040" windowHeight="16560" xr2:uid="{7C08584A-5D47-2049-B143-911B93E5D6E0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="124">
   <si>
     <t>Date</t>
   </si>
@@ -807,7 +807,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C578346-EE80-DF41-8099-4E3028D96EBE}">
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -2719,23 +2719,6 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A94" s="2">
-        <v>46267</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D94" s="5">
-        <v>80000</v>
-      </c>
-      <c r="E94" s="5">
-        <v>80000</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Plan.xlsx
+++ b/data/Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raman/Documents/GitHub/production-board/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81EC1C64-8CF6-B64A-B94F-1BFB1FFD2E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A8F523-D95B-DA42-842B-04093A2BE9F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="680" yWindow="660" windowWidth="28040" windowHeight="16560" xr2:uid="{7C08584A-5D47-2049-B143-911B93E5D6E0}"/>
   </bookViews>
@@ -2467,7 +2467,9 @@
         <v>6000</v>
       </c>
       <c r="F79" s="6"/>
-      <c r="G79" s="6"/>
+      <c r="G79" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
@@ -2486,7 +2488,9 @@
         <v>10000</v>
       </c>
       <c r="F80" s="6"/>
-      <c r="G80" s="6"/>
+      <c r="G80" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
@@ -2526,7 +2530,9 @@
         <v>20000</v>
       </c>
       <c r="F82" s="6"/>
-      <c r="G82" s="6"/>
+      <c r="G82" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
@@ -2545,7 +2551,9 @@
         <v>40000</v>
       </c>
       <c r="F83" s="6"/>
-      <c r="G83" s="6"/>
+      <c r="G83" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
@@ -2564,7 +2572,9 @@
         <v>40000</v>
       </c>
       <c r="F84" s="6"/>
-      <c r="G84" s="6"/>
+      <c r="G84" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
@@ -2582,6 +2592,9 @@
       <c r="E85" s="5">
         <v>50000</v>
       </c>
+      <c r="G85" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
@@ -2599,6 +2612,9 @@
       <c r="E86" s="5">
         <v>50000</v>
       </c>
+      <c r="G86" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
@@ -2616,6 +2632,9 @@
       <c r="E87" s="5">
         <v>4000</v>
       </c>
+      <c r="G87" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
@@ -2633,6 +2652,9 @@
       <c r="E88" s="5">
         <v>22000</v>
       </c>
+      <c r="G88" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
@@ -2650,6 +2672,9 @@
       <c r="E89" s="5">
         <v>93480</v>
       </c>
+      <c r="G89" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
@@ -2667,6 +2692,9 @@
       <c r="E90" s="5">
         <v>64000</v>
       </c>
+      <c r="G90" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
@@ -2684,6 +2712,9 @@
       <c r="E91" s="5">
         <v>8000</v>
       </c>
+      <c r="G91" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
@@ -2701,6 +2732,9 @@
       <c r="E92" s="5">
         <v>50000</v>
       </c>
+      <c r="G92" s="4">
+        <v>0</v>
+      </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
@@ -2717,6 +2751,9 @@
       </c>
       <c r="E93" s="5">
         <v>80000</v>
+      </c>
+      <c r="G93" s="4">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/Plan.xlsx
+++ b/data/Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raman/Documents/GitHub/production-board/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A8F523-D95B-DA42-842B-04093A2BE9F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D1DE873-015A-6D4B-8B52-4943FAFC02F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="680" yWindow="660" windowWidth="28040" windowHeight="16560" xr2:uid="{7C08584A-5D47-2049-B143-911B93E5D6E0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="103">
   <si>
     <t>Date</t>
   </si>
@@ -86,18 +86,6 @@
     <t>Anti-Hairfall Conditioner - 175gm</t>
   </si>
   <si>
-    <t>BA22</t>
-  </si>
-  <si>
-    <t>BA Expert | Anti Hairfall Shampoo 250 ml</t>
-  </si>
-  <si>
-    <t>USTTBA93</t>
-  </si>
-  <si>
-    <t>EXPERT | Ultra Smoothing Serum (100 ML) - TikTok US</t>
-  </si>
-  <si>
     <t>BA24</t>
   </si>
   <si>
@@ -158,12 +146,6 @@
     <t>Brightening Face Serum(10% VitaminC)30ml</t>
   </si>
   <si>
-    <t>BA98</t>
-  </si>
-  <si>
-    <t>Anti-Dandruff Conditioner -175gm</t>
-  </si>
-  <si>
     <t>CAP53</t>
   </si>
   <si>
@@ -176,24 +158,12 @@
     <t>Rosemary hair growth oil 100ml</t>
   </si>
   <si>
-    <t>CAP65</t>
-  </si>
-  <si>
-    <t>Neck, Knee, Elbow Brightening Roll On</t>
-  </si>
-  <si>
     <t>BA104</t>
   </si>
   <si>
     <t>Anti-Dandruff Conditioner 100 gm</t>
   </si>
   <si>
-    <t>BA50</t>
-  </si>
-  <si>
-    <t>Curl Intensifying Leave in Conditioner 140 ml</t>
-  </si>
-  <si>
     <t>UKTTCAP1</t>
   </si>
   <si>
@@ -212,42 +182,15 @@
     <t>Oil &amp; Acne Control Face Wash</t>
   </si>
   <si>
-    <t>USTTCAP24</t>
-  </si>
-  <si>
-    <t>Exfoliating Body Wash-236ml</t>
-  </si>
-  <si>
     <t>BA109</t>
   </si>
   <si>
     <t>Advanced Anti Dandruff Serum - 50ml</t>
   </si>
   <si>
-    <t>CAP136</t>
-  </si>
-  <si>
-    <t>Gentle and Soothing Face Wash 75 ml</t>
-  </si>
-  <si>
-    <t>USTTBA50</t>
-  </si>
-  <si>
-    <t>Curl Intensifying Leave in Conditioner USTT</t>
-  </si>
-  <si>
-    <t>CAP165</t>
-  </si>
-  <si>
-    <t>Epsom Body Wash - 236ml</t>
-  </si>
-  <si>
     <t>CAP24</t>
   </si>
   <si>
-    <t>Exfoliating Body Wash (236 ml)</t>
-  </si>
-  <si>
     <t>CAP146</t>
   </si>
   <si>
@@ -390,12 +333,6 @@
   </si>
   <si>
     <t>Natural Lip Balm 4.5gm</t>
-  </si>
-  <si>
-    <t>CAP157</t>
-  </si>
-  <si>
-    <t>Age Defence Night Cream-30gm</t>
   </si>
   <si>
     <t>BA107</t>
@@ -807,7 +744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C578346-EE80-DF41-8099-4E3028D96EBE}">
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -835,19 +772,19 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="D2" s="5">
-        <v>2000</v>
-      </c>
-      <c r="E2" s="5">
-        <v>2000</v>
+        <v>1500</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0</v>
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="4">
@@ -856,19 +793,19 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="D3" s="5">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="E3" s="5">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="4">
@@ -877,19 +814,19 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="D4" s="5">
-        <v>6000</v>
+        <v>4500</v>
       </c>
       <c r="E4" s="5">
-        <v>6000</v>
+        <v>4500</v>
       </c>
       <c r="F4" s="6"/>
       <c r="G4" s="4">
@@ -898,19 +835,19 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D5" s="5">
-        <v>8000</v>
+        <v>6000</v>
       </c>
       <c r="E5" s="5">
-        <v>8000</v>
+        <v>6000</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="4">
@@ -919,19 +856,19 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="D6" s="5">
-        <v>8000</v>
+        <v>7000</v>
       </c>
       <c r="E6" s="5">
-        <v>8000</v>
+        <v>7000</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="4">
@@ -940,19 +877,19 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D7" s="5">
-        <v>10000</v>
+        <v>7000</v>
       </c>
       <c r="E7" s="5">
-        <v>10000</v>
+        <v>7000</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="4">
@@ -961,19 +898,19 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D8" s="5">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="E8" s="5">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="4">
@@ -982,19 +919,19 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D9" s="5">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="E9" s="5">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="4">
@@ -1003,19 +940,19 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="D10" s="5">
-        <v>12000</v>
+        <v>20000</v>
       </c>
       <c r="E10" s="5">
-        <v>12000</v>
+        <v>20000</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="4">
@@ -1024,19 +961,19 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D11" s="5">
-        <v>15000</v>
+        <v>35000</v>
       </c>
       <c r="E11" s="5">
-        <v>15000</v>
+        <v>35000</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="4">
@@ -1045,19 +982,19 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="D12" s="5">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="E12" s="5">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="4">
@@ -1066,19 +1003,19 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="D13" s="5">
-        <v>24000</v>
+        <v>8000</v>
       </c>
       <c r="E13" s="5">
-        <v>24000</v>
+        <v>8000</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="4">
@@ -1087,19 +1024,19 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="D14" s="5">
-        <v>28000</v>
+        <v>10000</v>
       </c>
       <c r="E14" s="5">
-        <v>28000</v>
+        <v>10000</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="4">
@@ -1108,19 +1045,19 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="D15" s="5">
-        <v>45000</v>
+        <v>10000</v>
       </c>
       <c r="E15" s="5">
-        <v>45000</v>
+        <v>10000</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="4">
@@ -1129,19 +1066,19 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="D16" s="5">
-        <v>1500</v>
-      </c>
-      <c r="E16" s="3">
-        <v>0</v>
+        <v>11000</v>
+      </c>
+      <c r="E16" s="5">
+        <v>11000</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="4">
@@ -1150,19 +1087,19 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="D17" s="5">
-        <v>5000</v>
+        <v>13000</v>
       </c>
       <c r="E17" s="5">
-        <v>5000</v>
+        <v>13000</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="4">
@@ -1171,19 +1108,19 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="D18" s="5">
-        <v>4500</v>
+        <v>20000</v>
       </c>
       <c r="E18" s="5">
-        <v>4500</v>
+        <v>20000</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="4">
@@ -1192,19 +1129,19 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D19" s="5">
-        <v>6000</v>
+        <v>20000</v>
       </c>
       <c r="E19" s="5">
-        <v>6000</v>
+        <v>20000</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="4">
@@ -1213,19 +1150,19 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="D20" s="5">
-        <v>7000</v>
+        <v>40000</v>
       </c>
       <c r="E20" s="5">
-        <v>7000</v>
+        <v>40000</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="4">
@@ -1234,19 +1171,19 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D21" s="5">
-        <v>7000</v>
+        <v>45000</v>
       </c>
       <c r="E21" s="5">
-        <v>7000</v>
+        <v>45000</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="4">
@@ -1255,19 +1192,19 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="D22" s="5">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="E22" s="5">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="4">
@@ -1276,19 +1213,19 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D23" s="5">
-        <v>20000</v>
+        <v>3200</v>
       </c>
       <c r="E23" s="5">
-        <v>20000</v>
+        <v>3200</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="4">
@@ -1297,19 +1234,19 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="D24" s="5">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="E24" s="5">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="4">
@@ -1318,19 +1255,19 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>9</v>
+        <v>66</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="D25" s="5">
-        <v>35000</v>
+        <v>10000</v>
       </c>
       <c r="E25" s="5">
-        <v>35000</v>
+        <v>10000</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="4">
@@ -1339,19 +1276,19 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D26" s="5">
-        <v>40000</v>
+        <v>10000</v>
       </c>
       <c r="E26" s="5">
-        <v>40000</v>
+        <v>10000</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="4">
@@ -1360,19 +1297,19 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="D27" s="5">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="E27" s="5">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="4">
@@ -1381,19 +1318,19 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="D28" s="5">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="E28" s="5">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="4">
@@ -1402,19 +1339,19 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="D29" s="5">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="E29" s="5">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="4">
@@ -1423,19 +1360,19 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>77</v>
+        <v>11</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="D30" s="5">
-        <v>11000</v>
+        <v>40000</v>
       </c>
       <c r="E30" s="5">
-        <v>11000</v>
+        <v>40000</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="4">
@@ -1444,19 +1381,19 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="D31" s="5">
-        <v>13000</v>
+        <v>40000</v>
       </c>
       <c r="E31" s="5">
-        <v>13000</v>
+        <v>40000</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="4">
@@ -1465,19 +1402,19 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>46254</v>
+        <v>46256</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="D32" s="5">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="E32" s="5">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="4">
@@ -1486,19 +1423,19 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>46254</v>
+        <v>46256</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="D33" s="5">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="E33" s="5">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="4">
@@ -1507,19 +1444,19 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>46254</v>
+        <v>46256</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="D34" s="5">
-        <v>40000</v>
+        <v>8000</v>
       </c>
       <c r="E34" s="5">
-        <v>40000</v>
+        <v>8000</v>
       </c>
       <c r="F34" s="6"/>
       <c r="G34" s="4">
@@ -1528,19 +1465,19 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>46254</v>
+        <v>46256</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="D35" s="5">
-        <v>45000</v>
+        <v>10000</v>
       </c>
       <c r="E35" s="5">
-        <v>45000</v>
+        <v>10000</v>
       </c>
       <c r="F35" s="6"/>
       <c r="G35" s="4">
@@ -1549,19 +1486,19 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D36" s="5">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="E36" s="5">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F36" s="6"/>
       <c r="G36" s="4">
@@ -1570,19 +1507,19 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D37" s="5">
-        <v>3200</v>
+        <v>15000</v>
       </c>
       <c r="E37" s="5">
-        <v>3200</v>
+        <v>15000</v>
       </c>
       <c r="F37" s="6"/>
       <c r="G37" s="4">
@@ -1591,19 +1528,19 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="D38" s="5">
-        <v>8000</v>
+        <v>20000</v>
       </c>
       <c r="E38" s="5">
-        <v>8000</v>
+        <v>20000</v>
       </c>
       <c r="F38" s="6"/>
       <c r="G38" s="4">
@@ -1612,19 +1549,19 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>85</v>
+        <v>7</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>86</v>
+        <v>8</v>
       </c>
       <c r="D39" s="5">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="E39" s="5">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="F39" s="6"/>
       <c r="G39" s="4">
@@ -1633,19 +1570,19 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="D40" s="5">
-        <v>10000</v>
+        <v>28000</v>
       </c>
       <c r="E40" s="5">
-        <v>10000</v>
+        <v>28000</v>
       </c>
       <c r="F40" s="6"/>
       <c r="G40" s="4">
@@ -1654,19 +1591,19 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D41" s="5">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="E41" s="5">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="F41" s="6"/>
       <c r="G41" s="4">
@@ -1675,19 +1612,19 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>46255</v>
+        <v>46257</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="D42" s="5">
-        <v>11000</v>
+        <v>8000</v>
       </c>
       <c r="E42" s="5">
-        <v>11000</v>
+        <v>8000</v>
       </c>
       <c r="F42" s="6"/>
       <c r="G42" s="4">
@@ -1696,19 +1633,19 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>46255</v>
+        <v>46257</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>36</v>
+        <v>79</v>
       </c>
       <c r="D43" s="5">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E43" s="5">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F43" s="6"/>
       <c r="G43" s="4">
@@ -1717,19 +1654,19 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>46255</v>
+        <v>46257</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D44" s="5">
-        <v>40000</v>
+        <v>10000</v>
       </c>
       <c r="E44" s="5">
-        <v>40000</v>
+        <v>10000</v>
       </c>
       <c r="F44" s="6"/>
       <c r="G44" s="4">
@@ -1738,19 +1675,19 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
-        <v>46255</v>
+        <v>46257</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="D45" s="5">
-        <v>40000</v>
+        <v>10000</v>
       </c>
       <c r="E45" s="5">
-        <v>40000</v>
+        <v>10000</v>
       </c>
       <c r="F45" s="6"/>
       <c r="G45" s="4">
@@ -1759,19 +1696,19 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>87</v>
+        <v>33</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>88</v>
+        <v>34</v>
       </c>
       <c r="D46" s="5">
-        <v>2000</v>
+        <v>15000</v>
       </c>
       <c r="E46" s="5">
-        <v>2000</v>
+        <v>15000</v>
       </c>
       <c r="F46" s="6"/>
       <c r="G46" s="4">
@@ -1780,19 +1717,19 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>90</v>
+        <v>28</v>
       </c>
       <c r="D47" s="5">
-        <v>5000</v>
+        <v>20000</v>
       </c>
       <c r="E47" s="5">
-        <v>5000</v>
+        <v>20000</v>
       </c>
       <c r="F47" s="6"/>
       <c r="G47" s="4">
@@ -1801,19 +1738,19 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>91</v>
+        <v>45</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="D48" s="5">
-        <v>8000</v>
+        <v>20000</v>
       </c>
       <c r="E48" s="5">
-        <v>8000</v>
+        <v>20000</v>
       </c>
       <c r="F48" s="6"/>
       <c r="G48" s="4">
@@ -1822,19 +1759,19 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D49" s="5">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="E49" s="5">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="F49" s="6"/>
       <c r="G49" s="4">
@@ -1843,19 +1780,19 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>93</v>
+        <v>23</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>94</v>
+        <v>24</v>
       </c>
       <c r="D50" s="5">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="E50" s="5">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="F50" s="6"/>
       <c r="G50" s="4">
@@ -1864,19 +1801,19 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="D51" s="5">
-        <v>15000</v>
+        <v>6000</v>
       </c>
       <c r="E51" s="5">
-        <v>15000</v>
+        <v>6000</v>
       </c>
       <c r="F51" s="6"/>
       <c r="G51" s="4">
@@ -1885,19 +1822,19 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="D52" s="5">
-        <v>20000</v>
+        <v>11000</v>
       </c>
       <c r="E52" s="5">
-        <v>20000</v>
+        <v>11000</v>
       </c>
       <c r="F52" s="6"/>
       <c r="G52" s="4">
@@ -1906,19 +1843,19 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D53" s="5">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="E53" s="5">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="F53" s="6"/>
       <c r="G53" s="4">
@@ -1927,19 +1864,19 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D54" s="5">
-        <v>28000</v>
+        <v>20000</v>
       </c>
       <c r="E54" s="5">
-        <v>28000</v>
+        <v>20000</v>
       </c>
       <c r="F54" s="6"/>
       <c r="G54" s="4">
@@ -1948,19 +1885,19 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D55" s="5">
-        <v>40000</v>
+        <v>30000</v>
       </c>
       <c r="E55" s="5">
-        <v>40000</v>
+        <v>30000</v>
       </c>
       <c r="F55" s="6"/>
       <c r="G55" s="4">
@@ -1969,19 +1906,19 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="D56" s="5">
-        <v>8000</v>
+        <v>40000</v>
       </c>
       <c r="E56" s="5">
-        <v>8000</v>
+        <v>40000</v>
       </c>
       <c r="F56" s="6"/>
       <c r="G56" s="4">
@@ -1990,19 +1927,19 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>97</v>
+        <v>23</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>98</v>
+        <v>24</v>
       </c>
       <c r="D57" s="5">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="E57" s="5">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="F57" s="6"/>
       <c r="G57" s="4">
@@ -2011,19 +1948,19 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="D58" s="5">
-        <v>10000</v>
+        <v>2300</v>
       </c>
       <c r="E58" s="5">
-        <v>10000</v>
+        <v>2300</v>
       </c>
       <c r="F58" s="6"/>
       <c r="G58" s="4">
@@ -2032,13 +1969,13 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="D59" s="5">
         <v>10000</v>
@@ -2053,19 +1990,19 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D60" s="5">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="E60" s="5">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="F60" s="6"/>
       <c r="G60" s="4">
@@ -2074,13 +2011,13 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="D61" s="5">
         <v>20000</v>
@@ -2095,19 +2032,19 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="D62" s="5">
-        <v>20000</v>
+        <v>28000</v>
       </c>
       <c r="E62" s="5">
-        <v>20000</v>
+        <v>28000</v>
       </c>
       <c r="F62" s="6"/>
       <c r="G62" s="4">
@@ -2116,19 +2053,19 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>101</v>
+        <v>23</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>102</v>
+        <v>24</v>
       </c>
       <c r="D63" s="5">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="E63" s="5">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="F63" s="6"/>
       <c r="G63" s="4">
@@ -2137,13 +2074,13 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D64" s="5">
         <v>40000</v>
@@ -2158,13 +2095,13 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="D65" s="5">
         <v>6000</v>
@@ -2179,19 +2116,19 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="D66" s="5">
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="E66" s="5">
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="F66" s="6"/>
       <c r="G66" s="4">
@@ -2200,19 +2137,19 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D67" s="5">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="E67" s="5">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="F67" s="6"/>
       <c r="G67" s="4">
@@ -2221,13 +2158,13 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="D68" s="5">
         <v>20000</v>
@@ -2242,19 +2179,19 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="D69" s="5">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="E69" s="5">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="F69" s="6"/>
       <c r="G69" s="4">
@@ -2263,13 +2200,13 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D70" s="5">
         <v>40000</v>
@@ -2284,475 +2221,141 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
-        <v>46258</v>
+        <v>46255</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>27</v>
+        <v>94</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="D71" s="5">
-        <v>40000</v>
+        <v>50000</v>
       </c>
       <c r="E71" s="5">
-        <v>40000</v>
-      </c>
-      <c r="F71" s="6"/>
+        <v>50000</v>
+      </c>
       <c r="G71" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
-        <v>46259</v>
+        <v>46255</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="D72" s="5">
-        <v>2300</v>
+        <v>50000</v>
       </c>
       <c r="E72" s="5">
-        <v>2300</v>
-      </c>
-      <c r="F72" s="6"/>
+        <v>50000</v>
+      </c>
       <c r="G72" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
-        <v>46259</v>
+        <v>46255</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="D73" s="5">
-        <v>10000</v>
+        <v>22000</v>
       </c>
       <c r="E73" s="5">
-        <v>10000</v>
-      </c>
-      <c r="F73" s="6"/>
+        <v>22000</v>
+      </c>
       <c r="G73" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
-        <v>46259</v>
+        <v>46255</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="D74" s="5">
-        <v>20000</v>
+        <v>64000</v>
       </c>
       <c r="E74" s="5">
-        <v>20000</v>
-      </c>
-      <c r="F74" s="6"/>
+        <v>64000</v>
+      </c>
       <c r="G74" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
-        <v>46259</v>
+        <v>46255</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>7</v>
+        <v>101</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>8</v>
+        <v>102</v>
       </c>
       <c r="D75" s="5">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="E75" s="5">
-        <v>20000</v>
-      </c>
-      <c r="F75" s="6"/>
+        <v>8000</v>
+      </c>
       <c r="G75" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
-        <v>46259</v>
+        <v>46257</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="D76" s="5">
-        <v>28000</v>
+        <v>50000</v>
       </c>
       <c r="E76" s="5">
-        <v>28000</v>
-      </c>
-      <c r="F76" s="6"/>
+        <v>50000</v>
+      </c>
       <c r="G76" s="4">
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
-        <v>46259</v>
+        <v>46262</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D77" s="5">
-        <v>40000</v>
+        <v>80000</v>
       </c>
       <c r="E77" s="5">
-        <v>40000</v>
-      </c>
-      <c r="F77" s="6"/>
+        <v>80000</v>
+      </c>
       <c r="G77" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A78" s="2">
-        <v>46259</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D78" s="5">
-        <v>40000</v>
-      </c>
-      <c r="E78" s="5">
-        <v>40000</v>
-      </c>
-      <c r="F78" s="6"/>
-      <c r="G78" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A79" s="2">
-        <v>46260</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D79" s="5">
-        <v>6000</v>
-      </c>
-      <c r="E79" s="5">
-        <v>6000</v>
-      </c>
-      <c r="F79" s="6"/>
-      <c r="G79" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A80" s="2">
-        <v>46260</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D80" s="5">
-        <v>10000</v>
-      </c>
-      <c r="E80" s="5">
-        <v>10000</v>
-      </c>
-      <c r="F80" s="6"/>
-      <c r="G80" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A81" s="2">
-        <v>46260</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D81" s="5">
-        <v>20000</v>
-      </c>
-      <c r="E81" s="5">
-        <v>20000</v>
-      </c>
-      <c r="F81" s="6"/>
-      <c r="G81" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A82" s="2">
-        <v>46260</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D82" s="5">
-        <v>20000</v>
-      </c>
-      <c r="E82" s="5">
-        <v>20000</v>
-      </c>
-      <c r="F82" s="6"/>
-      <c r="G82" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A83" s="2">
-        <v>46260</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D83" s="5">
-        <v>40000</v>
-      </c>
-      <c r="E83" s="5">
-        <v>40000</v>
-      </c>
-      <c r="F83" s="6"/>
-      <c r="G83" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A84" s="2">
-        <v>46260</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D84" s="5">
-        <v>40000</v>
-      </c>
-      <c r="E84" s="5">
-        <v>40000</v>
-      </c>
-      <c r="F84" s="6"/>
-      <c r="G84" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A85" s="2">
-        <v>46255</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D85" s="5">
-        <v>50000</v>
-      </c>
-      <c r="E85" s="5">
-        <v>50000</v>
-      </c>
-      <c r="G85" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A86" s="2">
-        <v>46255</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D86" s="5">
-        <v>50000</v>
-      </c>
-      <c r="E86" s="5">
-        <v>50000</v>
-      </c>
-      <c r="G86" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A87" s="2">
-        <v>46252</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D87" s="5">
-        <v>4000</v>
-      </c>
-      <c r="E87" s="5">
-        <v>4000</v>
-      </c>
-      <c r="G87" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A88" s="2">
-        <v>46255</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D88" s="5">
-        <v>22000</v>
-      </c>
-      <c r="E88" s="5">
-        <v>22000</v>
-      </c>
-      <c r="G88" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A89" s="2">
-        <v>46252</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D89" s="5">
-        <v>93480</v>
-      </c>
-      <c r="E89" s="5">
-        <v>93480</v>
-      </c>
-      <c r="G89" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A90" s="2">
-        <v>46255</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D90" s="5">
-        <v>64000</v>
-      </c>
-      <c r="E90" s="5">
-        <v>64000</v>
-      </c>
-      <c r="G90" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A91" s="2">
-        <v>46255</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D91" s="5">
-        <v>8000</v>
-      </c>
-      <c r="E91" s="5">
-        <v>8000</v>
-      </c>
-      <c r="G91" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A92" s="2">
-        <v>46257</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D92" s="5">
-        <v>50000</v>
-      </c>
-      <c r="E92" s="5">
-        <v>50000</v>
-      </c>
-      <c r="G92" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A93" s="2">
-        <v>46262</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D93" s="5">
-        <v>80000</v>
-      </c>
-      <c r="E93" s="5">
-        <v>80000</v>
-      </c>
-      <c r="G93" s="4">
         <v>0</v>
       </c>
     </row>

--- a/data/Plan.xlsx
+++ b/data/Plan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raman/Documents/GitHub/production-board/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D1DE873-015A-6D4B-8B52-4943FAFC02F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C539DF1C-2490-634E-BC09-72BB56AFE043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="660" windowWidth="28040" windowHeight="16560" xr2:uid="{7C08584A-5D47-2049-B143-911B93E5D6E0}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{7C08584A-5D47-2049-B143-911B93E5D6E0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="116">
   <si>
     <t>Date</t>
   </si>
@@ -348,6 +348,45 @@
   </si>
   <si>
     <t>Anti Frizz Mask 250 g</t>
+  </si>
+  <si>
+    <t>BA110</t>
+  </si>
+  <si>
+    <t>Instant Cover-Up Hair Powder Black-4gm</t>
+  </si>
+  <si>
+    <t>BA111</t>
+  </si>
+  <si>
+    <t>Instant Cover-Up Hair Powder Brown-4gm</t>
+  </si>
+  <si>
+    <t>BA77</t>
+  </si>
+  <si>
+    <t>Scalp Massager</t>
+  </si>
+  <si>
+    <t>CAP157</t>
+  </si>
+  <si>
+    <t>Age Defence Night Cream-30gm</t>
+  </si>
+  <si>
+    <t>SS42</t>
+  </si>
+  <si>
+    <t>3% Niacinamide Featherlight Fluid Sunscreen 45g</t>
+  </si>
+  <si>
+    <t>Bare Anatomy Advanced Hair Growth Serum</t>
+  </si>
+  <si>
+    <t>UKTTBA107</t>
+  </si>
+  <si>
+    <t>UKTTBA6</t>
   </si>
 </sst>
 </file>
@@ -744,7 +783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C578346-EE80-DF41-8099-4E3028D96EBE}">
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -2359,6 +2398,206 @@
         <v>0</v>
       </c>
     </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A78" s="2">
+        <v>46255</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D78" s="5">
+        <v>50000</v>
+      </c>
+      <c r="E78" s="5">
+        <v>50000</v>
+      </c>
+      <c r="G78" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A79" s="2">
+        <v>46255</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D79" s="5">
+        <v>50000</v>
+      </c>
+      <c r="E79" s="5">
+        <v>50000</v>
+      </c>
+      <c r="G79" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A80" s="2">
+        <v>46292</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D80" s="5">
+        <v>25000</v>
+      </c>
+      <c r="E80" s="5">
+        <v>25000</v>
+      </c>
+      <c r="G80" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A81" s="2">
+        <v>46292</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D81" s="5">
+        <v>25000</v>
+      </c>
+      <c r="E81" s="5">
+        <v>25000</v>
+      </c>
+      <c r="G81" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A82" s="2">
+        <v>46256</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D82" s="5">
+        <v>7500</v>
+      </c>
+      <c r="E82" s="5">
+        <v>7500</v>
+      </c>
+      <c r="G82" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A83" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D83" s="5">
+        <v>20000</v>
+      </c>
+      <c r="E83" s="5">
+        <v>20000</v>
+      </c>
+      <c r="G83" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A84" s="2">
+        <v>46258</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D84" s="5">
+        <v>30000</v>
+      </c>
+      <c r="E84" s="5">
+        <v>30000</v>
+      </c>
+      <c r="G84" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A85" s="2">
+        <v>46255</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D85" s="5">
+        <v>20000</v>
+      </c>
+      <c r="E85" s="5">
+        <v>20000</v>
+      </c>
+      <c r="G85" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A86" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D86" s="5">
+        <v>20000</v>
+      </c>
+      <c r="E86" s="5">
+        <v>20000</v>
+      </c>
+      <c r="G86" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A87" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D87" s="5">
+        <v>30000</v>
+      </c>
+      <c r="E87" s="5">
+        <v>30000</v>
+      </c>
+      <c r="G87" s="4">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Plan.xlsx
+++ b/data/Plan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raman/Documents/GitHub/production-board/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C539DF1C-2490-634E-BC09-72BB56AFE043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3E1619B-1D88-1649-813F-112B8F2DF317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{7C08584A-5D47-2049-B143-911B93E5D6E0}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16600" xr2:uid="{7C08584A-5D47-2049-B143-911B93E5D6E0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="116">
   <si>
     <t>Date</t>
   </si>
@@ -783,7 +783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C578346-EE80-DF41-8099-4E3028D96EBE}">
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -2400,19 +2400,19 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
-        <v>46255</v>
+        <v>46292</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D78" s="5">
-        <v>50000</v>
+        <v>25000</v>
       </c>
       <c r="E78" s="5">
-        <v>50000</v>
+        <v>25000</v>
       </c>
       <c r="G78" s="4">
         <v>0</v>
@@ -2420,19 +2420,19 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
-        <v>46255</v>
+        <v>46292</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="D79" s="5">
-        <v>50000</v>
+        <v>25000</v>
       </c>
       <c r="E79" s="5">
-        <v>50000</v>
+        <v>25000</v>
       </c>
       <c r="G79" s="4">
         <v>0</v>
@@ -2440,19 +2440,19 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
-        <v>46292</v>
+        <v>46256</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D80" s="5">
-        <v>25000</v>
+        <v>7500</v>
       </c>
       <c r="E80" s="5">
-        <v>25000</v>
+        <v>7500</v>
       </c>
       <c r="G80" s="4">
         <v>0</v>
@@ -2460,19 +2460,19 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
-        <v>46292</v>
+        <v>46267</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D81" s="5">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="E81" s="5">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="G81" s="4">
         <v>0</v>
@@ -2480,19 +2480,19 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D82" s="5">
-        <v>7500</v>
+        <v>30000</v>
       </c>
       <c r="E82" s="5">
-        <v>7500</v>
+        <v>30000</v>
       </c>
       <c r="G82" s="4">
         <v>0</v>
@@ -2500,13 +2500,13 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
-        <v>46267</v>
+        <v>46262</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D83" s="5">
         <v>20000</v>
@@ -2520,13 +2520,13 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
-        <v>46258</v>
+        <v>46262</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D84" s="5">
         <v>30000</v>
@@ -2535,66 +2535,6 @@
         <v>30000</v>
       </c>
       <c r="G84" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A85" s="2">
-        <v>46255</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D85" s="5">
-        <v>20000</v>
-      </c>
-      <c r="E85" s="5">
-        <v>20000</v>
-      </c>
-      <c r="G85" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A86" s="2">
-        <v>46262</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D86" s="5">
-        <v>20000</v>
-      </c>
-      <c r="E86" s="5">
-        <v>20000</v>
-      </c>
-      <c r="G86" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A87" s="2">
-        <v>46262</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D87" s="5">
-        <v>30000</v>
-      </c>
-      <c r="E87" s="5">
-        <v>30000</v>
-      </c>
-      <c r="G87" s="4">
         <v>0</v>
       </c>
     </row>

--- a/data/Plan.xlsx
+++ b/data/Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raman/Documents/GitHub/production-board/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3E1619B-1D88-1649-813F-112B8F2DF317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{874E316D-B999-A945-B993-CCEAAF370A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16600" xr2:uid="{7C08584A-5D47-2049-B143-911B93E5D6E0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="116">
   <si>
     <t>Date</t>
   </si>
@@ -783,7 +783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C578346-EE80-DF41-8099-4E3028D96EBE}">
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -2260,20 +2260,21 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
-        <v>46255</v>
+        <v>46253</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>94</v>
+        <v>49</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D71" s="5">
-        <v>50000</v>
+        <v>93480</v>
       </c>
       <c r="E71" s="5">
-        <v>50000</v>
-      </c>
+        <v>93480</v>
+      </c>
+      <c r="F71" s="6"/>
       <c r="G71" s="4">
         <v>0</v>
       </c>
@@ -2283,10 +2284,10 @@
         <v>46255</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D72" s="5">
         <v>50000</v>
@@ -2303,16 +2304,16 @@
         <v>46255</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D73" s="5">
-        <v>22000</v>
+        <v>50000</v>
       </c>
       <c r="E73" s="5">
-        <v>22000</v>
+        <v>50000</v>
       </c>
       <c r="G73" s="4">
         <v>0</v>
@@ -2323,16 +2324,16 @@
         <v>46255</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>26</v>
+        <v>99</v>
       </c>
       <c r="D74" s="5">
-        <v>64000</v>
+        <v>22000</v>
       </c>
       <c r="E74" s="5">
-        <v>64000</v>
+        <v>22000</v>
       </c>
       <c r="G74" s="4">
         <v>0</v>
@@ -2343,16 +2344,16 @@
         <v>46255</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>101</v>
+        <v>25</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>102</v>
+        <v>26</v>
       </c>
       <c r="D75" s="5">
-        <v>8000</v>
+        <v>64000</v>
       </c>
       <c r="E75" s="5">
-        <v>8000</v>
+        <v>64000</v>
       </c>
       <c r="G75" s="4">
         <v>0</v>
@@ -2360,19 +2361,19 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
-        <v>46257</v>
+        <v>46255</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D76" s="5">
-        <v>50000</v>
+        <v>8000</v>
       </c>
       <c r="E76" s="5">
-        <v>50000</v>
+        <v>8000</v>
       </c>
       <c r="G76" s="4">
         <v>0</v>
@@ -2380,19 +2381,19 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
-        <v>46262</v>
+        <v>46257</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>26</v>
+        <v>100</v>
       </c>
       <c r="D77" s="5">
-        <v>80000</v>
+        <v>50000</v>
       </c>
       <c r="E77" s="5">
-        <v>80000</v>
+        <v>50000</v>
       </c>
       <c r="G77" s="4">
         <v>0</v>
@@ -2400,19 +2401,19 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
-        <v>46292</v>
+        <v>46262</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="D78" s="5">
-        <v>25000</v>
+        <v>80000</v>
       </c>
       <c r="E78" s="5">
-        <v>25000</v>
+        <v>80000</v>
       </c>
       <c r="G78" s="4">
         <v>0</v>
@@ -2423,10 +2424,10 @@
         <v>46292</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D79" s="5">
         <v>25000</v>
@@ -2440,19 +2441,19 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
-        <v>46256</v>
+        <v>46292</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D80" s="5">
-        <v>7500</v>
+        <v>25000</v>
       </c>
       <c r="E80" s="5">
-        <v>7500</v>
+        <v>25000</v>
       </c>
       <c r="G80" s="4">
         <v>0</v>
@@ -2460,19 +2461,19 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
-        <v>46267</v>
+        <v>46256</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D81" s="5">
-        <v>20000</v>
+        <v>7500</v>
       </c>
       <c r="E81" s="5">
-        <v>20000</v>
+        <v>7500</v>
       </c>
       <c r="G81" s="4">
         <v>0</v>
@@ -2480,19 +2481,19 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
-        <v>46258</v>
+        <v>46267</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D82" s="5">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="E82" s="5">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="G82" s="4">
         <v>0</v>
@@ -2500,19 +2501,19 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
-        <v>46262</v>
+        <v>46258</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="D83" s="5">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="E83" s="5">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="G83" s="4">
         <v>0</v>
@@ -2523,18 +2524,38 @@
         <v>46262</v>
       </c>
       <c r="B84" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D84" s="5">
+        <v>20000</v>
+      </c>
+      <c r="E84" s="5">
+        <v>20000</v>
+      </c>
+      <c r="G84" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A85" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B85" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="C85" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D84" s="5">
+      <c r="D85" s="5">
         <v>30000</v>
       </c>
-      <c r="E84" s="5">
+      <c r="E85" s="5">
         <v>30000</v>
       </c>
-      <c r="G84" s="4">
+      <c r="G85" s="4">
         <v>0</v>
       </c>
     </row>

--- a/data/Plan.xlsx
+++ b/data/Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raman/Documents/GitHub/production-board/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BFB05FE-B53E-B74F-ADE1-869BC91BD3C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A688F7-C375-E74A-BACA-5665A3F1CE3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16560" xr2:uid="{7C08584A-5D47-2049-B143-911B93E5D6E0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="148">
   <si>
     <t>Date</t>
   </si>
@@ -167,24 +167,6 @@
     <t>Combo- Anti-Dandruff Shampoo (100ml) + Anti-Dandruff Conditioner (100g)</t>
   </si>
   <si>
-    <t>CAP144</t>
-  </si>
-  <si>
-    <t>Oil &amp; Acne Control Face Wash - Flipkart pack of 2</t>
-  </si>
-  <si>
-    <t>BA94</t>
-  </si>
-  <si>
-    <t>Damage Repair Hair Serum 100ml</t>
-  </si>
-  <si>
-    <t>BA47</t>
-  </si>
-  <si>
-    <t>Curl Defining Hair Gel 140 ml</t>
-  </si>
-  <si>
     <t>CAP1</t>
   </si>
   <si>
@@ -377,12 +359,6 @@
     <t>EXPERT | Color Protect Shampoo (250 ML)</t>
   </si>
   <si>
-    <t>BA118</t>
-  </si>
-  <si>
-    <t>Fenugreek &amp; Curry Leaves Hair Strengthening Spray - 200ml</t>
-  </si>
-  <si>
     <t>BA75</t>
   </si>
   <si>
@@ -407,23 +383,113 @@
     <t>EXPERT | Anti-Frizz Shampoo (250 ML)</t>
   </si>
   <si>
-    <t>USTTBA10</t>
-  </si>
-  <si>
-    <t>EXPERT | Ultra Smoothing Shampoo (250 ML) -  TikTok US</t>
-  </si>
-  <si>
     <t>Inhouse</t>
   </si>
   <si>
     <t>Outsource</t>
+  </si>
+  <si>
+    <t>CAP166</t>
+  </si>
+  <si>
+    <t>Under Arm Roll On- Fragrance Free - 75ml</t>
+  </si>
+  <si>
+    <t>CAP2</t>
+  </si>
+  <si>
+    <t>Acne Control Body Wash (473 ml)</t>
+  </si>
+  <si>
+    <t>BA108</t>
+  </si>
+  <si>
+    <t>Neem &amp; Lemon Dandruff Control Scalp Spray - 200ml</t>
+  </si>
+  <si>
+    <t>BA26</t>
+  </si>
+  <si>
+    <t>EXPERT | Scalp Scrub (250 gms)</t>
+  </si>
+  <si>
+    <t>BA87</t>
+  </si>
+  <si>
+    <t>Advanced Anti-Grey Hair Serum 50ml</t>
+  </si>
+  <si>
+    <t>CAP145</t>
+  </si>
+  <si>
+    <t>Oil &amp; Acne Control Face Wash - Flipkart pack of 3</t>
+  </si>
+  <si>
+    <t>CAP80</t>
+  </si>
+  <si>
+    <t>CAP Retinol Body Lotion 200 ml</t>
+  </si>
+  <si>
+    <t>BA55</t>
+  </si>
+  <si>
+    <t>Rosemary and Coconut Milk Hydrating Conditioner</t>
+  </si>
+  <si>
+    <t>CAP140</t>
+  </si>
+  <si>
+    <t>Tri Active Roll On Aqua 40ml</t>
+  </si>
+  <si>
+    <t>BA49</t>
+  </si>
+  <si>
+    <t>Curl Defining Shampoo 250 ml</t>
+  </si>
+  <si>
+    <t>BA51</t>
+  </si>
+  <si>
+    <t>BA Gentle Cleansing Shampoo</t>
+  </si>
+  <si>
+    <t>CAP50</t>
+  </si>
+  <si>
+    <t>Under Arm Roll On - 40 ml / Peach (Rectangular Monocarton)-399</t>
+  </si>
+  <si>
+    <t>CAP154</t>
+  </si>
+  <si>
+    <t>Exfoliating face wash 75 ml</t>
+  </si>
+  <si>
+    <t>CAP173</t>
+  </si>
+  <si>
+    <t>Gentle Exfoliating Face Wash 75ml- Pack of 2</t>
+  </si>
+  <si>
+    <t>BA2</t>
+  </si>
+  <si>
+    <t>EXPERT | Color Protect Hair Mask (250 gms)</t>
+  </si>
+  <si>
+    <t>BA48</t>
+  </si>
+  <si>
+    <t>Curl Enhancing Hair Mask 250 gm</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -442,12 +508,6 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -471,14 +531,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -813,7 +872,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C578346-EE80-DF41-8099-4E3028D96EBE}">
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
@@ -841,26 +900,25 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D2" s="5">
-        <v>47480</v>
+        <v>50000</v>
       </c>
       <c r="E2" s="5">
-        <v>47480</v>
-      </c>
-      <c r="F2" s="6"/>
+        <v>50000</v>
+      </c>
       <c r="G2" s="4">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -868,10 +926,10 @@
         <v>46255</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D3" s="5">
         <v>50000</v>
@@ -883,7 +941,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -891,22 +949,22 @@
         <v>46255</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D4" s="5">
-        <v>50000</v>
+        <v>22000</v>
       </c>
       <c r="E4" s="5">
-        <v>50000</v>
+        <v>22000</v>
       </c>
       <c r="G4" s="4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -914,22 +972,22 @@
         <v>46255</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>74</v>
+        <v>21</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="D5" s="5">
-        <v>22000</v>
+        <v>64000</v>
       </c>
       <c r="E5" s="5">
-        <v>22000</v>
+        <v>64000</v>
       </c>
       <c r="G5" s="4">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -937,91 +995,91 @@
         <v>46255</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="D6" s="5">
-        <v>64000</v>
+        <v>8000</v>
       </c>
       <c r="E6" s="5">
-        <v>64000</v>
+        <v>8000</v>
       </c>
       <c r="G6" s="4">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>46255</v>
+        <v>46257</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D7" s="5">
-        <v>8000</v>
+        <v>50000</v>
       </c>
       <c r="E7" s="5">
-        <v>8000</v>
+        <v>50000</v>
       </c>
       <c r="G7" s="4">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>46257</v>
+        <v>46262</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="D8" s="5">
-        <v>50000</v>
+        <v>80000</v>
       </c>
       <c r="E8" s="5">
-        <v>50000</v>
+        <v>80000</v>
       </c>
       <c r="G8" s="4">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
-        <v>46262</v>
+        <v>46292</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>21</v>
+        <v>73</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="D9" s="5">
-        <v>80000</v>
+        <v>25000</v>
       </c>
       <c r="E9" s="5">
-        <v>80000</v>
+        <v>25000</v>
       </c>
       <c r="G9" s="4">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -1029,10 +1087,10 @@
         <v>46292</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D10" s="5">
         <v>25000</v>
@@ -1044,99 +1102,99 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
-        <v>46292</v>
+        <v>46256</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D11" s="5">
-        <v>25000</v>
+        <v>7500</v>
       </c>
       <c r="E11" s="5">
-        <v>25000</v>
+        <v>7500</v>
       </c>
       <c r="G11" s="4">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>46256</v>
+        <v>46267</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D12" s="5">
-        <v>7500</v>
+        <v>20000</v>
       </c>
       <c r="E12" s="5">
-        <v>7500</v>
+        <v>20000</v>
       </c>
       <c r="G12" s="4">
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
-        <v>46267</v>
+        <v>46258</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D13" s="5">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="E13" s="5">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="G13" s="4">
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <v>46258</v>
+        <v>46262</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="D14" s="5">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="E14" s="5">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="G14" s="4">
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -1144,125 +1202,125 @@
         <v>46262</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="D15" s="5">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="E15" s="5">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="G15" s="4">
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>46262</v>
+        <v>46255</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D16" s="5">
-        <v>30000</v>
-      </c>
-      <c r="E16" s="5">
-        <v>30000</v>
+        <v>1000</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
       </c>
       <c r="G16" s="4">
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="D17" s="5">
-        <v>3200</v>
+        <v>4000</v>
       </c>
       <c r="E17" s="5">
-        <v>3200</v>
+        <v>4000</v>
       </c>
       <c r="G17" s="4">
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>29</v>
+        <v>116</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>30</v>
+        <v>117</v>
       </c>
       <c r="D18" s="5">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="E18" s="5">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="G18" s="4">
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D19" s="5">
-        <v>5000</v>
+        <v>7000</v>
       </c>
       <c r="E19" s="5">
-        <v>5000</v>
+        <v>7000</v>
       </c>
       <c r="G19" s="4">
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="D20" s="5">
         <v>8000</v>
@@ -1274,41 +1332,41 @@
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="D21" s="5">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="E21" s="5">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="G21" s="4">
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D22" s="5">
         <v>10000</v>
@@ -1320,18 +1378,18 @@
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="D23" s="5">
         <v>10000</v>
@@ -1343,133 +1401,133 @@
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="D24" s="5">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="E24" s="5">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="G24" s="4">
         <v>0</v>
       </c>
       <c r="H24" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="D25" s="5">
-        <v>10000</v>
+        <v>17000</v>
       </c>
       <c r="E25" s="5">
-        <v>10000</v>
+        <v>17000</v>
       </c>
       <c r="G25" s="4">
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D26" s="5">
-        <v>13000</v>
+        <v>18797</v>
       </c>
       <c r="E26" s="5">
-        <v>13000</v>
+        <v>18797</v>
       </c>
       <c r="G26" s="4">
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>23</v>
+        <v>94</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="D27" s="5">
-        <v>18000</v>
+        <v>20000</v>
       </c>
       <c r="E27" s="5">
-        <v>18000</v>
+        <v>20000</v>
       </c>
       <c r="G27" s="4">
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D28" s="5">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="E28" s="5">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="G28" s="4">
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D29" s="5">
         <v>30000</v>
@@ -1481,18 +1539,18 @@
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="D30" s="5">
         <v>1000</v>
@@ -1504,18 +1562,18 @@
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D31" s="5">
         <v>6000</v>
@@ -1527,18 +1585,18 @@
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="D32" s="5">
         <v>8000</v>
@@ -1550,18 +1608,18 @@
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D33" s="5">
         <v>10000</v>
@@ -1573,18 +1631,18 @@
         <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="D34" s="5">
         <v>10000</v>
@@ -1596,18 +1654,18 @@
         <v>0</v>
       </c>
       <c r="H34" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="D35" s="5">
         <v>10000</v>
@@ -1619,58 +1677,58 @@
         <v>0</v>
       </c>
       <c r="H35" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D36" s="5">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E36" s="5">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="G36" s="4">
         <v>0</v>
       </c>
       <c r="H36" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="D37" s="5">
-        <v>30000</v>
+        <v>24000</v>
       </c>
       <c r="E37" s="5">
-        <v>30000</v>
+        <v>24000</v>
       </c>
       <c r="G37" s="4">
         <v>0</v>
       </c>
       <c r="H37" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>9</v>
@@ -1688,7 +1746,7 @@
         <v>0</v>
       </c>
       <c r="H38" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
@@ -1696,73 +1754,73 @@
         <v>46256</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="D39" s="5">
-        <v>8000</v>
+        <v>40000</v>
       </c>
       <c r="E39" s="5">
-        <v>8000</v>
+        <v>40000</v>
       </c>
       <c r="G39" s="4">
         <v>0</v>
       </c>
       <c r="H39" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="D40" s="5">
-        <v>8000</v>
+        <v>2000</v>
       </c>
       <c r="E40" s="5">
-        <v>8000</v>
+        <v>2000</v>
       </c>
       <c r="G40" s="4">
         <v>0</v>
       </c>
       <c r="H40" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D41" s="5">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="E41" s="5">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="G41" s="4">
         <v>0</v>
       </c>
       <c r="H41" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>96</v>
@@ -1771,154 +1829,154 @@
         <v>97</v>
       </c>
       <c r="D42" s="5">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="E42" s="5">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="G42" s="4">
         <v>0</v>
       </c>
       <c r="H42" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>26</v>
+        <v>99</v>
       </c>
       <c r="D43" s="5">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="E43" s="5">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="G43" s="4">
         <v>0</v>
       </c>
       <c r="H43" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="D44" s="5">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="E44" s="5">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="G44" s="4">
         <v>0</v>
       </c>
       <c r="H44" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="D45" s="5">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="E45" s="5">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="G45" s="4">
         <v>0</v>
       </c>
       <c r="H45" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D46" s="5">
-        <v>24000</v>
+        <v>12000</v>
       </c>
       <c r="E46" s="5">
-        <v>24000</v>
+        <v>12000</v>
       </c>
       <c r="G46" s="4">
         <v>0</v>
       </c>
       <c r="H46" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>9</v>
+        <v>120</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>10</v>
+        <v>121</v>
       </c>
       <c r="D47" s="5">
-        <v>40000</v>
+        <v>15000</v>
       </c>
       <c r="E47" s="5">
-        <v>40000</v>
+        <v>15000</v>
       </c>
       <c r="G47" s="4">
         <v>0</v>
       </c>
       <c r="H47" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>101</v>
+        <v>63</v>
       </c>
       <c r="D48" s="5">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="E48" s="5">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="G48" s="4">
         <v>0</v>
       </c>
       <c r="H48" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
@@ -1926,22 +1984,22 @@
         <v>46257</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D49" s="5">
-        <v>2000</v>
+        <v>35000</v>
       </c>
       <c r="E49" s="5">
-        <v>2000</v>
+        <v>35000</v>
       </c>
       <c r="G49" s="4">
         <v>0</v>
       </c>
       <c r="H49" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
@@ -1949,79 +2007,79 @@
         <v>46257</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="D50" s="5">
-        <v>5000</v>
+        <v>40000</v>
       </c>
       <c r="E50" s="5">
-        <v>5000</v>
+        <v>40000</v>
       </c>
       <c r="G50" s="4">
         <v>0</v>
       </c>
       <c r="H50" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D51" s="5">
-        <v>8000</v>
-      </c>
-      <c r="E51" s="5">
-        <v>8000</v>
+        <v>123</v>
+      </c>
+      <c r="D51" s="3">
+        <v>900</v>
+      </c>
+      <c r="E51" s="3">
+        <v>900</v>
       </c>
       <c r="G51" s="4">
         <v>0</v>
       </c>
       <c r="H51" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D52" s="5">
-        <v>8000</v>
+        <v>3700</v>
       </c>
       <c r="E52" s="5">
-        <v>8000</v>
+        <v>3700</v>
       </c>
       <c r="G52" s="4">
         <v>0</v>
       </c>
       <c r="H52" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="D53" s="5">
         <v>8000</v>
@@ -2033,81 +2091,81 @@
         <v>0</v>
       </c>
       <c r="H53" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>108</v>
+        <v>48</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>109</v>
+        <v>49</v>
       </c>
       <c r="D54" s="5">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="E54" s="5">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="G54" s="4">
         <v>0</v>
       </c>
       <c r="H54" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>110</v>
+        <v>56</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>111</v>
+        <v>57</v>
       </c>
       <c r="D55" s="5">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="E55" s="5">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="G55" s="4">
         <v>0</v>
       </c>
       <c r="H55" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="D56" s="5">
-        <v>15000</v>
+        <v>11000</v>
       </c>
       <c r="E56" s="5">
-        <v>15000</v>
+        <v>11000</v>
       </c>
       <c r="G56" s="4">
         <v>0</v>
       </c>
       <c r="H56" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>112</v>
@@ -2116,50 +2174,50 @@
         <v>113</v>
       </c>
       <c r="D57" s="5">
-        <v>15000</v>
+        <v>12000</v>
       </c>
       <c r="E57" s="5">
-        <v>15000</v>
+        <v>12000</v>
       </c>
       <c r="G57" s="4">
         <v>0</v>
       </c>
       <c r="H57" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="D58" s="5">
-        <v>8000</v>
+        <v>20000</v>
       </c>
       <c r="E58" s="5">
-        <v>8000</v>
+        <v>20000</v>
       </c>
       <c r="G58" s="4">
         <v>0</v>
       </c>
       <c r="H58" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>69</v>
+        <v>109</v>
       </c>
       <c r="D59" s="5">
         <v>20000</v>
@@ -2171,30 +2229,30 @@
         <v>0</v>
       </c>
       <c r="H59" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="D60" s="5">
-        <v>48000</v>
+        <v>20000</v>
       </c>
       <c r="E60" s="5">
-        <v>48000</v>
+        <v>20000</v>
       </c>
       <c r="G60" s="4">
         <v>0</v>
       </c>
       <c r="H60" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
@@ -2202,102 +2260,102 @@
         <v>46258</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>115</v>
+        <v>26</v>
       </c>
       <c r="D61" s="5">
-        <v>3700</v>
+        <v>20000</v>
       </c>
       <c r="E61" s="5">
-        <v>3700</v>
+        <v>20000</v>
       </c>
       <c r="G61" s="4">
         <v>0</v>
       </c>
       <c r="H61" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>64</v>
+        <v>126</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>65</v>
+        <v>127</v>
       </c>
       <c r="D62" s="5">
-        <v>10000</v>
+        <v>2300</v>
       </c>
       <c r="E62" s="5">
-        <v>10000</v>
+        <v>2300</v>
       </c>
       <c r="G62" s="4">
         <v>0</v>
       </c>
       <c r="H62" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>62</v>
+        <v>128</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>63</v>
+        <v>129</v>
       </c>
       <c r="D63" s="5">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="E63" s="5">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="G63" s="4">
         <v>0</v>
       </c>
       <c r="H63" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>37</v>
+        <v>130</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>38</v>
+        <v>131</v>
       </c>
       <c r="D64" s="5">
-        <v>10000</v>
+        <v>6300</v>
       </c>
       <c r="E64" s="5">
-        <v>10000</v>
+        <v>6300</v>
       </c>
       <c r="G64" s="4">
         <v>0</v>
       </c>
       <c r="H64" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D65" s="5">
         <v>10000</v>
@@ -2309,214 +2367,513 @@
         <v>0</v>
       </c>
       <c r="H65" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>118</v>
+        <v>17</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>119</v>
+        <v>18</v>
       </c>
       <c r="D66" s="5">
-        <v>11000</v>
+        <v>14000</v>
       </c>
       <c r="E66" s="5">
-        <v>11000</v>
+        <v>14000</v>
       </c>
       <c r="G66" s="4">
         <v>0</v>
       </c>
       <c r="H66" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>120</v>
+        <v>27</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>121</v>
+        <v>28</v>
       </c>
       <c r="D67" s="5">
-        <v>12000</v>
+        <v>18000</v>
       </c>
       <c r="E67" s="5">
-        <v>12000</v>
+        <v>18000</v>
       </c>
       <c r="G67" s="4">
         <v>0</v>
       </c>
       <c r="H67" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D68" s="5">
-        <v>14000</v>
+        <v>18000</v>
       </c>
       <c r="E68" s="5">
-        <v>14000</v>
+        <v>18000</v>
       </c>
       <c r="G68" s="4">
         <v>0</v>
       </c>
       <c r="H68" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="D69" s="5">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="E69" s="5">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="G69" s="4">
         <v>0</v>
       </c>
       <c r="H69" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D70" s="5">
-        <v>28000</v>
+        <v>40000</v>
       </c>
       <c r="E70" s="5">
-        <v>28000</v>
+        <v>40000</v>
       </c>
       <c r="G70" s="4">
         <v>0</v>
       </c>
       <c r="H70" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>25</v>
+        <v>132</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>26</v>
+        <v>133</v>
       </c>
       <c r="D71" s="5">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="E71" s="5">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="G71" s="4">
         <v>0</v>
       </c>
       <c r="H71" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="D72" s="5">
-        <v>24000</v>
+        <v>8000</v>
       </c>
       <c r="E72" s="5">
-        <v>24000</v>
+        <v>8000</v>
       </c>
       <c r="G72" s="4">
         <v>0</v>
       </c>
       <c r="H72" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>7</v>
+        <v>136</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>8</v>
+        <v>137</v>
       </c>
       <c r="D73" s="5">
-        <v>25000</v>
+        <v>8000</v>
       </c>
       <c r="E73" s="5">
-        <v>25000</v>
+        <v>8000</v>
       </c>
       <c r="G73" s="4">
         <v>0</v>
       </c>
       <c r="H73" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B74" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D74" s="5">
+        <v>24000</v>
+      </c>
+      <c r="E74" s="5">
+        <v>24000</v>
+      </c>
+      <c r="G74" s="4">
+        <v>0</v>
+      </c>
+      <c r="H74" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A75" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D75" s="5">
+        <v>24000</v>
+      </c>
+      <c r="E75" s="5">
+        <v>24000</v>
+      </c>
+      <c r="G75" s="4">
+        <v>0</v>
+      </c>
+      <c r="H75" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A76" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B76" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="C76" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D74" s="5">
+      <c r="D76" s="5">
         <v>40000</v>
       </c>
-      <c r="E74" s="5">
+      <c r="E76" s="5">
         <v>40000</v>
       </c>
-      <c r="G74" s="4">
-        <v>0</v>
-      </c>
-      <c r="H74" t="s">
-        <v>124</v>
+      <c r="G76" s="4">
+        <v>0</v>
+      </c>
+      <c r="H76" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A77" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D77" s="5">
+        <v>40000</v>
+      </c>
+      <c r="E77" s="5">
+        <v>40000</v>
+      </c>
+      <c r="G77" s="4">
+        <v>0</v>
+      </c>
+      <c r="H77" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A78" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D78" s="5">
+        <v>6500</v>
+      </c>
+      <c r="E78" s="5">
+        <v>6500</v>
+      </c>
+      <c r="G78" s="4">
+        <v>0</v>
+      </c>
+      <c r="H78" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A79" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D79" s="5">
+        <v>7300</v>
+      </c>
+      <c r="E79" s="5">
+        <v>7300</v>
+      </c>
+      <c r="G79" s="4">
+        <v>0</v>
+      </c>
+      <c r="H79" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A80" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D80" s="5">
+        <v>7300</v>
+      </c>
+      <c r="E80" s="5">
+        <v>7300</v>
+      </c>
+      <c r="G80" s="4">
+        <v>0</v>
+      </c>
+      <c r="H80" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A81" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D81" s="5">
+        <v>4000</v>
+      </c>
+      <c r="E81" s="5">
+        <v>4000</v>
+      </c>
+      <c r="G81" s="4">
+        <v>0</v>
+      </c>
+      <c r="H81" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A82" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D82" s="5">
+        <v>10000</v>
+      </c>
+      <c r="E82" s="5">
+        <v>10000</v>
+      </c>
+      <c r="G82" s="4">
+        <v>0</v>
+      </c>
+      <c r="H82" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A83" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D83" s="5">
+        <v>20000</v>
+      </c>
+      <c r="E83" s="5">
+        <v>20000</v>
+      </c>
+      <c r="G83" s="4">
+        <v>0</v>
+      </c>
+      <c r="H83" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A84" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D84" s="5">
+        <v>20000</v>
+      </c>
+      <c r="E84" s="5">
+        <v>20000</v>
+      </c>
+      <c r="G84" s="4">
+        <v>0</v>
+      </c>
+      <c r="H84" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A85" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D85" s="5">
+        <v>20000</v>
+      </c>
+      <c r="E85" s="5">
+        <v>20000</v>
+      </c>
+      <c r="G85" s="4">
+        <v>0</v>
+      </c>
+      <c r="H85" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A86" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D86" s="5">
+        <v>20000</v>
+      </c>
+      <c r="E86" s="5">
+        <v>20000</v>
+      </c>
+      <c r="G86" s="4">
+        <v>0</v>
+      </c>
+      <c r="H86" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A87" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D87" s="5">
+        <v>40000</v>
+      </c>
+      <c r="E87" s="5">
+        <v>40000</v>
+      </c>
+      <c r="G87" s="4">
+        <v>0</v>
+      </c>
+      <c r="H87" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/data/Plan.xlsx
+++ b/data/Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raman/Documents/GitHub/production-board/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A688F7-C375-E74A-BACA-5665A3F1CE3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D62E5EC2-E660-5147-AE54-E2CC8F3CF1B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16560" xr2:uid="{7C08584A-5D47-2049-B143-911B93E5D6E0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="152">
   <si>
     <t>Date</t>
   </si>
@@ -134,12 +134,6 @@
     <t>Brightening Face Serum(10% VitaminC)30ml</t>
   </si>
   <si>
-    <t>CAP53</t>
-  </si>
-  <si>
-    <t>Anti-Frizz Leave-In Conditioner</t>
-  </si>
-  <si>
     <t>UKTTCAP1</t>
   </si>
   <si>
@@ -173,12 +167,6 @@
     <t>Acne Control Body Wash (236 ml)</t>
   </si>
   <si>
-    <t>CAP83</t>
-  </si>
-  <si>
-    <t>Brightening Boost Face Wash</t>
-  </si>
-  <si>
     <t>CAP17</t>
   </si>
   <si>
@@ -215,12 +203,6 @@
     <t>Combo- Anti-Hairfall Shampoo (100ml) + Anti-Hairfall Conditioner (100g)</t>
   </si>
   <si>
-    <t>CO343</t>
-  </si>
-  <si>
-    <t>Ultra smoothing kit ( shampoo 40 ml + mask 40 gm)</t>
-  </si>
-  <si>
     <t>CAP25</t>
   </si>
   <si>
@@ -299,18 +281,6 @@
     <t>UKTTBA6</t>
   </si>
   <si>
-    <t>BA89</t>
-  </si>
-  <si>
-    <t>100% Pure &amp; Natural Rosemary Essential Oil 15 ml</t>
-  </si>
-  <si>
-    <t>USTTCAP62</t>
-  </si>
-  <si>
-    <t>AHA Body Lotion 236ml - Tik Tok US</t>
-  </si>
-  <si>
     <t>BA93</t>
   </si>
   <si>
@@ -389,12 +359,6 @@
     <t>Outsource</t>
   </si>
   <si>
-    <t>CAP166</t>
-  </si>
-  <si>
-    <t>Under Arm Roll On- Fragrance Free - 75ml</t>
-  </si>
-  <si>
     <t>CAP2</t>
   </si>
   <si>
@@ -483,13 +447,61 @@
   </si>
   <si>
     <t>Curl Enhancing Hair Mask 250 gm</t>
+  </si>
+  <si>
+    <t>CAP119</t>
+  </si>
+  <si>
+    <t>AHA Body Lotion - 473 ml</t>
+  </si>
+  <si>
+    <t>CAP126</t>
+  </si>
+  <si>
+    <t>Chemist at Play Underarm Roll On Aqua 75ml</t>
+  </si>
+  <si>
+    <t>BA72</t>
+  </si>
+  <si>
+    <t>Bare Anatomy Nature x Science Argan Oil &amp; Vitamin E Anti Frizz Serum 75 ml</t>
+  </si>
+  <si>
+    <t>CAP153</t>
+  </si>
+  <si>
+    <t>Exfoliating face wash 100 ml</t>
+  </si>
+  <si>
+    <t>BA4</t>
+  </si>
+  <si>
+    <t>EXPERT | Damage Repair Shampoo (250 ML)</t>
+  </si>
+  <si>
+    <t>CAP49</t>
+  </si>
+  <si>
+    <t>Roll On: Fragrance Free (40 ml) (Rectangular)-399</t>
+  </si>
+  <si>
+    <t>CAP128</t>
+  </si>
+  <si>
+    <t>Chemist at Play Gentle &amp; Soothing Face Wash - 150ml</t>
+  </si>
+  <si>
+    <t>CAP136</t>
+  </si>
+  <si>
+    <t>Gentle and Soothing Face Wash 75 ml</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -508,6 +520,12 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -531,13 +549,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -874,6 +893,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C578346-EE80-DF41-8099-4E3028D96EBE}">
   <dimension ref="A1:H87"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="57.1640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -900,13 +922,13 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D2" s="5">
         <v>50000</v>
@@ -918,18 +940,18 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D3" s="5">
         <v>50000</v>
@@ -941,18 +963,18 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D4" s="5">
         <v>22000</v>
@@ -964,12 +986,12 @@
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>21</v>
@@ -987,18 +1009,18 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D6" s="5">
         <v>8000</v>
@@ -1010,7 +1032,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -1018,10 +1040,10 @@
         <v>46257</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D7" s="5">
         <v>50000</v>
@@ -1033,7 +1055,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -1056,7 +1078,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -1064,10 +1086,10 @@
         <v>46292</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D9" s="5">
         <v>25000</v>
@@ -1079,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -1087,10 +1109,10 @@
         <v>46292</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D10" s="5">
         <v>25000</v>
@@ -1102,7 +1124,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -1110,10 +1132,10 @@
         <v>46256</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D11" s="5">
         <v>7500</v>
@@ -1125,7 +1147,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -1133,10 +1155,10 @@
         <v>46267</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D12" s="5">
         <v>20000</v>
@@ -1148,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -1156,10 +1178,10 @@
         <v>46258</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D13" s="5">
         <v>30000</v>
@@ -1171,7 +1193,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -1179,10 +1201,10 @@
         <v>46262</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D14" s="5">
         <v>20000</v>
@@ -1194,7 +1216,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -1202,10 +1224,10 @@
         <v>46262</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D15" s="5">
         <v>30000</v>
@@ -1217,329 +1239,343 @@
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>86</v>
+        <v>136</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D16" s="5">
-        <v>1000</v>
+        <v>137</v>
+      </c>
+      <c r="D16" s="3">
+        <v>500</v>
       </c>
       <c r="E16" s="3">
-        <v>0</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="F16" s="6"/>
       <c r="G16" s="4">
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>11</v>
+        <v>106</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>12</v>
+        <v>107</v>
       </c>
       <c r="D17" s="5">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="E17" s="5">
-        <v>4000</v>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="F17" s="6"/>
       <c r="G17" s="4">
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>116</v>
+        <v>48</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>117</v>
+        <v>49</v>
       </c>
       <c r="D18" s="5">
-        <v>6000</v>
+        <v>2100</v>
       </c>
       <c r="E18" s="5">
-        <v>6000</v>
-      </c>
+        <v>2100</v>
+      </c>
+      <c r="F18" s="6"/>
       <c r="G18" s="4">
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>31</v>
+        <v>138</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>32</v>
+        <v>139</v>
       </c>
       <c r="D19" s="5">
-        <v>7000</v>
+        <v>3000</v>
       </c>
       <c r="E19" s="5">
-        <v>7000</v>
-      </c>
+        <v>3000</v>
+      </c>
+      <c r="F19" s="6"/>
       <c r="G19" s="4">
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="D20" s="5">
-        <v>8000</v>
+        <v>6000</v>
       </c>
       <c r="E20" s="5">
-        <v>8000</v>
-      </c>
+        <v>6000</v>
+      </c>
+      <c r="F20" s="6"/>
       <c r="G20" s="4">
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="D21" s="5">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="E21" s="5">
-        <v>10000</v>
-      </c>
+        <v>8000</v>
+      </c>
+      <c r="F21" s="6"/>
       <c r="G21" s="4">
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="D22" s="5">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="E22" s="5">
-        <v>10000</v>
-      </c>
+        <v>8000</v>
+      </c>
+      <c r="F22" s="6"/>
       <c r="G22" s="4">
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D23" s="5">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="E23" s="5">
-        <v>10000</v>
-      </c>
+        <v>8000</v>
+      </c>
+      <c r="F23" s="6"/>
       <c r="G23" s="4">
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="D24" s="5">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="E24" s="5">
-        <v>10000</v>
-      </c>
+        <v>8000</v>
+      </c>
+      <c r="F24" s="6"/>
       <c r="G24" s="4">
         <v>0</v>
       </c>
       <c r="H24" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>28</v>
+        <v>91</v>
       </c>
       <c r="D25" s="5">
-        <v>17000</v>
+        <v>8000</v>
       </c>
       <c r="E25" s="5">
-        <v>17000</v>
-      </c>
+        <v>8000</v>
+      </c>
+      <c r="F25" s="6"/>
       <c r="G25" s="4">
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="D26" s="5">
-        <v>18797</v>
+        <v>10000</v>
       </c>
       <c r="E26" s="5">
-        <v>18797</v>
-      </c>
+        <v>10000</v>
+      </c>
+      <c r="F26" s="6"/>
       <c r="G26" s="4">
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="D27" s="5">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E27" s="5">
-        <v>20000</v>
-      </c>
+        <v>10000</v>
+      </c>
+      <c r="F27" s="6"/>
       <c r="G27" s="4">
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D28" s="5">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E28" s="5">
-        <v>20000</v>
-      </c>
+        <v>10000</v>
+      </c>
+      <c r="F28" s="6"/>
       <c r="G28" s="4">
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="D29" s="5">
-        <v>30000</v>
+        <v>14000</v>
       </c>
       <c r="E29" s="5">
-        <v>30000</v>
-      </c>
+        <v>14000</v>
+      </c>
+      <c r="F29" s="6"/>
       <c r="G29" s="4">
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
@@ -1547,22 +1583,23 @@
         <v>46256</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="D30" s="5">
-        <v>1000</v>
+        <v>24200</v>
       </c>
       <c r="E30" s="5">
-        <v>1000</v>
-      </c>
+        <v>24200</v>
+      </c>
+      <c r="F30" s="6"/>
       <c r="G30" s="4">
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
@@ -1570,22 +1607,23 @@
         <v>46256</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="D31" s="5">
-        <v>6000</v>
+        <v>35000</v>
       </c>
       <c r="E31" s="5">
-        <v>6000</v>
-      </c>
+        <v>35000</v>
+      </c>
+      <c r="F31" s="6"/>
       <c r="G31" s="4">
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
@@ -1593,183 +1631,191 @@
         <v>46256</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="D32" s="5">
-        <v>8000</v>
+        <v>40000</v>
       </c>
       <c r="E32" s="5">
-        <v>8000</v>
-      </c>
+        <v>40000</v>
+      </c>
+      <c r="F32" s="6"/>
       <c r="G32" s="4">
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D33" s="5">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="E33" s="5">
-        <v>10000</v>
-      </c>
+        <v>2000</v>
+      </c>
+      <c r="F33" s="6"/>
       <c r="G33" s="4">
         <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="D34" s="5">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="E34" s="5">
-        <v>10000</v>
-      </c>
+        <v>5000</v>
+      </c>
+      <c r="F34" s="6"/>
       <c r="G34" s="4">
         <v>0</v>
       </c>
       <c r="H34" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D35" s="5">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="E35" s="5">
-        <v>10000</v>
-      </c>
+        <v>8000</v>
+      </c>
+      <c r="F35" s="6"/>
       <c r="G35" s="4">
         <v>0</v>
       </c>
       <c r="H35" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>25</v>
+        <v>94</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="D36" s="5">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="E36" s="5">
-        <v>10000</v>
-      </c>
+        <v>12000</v>
+      </c>
+      <c r="F36" s="6"/>
       <c r="G36" s="4">
         <v>0</v>
       </c>
       <c r="H36" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="D37" s="5">
-        <v>24000</v>
+        <v>15000</v>
       </c>
       <c r="E37" s="5">
-        <v>24000</v>
-      </c>
+        <v>15000</v>
+      </c>
+      <c r="F37" s="6"/>
       <c r="G37" s="4">
         <v>0</v>
       </c>
       <c r="H37" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>9</v>
+        <v>98</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="D38" s="5">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="E38" s="5">
-        <v>40000</v>
-      </c>
+        <v>20000</v>
+      </c>
+      <c r="F38" s="6"/>
       <c r="G38" s="4">
         <v>0</v>
       </c>
       <c r="H38" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>94</v>
+        <v>56</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="D39" s="5">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="E39" s="5">
-        <v>40000</v>
-      </c>
+        <v>20000</v>
+      </c>
+      <c r="F39" s="6"/>
       <c r="G39" s="4">
         <v>0</v>
       </c>
       <c r="H39" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
@@ -1777,22 +1823,23 @@
         <v>46257</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="D40" s="5">
-        <v>2000</v>
+        <v>35000</v>
       </c>
       <c r="E40" s="5">
-        <v>2000</v>
-      </c>
+        <v>35000</v>
+      </c>
+      <c r="F40" s="6"/>
       <c r="G40" s="4">
         <v>0</v>
       </c>
       <c r="H40" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
@@ -1800,125 +1847,130 @@
         <v>46257</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="D41" s="5">
-        <v>8000</v>
+        <v>35000</v>
       </c>
       <c r="E41" s="5">
-        <v>8000</v>
-      </c>
+        <v>35000</v>
+      </c>
+      <c r="F41" s="6"/>
       <c r="G41" s="4">
         <v>0</v>
       </c>
       <c r="H41" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D42" s="5">
-        <v>8000</v>
-      </c>
-      <c r="E42" s="5">
-        <v>8000</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="D42" s="3">
+        <v>900</v>
+      </c>
+      <c r="E42" s="3">
+        <v>900</v>
+      </c>
+      <c r="F42" s="6"/>
       <c r="G42" s="4">
         <v>0</v>
       </c>
       <c r="H42" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D43" s="5">
-        <v>8000</v>
+        <v>3700</v>
       </c>
       <c r="E43" s="5">
-        <v>8000</v>
-      </c>
+        <v>3700</v>
+      </c>
+      <c r="F43" s="6"/>
       <c r="G43" s="4">
         <v>0</v>
       </c>
       <c r="H43" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>101</v>
+        <v>45</v>
       </c>
       <c r="D44" s="5">
-        <v>8000</v>
+        <v>6000</v>
       </c>
       <c r="E44" s="5">
-        <v>8000</v>
-      </c>
+        <v>6000</v>
+      </c>
+      <c r="F44" s="6"/>
       <c r="G44" s="4">
         <v>0</v>
       </c>
       <c r="H44" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D45" s="5">
-        <v>8000</v>
+        <v>11000</v>
       </c>
       <c r="E45" s="5">
-        <v>8000</v>
-      </c>
+        <v>11000</v>
+      </c>
+      <c r="F45" s="6"/>
       <c r="G45" s="4">
         <v>0</v>
       </c>
       <c r="H45" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D46" s="5">
         <v>12000</v>
@@ -1926,45 +1978,47 @@
       <c r="E46" s="5">
         <v>12000</v>
       </c>
+      <c r="F46" s="6"/>
       <c r="G46" s="4">
         <v>0</v>
       </c>
       <c r="H46" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>120</v>
+        <v>23</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>121</v>
+        <v>24</v>
       </c>
       <c r="D47" s="5">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="E47" s="5">
-        <v>15000</v>
-      </c>
+        <v>18000</v>
+      </c>
+      <c r="F47" s="6"/>
       <c r="G47" s="4">
         <v>0</v>
       </c>
       <c r="H47" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D48" s="5">
         <v>20000</v>
@@ -1972,137 +2026,143 @@
       <c r="E48" s="5">
         <v>20000</v>
       </c>
+      <c r="F48" s="6"/>
       <c r="G48" s="4">
         <v>0</v>
       </c>
       <c r="H48" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>54</v>
+        <v>112</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>55</v>
+        <v>113</v>
       </c>
       <c r="D49" s="5">
-        <v>35000</v>
+        <v>20000</v>
       </c>
       <c r="E49" s="5">
-        <v>35000</v>
-      </c>
+        <v>20000</v>
+      </c>
+      <c r="F49" s="6"/>
       <c r="G49" s="4">
         <v>0</v>
       </c>
       <c r="H49" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>93</v>
+        <v>26</v>
       </c>
       <c r="D50" s="5">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="E50" s="5">
-        <v>40000</v>
-      </c>
+        <v>20000</v>
+      </c>
+      <c r="F50" s="6"/>
       <c r="G50" s="4">
         <v>0</v>
       </c>
       <c r="H50" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D51" s="3">
-        <v>900</v>
-      </c>
-      <c r="E51" s="3">
-        <v>900</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="D51" s="5">
+        <v>2300</v>
+      </c>
+      <c r="E51" s="5">
+        <v>2300</v>
+      </c>
+      <c r="F51" s="6"/>
       <c r="G51" s="4">
         <v>0</v>
       </c>
       <c r="H51" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="D52" s="5">
-        <v>3700</v>
+        <v>2500</v>
       </c>
       <c r="E52" s="5">
-        <v>3700</v>
-      </c>
+        <v>2500</v>
+      </c>
+      <c r="F52" s="6"/>
       <c r="G52" s="4">
         <v>0</v>
       </c>
       <c r="H52" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="D53" s="5">
-        <v>8000</v>
+        <v>6300</v>
       </c>
       <c r="E53" s="5">
-        <v>8000</v>
-      </c>
+        <v>6300</v>
+      </c>
+      <c r="F53" s="6"/>
       <c r="G53" s="4">
         <v>0</v>
       </c>
       <c r="H53" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="D54" s="5">
         <v>10000</v>
@@ -2110,91 +2170,95 @@
       <c r="E54" s="5">
         <v>10000</v>
       </c>
+      <c r="F54" s="6"/>
       <c r="G54" s="4">
         <v>0</v>
       </c>
       <c r="H54" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>56</v>
+        <v>124</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>57</v>
+        <v>125</v>
       </c>
       <c r="D55" s="5">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="E55" s="5">
-        <v>10000</v>
-      </c>
+        <v>12000</v>
+      </c>
+      <c r="F55" s="6"/>
       <c r="G55" s="4">
         <v>0</v>
       </c>
       <c r="H55" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>110</v>
+        <v>17</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>111</v>
+        <v>18</v>
       </c>
       <c r="D56" s="5">
-        <v>11000</v>
+        <v>14000</v>
       </c>
       <c r="E56" s="5">
-        <v>11000</v>
-      </c>
+        <v>14000</v>
+      </c>
+      <c r="F56" s="6"/>
       <c r="G56" s="4">
         <v>0</v>
       </c>
       <c r="H56" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>112</v>
+        <v>27</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>113</v>
+        <v>28</v>
       </c>
       <c r="D57" s="5">
-        <v>12000</v>
+        <v>18000</v>
       </c>
       <c r="E57" s="5">
-        <v>12000</v>
-      </c>
+        <v>18000</v>
+      </c>
+      <c r="F57" s="6"/>
       <c r="G57" s="4">
         <v>0</v>
       </c>
       <c r="H57" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="D58" s="5">
         <v>20000</v>
@@ -2202,160 +2266,167 @@
       <c r="E58" s="5">
         <v>20000</v>
       </c>
+      <c r="F58" s="6"/>
       <c r="G58" s="4">
         <v>0</v>
       </c>
       <c r="H58" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>108</v>
+        <v>13</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>109</v>
+        <v>14</v>
       </c>
       <c r="D59" s="5">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="E59" s="5">
-        <v>20000</v>
-      </c>
+        <v>40000</v>
+      </c>
+      <c r="F59" s="6"/>
       <c r="G59" s="4">
         <v>0</v>
       </c>
       <c r="H59" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D60" s="5">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="E60" s="5">
-        <v>20000</v>
-      </c>
+        <v>5000</v>
+      </c>
+      <c r="F60" s="6"/>
       <c r="G60" s="4">
         <v>0</v>
       </c>
       <c r="H60" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>25</v>
+        <v>140</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>26</v>
+        <v>141</v>
       </c>
       <c r="D61" s="5">
-        <v>20000</v>
+        <v>3000</v>
       </c>
       <c r="E61" s="5">
-        <v>20000</v>
-      </c>
+        <v>3000</v>
+      </c>
+      <c r="F61" s="6"/>
       <c r="G61" s="4">
         <v>0</v>
       </c>
       <c r="H61" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="D62" s="5">
-        <v>2300</v>
+        <v>7300</v>
       </c>
       <c r="E62" s="5">
-        <v>2300</v>
-      </c>
+        <v>7300</v>
+      </c>
+      <c r="F62" s="6"/>
       <c r="G62" s="4">
         <v>0</v>
       </c>
       <c r="H62" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D63" s="5">
-        <v>2500</v>
+        <v>8000</v>
       </c>
       <c r="E63" s="5">
-        <v>2500</v>
-      </c>
+        <v>8000</v>
+      </c>
+      <c r="F63" s="6"/>
       <c r="G63" s="4">
         <v>0</v>
       </c>
       <c r="H63" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D64" s="5">
-        <v>6300</v>
+        <v>24000</v>
       </c>
       <c r="E64" s="5">
-        <v>6300</v>
-      </c>
+        <v>24000</v>
+      </c>
+      <c r="F64" s="6"/>
       <c r="G64" s="4">
         <v>0</v>
       </c>
       <c r="H64" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>37</v>
+        <v>142</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>38</v>
+        <v>143</v>
       </c>
       <c r="D65" s="5">
         <v>10000</v>
@@ -2363,229 +2434,239 @@
       <c r="E65" s="5">
         <v>10000</v>
       </c>
+      <c r="F65" s="6"/>
       <c r="G65" s="4">
         <v>0</v>
       </c>
       <c r="H65" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>17</v>
+        <v>128</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>18</v>
+        <v>129</v>
       </c>
       <c r="D66" s="5">
-        <v>14000</v>
+        <v>12000</v>
       </c>
       <c r="E66" s="5">
-        <v>14000</v>
-      </c>
+        <v>12000</v>
+      </c>
+      <c r="F66" s="6"/>
       <c r="G66" s="4">
         <v>0</v>
       </c>
       <c r="H66" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D67" s="5">
-        <v>18000</v>
+        <v>40000</v>
       </c>
       <c r="E67" s="5">
-        <v>18000</v>
-      </c>
+        <v>40000</v>
+      </c>
+      <c r="F67" s="6"/>
       <c r="G67" s="4">
         <v>0</v>
       </c>
       <c r="H67" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D68" s="5">
-        <v>18000</v>
+        <v>40000</v>
       </c>
       <c r="E68" s="5">
-        <v>18000</v>
-      </c>
+        <v>40000</v>
+      </c>
+      <c r="F68" s="6"/>
       <c r="G68" s="4">
         <v>0</v>
       </c>
       <c r="H68" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>13</v>
+        <v>130</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>14</v>
+        <v>131</v>
       </c>
       <c r="D69" s="5">
-        <v>40000</v>
+        <v>6000</v>
       </c>
       <c r="E69" s="5">
-        <v>40000</v>
-      </c>
+        <v>6000</v>
+      </c>
+      <c r="F69" s="6"/>
       <c r="G69" s="4">
         <v>0</v>
       </c>
       <c r="H69" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>20</v>
+        <v>135</v>
       </c>
       <c r="D70" s="5">
-        <v>40000</v>
+        <v>7300</v>
       </c>
       <c r="E70" s="5">
-        <v>40000</v>
-      </c>
+        <v>7300</v>
+      </c>
+      <c r="F70" s="6"/>
       <c r="G70" s="4">
         <v>0</v>
       </c>
       <c r="H70" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="D71" s="5">
-        <v>5000</v>
+        <v>7500</v>
       </c>
       <c r="E71" s="5">
-        <v>5000</v>
-      </c>
+        <v>7500</v>
+      </c>
+      <c r="F71" s="6"/>
       <c r="G71" s="4">
         <v>0</v>
       </c>
       <c r="H71" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>134</v>
+        <v>15</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>135</v>
+        <v>16</v>
       </c>
       <c r="D72" s="5">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="E72" s="5">
-        <v>8000</v>
-      </c>
+        <v>10000</v>
+      </c>
+      <c r="F72" s="6"/>
       <c r="G72" s="4">
         <v>0</v>
       </c>
       <c r="H72" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>136</v>
+        <v>7</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>137</v>
+        <v>8</v>
       </c>
       <c r="D73" s="5">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="E73" s="5">
-        <v>8000</v>
-      </c>
+        <v>10000</v>
+      </c>
+      <c r="F73" s="6"/>
       <c r="G73" s="4">
         <v>0</v>
       </c>
       <c r="H73" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>138</v>
+        <v>33</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="D74" s="5">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="E74" s="5">
-        <v>24000</v>
-      </c>
+        <v>20000</v>
+      </c>
+      <c r="F74" s="6"/>
       <c r="G74" s="4">
         <v>0</v>
       </c>
       <c r="H74" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D75" s="5">
         <v>24000</v>
@@ -2593,22 +2674,23 @@
       <c r="E75" s="5">
         <v>24000</v>
       </c>
+      <c r="F75" s="6"/>
       <c r="G75" s="4">
         <v>0</v>
       </c>
       <c r="H75" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D76" s="5">
         <v>40000</v>
@@ -2616,22 +2698,23 @@
       <c r="E76" s="5">
         <v>40000</v>
       </c>
+      <c r="F76" s="6"/>
       <c r="G76" s="4">
         <v>0</v>
       </c>
       <c r="H76" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>9</v>
+        <v>84</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>10</v>
+        <v>85</v>
       </c>
       <c r="D77" s="5">
         <v>40000</v>
@@ -2639,137 +2722,143 @@
       <c r="E77" s="5">
         <v>40000</v>
       </c>
+      <c r="F77" s="6"/>
       <c r="G77" s="4">
         <v>0</v>
       </c>
       <c r="H77" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
-        <v>46261</v>
+        <v>46263</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>142</v>
+        <v>29</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>143</v>
+        <v>30</v>
       </c>
       <c r="D78" s="5">
-        <v>6500</v>
+        <v>4000</v>
       </c>
       <c r="E78" s="5">
-        <v>6500</v>
-      </c>
+        <v>4000</v>
+      </c>
+      <c r="F78" s="6"/>
       <c r="G78" s="4">
         <v>0</v>
       </c>
       <c r="H78" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
-        <v>46261</v>
+        <v>46263</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>144</v>
+        <v>15</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>145</v>
+        <v>16</v>
       </c>
       <c r="D79" s="5">
-        <v>7300</v>
+        <v>5000</v>
       </c>
       <c r="E79" s="5">
-        <v>7300</v>
-      </c>
+        <v>5000</v>
+      </c>
+      <c r="F79" s="6"/>
       <c r="G79" s="4">
         <v>0</v>
       </c>
       <c r="H79" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
-        <v>46261</v>
+        <v>46263</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>146</v>
+        <v>11</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>147</v>
+        <v>12</v>
       </c>
       <c r="D80" s="5">
-        <v>7300</v>
+        <v>8000</v>
       </c>
       <c r="E80" s="5">
-        <v>7300</v>
-      </c>
+        <v>8000</v>
+      </c>
+      <c r="F80" s="6"/>
       <c r="G80" s="4">
         <v>0</v>
       </c>
       <c r="H80" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
-        <v>46261</v>
+        <v>46263</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="D81" s="5">
-        <v>4000</v>
+        <v>10000</v>
       </c>
       <c r="E81" s="5">
-        <v>4000</v>
-      </c>
+        <v>10000</v>
+      </c>
+      <c r="F81" s="6"/>
       <c r="G81" s="4">
         <v>0</v>
       </c>
       <c r="H81" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
-        <v>46261</v>
+        <v>46263</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D82" s="5">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="E82" s="5">
-        <v>10000</v>
-      </c>
+        <v>20000</v>
+      </c>
+      <c r="F82" s="6"/>
       <c r="G82" s="4">
         <v>0</v>
       </c>
       <c r="H82" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
-        <v>46261</v>
+        <v>46263</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D83" s="5">
         <v>20000</v>
@@ -2777,22 +2866,23 @@
       <c r="E83" s="5">
         <v>20000</v>
       </c>
+      <c r="F83" s="6"/>
       <c r="G83" s="4">
         <v>0</v>
       </c>
       <c r="H83" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
-        <v>46261</v>
+        <v>46263</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="D84" s="5">
         <v>20000</v>
@@ -2800,22 +2890,23 @@
       <c r="E84" s="5">
         <v>20000</v>
       </c>
+      <c r="F84" s="6"/>
       <c r="G84" s="4">
         <v>0</v>
       </c>
       <c r="H84" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
-        <v>46261</v>
+        <v>46263</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="D85" s="5">
         <v>20000</v>
@@ -2823,57 +2914,60 @@
       <c r="E85" s="5">
         <v>20000</v>
       </c>
+      <c r="F85" s="6"/>
       <c r="G85" s="4">
         <v>0</v>
       </c>
       <c r="H85" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
-        <v>46261</v>
+        <v>46264</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>7</v>
+        <v>148</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>8</v>
+        <v>149</v>
       </c>
       <c r="D86" s="5">
-        <v>20000</v>
+        <v>1200</v>
       </c>
       <c r="E86" s="5">
-        <v>20000</v>
-      </c>
+        <v>1200</v>
+      </c>
+      <c r="F86" s="6"/>
       <c r="G86" s="4">
         <v>0</v>
       </c>
       <c r="H86" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
-        <v>46261</v>
+        <v>46264</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>19</v>
+        <v>150</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>20</v>
+        <v>151</v>
       </c>
       <c r="D87" s="5">
-        <v>40000</v>
+        <v>8000</v>
       </c>
       <c r="E87" s="5">
-        <v>40000</v>
-      </c>
+        <v>8000</v>
+      </c>
+      <c r="F87" s="6"/>
       <c r="G87" s="4">
         <v>0</v>
       </c>
       <c r="H87" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/data/Plan.xlsx
+++ b/data/Plan.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raman/Documents/GitHub/production-board/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D62E5EC2-E660-5147-AE54-E2CC8F3CF1B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57B01806-35C6-774D-B1FC-676ABF4D1E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16560" xr2:uid="{7C08584A-5D47-2049-B143-911B93E5D6E0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="114">
   <si>
     <t>Date</t>
   </si>
@@ -68,12 +68,6 @@
     <t>Brightening face serum (10% Vitamin C) 10ml</t>
   </si>
   <si>
-    <t>BA76</t>
-  </si>
-  <si>
-    <t>Rosemary &amp; Rice Water Hair Growth Spray-200ml</t>
-  </si>
-  <si>
     <t>BA97</t>
   </si>
   <si>
@@ -116,12 +110,6 @@
     <t>BA Expert Anti Hairfall Shampoo 100 ml</t>
   </si>
   <si>
-    <t>CAP105</t>
-  </si>
-  <si>
-    <t>Gentle Exfoliating Face Scrub 100ML</t>
-  </si>
-  <si>
     <t>BA74</t>
   </si>
   <si>
@@ -134,87 +122,27 @@
     <t>Brightening Face Serum(10% VitaminC)30ml</t>
   </si>
   <si>
-    <t>UKTTCAP1</t>
-  </si>
-  <si>
-    <t>Acne Body Wash 236 ml-TikTok UK</t>
-  </si>
-  <si>
     <t>CAP82</t>
   </si>
   <si>
     <t>Oil &amp; Acne Control Face Wash</t>
   </si>
   <si>
-    <t>BA109</t>
-  </si>
-  <si>
-    <t>Advanced Anti Dandruff Serum - 50ml</t>
-  </si>
-  <si>
     <t>CAP24</t>
   </si>
   <si>
-    <t>CO358</t>
-  </si>
-  <si>
-    <t>Combo- Anti-Dandruff Shampoo (100ml) + Anti-Dandruff Conditioner (100g)</t>
-  </si>
-  <si>
-    <t>CAP1</t>
-  </si>
-  <si>
-    <t>Acne Control Body Wash (236 ml)</t>
-  </si>
-  <si>
-    <t>CAP17</t>
-  </si>
-  <si>
-    <t>Brightening Body Wash (473 ml)</t>
-  </si>
-  <si>
     <t>CAP77</t>
   </si>
   <si>
     <t>Exfoliating Body Scrub - 75 gms</t>
   </si>
   <si>
-    <t>CAP34</t>
-  </si>
-  <si>
-    <t>Hydrating Body Wash (236 ml)</t>
-  </si>
-  <si>
-    <t>BA105</t>
-  </si>
-  <si>
-    <t>Ultra smoothing shampoo 100 ml</t>
-  </si>
-  <si>
-    <t>CAP16</t>
-  </si>
-  <si>
-    <t>Brightening Body Wash (236 ml)</t>
-  </si>
-  <si>
     <t>CO357</t>
   </si>
   <si>
     <t>Combo- Anti-Hairfall Shampoo (100ml) + Anti-Hairfall Conditioner (100g)</t>
   </si>
   <si>
-    <t>CAP25</t>
-  </si>
-  <si>
-    <t>Exfoliating Body Wash (473 ml)</t>
-  </si>
-  <si>
-    <t>CAP137</t>
-  </si>
-  <si>
-    <t>Oil &amp; Acne Control Face Wash 100ml - Flipkart</t>
-  </si>
-  <si>
     <t>CAP139</t>
   </si>
   <si>
@@ -281,120 +209,18 @@
     <t>UKTTBA6</t>
   </si>
   <si>
-    <t>BA93</t>
-  </si>
-  <si>
-    <t>EXPERT | Ultra Smoothing Serum (100 ML)</t>
-  </si>
-  <si>
-    <t>CAP48</t>
-  </si>
-  <si>
-    <t>Roll On: Aqua 40 ml (Rectangular Monocarton)-399</t>
-  </si>
-  <si>
     <t>BA22</t>
   </si>
   <si>
     <t>BA Expert | Anti Hairfall Shampoo 250 ml</t>
   </si>
   <si>
-    <t>SV05</t>
-  </si>
-  <si>
-    <t>Stay vista shower gel 30 ml</t>
-  </si>
-  <si>
-    <t>SV02</t>
-  </si>
-  <si>
-    <t>Stay Vista Nourishing Shampoo 30ml</t>
-  </si>
-  <si>
-    <t>SV06</t>
-  </si>
-  <si>
-    <t>Stay vista body lotion 30 ml</t>
-  </si>
-  <si>
-    <t>SV04</t>
-  </si>
-  <si>
-    <t>Stay Vista Smoothing Conditioner 30ml</t>
-  </si>
-  <si>
-    <t>BA3</t>
-  </si>
-  <si>
-    <t>EXPERT | Color Protect Shampoo (250 ML)</t>
-  </si>
-  <si>
-    <t>BA75</t>
-  </si>
-  <si>
-    <t>Anti Dandruff Shampoo- 750ml</t>
-  </si>
-  <si>
-    <t>USTTBA93</t>
-  </si>
-  <si>
-    <t>EXPERT | Ultra Smoothing Serum (100 ML) - TikTok US</t>
-  </si>
-  <si>
-    <t>BA98</t>
-  </si>
-  <si>
-    <t>Anti-Dandruff Conditioner -175gm</t>
-  </si>
-  <si>
-    <t>BA1</t>
-  </si>
-  <si>
-    <t>EXPERT | Anti-Frizz Shampoo (250 ML)</t>
-  </si>
-  <si>
     <t>Inhouse</t>
   </si>
   <si>
     <t>Outsource</t>
   </si>
   <si>
-    <t>CAP2</t>
-  </si>
-  <si>
-    <t>Acne Control Body Wash (473 ml)</t>
-  </si>
-  <si>
-    <t>BA108</t>
-  </si>
-  <si>
-    <t>Neem &amp; Lemon Dandruff Control Scalp Spray - 200ml</t>
-  </si>
-  <si>
-    <t>BA26</t>
-  </si>
-  <si>
-    <t>EXPERT | Scalp Scrub (250 gms)</t>
-  </si>
-  <si>
-    <t>BA87</t>
-  </si>
-  <si>
-    <t>Advanced Anti-Grey Hair Serum 50ml</t>
-  </si>
-  <si>
-    <t>CAP145</t>
-  </si>
-  <si>
-    <t>Oil &amp; Acne Control Face Wash - Flipkart pack of 3</t>
-  </si>
-  <si>
-    <t>CAP80</t>
-  </si>
-  <si>
-    <t>CAP Retinol Body Lotion 200 ml</t>
-  </si>
-  <si>
     <t>BA55</t>
   </si>
   <si>
@@ -449,12 +275,6 @@
     <t>Curl Enhancing Hair Mask 250 gm</t>
   </si>
   <si>
-    <t>CAP119</t>
-  </si>
-  <si>
-    <t>AHA Body Lotion - 473 ml</t>
-  </si>
-  <si>
     <t>CAP126</t>
   </si>
   <si>
@@ -479,12 +299,6 @@
     <t>EXPERT | Damage Repair Shampoo (250 ML)</t>
   </si>
   <si>
-    <t>CAP49</t>
-  </si>
-  <si>
-    <t>Roll On: Fragrance Free (40 ml) (Rectangular)-399</t>
-  </si>
-  <si>
     <t>CAP128</t>
   </si>
   <si>
@@ -495,6 +309,78 @@
   </si>
   <si>
     <t>Gentle and Soothing Face Wash 75 ml</t>
+  </si>
+  <si>
+    <t>VIE12</t>
+  </si>
+  <si>
+    <t>Vinci Elivaas Shampoo 5ltr</t>
+  </si>
+  <si>
+    <t>VIE13</t>
+  </si>
+  <si>
+    <t>Vinci Elivaas conditioner 5Ltr</t>
+  </si>
+  <si>
+    <t>CAP83</t>
+  </si>
+  <si>
+    <t>Brightening Boost Face Wash</t>
+  </si>
+  <si>
+    <t>BA121</t>
+  </si>
+  <si>
+    <t>NxS Flaxseed &amp; Rice Water Hair Gel 300ml</t>
+  </si>
+  <si>
+    <t>USTTCAP62</t>
+  </si>
+  <si>
+    <t>AHA Body Lotion 236ml - Tik Tok US</t>
+  </si>
+  <si>
+    <t>USTTCAP16</t>
+  </si>
+  <si>
+    <t>Brightening body wash 236 ml - Tik Tok US</t>
+  </si>
+  <si>
+    <t>VIE11</t>
+  </si>
+  <si>
+    <t>Vinci Elivaas Lotion 5ltr</t>
+  </si>
+  <si>
+    <t>VIE09</t>
+  </si>
+  <si>
+    <t>Vinci Elivaas Bodywash 5ltr</t>
+  </si>
+  <si>
+    <t>CAP62</t>
+  </si>
+  <si>
+    <t>AHA Body Lotion 236 ml</t>
+  </si>
+  <si>
+    <t>BA10</t>
+  </si>
+  <si>
+    <t>EXPERT | Ultra Smoothing Shampoo (250 ML) -  TikTok US</t>
+  </si>
+  <si>
+    <t>USTTBA10</t>
+  </si>
+  <si>
+    <t>Exfoliating Body Wash (236 ml)</t>
+  </si>
+  <si>
+    <t>SS43</t>
+  </si>
+  <si>
+    <t>5% Niacinamide Sunscreen Body Lotion 200 ml</t>
   </si>
 </sst>
 </file>
@@ -891,7 +777,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C578346-EE80-DF41-8099-4E3028D96EBE}">
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="57.1640625" customWidth="1"/>
@@ -922,13 +808,13 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="D2" s="5">
         <v>50000</v>
@@ -940,18 +826,18 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>105</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="D3" s="5">
         <v>50000</v>
@@ -963,41 +849,41 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>105</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="D4" s="5">
-        <v>22000</v>
+        <v>2000</v>
       </c>
       <c r="E4" s="5">
-        <v>22000</v>
+        <v>2000</v>
       </c>
       <c r="G4" s="4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>105</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D5" s="5">
         <v>64000</v>
@@ -1009,18 +895,18 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>105</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="D6" s="5">
         <v>8000</v>
@@ -1032,18 +918,18 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>105</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="D7" s="5">
         <v>50000</v>
@@ -1055,7 +941,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>105</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -1063,10 +949,10 @@
         <v>46262</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D8" s="5">
         <v>80000</v>
@@ -1078,7 +964,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>105</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -1086,10 +972,10 @@
         <v>46292</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="D9" s="5">
         <v>25000</v>
@@ -1101,7 +987,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>105</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -1109,10 +995,10 @@
         <v>46292</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="D10" s="5">
         <v>25000</v>
@@ -1124,7 +1010,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>105</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -1132,10 +1018,10 @@
         <v>46256</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="D11" s="5">
         <v>7500</v>
@@ -1147,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>105</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -1155,10 +1041,10 @@
         <v>46267</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="D12" s="5">
         <v>20000</v>
@@ -1170,7 +1056,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>105</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -1178,10 +1064,10 @@
         <v>46258</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="D13" s="5">
         <v>30000</v>
@@ -1193,7 +1079,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>105</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -1201,10 +1087,10 @@
         <v>46262</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="D14" s="5">
         <v>20000</v>
@@ -1216,7 +1102,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>105</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -1224,10 +1110,10 @@
         <v>46262</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="D15" s="5">
         <v>30000</v>
@@ -1239,276 +1125,276 @@
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>105</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>137</v>
+        <v>91</v>
       </c>
       <c r="D16" s="3">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="E16" s="3">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="4">
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D17" s="5">
-        <v>1000</v>
-      </c>
-      <c r="E17" s="5">
-        <v>1000</v>
+        <v>93</v>
+      </c>
+      <c r="D17" s="3">
+        <v>50</v>
+      </c>
+      <c r="E17" s="3">
+        <v>50</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="4">
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="D18" s="5">
-        <v>2100</v>
+        <v>5000</v>
       </c>
       <c r="E18" s="5">
-        <v>2100</v>
+        <v>3200</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="4">
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>138</v>
+        <v>30</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>139</v>
+        <v>31</v>
       </c>
       <c r="D19" s="5">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="E19" s="5">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="4">
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="D20" s="5">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="E20" s="5">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="4">
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D21" s="5">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="E21" s="5">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="4">
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>88</v>
+        <v>9</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="D22" s="5">
-        <v>8000</v>
+        <v>11000</v>
       </c>
       <c r="E22" s="5">
-        <v>8000</v>
+        <v>11000</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="4">
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="D23" s="5">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="E23" s="5">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="4">
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>93</v>
+        <v>24</v>
       </c>
       <c r="D24" s="5">
-        <v>8000</v>
+        <v>18000</v>
       </c>
       <c r="E24" s="5">
-        <v>8000</v>
+        <v>18000</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="4">
         <v>0</v>
       </c>
       <c r="H24" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="D25" s="5">
-        <v>8000</v>
+        <v>24000</v>
       </c>
       <c r="E25" s="5">
-        <v>8000</v>
+        <v>24000</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="4">
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="D26" s="5">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="E26" s="5">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="4">
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>46256</v>
+        <v>46260</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>80</v>
@@ -1517,94 +1403,94 @@
         <v>81</v>
       </c>
       <c r="D27" s="5">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="E27" s="5">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="4">
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>46256</v>
+        <v>46260</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="D28" s="5">
-        <v>10000</v>
+        <v>6300</v>
       </c>
       <c r="E28" s="5">
-        <v>10000</v>
+        <v>6300</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="4">
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
-        <v>46256</v>
+        <v>46260</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="D29" s="5">
-        <v>14000</v>
+        <v>7300</v>
       </c>
       <c r="E29" s="5">
-        <v>14000</v>
+        <v>7300</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="4">
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
-        <v>46256</v>
+        <v>46260</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D30" s="5">
-        <v>24200</v>
-      </c>
-      <c r="E30" s="5">
-        <v>24200</v>
+        <v>10000</v>
+      </c>
+      <c r="E30" s="3">
+        <v>0</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="4">
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <v>46256</v>
+        <v>46260</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>82</v>
@@ -1613,598 +1499,598 @@
         <v>83</v>
       </c>
       <c r="D31" s="5">
-        <v>35000</v>
+        <v>10000</v>
       </c>
       <c r="E31" s="5">
-        <v>35000</v>
+        <v>10000</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="4">
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>46256</v>
+        <v>46260</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="D32" s="5">
-        <v>40000</v>
+        <v>14000</v>
       </c>
       <c r="E32" s="5">
-        <v>40000</v>
+        <v>14000</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="4">
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>46257</v>
+        <v>46260</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="D33" s="5">
-        <v>2000</v>
+        <v>14000</v>
       </c>
       <c r="E33" s="5">
-        <v>2000</v>
+        <v>14000</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="4">
         <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>46257</v>
+        <v>46260</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="D34" s="5">
-        <v>5000</v>
+        <v>20000</v>
       </c>
       <c r="E34" s="5">
-        <v>5000</v>
+        <v>20000</v>
       </c>
       <c r="F34" s="6"/>
       <c r="G34" s="4">
         <v>0</v>
       </c>
       <c r="H34" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>46257</v>
+        <v>46260</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D35" s="5">
-        <v>8000</v>
+        <v>40000</v>
       </c>
       <c r="E35" s="5">
-        <v>8000</v>
+        <v>40000</v>
       </c>
       <c r="F35" s="6"/>
       <c r="G35" s="4">
         <v>0</v>
       </c>
       <c r="H35" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>46257</v>
+        <v>46261</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D36" s="5">
-        <v>12000</v>
+        <v>1600</v>
       </c>
       <c r="E36" s="5">
-        <v>12000</v>
+        <v>1600</v>
       </c>
       <c r="F36" s="6"/>
       <c r="G36" s="4">
         <v>0</v>
       </c>
       <c r="H36" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>46257</v>
+        <v>46261</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>108</v>
+        <v>30</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>109</v>
+        <v>31</v>
       </c>
       <c r="D37" s="5">
-        <v>15000</v>
+        <v>8000</v>
       </c>
       <c r="E37" s="5">
-        <v>15000</v>
+        <v>8000</v>
       </c>
       <c r="F37" s="6"/>
       <c r="G37" s="4">
         <v>0</v>
       </c>
       <c r="H37" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <v>46257</v>
+        <v>46261</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="D38" s="5">
-        <v>20000</v>
+        <v>12000</v>
       </c>
       <c r="E38" s="5">
-        <v>20000</v>
+        <v>12000</v>
       </c>
       <c r="F38" s="6"/>
       <c r="G38" s="4">
         <v>0</v>
       </c>
       <c r="H38" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
-        <v>46257</v>
+        <v>46261</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="D39" s="5">
-        <v>20000</v>
+        <v>7300</v>
       </c>
       <c r="E39" s="5">
-        <v>20000</v>
+        <v>7300</v>
       </c>
       <c r="F39" s="6"/>
       <c r="G39" s="4">
         <v>0</v>
       </c>
       <c r="H39" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
-        <v>46257</v>
+        <v>46261</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="D40" s="5">
-        <v>35000</v>
+        <v>8000</v>
       </c>
       <c r="E40" s="5">
-        <v>35000</v>
+        <v>8000</v>
       </c>
       <c r="F40" s="6"/>
       <c r="G40" s="4">
         <v>0</v>
       </c>
       <c r="H40" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
-        <v>46257</v>
+        <v>46261</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="D41" s="5">
-        <v>35000</v>
+        <v>20000</v>
       </c>
       <c r="E41" s="5">
-        <v>35000</v>
+        <v>20000</v>
       </c>
       <c r="F41" s="6"/>
       <c r="G41" s="4">
         <v>0</v>
       </c>
       <c r="H41" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>46258</v>
+        <v>46261</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D42" s="3">
-        <v>900</v>
-      </c>
-      <c r="E42" s="3">
-        <v>900</v>
+        <v>101</v>
+      </c>
+      <c r="D42" s="5">
+        <v>24000</v>
+      </c>
+      <c r="E42" s="5">
+        <v>24000</v>
       </c>
       <c r="F42" s="6"/>
       <c r="G42" s="4">
         <v>0</v>
       </c>
       <c r="H42" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>46258</v>
+        <v>46261</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="D43" s="5">
-        <v>3700</v>
+        <v>30000</v>
       </c>
       <c r="E43" s="5">
-        <v>3700</v>
+        <v>30000</v>
       </c>
       <c r="F43" s="6"/>
       <c r="G43" s="4">
         <v>0</v>
       </c>
       <c r="H43" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>46258</v>
+        <v>46261</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="D44" s="5">
-        <v>6000</v>
+        <v>40000</v>
       </c>
       <c r="E44" s="5">
-        <v>6000</v>
+        <v>40000</v>
       </c>
       <c r="F44" s="6"/>
       <c r="G44" s="4">
         <v>0</v>
       </c>
       <c r="H44" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
-        <v>46258</v>
+        <v>46263</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D45" s="3">
         <v>100</v>
       </c>
-      <c r="C45" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D45" s="5">
-        <v>11000</v>
-      </c>
-      <c r="E45" s="5">
-        <v>11000</v>
+      <c r="E45" s="3">
+        <v>100</v>
       </c>
       <c r="F45" s="6"/>
       <c r="G45" s="4">
         <v>0</v>
       </c>
       <c r="H45" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <v>46258</v>
+        <v>46263</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D46" s="5">
-        <v>12000</v>
-      </c>
-      <c r="E46" s="5">
-        <v>12000</v>
+        <v>105</v>
+      </c>
+      <c r="D46" s="3">
+        <v>100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>100</v>
       </c>
       <c r="F46" s="6"/>
       <c r="G46" s="4">
         <v>0</v>
       </c>
       <c r="H46" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <v>46259</v>
+        <v>46263</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D47" s="5">
-        <v>18000</v>
+        <v>4000</v>
       </c>
       <c r="E47" s="5">
-        <v>18000</v>
+        <v>4000</v>
       </c>
       <c r="F47" s="6"/>
       <c r="G47" s="4">
         <v>0</v>
       </c>
       <c r="H47" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>46258</v>
+        <v>46263</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="D48" s="5">
-        <v>20000</v>
+        <v>6000</v>
       </c>
       <c r="E48" s="5">
-        <v>20000</v>
+        <v>6000</v>
       </c>
       <c r="F48" s="6"/>
       <c r="G48" s="4">
         <v>0</v>
       </c>
       <c r="H48" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>46258</v>
+        <v>46263</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>113</v>
+        <v>10</v>
       </c>
       <c r="D49" s="5">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="E49" s="5">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="F49" s="6"/>
       <c r="G49" s="4">
         <v>0</v>
       </c>
       <c r="H49" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <v>46258</v>
+        <v>46263</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>25</v>
+        <v>106</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="D50" s="5">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="E50" s="5">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="F50" s="6"/>
       <c r="G50" s="4">
         <v>0</v>
       </c>
       <c r="H50" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <v>46259</v>
+        <v>46263</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>114</v>
+        <v>13</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>115</v>
+        <v>14</v>
       </c>
       <c r="D51" s="5">
-        <v>2300</v>
-      </c>
-      <c r="E51" s="5">
-        <v>2300</v>
+        <v>15000</v>
+      </c>
+      <c r="E51" s="3">
+        <v>0</v>
       </c>
       <c r="F51" s="6"/>
       <c r="G51" s="4">
         <v>0</v>
       </c>
       <c r="H51" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <v>46259</v>
+        <v>46263</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>116</v>
+        <v>7</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>117</v>
+        <v>8</v>
       </c>
       <c r="D52" s="5">
-        <v>2500</v>
+        <v>20000</v>
       </c>
       <c r="E52" s="5">
-        <v>2500</v>
+        <v>20000</v>
       </c>
       <c r="F52" s="6"/>
       <c r="G52" s="4">
         <v>0</v>
       </c>
       <c r="H52" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
-        <v>46259</v>
+        <v>46263</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>118</v>
+        <v>23</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>119</v>
+        <v>24</v>
       </c>
       <c r="D53" s="5">
-        <v>6300</v>
+        <v>18000</v>
       </c>
       <c r="E53" s="5">
-        <v>6300</v>
+        <v>18000</v>
       </c>
       <c r="F53" s="6"/>
       <c r="G53" s="4">
         <v>0</v>
       </c>
       <c r="H53" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
-        <v>46259</v>
+        <v>46263</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>35</v>
+        <v>108</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>36</v>
+        <v>109</v>
       </c>
       <c r="D54" s="5">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="E54" s="5">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="F54" s="6"/>
       <c r="G54" s="4">
         <v>0</v>
       </c>
       <c r="H54" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
-        <v>46259</v>
+        <v>46263</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="D55" s="5">
-        <v>12000</v>
+        <v>20000</v>
       </c>
       <c r="E55" s="5">
-        <v>12000</v>
+        <v>20000</v>
       </c>
       <c r="F55" s="6"/>
       <c r="G55" s="4">
         <v>0</v>
       </c>
       <c r="H55" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
-        <v>46259</v>
+        <v>46263</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>17</v>
@@ -2213,761 +2099,233 @@
         <v>18</v>
       </c>
       <c r="D56" s="5">
-        <v>14000</v>
+        <v>40000</v>
       </c>
       <c r="E56" s="5">
-        <v>14000</v>
+        <v>40000</v>
       </c>
       <c r="F56" s="6"/>
       <c r="G56" s="4">
         <v>0</v>
       </c>
       <c r="H56" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
-        <v>46259</v>
+        <v>46264</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="D57" s="5">
-        <v>18000</v>
+        <v>1200</v>
       </c>
       <c r="E57" s="5">
-        <v>18000</v>
+        <v>1200</v>
       </c>
       <c r="F57" s="6"/>
       <c r="G57" s="4">
         <v>0</v>
       </c>
       <c r="H57" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
-        <v>46259</v>
+        <v>46264</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="D58" s="5">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="E58" s="5">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="F58" s="6"/>
       <c r="G58" s="4">
         <v>0</v>
       </c>
       <c r="H58" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
-        <v>46259</v>
+        <v>46264</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="D59" s="5">
-        <v>40000</v>
+        <v>10000</v>
       </c>
       <c r="E59" s="5">
-        <v>40000</v>
+        <v>10000</v>
       </c>
       <c r="F59" s="6"/>
       <c r="G59" s="4">
         <v>0</v>
       </c>
       <c r="H59" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
-        <v>46260</v>
+        <v>46264</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>120</v>
+        <v>23</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>121</v>
+        <v>24</v>
       </c>
       <c r="D60" s="5">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="E60" s="5">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F60" s="6"/>
       <c r="G60" s="4">
         <v>0</v>
       </c>
       <c r="H60" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
-        <v>46260</v>
+        <v>46264</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>140</v>
+        <v>84</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
       <c r="D61" s="5">
-        <v>3000</v>
+        <v>7500</v>
       </c>
       <c r="E61" s="5">
-        <v>3000</v>
+        <v>7500</v>
       </c>
       <c r="F61" s="6"/>
       <c r="G61" s="4">
         <v>0</v>
       </c>
       <c r="H61" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
-        <v>46260</v>
+        <v>46264</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>132</v>
+        <v>7</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="D62" s="5">
-        <v>7300</v>
+        <v>20000</v>
       </c>
       <c r="E62" s="5">
-        <v>7300</v>
+        <v>20000</v>
       </c>
       <c r="F62" s="6"/>
       <c r="G62" s="4">
         <v>0</v>
       </c>
       <c r="H62" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
-        <v>46260</v>
+        <v>46264</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>122</v>
+        <v>17</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>123</v>
+        <v>18</v>
       </c>
       <c r="D63" s="5">
-        <v>8000</v>
+        <v>40000</v>
       </c>
       <c r="E63" s="5">
-        <v>8000</v>
+        <v>40000</v>
       </c>
       <c r="F63" s="6"/>
       <c r="G63" s="4">
         <v>0</v>
       </c>
       <c r="H63" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
-        <v>46260</v>
+        <v>46264</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>126</v>
+        <v>29</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="D64" s="5">
-        <v>24000</v>
+        <v>40000</v>
       </c>
       <c r="E64" s="5">
-        <v>24000</v>
+        <v>40000</v>
       </c>
       <c r="F64" s="6"/>
       <c r="G64" s="4">
         <v>0</v>
       </c>
       <c r="H64" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="D65" s="5">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="E65" s="5">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="F65" s="6"/>
       <c r="G65" s="4">
         <v>0</v>
       </c>
       <c r="H65" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A66" s="2">
-        <v>46260</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D66" s="5">
-        <v>12000</v>
-      </c>
-      <c r="E66" s="5">
-        <v>12000</v>
-      </c>
-      <c r="F66" s="6"/>
-      <c r="G66" s="4">
-        <v>0</v>
-      </c>
-      <c r="H66" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A67" s="2">
-        <v>46260</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D67" s="5">
-        <v>40000</v>
-      </c>
-      <c r="E67" s="5">
-        <v>40000</v>
-      </c>
-      <c r="F67" s="6"/>
-      <c r="G67" s="4">
-        <v>0</v>
-      </c>
-      <c r="H67" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A68" s="2">
-        <v>46260</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D68" s="5">
-        <v>40000</v>
-      </c>
-      <c r="E68" s="5">
-        <v>40000</v>
-      </c>
-      <c r="F68" s="6"/>
-      <c r="G68" s="4">
-        <v>0</v>
-      </c>
-      <c r="H68" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A69" s="2">
-        <v>46261</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D69" s="5">
-        <v>6000</v>
-      </c>
-      <c r="E69" s="5">
-        <v>6000</v>
-      </c>
-      <c r="F69" s="6"/>
-      <c r="G69" s="4">
-        <v>0</v>
-      </c>
-      <c r="H69" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A70" s="2">
-        <v>46261</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D70" s="5">
-        <v>7300</v>
-      </c>
-      <c r="E70" s="5">
-        <v>7300</v>
-      </c>
-      <c r="F70" s="6"/>
-      <c r="G70" s="4">
-        <v>0</v>
-      </c>
-      <c r="H70" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A71" s="2">
-        <v>46261</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="D71" s="5">
-        <v>7500</v>
-      </c>
-      <c r="E71" s="5">
-        <v>7500</v>
-      </c>
-      <c r="F71" s="6"/>
-      <c r="G71" s="4">
-        <v>0</v>
-      </c>
-      <c r="H71" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A72" s="2">
-        <v>46261</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D72" s="5">
-        <v>10000</v>
-      </c>
-      <c r="E72" s="5">
-        <v>10000</v>
-      </c>
-      <c r="F72" s="6"/>
-      <c r="G72" s="4">
-        <v>0</v>
-      </c>
-      <c r="H72" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A73" s="2">
-        <v>46261</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D73" s="5">
-        <v>10000</v>
-      </c>
-      <c r="E73" s="5">
-        <v>10000</v>
-      </c>
-      <c r="F73" s="6"/>
-      <c r="G73" s="4">
-        <v>0</v>
-      </c>
-      <c r="H73" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A74" s="2">
-        <v>46261</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D74" s="5">
-        <v>20000</v>
-      </c>
-      <c r="E74" s="5">
-        <v>20000</v>
-      </c>
-      <c r="F74" s="6"/>
-      <c r="G74" s="4">
-        <v>0</v>
-      </c>
-      <c r="H74" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A75" s="2">
-        <v>46261</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D75" s="5">
-        <v>24000</v>
-      </c>
-      <c r="E75" s="5">
-        <v>24000</v>
-      </c>
-      <c r="F75" s="6"/>
-      <c r="G75" s="4">
-        <v>0</v>
-      </c>
-      <c r="H75" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A76" s="2">
-        <v>46261</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D76" s="5">
-        <v>40000</v>
-      </c>
-      <c r="E76" s="5">
-        <v>40000</v>
-      </c>
-      <c r="F76" s="6"/>
-      <c r="G76" s="4">
-        <v>0</v>
-      </c>
-      <c r="H76" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A77" s="2">
-        <v>46261</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D77" s="5">
-        <v>40000</v>
-      </c>
-      <c r="E77" s="5">
-        <v>40000</v>
-      </c>
-      <c r="F77" s="6"/>
-      <c r="G77" s="4">
-        <v>0</v>
-      </c>
-      <c r="H77" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A78" s="2">
-        <v>46263</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D78" s="5">
-        <v>4000</v>
-      </c>
-      <c r="E78" s="5">
-        <v>4000</v>
-      </c>
-      <c r="F78" s="6"/>
-      <c r="G78" s="4">
-        <v>0</v>
-      </c>
-      <c r="H78" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A79" s="2">
-        <v>46263</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D79" s="5">
-        <v>5000</v>
-      </c>
-      <c r="E79" s="5">
-        <v>5000</v>
-      </c>
-      <c r="F79" s="6"/>
-      <c r="G79" s="4">
-        <v>0</v>
-      </c>
-      <c r="H79" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A80" s="2">
-        <v>46263</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D80" s="5">
-        <v>8000</v>
-      </c>
-      <c r="E80" s="5">
-        <v>8000</v>
-      </c>
-      <c r="F80" s="6"/>
-      <c r="G80" s="4">
-        <v>0</v>
-      </c>
-      <c r="H80" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A81" s="2">
-        <v>46263</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D81" s="5">
-        <v>10000</v>
-      </c>
-      <c r="E81" s="5">
-        <v>10000</v>
-      </c>
-      <c r="F81" s="6"/>
-      <c r="G81" s="4">
-        <v>0</v>
-      </c>
-      <c r="H81" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A82" s="2">
-        <v>46263</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D82" s="5">
-        <v>20000</v>
-      </c>
-      <c r="E82" s="5">
-        <v>20000</v>
-      </c>
-      <c r="F82" s="6"/>
-      <c r="G82" s="4">
-        <v>0</v>
-      </c>
-      <c r="H82" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A83" s="2">
-        <v>46263</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D83" s="5">
-        <v>20000</v>
-      </c>
-      <c r="E83" s="5">
-        <v>20000</v>
-      </c>
-      <c r="F83" s="6"/>
-      <c r="G83" s="4">
-        <v>0</v>
-      </c>
-      <c r="H83" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A84" s="2">
-        <v>46263</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D84" s="5">
-        <v>20000</v>
-      </c>
-      <c r="E84" s="5">
-        <v>20000</v>
-      </c>
-      <c r="F84" s="6"/>
-      <c r="G84" s="4">
-        <v>0</v>
-      </c>
-      <c r="H84" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A85" s="2">
-        <v>46263</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D85" s="5">
-        <v>20000</v>
-      </c>
-      <c r="E85" s="5">
-        <v>20000</v>
-      </c>
-      <c r="F85" s="6"/>
-      <c r="G85" s="4">
-        <v>0</v>
-      </c>
-      <c r="H85" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A86" s="2">
-        <v>46264</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="D86" s="5">
-        <v>1200</v>
-      </c>
-      <c r="E86" s="5">
-        <v>1200</v>
-      </c>
-      <c r="F86" s="6"/>
-      <c r="G86" s="4">
-        <v>0</v>
-      </c>
-      <c r="H86" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A87" s="2">
-        <v>46264</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D87" s="5">
-        <v>8000</v>
-      </c>
-      <c r="E87" s="5">
-        <v>8000</v>
-      </c>
-      <c r="F87" s="6"/>
-      <c r="G87" s="4">
-        <v>0</v>
-      </c>
-      <c r="H87" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/data/Plan.xlsx
+++ b/data/Plan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raman/Documents/GitHub/production-board/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57B01806-35C6-774D-B1FC-676ABF4D1E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06FC84D8-EA11-8046-A8A5-0B59FE139283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16560" xr2:uid="{7C08584A-5D47-2049-B143-911B93E5D6E0}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{7C08584A-5D47-2049-B143-911B93E5D6E0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="111">
   <si>
     <t>Date</t>
   </si>
@@ -137,12 +137,6 @@
     <t>Exfoliating Body Scrub - 75 gms</t>
   </si>
   <si>
-    <t>CO357</t>
-  </si>
-  <si>
-    <t>Combo- Anti-Hairfall Shampoo (100ml) + Anti-Hairfall Conditioner (100g)</t>
-  </si>
-  <si>
     <t>CAP139</t>
   </si>
   <si>
@@ -176,12 +170,6 @@
     <t>Instant Cover-Up Hair Powder Black-4gm</t>
   </si>
   <si>
-    <t>BA111</t>
-  </si>
-  <si>
-    <t>Instant Cover-Up Hair Powder Brown-4gm</t>
-  </si>
-  <si>
     <t>BA77</t>
   </si>
   <si>
@@ -200,15 +188,6 @@
     <t>3% Niacinamide Featherlight Fluid Sunscreen 45g</t>
   </si>
   <si>
-    <t>Bare Anatomy Advanced Hair Growth Serum</t>
-  </si>
-  <si>
-    <t>UKTTBA107</t>
-  </si>
-  <si>
-    <t>UKTTBA6</t>
-  </si>
-  <si>
     <t>BA22</t>
   </si>
   <si>
@@ -227,12 +206,6 @@
     <t>Rosemary and Coconut Milk Hydrating Conditioner</t>
   </si>
   <si>
-    <t>CAP140</t>
-  </si>
-  <si>
-    <t>Tri Active Roll On Aqua 40ml</t>
-  </si>
-  <si>
     <t>BA49</t>
   </si>
   <si>
@@ -251,24 +224,6 @@
     <t>Under Arm Roll On - 40 ml / Peach (Rectangular Monocarton)-399</t>
   </si>
   <si>
-    <t>CAP154</t>
-  </si>
-  <si>
-    <t>Exfoliating face wash 75 ml</t>
-  </si>
-  <si>
-    <t>CAP173</t>
-  </si>
-  <si>
-    <t>Gentle Exfoliating Face Wash 75ml- Pack of 2</t>
-  </si>
-  <si>
-    <t>BA2</t>
-  </si>
-  <si>
-    <t>EXPERT | Color Protect Hair Mask (250 gms)</t>
-  </si>
-  <si>
     <t>BA48</t>
   </si>
   <si>
@@ -374,13 +329,49 @@
     <t>USTTBA10</t>
   </si>
   <si>
-    <t>Exfoliating Body Wash (236 ml)</t>
-  </si>
-  <si>
-    <t>SS43</t>
-  </si>
-  <si>
-    <t>5% Niacinamide Sunscreen Body Lotion 200 ml</t>
+    <t>BA119</t>
+  </si>
+  <si>
+    <t>Anti hairfall shampoo 750 ml</t>
+  </si>
+  <si>
+    <t>CAP49</t>
+  </si>
+  <si>
+    <t>Roll On: Fragrance Free (40 ml) (Rectangular)-399</t>
+  </si>
+  <si>
+    <t>USTTCAP24</t>
+  </si>
+  <si>
+    <t>Exfoliating Body Wash-236ml</t>
+  </si>
+  <si>
+    <t>CAP70</t>
+  </si>
+  <si>
+    <t>Underarm Roll On - 40 ml / White jasmine (Rectangular Monocarton)-399</t>
+  </si>
+  <si>
+    <t>EXPERT | Ultra Smoothing Shampoo (250 ML)</t>
+  </si>
+  <si>
+    <t>CAP105</t>
+  </si>
+  <si>
+    <t>Gentle Exfoliating Face Scrub 100ML</t>
+  </si>
+  <si>
+    <t>USTTBA93</t>
+  </si>
+  <si>
+    <t>EXPERT | Ultra Smoothing Serum (100 ML) - TikTok US</t>
+  </si>
+  <si>
+    <t>Advance hair growth Serum- Roll On</t>
+  </si>
+  <si>
+    <t>UKTBA107</t>
   </si>
 </sst>
 </file>
@@ -777,7 +768,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C578346-EE80-DF41-8099-4E3028D96EBE}">
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="57.1640625" customWidth="1"/>
@@ -808,1247 +799,1261 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D2" s="5">
-        <v>50000</v>
-      </c>
-      <c r="E2" s="5">
-        <v>50000</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="D2" s="3">
+        <v>50</v>
+      </c>
+      <c r="E2" s="3">
+        <v>50</v>
+      </c>
+      <c r="F2" s="6"/>
       <c r="G2" s="4">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="D3" s="5">
-        <v>50000</v>
+        <v>2500</v>
       </c>
       <c r="E3" s="5">
-        <v>50000</v>
-      </c>
+        <v>2500</v>
+      </c>
+      <c r="F3" s="6"/>
       <c r="G3" s="4">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D4" s="5">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="E4" s="5">
-        <v>2000</v>
-      </c>
+        <v>4000</v>
+      </c>
+      <c r="F4" s="6"/>
       <c r="G4" s="4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D5" s="5">
-        <v>64000</v>
+        <v>6000</v>
       </c>
       <c r="E5" s="5">
-        <v>64000</v>
-      </c>
+        <v>6000</v>
+      </c>
+      <c r="F5" s="6"/>
       <c r="G5" s="4">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="D6" s="5">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="E6" s="5">
-        <v>8000</v>
-      </c>
+        <v>10000</v>
+      </c>
+      <c r="F6" s="6"/>
       <c r="G6" s="4">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>29</v>
+        <v>79</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="D7" s="5">
-        <v>50000</v>
+        <v>10000</v>
       </c>
       <c r="E7" s="5">
-        <v>50000</v>
-      </c>
+        <v>10000</v>
+      </c>
+      <c r="F7" s="6"/>
       <c r="G7" s="4">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>46262</v>
+        <v>46259</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D8" s="5">
-        <v>80000</v>
+        <v>11000</v>
       </c>
       <c r="E8" s="5">
-        <v>80000</v>
-      </c>
+        <v>11000</v>
+      </c>
+      <c r="F8" s="6"/>
       <c r="G8" s="4">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
-        <v>46292</v>
+        <v>46259</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="D9" s="5">
-        <v>25000</v>
+        <v>18000</v>
       </c>
       <c r="E9" s="5">
-        <v>25000</v>
-      </c>
+        <v>14000</v>
+      </c>
+      <c r="F9" s="6"/>
       <c r="G9" s="4">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
-        <v>46292</v>
+        <v>46259</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D10" s="5">
-        <v>25000</v>
+        <v>24000</v>
       </c>
       <c r="E10" s="5">
-        <v>25000</v>
-      </c>
+        <v>24000</v>
+      </c>
+      <c r="F10" s="6"/>
       <c r="G10" s="4">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="D11" s="5">
-        <v>7500</v>
+        <v>40000</v>
       </c>
       <c r="E11" s="5">
-        <v>7500</v>
-      </c>
+        <v>40000</v>
+      </c>
+      <c r="F11" s="6"/>
       <c r="G11" s="4">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>46267</v>
+        <v>46260</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="3">
         <v>50</v>
       </c>
-      <c r="D12" s="5">
-        <v>20000</v>
-      </c>
-      <c r="E12" s="5">
-        <v>20000</v>
-      </c>
+      <c r="E12" s="3">
+        <v>50</v>
+      </c>
+      <c r="F12" s="6"/>
       <c r="G12" s="4">
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="D13" s="5">
-        <v>30000</v>
+        <v>3000</v>
       </c>
       <c r="E13" s="5">
-        <v>30000</v>
-      </c>
+        <v>3000</v>
+      </c>
+      <c r="F13" s="6"/>
       <c r="G13" s="4">
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <v>46262</v>
+        <v>46260</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="D14" s="5">
-        <v>20000</v>
+        <v>6300</v>
       </c>
       <c r="E14" s="5">
-        <v>20000</v>
-      </c>
+        <v>6300</v>
+      </c>
+      <c r="F14" s="6"/>
       <c r="G14" s="4">
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <v>46262</v>
+        <v>46260</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="D15" s="5">
-        <v>30000</v>
+        <v>8000</v>
       </c>
       <c r="E15" s="5">
-        <v>30000</v>
-      </c>
+        <v>8000</v>
+      </c>
+      <c r="F15" s="6"/>
       <c r="G15" s="4">
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D16" s="3">
-        <v>50</v>
-      </c>
-      <c r="E16" s="3">
-        <v>50</v>
+        <v>84</v>
+      </c>
+      <c r="D16" s="5">
+        <v>8000</v>
+      </c>
+      <c r="E16" s="5">
+        <v>8000</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="4">
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D17" s="3">
-        <v>50</v>
-      </c>
-      <c r="E17" s="3">
-        <v>50</v>
+        <v>68</v>
+      </c>
+      <c r="D17" s="5">
+        <v>10000</v>
+      </c>
+      <c r="E17" s="5">
+        <v>10000</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="4">
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D18" s="5">
-        <v>5000</v>
+        <v>12000</v>
       </c>
       <c r="E18" s="5">
-        <v>3200</v>
+        <v>12000</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="4">
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>31</v>
+        <v>99</v>
       </c>
       <c r="D19" s="5">
-        <v>4000</v>
+        <v>24000</v>
       </c>
       <c r="E19" s="5">
-        <v>4000</v>
+        <v>24000</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="4">
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="D20" s="5">
-        <v>10000</v>
+        <v>14000</v>
       </c>
       <c r="E20" s="5">
-        <v>10000</v>
+        <v>14000</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="4">
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>94</v>
+        <v>49</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="D21" s="5">
-        <v>10000</v>
+        <v>14000</v>
       </c>
       <c r="E21" s="5">
-        <v>10000</v>
+        <v>14000</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="4">
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D22" s="5">
-        <v>11000</v>
+        <v>20000</v>
       </c>
       <c r="E22" s="5">
-        <v>11000</v>
+        <v>20000</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="4">
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="D23" s="5">
-        <v>12000</v>
+        <v>40000</v>
       </c>
       <c r="E23" s="5">
-        <v>12000</v>
+        <v>40000</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="4">
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="D24" s="5">
-        <v>18000</v>
+        <v>1600</v>
       </c>
       <c r="E24" s="5">
-        <v>18000</v>
+        <v>1600</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="4">
         <v>0</v>
       </c>
       <c r="H24" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="D25" s="5">
-        <v>24000</v>
+        <v>8000</v>
       </c>
       <c r="E25" s="5">
-        <v>24000</v>
+        <v>8000</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="4">
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>11</v>
+        <v>91</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="D26" s="5">
-        <v>40000</v>
+        <v>8000</v>
       </c>
       <c r="E26" s="5">
-        <v>40000</v>
+        <v>8000</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="4">
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>81</v>
+        <v>28</v>
       </c>
       <c r="D27" s="5">
-        <v>3000</v>
+        <v>20000</v>
       </c>
       <c r="E27" s="5">
-        <v>3000</v>
+        <v>20000</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="4">
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="D28" s="5">
-        <v>6300</v>
+        <v>20000</v>
       </c>
       <c r="E28" s="5">
-        <v>6300</v>
+        <v>20000</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="4">
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D29" s="5">
-        <v>7300</v>
+        <v>20000</v>
       </c>
       <c r="E29" s="5">
-        <v>7300</v>
+        <v>20000</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="4">
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="D30" s="5">
-        <v>10000</v>
-      </c>
-      <c r="E30" s="3">
-        <v>0</v>
+        <v>24000</v>
+      </c>
+      <c r="E30" s="5">
+        <v>24000</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="4">
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="D31" s="5">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="E31" s="5">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="4">
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>46260</v>
+        <v>46263</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D32" s="5">
-        <v>14000</v>
-      </c>
-      <c r="E32" s="5">
-        <v>14000</v>
+        <v>88</v>
+      </c>
+      <c r="D32" s="3">
+        <v>100</v>
+      </c>
+      <c r="E32" s="3">
+        <v>100</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="4">
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>46260</v>
+        <v>46263</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D33" s="5">
-        <v>14000</v>
-      </c>
-      <c r="E33" s="5">
-        <v>14000</v>
+        <v>90</v>
+      </c>
+      <c r="D33" s="3">
+        <v>100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>100</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="4">
         <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>46260</v>
+        <v>46263</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D34" s="5">
-        <v>20000</v>
+        <v>4000</v>
       </c>
       <c r="E34" s="5">
-        <v>20000</v>
+        <v>4000</v>
       </c>
       <c r="F34" s="6"/>
       <c r="G34" s="4">
         <v>0</v>
       </c>
       <c r="H34" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>46260</v>
+        <v>46263</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="D35" s="5">
-        <v>40000</v>
+        <v>7300</v>
       </c>
       <c r="E35" s="5">
-        <v>40000</v>
+        <v>7300</v>
       </c>
       <c r="F35" s="6"/>
       <c r="G35" s="4">
         <v>0</v>
       </c>
       <c r="H35" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>46261</v>
+        <v>46263</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>96</v>
+        <v>9</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>97</v>
+        <v>10</v>
       </c>
       <c r="D36" s="5">
-        <v>1600</v>
+        <v>8000</v>
       </c>
       <c r="E36" s="5">
-        <v>1600</v>
+        <v>8000</v>
       </c>
       <c r="F36" s="6"/>
       <c r="G36" s="4">
         <v>0</v>
       </c>
       <c r="H36" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>46261</v>
+        <v>46263</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="D37" s="5">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="E37" s="5">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="F37" s="6"/>
       <c r="G37" s="4">
         <v>0</v>
       </c>
       <c r="H37" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <v>46261</v>
+        <v>46263</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="D38" s="5">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="E38" s="5">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="F38" s="6"/>
       <c r="G38" s="4">
         <v>0</v>
       </c>
       <c r="H38" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
-        <v>46261</v>
+        <v>46263</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="D39" s="5">
-        <v>7300</v>
-      </c>
-      <c r="E39" s="5">
-        <v>7300</v>
+        <v>15000</v>
+      </c>
+      <c r="E39" s="3">
+        <v>0</v>
       </c>
       <c r="F39" s="6"/>
       <c r="G39" s="4">
         <v>0</v>
       </c>
       <c r="H39" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
-        <v>46261</v>
+        <v>46263</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D40" s="5">
-        <v>8000</v>
+        <v>24000</v>
       </c>
       <c r="E40" s="5">
-        <v>8000</v>
+        <v>24000</v>
       </c>
       <c r="F40" s="6"/>
       <c r="G40" s="4">
         <v>0</v>
       </c>
       <c r="H40" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
-        <v>46261</v>
+        <v>46263</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D41" s="5">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="E41" s="5">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="F41" s="6"/>
       <c r="G41" s="4">
         <v>0</v>
       </c>
       <c r="H41" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>46261</v>
+        <v>46263</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D42" s="5">
-        <v>24000</v>
+        <v>40000</v>
       </c>
       <c r="E42" s="5">
-        <v>24000</v>
+        <v>40000</v>
       </c>
       <c r="F42" s="6"/>
       <c r="G42" s="4">
         <v>0</v>
       </c>
       <c r="H42" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>46261</v>
+        <v>46264</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="D43" s="5">
-        <v>30000</v>
+        <v>7500</v>
       </c>
       <c r="E43" s="5">
-        <v>30000</v>
+        <v>7500</v>
       </c>
       <c r="F43" s="6"/>
       <c r="G43" s="4">
         <v>0</v>
       </c>
       <c r="H43" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>46261</v>
+        <v>46264</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="D44" s="5">
-        <v>40000</v>
+        <v>10000</v>
       </c>
       <c r="E44" s="5">
-        <v>40000</v>
+        <v>10000</v>
       </c>
       <c r="F44" s="6"/>
       <c r="G44" s="4">
         <v>0</v>
       </c>
       <c r="H44" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>102</v>
+        <v>23</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D45" s="3">
-        <v>100</v>
-      </c>
-      <c r="E45" s="3">
-        <v>100</v>
+        <v>24</v>
+      </c>
+      <c r="D45" s="5">
+        <v>13000</v>
+      </c>
+      <c r="E45" s="5">
+        <v>13000</v>
       </c>
       <c r="F45" s="6"/>
       <c r="G45" s="4">
         <v>0</v>
       </c>
       <c r="H45" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>104</v>
+        <v>7</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D46" s="3">
-        <v>100</v>
-      </c>
-      <c r="E46" s="3">
-        <v>100</v>
+        <v>8</v>
+      </c>
+      <c r="D46" s="5">
+        <v>20000</v>
+      </c>
+      <c r="E46" s="5">
+        <v>20000</v>
       </c>
       <c r="F46" s="6"/>
       <c r="G46" s="4">
         <v>0</v>
       </c>
       <c r="H46" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>26</v>
+        <v>106</v>
       </c>
       <c r="D47" s="5">
-        <v>4000</v>
+        <v>20000</v>
       </c>
       <c r="E47" s="5">
-        <v>4000</v>
+        <v>20000</v>
       </c>
       <c r="F47" s="6"/>
       <c r="G47" s="4">
         <v>0</v>
       </c>
       <c r="H47" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="D48" s="5">
-        <v>6000</v>
+        <v>40000</v>
       </c>
       <c r="E48" s="5">
-        <v>6000</v>
+        <v>40000</v>
       </c>
       <c r="F48" s="6"/>
       <c r="G48" s="4">
         <v>0</v>
       </c>
       <c r="H48" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D49" s="5">
-        <v>8000</v>
+        <v>40000</v>
       </c>
       <c r="E49" s="5">
-        <v>8000</v>
+        <v>40000</v>
       </c>
       <c r="F49" s="6"/>
       <c r="G49" s="4">
         <v>0</v>
       </c>
       <c r="H49" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="D50" s="5">
-        <v>8000</v>
+        <v>1200</v>
       </c>
       <c r="E50" s="5">
-        <v>8000</v>
+        <v>1200</v>
       </c>
       <c r="F50" s="6"/>
       <c r="G50" s="4">
         <v>0</v>
       </c>
       <c r="H50" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="D51" s="5">
-        <v>15000</v>
-      </c>
-      <c r="E51" s="3">
-        <v>0</v>
+        <v>8000</v>
+      </c>
+      <c r="E51" s="5">
+        <v>8000</v>
       </c>
       <c r="F51" s="6"/>
       <c r="G51" s="4">
         <v>0</v>
       </c>
       <c r="H51" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="D52" s="5">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E52" s="5">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F52" s="6"/>
       <c r="G52" s="4">
         <v>0</v>
       </c>
       <c r="H52" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>23</v>
+        <v>107</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="D53" s="5">
-        <v>18000</v>
+        <v>20000</v>
       </c>
       <c r="E53" s="5">
-        <v>18000</v>
+        <v>20000</v>
       </c>
       <c r="F53" s="6"/>
       <c r="G53" s="4">
         <v>0</v>
       </c>
       <c r="H53" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>108</v>
+        <v>7</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>109</v>
+        <v>8</v>
       </c>
       <c r="D54" s="5">
         <v>20000</v>
@@ -2061,36 +2066,36 @@
         <v>0</v>
       </c>
       <c r="H54" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="D55" s="5">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="E55" s="5">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="F55" s="6"/>
       <c r="G55" s="4">
         <v>0</v>
       </c>
       <c r="H55" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>17</v>
@@ -2109,90 +2114,90 @@
         <v>0</v>
       </c>
       <c r="H56" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
-        <v>46264</v>
+        <v>46259</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>87</v>
+        <v>33</v>
       </c>
       <c r="D57" s="5">
-        <v>1200</v>
+        <v>50000</v>
       </c>
       <c r="E57" s="5">
-        <v>1200</v>
+        <v>50000</v>
       </c>
       <c r="F57" s="6"/>
       <c r="G57" s="4">
         <v>0</v>
       </c>
       <c r="H57" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
-        <v>46264</v>
+        <v>46259</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>88</v>
+        <v>34</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>89</v>
+        <v>35</v>
       </c>
       <c r="D58" s="5">
-        <v>8000</v>
+        <v>50000</v>
       </c>
       <c r="E58" s="5">
-        <v>8000</v>
+        <v>50000</v>
       </c>
       <c r="F58" s="6"/>
       <c r="G58" s="4">
         <v>0</v>
       </c>
       <c r="H58" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
-        <v>46264</v>
+        <v>46292</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D59" s="5">
-        <v>10000</v>
+        <v>25000</v>
       </c>
       <c r="E59" s="5">
-        <v>10000</v>
+        <v>25000</v>
       </c>
       <c r="F59" s="6"/>
       <c r="G59" s="4">
         <v>0</v>
       </c>
       <c r="H59" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
-        <v>46264</v>
+        <v>46275</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="D60" s="5">
         <v>10000</v>
@@ -2205,127 +2210,199 @@
         <v>0</v>
       </c>
       <c r="H60" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
-        <v>46264</v>
+        <v>46268</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="D61" s="5">
-        <v>7500</v>
+        <v>30000</v>
       </c>
       <c r="E61" s="5">
-        <v>7500</v>
+        <v>30000</v>
       </c>
       <c r="F61" s="6"/>
       <c r="G61" s="4">
         <v>0</v>
       </c>
       <c r="H61" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
-        <v>46264</v>
+        <v>46267</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="D62" s="5">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="E62" s="5">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="F62" s="6"/>
       <c r="G62" s="4">
         <v>0</v>
       </c>
       <c r="H62" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="D63" s="5">
-        <v>40000</v>
+        <v>25000</v>
       </c>
       <c r="E63" s="5">
-        <v>40000</v>
+        <v>25000</v>
       </c>
       <c r="F63" s="6"/>
       <c r="G63" s="4">
         <v>0</v>
       </c>
       <c r="H63" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>29</v>
+        <v>110</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D64" s="5">
-        <v>40000</v>
+        <v>6000</v>
       </c>
       <c r="E64" s="5">
-        <v>40000</v>
+        <v>6000</v>
       </c>
       <c r="F64" s="6"/>
       <c r="G64" s="4">
         <v>0</v>
       </c>
       <c r="H64" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
-        <v>46265</v>
+        <v>46259</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>112</v>
+        <v>19</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="D65" s="5">
-        <v>20000</v>
+        <v>64000</v>
       </c>
       <c r="E65" s="5">
-        <v>20000</v>
+        <v>64000</v>
       </c>
       <c r="F65" s="6"/>
       <c r="G65" s="4">
         <v>0</v>
       </c>
       <c r="H65" t="s">
-        <v>58</v>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A66" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D66" s="5">
+        <v>8000</v>
+      </c>
+      <c r="E66" s="5">
+        <v>8000</v>
+      </c>
+      <c r="F66" s="6"/>
+      <c r="G66" s="4">
+        <v>0</v>
+      </c>
+      <c r="H66" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A67" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D67" s="5">
+        <v>50000</v>
+      </c>
+      <c r="E67" s="5">
+        <v>50000</v>
+      </c>
+      <c r="F67" s="6"/>
+      <c r="G67" s="4">
+        <v>0</v>
+      </c>
+      <c r="H67" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A68" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D68" s="5">
+        <v>80000</v>
+      </c>
+      <c r="E68" s="5">
+        <v>80000</v>
+      </c>
+      <c r="F68" s="6"/>
+      <c r="G68" s="4">
+        <v>0</v>
+      </c>
+      <c r="H68" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/data/Plan.xlsx
+++ b/data/Plan.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raman/Documents/GitHub/production-board/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06FC84D8-EA11-8046-A8A5-0B59FE139283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{463D0720-0698-6743-9896-D749511DB5C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{7C08584A-5D47-2049-B143-911B93E5D6E0}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16560" xr2:uid="{7C08584A-5D47-2049-B143-911B93E5D6E0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="111">
   <si>
     <t>Date</t>
   </si>
@@ -155,15 +155,9 @@
     <t>Advanced Hair Growth Serum Roll-On</t>
   </si>
   <si>
-    <t>Exfoliating Body Wash 236 ml</t>
-  </si>
-  <si>
     <t>BA5</t>
   </si>
   <si>
-    <t>Anti Frizz Mask 250 g</t>
-  </si>
-  <si>
     <t>BA110</t>
   </si>
   <si>
@@ -372,6 +366,12 @@
   </si>
   <si>
     <t>UKTBA107</t>
+  </si>
+  <si>
+    <t>EXPERT | Anti-Frizz Hair Mask (250 gms)</t>
+  </si>
+  <si>
+    <t>Exfoliating Body Wash (236 ml)</t>
   </si>
 </sst>
 </file>
@@ -768,7 +768,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C578346-EE80-DF41-8099-4E3028D96EBE}">
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="57.1640625" customWidth="1"/>
@@ -802,10 +802,10 @@
         <v>46259</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D2" s="3">
         <v>50</v>
@@ -818,7 +818,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -826,10 +826,10 @@
         <v>46259</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D3" s="5">
         <v>2500</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -866,7 +866,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -890,7 +890,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -898,10 +898,10 @@
         <v>46259</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D6" s="5">
         <v>10000</v>
@@ -914,7 +914,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -922,10 +922,10 @@
         <v>46259</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D7" s="5">
         <v>10000</v>
@@ -938,7 +938,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -962,7 +962,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -986,7 +986,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -994,10 +994,10 @@
         <v>46259</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D10" s="5">
         <v>24000</v>
@@ -1010,7 +1010,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -1034,7 +1034,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -1042,10 +1042,10 @@
         <v>46260</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D12" s="3">
         <v>50</v>
@@ -1058,7 +1058,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -1066,10 +1066,10 @@
         <v>46260</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D13" s="5">
         <v>3000</v>
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -1090,10 +1090,10 @@
         <v>46260</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D14" s="5">
         <v>6300</v>
@@ -1106,7 +1106,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -1130,7 +1130,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -1138,10 +1138,10 @@
         <v>46260</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D16" s="5">
         <v>8000</v>
@@ -1154,7 +1154,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
@@ -1162,10 +1162,10 @@
         <v>46260</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D17" s="5">
         <v>10000</v>
@@ -1178,7 +1178,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -1186,10 +1186,10 @@
         <v>46260</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D18" s="5">
         <v>12000</v>
@@ -1202,7 +1202,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -1210,10 +1210,10 @@
         <v>46260</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D19" s="5">
         <v>24000</v>
@@ -1226,7 +1226,7 @@
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
@@ -1250,7 +1250,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
@@ -1258,10 +1258,10 @@
         <v>46260</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D21" s="5">
         <v>14000</v>
@@ -1274,7 +1274,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
@@ -1298,7 +1298,7 @@
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
@@ -1330,10 +1330,10 @@
         <v>46261</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D24" s="5">
         <v>1600</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="H24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
@@ -1354,10 +1354,10 @@
         <v>46261</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D25" s="5">
         <v>8000</v>
@@ -1370,7 +1370,7 @@
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
@@ -1378,10 +1378,10 @@
         <v>46261</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D26" s="5">
         <v>8000</v>
@@ -1394,7 +1394,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -1418,7 +1418,7 @@
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
@@ -1426,10 +1426,10 @@
         <v>46261</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D28" s="5">
         <v>20000</v>
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
@@ -1450,10 +1450,10 @@
         <v>46261</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D29" s="5">
         <v>20000</v>
@@ -1466,7 +1466,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
@@ -1474,10 +1474,10 @@
         <v>46261</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D30" s="5">
         <v>24000</v>
@@ -1490,7 +1490,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
@@ -1498,10 +1498,10 @@
         <v>46261</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D31" s="5">
         <v>40000</v>
@@ -1514,7 +1514,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
@@ -1522,10 +1522,10 @@
         <v>46263</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D32" s="3">
         <v>100</v>
@@ -1538,7 +1538,7 @@
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
@@ -1546,10 +1546,10 @@
         <v>46263</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D33" s="3">
         <v>100</v>
@@ -1562,7 +1562,7 @@
         <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
@@ -1586,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="H34" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
@@ -1594,10 +1594,10 @@
         <v>46263</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D35" s="5">
         <v>7300</v>
@@ -1610,7 +1610,7 @@
         <v>0</v>
       </c>
       <c r="H35" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
@@ -1634,7 +1634,7 @@
         <v>0</v>
       </c>
       <c r="H36" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
@@ -1658,7 +1658,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
@@ -1682,7 +1682,7 @@
         <v>0</v>
       </c>
       <c r="H38" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
@@ -1706,7 +1706,7 @@
         <v>0</v>
       </c>
       <c r="H39" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
@@ -1714,10 +1714,10 @@
         <v>46263</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D40" s="5">
         <v>24000</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="H40" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
@@ -1754,7 +1754,7 @@
         <v>0</v>
       </c>
       <c r="H41" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
@@ -1762,10 +1762,10 @@
         <v>46263</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D42" s="5">
         <v>40000</v>
@@ -1778,7 +1778,7 @@
         <v>0</v>
       </c>
       <c r="H42" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
@@ -1786,10 +1786,10 @@
         <v>46264</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D43" s="5">
         <v>7500</v>
@@ -1802,7 +1802,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
@@ -1826,7 +1826,7 @@
         <v>0</v>
       </c>
       <c r="H44" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
@@ -1850,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
@@ -1874,7 +1874,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
@@ -1882,10 +1882,10 @@
         <v>46264</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D47" s="5">
         <v>20000</v>
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="H47" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
@@ -1906,10 +1906,10 @@
         <v>46264</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D48" s="5">
         <v>40000</v>
@@ -1922,7 +1922,7 @@
         <v>0</v>
       </c>
       <c r="H48" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
@@ -1946,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
@@ -1954,10 +1954,10 @@
         <v>46265</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D50" s="5">
         <v>1200</v>
@@ -1970,7 +1970,7 @@
         <v>0</v>
       </c>
       <c r="H50" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
@@ -1978,10 +1978,10 @@
         <v>46265</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D51" s="5">
         <v>8000</v>
@@ -1994,7 +1994,7 @@
         <v>0</v>
       </c>
       <c r="H51" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
@@ -2018,7 +2018,7 @@
         <v>0</v>
       </c>
       <c r="H52" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
@@ -2026,10 +2026,10 @@
         <v>46265</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D53" s="5">
         <v>20000</v>
@@ -2042,7 +2042,7 @@
         <v>0</v>
       </c>
       <c r="H53" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
@@ -2066,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="H54" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
@@ -2074,10 +2074,10 @@
         <v>46265</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D55" s="5">
         <v>40000</v>
@@ -2090,7 +2090,7 @@
         <v>0</v>
       </c>
       <c r="H55" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
@@ -2114,7 +2114,7 @@
         <v>0</v>
       </c>
       <c r="H56" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
@@ -2138,7 +2138,7 @@
         <v>0</v>
       </c>
       <c r="H57" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
@@ -2162,7 +2162,7 @@
         <v>0</v>
       </c>
       <c r="H58" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
@@ -2170,10 +2170,10 @@
         <v>46292</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D59" s="5">
         <v>25000</v>
@@ -2186,7 +2186,7 @@
         <v>0</v>
       </c>
       <c r="H59" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
@@ -2194,10 +2194,10 @@
         <v>46275</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D60" s="5">
         <v>10000</v>
@@ -2210,7 +2210,7 @@
         <v>0</v>
       </c>
       <c r="H60" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
@@ -2218,10 +2218,10 @@
         <v>46268</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D61" s="5">
         <v>30000</v>
@@ -2234,7 +2234,7 @@
         <v>0</v>
       </c>
       <c r="H61" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
@@ -2242,10 +2242,10 @@
         <v>46267</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D62" s="5">
         <v>30000</v>
@@ -2258,7 +2258,7 @@
         <v>0</v>
       </c>
       <c r="H62" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
@@ -2282,7 +2282,7 @@
         <v>0</v>
       </c>
       <c r="H63" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
@@ -2290,10 +2290,10 @@
         <v>46263</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D64" s="5">
         <v>6000</v>
@@ -2306,79 +2306,79 @@
         <v>0</v>
       </c>
       <c r="H64" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>20</v>
+        <v>109</v>
       </c>
       <c r="D65" s="5">
-        <v>64000</v>
+        <v>7904</v>
       </c>
       <c r="E65" s="5">
-        <v>64000</v>
+        <v>7904</v>
       </c>
       <c r="F65" s="6"/>
       <c r="G65" s="4">
         <v>0</v>
       </c>
       <c r="H65" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="D66" s="5">
-        <v>8000</v>
+        <v>8600</v>
       </c>
       <c r="E66" s="5">
-        <v>8000</v>
+        <v>8600</v>
       </c>
       <c r="F66" s="6"/>
       <c r="G66" s="4">
         <v>0</v>
       </c>
       <c r="H66" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D67" s="5">
-        <v>50000</v>
+        <v>63104</v>
       </c>
       <c r="E67" s="5">
-        <v>50000</v>
+        <v>63104</v>
       </c>
       <c r="F67" s="6"/>
       <c r="G67" s="4">
         <v>0</v>
       </c>
       <c r="H67" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
@@ -2386,23 +2386,47 @@
         <v>46262</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="D68" s="5">
-        <v>80000</v>
+        <v>35000</v>
       </c>
       <c r="E68" s="5">
-        <v>80000</v>
+        <v>35000</v>
       </c>
       <c r="F68" s="6"/>
       <c r="G68" s="4">
         <v>0</v>
       </c>
       <c r="H68" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A69" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D69" s="5">
+        <v>32000</v>
+      </c>
+      <c r="E69" s="5">
+        <v>32000</v>
+      </c>
+      <c r="F69" s="6"/>
+      <c r="G69" s="4">
+        <v>0</v>
+      </c>
+      <c r="H69" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/data/Plan.xlsx
+++ b/data/Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raman/Documents/GitHub/production-board/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{463D0720-0698-6743-9896-D749511DB5C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2C1C75C-548B-CB4F-884B-C978D4ED964B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16560" xr2:uid="{7C08584A-5D47-2049-B143-911B93E5D6E0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="101">
   <si>
     <t>Date</t>
   </si>
@@ -110,12 +110,6 @@
     <t>BA Expert Anti Hairfall Shampoo 100 ml</t>
   </si>
   <si>
-    <t>BA74</t>
-  </si>
-  <si>
-    <t>BA Expert Anti Dandruff Shampoo 100 ml</t>
-  </si>
-  <si>
     <t>CAP106</t>
   </si>
   <si>
@@ -131,12 +125,6 @@
     <t>CAP24</t>
   </si>
   <si>
-    <t>CAP77</t>
-  </si>
-  <si>
-    <t>Exfoliating Body Scrub - 75 gms</t>
-  </si>
-  <si>
     <t>CAP139</t>
   </si>
   <si>
@@ -155,33 +143,6 @@
     <t>Advanced Hair Growth Serum Roll-On</t>
   </si>
   <si>
-    <t>BA5</t>
-  </si>
-  <si>
-    <t>BA110</t>
-  </si>
-  <si>
-    <t>Instant Cover-Up Hair Powder Black-4gm</t>
-  </si>
-  <si>
-    <t>BA77</t>
-  </si>
-  <si>
-    <t>Scalp Massager</t>
-  </si>
-  <si>
-    <t>CAP157</t>
-  </si>
-  <si>
-    <t>Age Defence Night Cream-30gm</t>
-  </si>
-  <si>
-    <t>SS42</t>
-  </si>
-  <si>
-    <t>3% Niacinamide Featherlight Fluid Sunscreen 45g</t>
-  </si>
-  <si>
     <t>BA22</t>
   </si>
   <si>
@@ -206,18 +167,6 @@
     <t>Curl Defining Shampoo 250 ml</t>
   </si>
   <si>
-    <t>BA51</t>
-  </si>
-  <si>
-    <t>BA Gentle Cleansing Shampoo</t>
-  </si>
-  <si>
-    <t>CAP50</t>
-  </si>
-  <si>
-    <t>Under Arm Roll On - 40 ml / Peach (Rectangular Monocarton)-399</t>
-  </si>
-  <si>
     <t>BA48</t>
   </si>
   <si>
@@ -260,24 +209,12 @@
     <t>Gentle and Soothing Face Wash 75 ml</t>
   </si>
   <si>
-    <t>VIE12</t>
-  </si>
-  <si>
-    <t>Vinci Elivaas Shampoo 5ltr</t>
-  </si>
-  <si>
     <t>VIE13</t>
   </si>
   <si>
     <t>Vinci Elivaas conditioner 5Ltr</t>
   </si>
   <si>
-    <t>CAP83</t>
-  </si>
-  <si>
-    <t>Brightening Boost Face Wash</t>
-  </si>
-  <si>
     <t>BA121</t>
   </si>
   <si>
@@ -323,12 +260,6 @@
     <t>USTTBA10</t>
   </si>
   <si>
-    <t>BA119</t>
-  </si>
-  <si>
-    <t>Anti hairfall shampoo 750 ml</t>
-  </si>
-  <si>
     <t>CAP49</t>
   </si>
   <si>
@@ -368,10 +299,49 @@
     <t>UKTBA107</t>
   </si>
   <si>
-    <t>EXPERT | Anti-Frizz Hair Mask (250 gms)</t>
-  </si>
-  <si>
     <t>Exfoliating Body Wash (236 ml)</t>
+  </si>
+  <si>
+    <t>CAP53</t>
+  </si>
+  <si>
+    <t>Anti-Frizz Leave-In Conditioner</t>
+  </si>
+  <si>
+    <t>UKTTCAP17</t>
+  </si>
+  <si>
+    <t>Brightening Body Wash (473 ml)-UKTT</t>
+  </si>
+  <si>
+    <t>CAP166</t>
+  </si>
+  <si>
+    <t>Under Arm Roll On- Fragrance Free - 75ml</t>
+  </si>
+  <si>
+    <t>BA93</t>
+  </si>
+  <si>
+    <t>EXPERT | Ultra Smoothing Serum (100 ML)</t>
+  </si>
+  <si>
+    <t>CAP1</t>
+  </si>
+  <si>
+    <t>Acne Control Body Wash (236 ml)</t>
+  </si>
+  <si>
+    <t>CAP154</t>
+  </si>
+  <si>
+    <t>Exfoliating face wash 75 ml</t>
+  </si>
+  <si>
+    <t>BA76</t>
+  </si>
+  <si>
+    <t>Rosemary &amp; Rice Water Hair Growth Spray-200ml</t>
   </si>
 </sst>
 </file>
@@ -768,7 +738,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C578346-EE80-DF41-8099-4E3028D96EBE}">
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="57.1640625" customWidth="1"/>
@@ -799,13 +769,13 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="D2" s="3">
         <v>50</v>
@@ -818,114 +788,114 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="D3" s="5">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="E3" s="5">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="4">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D4" s="5">
-        <v>4000</v>
+        <v>6300</v>
       </c>
       <c r="E4" s="5">
-        <v>4000</v>
+        <v>6300</v>
       </c>
       <c r="F4" s="6"/>
       <c r="G4" s="4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D5" s="5">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="E5" s="5">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="4">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="D6" s="5">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="E6" s="5">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="4">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="D7" s="5">
         <v>10000</v>
@@ -938,66 +908,66 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="D8" s="5">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="E8" s="5">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="4">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D9" s="5">
-        <v>18000</v>
+        <v>20000</v>
       </c>
       <c r="E9" s="5">
-        <v>14000</v>
+        <v>20000</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="4">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="D10" s="5">
         <v>24000</v>
@@ -1010,31 +980,31 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D11" s="5">
-        <v>40000</v>
+        <v>14000</v>
       </c>
       <c r="E11" s="5">
-        <v>40000</v>
+        <v>14000</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="4">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -1042,322 +1012,322 @@
         <v>46260</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>75</v>
+        <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D12" s="3">
-        <v>50</v>
-      </c>
-      <c r="E12" s="3">
-        <v>50</v>
+        <v>12</v>
+      </c>
+      <c r="D12" s="5">
+        <v>40000</v>
+      </c>
+      <c r="E12" s="5">
+        <v>40000</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="4">
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="D13" s="5">
-        <v>3000</v>
+        <v>8000</v>
       </c>
       <c r="E13" s="5">
-        <v>3000</v>
+        <v>8000</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="4">
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D14" s="5">
-        <v>6300</v>
+        <v>10000</v>
       </c>
       <c r="E14" s="5">
-        <v>6300</v>
+        <v>10000</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="4">
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="D15" s="5">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="E15" s="5">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="4">
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="D16" s="5">
-        <v>8000</v>
+        <v>16000</v>
       </c>
       <c r="E16" s="5">
-        <v>8000</v>
+        <v>16000</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="4">
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="D17" s="5">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="E17" s="5">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="4">
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="D18" s="5">
-        <v>12000</v>
+        <v>20000</v>
       </c>
       <c r="E18" s="5">
-        <v>12000</v>
+        <v>20000</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="4">
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="D19" s="5">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="E19" s="5">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="4">
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="D20" s="5">
-        <v>14000</v>
+        <v>24000</v>
       </c>
       <c r="E20" s="5">
-        <v>14000</v>
+        <v>24000</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="4">
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D21" s="5">
-        <v>14000</v>
-      </c>
-      <c r="E21" s="5">
-        <v>14000</v>
+        <v>65</v>
+      </c>
+      <c r="D21" s="3">
+        <v>100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>100</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="4">
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="D22" s="5">
-        <v>20000</v>
+        <v>3000</v>
       </c>
       <c r="E22" s="5">
-        <v>20000</v>
+        <v>3000</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="4">
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>11</v>
+        <v>89</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>12</v>
+        <v>90</v>
       </c>
       <c r="D23" s="5">
-        <v>40000</v>
+        <v>6000</v>
       </c>
       <c r="E23" s="5">
-        <v>40000</v>
+        <v>6000</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="4">
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D24" s="5">
-        <v>1600</v>
+        <v>8000</v>
       </c>
       <c r="E24" s="5">
-        <v>1600</v>
+        <v>8000</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="4">
         <v>0</v>
       </c>
       <c r="H24" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="D25" s="5">
         <v>8000</v>
@@ -1370,175 +1340,175 @@
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="D26" s="5">
-        <v>8000</v>
+        <v>1200</v>
       </c>
       <c r="E26" s="5">
-        <v>8000</v>
+        <v>1200</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="4">
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="D27" s="5">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="E27" s="5">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="4">
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>98</v>
+        <v>7</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>99</v>
+        <v>8</v>
       </c>
       <c r="D28" s="5">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E28" s="5">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="4">
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="D29" s="5">
-        <v>20000</v>
+        <v>12000</v>
       </c>
       <c r="E29" s="5">
-        <v>20000</v>
+        <v>12000</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="4">
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D30" s="5">
-        <v>24000</v>
+        <v>12000</v>
       </c>
       <c r="E30" s="5">
-        <v>24000</v>
+        <v>12000</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="4">
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="D31" s="5">
-        <v>40000</v>
+        <v>30000</v>
       </c>
       <c r="E31" s="5">
-        <v>40000</v>
+        <v>30000</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="4">
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>46263</v>
+        <v>46262</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D32" s="3">
-        <v>100</v>
-      </c>
-      <c r="E32" s="3">
-        <v>100</v>
+        <v>35</v>
+      </c>
+      <c r="D32" s="5">
+        <v>40000</v>
+      </c>
+      <c r="E32" s="5">
+        <v>40000</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="4">
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
@@ -1546,10 +1516,10 @@
         <v>46263</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="D33" s="3">
         <v>100</v>
@@ -1562,7 +1532,7 @@
         <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
@@ -1570,23 +1540,23 @@
         <v>46263</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="D34" s="5">
-        <v>4000</v>
+        <v>1600</v>
       </c>
       <c r="E34" s="5">
-        <v>4000</v>
+        <v>1600</v>
       </c>
       <c r="F34" s="6"/>
       <c r="G34" s="4">
         <v>0</v>
       </c>
       <c r="H34" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
@@ -1594,23 +1564,23 @@
         <v>46263</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="D35" s="5">
-        <v>7300</v>
+        <v>4000</v>
       </c>
       <c r="E35" s="5">
-        <v>7300</v>
+        <v>4000</v>
       </c>
       <c r="F35" s="6"/>
       <c r="G35" s="4">
         <v>0</v>
       </c>
       <c r="H35" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
@@ -1618,23 +1588,23 @@
         <v>46263</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="D36" s="5">
-        <v>8000</v>
+        <v>7300</v>
       </c>
       <c r="E36" s="5">
-        <v>8000</v>
+        <v>7300</v>
       </c>
       <c r="F36" s="6"/>
       <c r="G36" s="4">
         <v>0</v>
       </c>
       <c r="H36" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
@@ -1642,23 +1612,23 @@
         <v>46263</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="D37" s="5">
-        <v>10000</v>
+        <v>7500</v>
       </c>
       <c r="E37" s="5">
-        <v>10000</v>
+        <v>7500</v>
       </c>
       <c r="F37" s="6"/>
       <c r="G37" s="4">
         <v>0</v>
       </c>
       <c r="H37" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
@@ -1666,23 +1636,23 @@
         <v>46263</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="D38" s="5">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="E38" s="5">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="F38" s="6"/>
       <c r="G38" s="4">
         <v>0</v>
       </c>
       <c r="H38" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
@@ -1690,23 +1660,23 @@
         <v>46263</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D39" s="5">
-        <v>15000</v>
-      </c>
-      <c r="E39" s="3">
-        <v>0</v>
+        <v>8000</v>
+      </c>
+      <c r="E39" s="5">
+        <v>8000</v>
       </c>
       <c r="F39" s="6"/>
       <c r="G39" s="4">
         <v>0</v>
       </c>
       <c r="H39" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
@@ -1714,23 +1684,23 @@
         <v>46263</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>101</v>
+        <v>14</v>
       </c>
       <c r="D40" s="5">
-        <v>24000</v>
-      </c>
-      <c r="E40" s="5">
-        <v>24000</v>
+        <v>15000</v>
+      </c>
+      <c r="E40" s="3">
+        <v>0</v>
       </c>
       <c r="F40" s="6"/>
       <c r="G40" s="4">
         <v>0</v>
       </c>
       <c r="H40" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
@@ -1738,23 +1708,23 @@
         <v>46263</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="D41" s="5">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="E41" s="5">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="F41" s="6"/>
       <c r="G41" s="4">
         <v>0</v>
       </c>
       <c r="H41" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
@@ -1762,71 +1732,71 @@
         <v>46263</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>102</v>
+        <v>8</v>
       </c>
       <c r="D42" s="5">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="E42" s="5">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="F42" s="6"/>
       <c r="G42" s="4">
         <v>0</v>
       </c>
       <c r="H42" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="D43" s="5">
-        <v>7500</v>
+        <v>20000</v>
       </c>
       <c r="E43" s="5">
-        <v>7500</v>
+        <v>20000</v>
       </c>
       <c r="F43" s="6"/>
       <c r="G43" s="4">
         <v>0</v>
       </c>
       <c r="H43" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D44" s="5">
-        <v>10000</v>
+        <v>30000</v>
       </c>
       <c r="E44" s="5">
-        <v>10000</v>
+        <v>30000</v>
       </c>
       <c r="F44" s="6"/>
       <c r="G44" s="4">
         <v>0</v>
       </c>
       <c r="H44" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
@@ -1834,23 +1804,23 @@
         <v>46264</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>23</v>
+        <v>93</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="D45" s="5">
-        <v>13000</v>
+        <v>3000</v>
       </c>
       <c r="E45" s="5">
-        <v>13000</v>
+        <v>3000</v>
       </c>
       <c r="F45" s="6"/>
       <c r="G45" s="4">
         <v>0</v>
       </c>
       <c r="H45" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
@@ -1858,23 +1828,21 @@
         <v>46264</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>7</v>
+        <v>95</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>8</v>
+        <v>96</v>
       </c>
       <c r="D46" s="5">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="E46" s="5">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="F46" s="6"/>
-      <c r="G46" s="4">
-        <v>0</v>
-      </c>
+      <c r="G46" s="6"/>
       <c r="H46" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
@@ -1882,23 +1850,23 @@
         <v>46264</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="D47" s="5">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E47" s="5">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F47" s="6"/>
       <c r="G47" s="4">
         <v>0</v>
       </c>
       <c r="H47" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
@@ -1906,23 +1874,23 @@
         <v>46264</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="D48" s="5">
-        <v>40000</v>
+        <v>24000</v>
       </c>
       <c r="E48" s="5">
-        <v>40000</v>
+        <v>24000</v>
       </c>
       <c r="F48" s="6"/>
       <c r="G48" s="4">
         <v>0</v>
       </c>
       <c r="H48" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
@@ -1930,95 +1898,95 @@
         <v>46264</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="D49" s="5">
-        <v>40000</v>
+        <v>15000</v>
       </c>
       <c r="E49" s="5">
-        <v>40000</v>
+        <v>15000</v>
       </c>
       <c r="F49" s="6"/>
       <c r="G49" s="4">
         <v>0</v>
       </c>
       <c r="H49" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>69</v>
+        <v>7</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="D50" s="5">
-        <v>1200</v>
+        <v>20000</v>
       </c>
       <c r="E50" s="5">
-        <v>1200</v>
+        <v>20000</v>
       </c>
       <c r="F50" s="6"/>
       <c r="G50" s="4">
         <v>0</v>
       </c>
       <c r="H50" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="D51" s="5">
-        <v>8000</v>
+        <v>40000</v>
       </c>
       <c r="E51" s="5">
-        <v>8000</v>
+        <v>40000</v>
       </c>
       <c r="F51" s="6"/>
       <c r="G51" s="4">
         <v>0</v>
       </c>
       <c r="H51" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="D52" s="5">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="E52" s="5">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="F52" s="6"/>
       <c r="G52" s="4">
         <v>0</v>
       </c>
       <c r="H52" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
@@ -2026,23 +1994,23 @@
         <v>46265</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>105</v>
+        <v>25</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>106</v>
+        <v>26</v>
       </c>
       <c r="D53" s="5">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E53" s="5">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F53" s="6"/>
       <c r="G53" s="4">
         <v>0</v>
       </c>
       <c r="H53" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
@@ -2050,23 +2018,23 @@
         <v>46265</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="D54" s="5">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="E54" s="5">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="F54" s="6"/>
       <c r="G54" s="4">
         <v>0</v>
       </c>
       <c r="H54" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
@@ -2074,10 +2042,10 @@
         <v>46265</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="D55" s="5">
         <v>40000</v>
@@ -2090,42 +2058,42 @@
         <v>0</v>
       </c>
       <c r="H55" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
-        <v>46265</v>
+        <v>46260</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D56" s="5">
-        <v>40000</v>
+        <v>50000</v>
       </c>
       <c r="E56" s="5">
-        <v>40000</v>
+        <v>50000</v>
       </c>
       <c r="F56" s="6"/>
       <c r="G56" s="4">
         <v>0</v>
       </c>
       <c r="H56" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D57" s="5">
         <v>50000</v>
@@ -2138,295 +2106,151 @@
         <v>0</v>
       </c>
       <c r="H57" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
-        <v>46259</v>
+        <v>46263</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D58" s="5">
-        <v>50000</v>
+        <v>25000</v>
       </c>
       <c r="E58" s="5">
-        <v>50000</v>
+        <v>25000</v>
       </c>
       <c r="F58" s="6"/>
       <c r="G58" s="4">
         <v>0</v>
       </c>
       <c r="H58" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
-        <v>46292</v>
+        <v>46263</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="D59" s="5">
-        <v>25000</v>
+        <v>6000</v>
       </c>
       <c r="E59" s="5">
-        <v>25000</v>
+        <v>6000</v>
       </c>
       <c r="F59" s="6"/>
       <c r="G59" s="4">
         <v>0</v>
       </c>
       <c r="H59" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
-        <v>46275</v>
+        <v>46260</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="D60" s="5">
-        <v>10000</v>
+        <v>8600</v>
       </c>
       <c r="E60" s="5">
-        <v>10000</v>
+        <v>8600</v>
       </c>
       <c r="F60" s="6"/>
       <c r="G60" s="4">
         <v>0</v>
       </c>
       <c r="H60" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
-        <v>46268</v>
+        <v>46260</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="D61" s="5">
-        <v>30000</v>
+        <v>63104</v>
       </c>
       <c r="E61" s="5">
-        <v>30000</v>
+        <v>63104</v>
       </c>
       <c r="F61" s="6"/>
       <c r="G61" s="4">
         <v>0</v>
       </c>
       <c r="H61" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
-        <v>46267</v>
+        <v>46262</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="D62" s="5">
-        <v>30000</v>
+        <v>35000</v>
       </c>
       <c r="E62" s="5">
-        <v>30000</v>
+        <v>35000</v>
       </c>
       <c r="F62" s="6"/>
       <c r="G62" s="4">
         <v>0</v>
       </c>
       <c r="H62" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D63" s="5">
-        <v>25000</v>
+        <v>32000</v>
       </c>
       <c r="E63" s="5">
-        <v>25000</v>
+        <v>32000</v>
       </c>
       <c r="F63" s="6"/>
       <c r="G63" s="4">
         <v>0</v>
       </c>
       <c r="H63" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A64" s="2">
-        <v>46263</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D64" s="5">
-        <v>6000</v>
-      </c>
-      <c r="E64" s="5">
-        <v>6000</v>
-      </c>
-      <c r="F64" s="6"/>
-      <c r="G64" s="4">
-        <v>0</v>
-      </c>
-      <c r="H64" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A65" s="2">
-        <v>46260</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D65" s="5">
-        <v>7904</v>
-      </c>
-      <c r="E65" s="5">
-        <v>7904</v>
-      </c>
-      <c r="F65" s="6"/>
-      <c r="G65" s="4">
-        <v>0</v>
-      </c>
-      <c r="H65" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A66" s="2">
-        <v>46260</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D66" s="5">
-        <v>8600</v>
-      </c>
-      <c r="E66" s="5">
-        <v>8600</v>
-      </c>
-      <c r="F66" s="6"/>
-      <c r="G66" s="4">
-        <v>0</v>
-      </c>
-      <c r="H66" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A67" s="2">
-        <v>46260</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D67" s="5">
-        <v>63104</v>
-      </c>
-      <c r="E67" s="5">
-        <v>63104</v>
-      </c>
-      <c r="F67" s="6"/>
-      <c r="G67" s="4">
-        <v>0</v>
-      </c>
-      <c r="H67" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A68" s="2">
-        <v>46262</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D68" s="5">
-        <v>35000</v>
-      </c>
-      <c r="E68" s="5">
-        <v>35000</v>
-      </c>
-      <c r="F68" s="6"/>
-      <c r="G68" s="4">
-        <v>0</v>
-      </c>
-      <c r="H68" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A69" s="2">
-        <v>46265</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D69" s="5">
-        <v>32000</v>
-      </c>
-      <c r="E69" s="5">
-        <v>32000</v>
-      </c>
-      <c r="F69" s="6"/>
-      <c r="G69" s="4">
-        <v>0</v>
-      </c>
-      <c r="H69" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/data/Plan.xlsx
+++ b/data/Plan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raman/Documents/GitHub/production-board/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2C1C75C-548B-CB4F-884B-C978D4ED964B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63C292AE-ED25-5246-B320-AF011BCF6EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16560" xr2:uid="{7C08584A-5D47-2049-B143-911B93E5D6E0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="83">
   <si>
     <t>Date</t>
   </si>
@@ -74,24 +74,12 @@
     <t>Anti-Hairfall Conditioner - 175gm</t>
   </si>
   <si>
-    <t>BA24</t>
-  </si>
-  <si>
-    <t>Anti Dandruff Shampoo</t>
-  </si>
-  <si>
     <t>BA103</t>
   </si>
   <si>
     <t>Anti-Hairfall Conditioner 100 gm</t>
   </si>
   <si>
-    <t>SS12</t>
-  </si>
-  <si>
-    <t>Hydrating Fluid Sunscreen 125 ml</t>
-  </si>
-  <si>
     <t>USTTBA76</t>
   </si>
   <si>
@@ -104,12 +92,6 @@
     <t>EXPERT | Ultra Smoothing Hair Mask (250 gms) - TikTok US</t>
   </si>
   <si>
-    <t>BA73</t>
-  </si>
-  <si>
-    <t>BA Expert Anti Hairfall Shampoo 100 ml</t>
-  </si>
-  <si>
     <t>CAP106</t>
   </si>
   <si>
@@ -155,18 +137,6 @@
     <t>Outsource</t>
   </si>
   <si>
-    <t>BA55</t>
-  </si>
-  <si>
-    <t>Rosemary and Coconut Milk Hydrating Conditioner</t>
-  </si>
-  <si>
-    <t>BA49</t>
-  </si>
-  <si>
-    <t>Curl Defining Shampoo 250 ml</t>
-  </si>
-  <si>
     <t>BA48</t>
   </si>
   <si>
@@ -209,12 +179,6 @@
     <t>Gentle and Soothing Face Wash 75 ml</t>
   </si>
   <si>
-    <t>VIE13</t>
-  </si>
-  <si>
-    <t>Vinci Elivaas conditioner 5Ltr</t>
-  </si>
-  <si>
     <t>BA121</t>
   </si>
   <si>
@@ -239,33 +203,18 @@
     <t>Vinci Elivaas Lotion 5ltr</t>
   </si>
   <si>
-    <t>VIE09</t>
-  </si>
-  <si>
-    <t>Vinci Elivaas Bodywash 5ltr</t>
-  </si>
-  <si>
     <t>CAP62</t>
   </si>
   <si>
     <t>AHA Body Lotion 236 ml</t>
   </si>
   <si>
-    <t>BA10</t>
-  </si>
-  <si>
     <t>EXPERT | Ultra Smoothing Shampoo (250 ML) -  TikTok US</t>
   </si>
   <si>
     <t>USTTBA10</t>
   </si>
   <si>
-    <t>CAP49</t>
-  </si>
-  <si>
-    <t>Roll On: Fragrance Free (40 ml) (Rectangular)-399</t>
-  </si>
-  <si>
     <t>USTTCAP24</t>
   </si>
   <si>
@@ -278,21 +227,12 @@
     <t>Underarm Roll On - 40 ml / White jasmine (Rectangular Monocarton)-399</t>
   </si>
   <si>
-    <t>EXPERT | Ultra Smoothing Shampoo (250 ML)</t>
-  </si>
-  <si>
     <t>CAP105</t>
   </si>
   <si>
     <t>Gentle Exfoliating Face Scrub 100ML</t>
   </si>
   <si>
-    <t>USTTBA93</t>
-  </si>
-  <si>
-    <t>EXPERT | Ultra Smoothing Serum (100 ML) - TikTok US</t>
-  </si>
-  <si>
     <t>Advance hair growth Serum- Roll On</t>
   </si>
   <si>
@@ -320,12 +260,6 @@
     <t>Under Arm Roll On- Fragrance Free - 75ml</t>
   </si>
   <si>
-    <t>BA93</t>
-  </si>
-  <si>
-    <t>EXPERT | Ultra Smoothing Serum (100 ML)</t>
-  </si>
-  <si>
     <t>CAP1</t>
   </si>
   <si>
@@ -338,10 +272,22 @@
     <t>Exfoliating face wash 75 ml</t>
   </si>
   <si>
-    <t>BA76</t>
-  </si>
-  <si>
-    <t>Rosemary &amp; Rice Water Hair Growth Spray-200ml</t>
+    <t>BA124</t>
+  </si>
+  <si>
+    <t>Rosemary &amp; Rice Water Hair Growth Spray- 100ml</t>
+  </si>
+  <si>
+    <t>BA27</t>
+  </si>
+  <si>
+    <t>EXPERT | Heat Protection Spray</t>
+  </si>
+  <si>
+    <t>BA74</t>
+  </si>
+  <si>
+    <t>BA Expert Anti Dandruff Shampoo 100 ml</t>
   </si>
 </sst>
 </file>
@@ -738,7 +684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C578346-EE80-DF41-8099-4E3028D96EBE}">
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="57.1640625" customWidth="1"/>
@@ -769,55 +715,55 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" s="3">
-        <v>50</v>
-      </c>
-      <c r="E2" s="3">
-        <v>50</v>
+        <v>78</v>
+      </c>
+      <c r="D2" s="5">
+        <v>1500</v>
+      </c>
+      <c r="E2" s="5">
+        <v>1500</v>
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="4">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D3" s="5">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="E3" s="5">
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="4">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>38</v>
@@ -826,124 +772,124 @@
         <v>39</v>
       </c>
       <c r="D4" s="5">
-        <v>6300</v>
+        <v>4000</v>
       </c>
       <c r="E4" s="5">
-        <v>6300</v>
+        <v>4000</v>
       </c>
       <c r="F4" s="6"/>
       <c r="G4" s="4">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="D5" s="5">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="E5" s="5">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="4">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="D6" s="5">
-        <v>8000</v>
+        <v>15000</v>
       </c>
       <c r="E6" s="5">
-        <v>8000</v>
+        <v>15000</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="4">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="D7" s="5">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="E7" s="5">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="4">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D8" s="5">
-        <v>12000</v>
+        <v>20000</v>
       </c>
       <c r="E8" s="5">
-        <v>12000</v>
+        <v>20000</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="4">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="D9" s="5">
         <v>20000</v>
@@ -956,18 +902,18 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D10" s="5">
         <v>24000</v>
@@ -980,372 +926,372 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="D11" s="5">
-        <v>14000</v>
+        <v>5000</v>
       </c>
       <c r="E11" s="5">
-        <v>14000</v>
+        <v>5000</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="4">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="D12" s="5">
-        <v>40000</v>
+        <v>8000</v>
       </c>
       <c r="E12" s="5">
-        <v>40000</v>
+        <v>8000</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="4">
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="D13" s="5">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="E13" s="5">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="4">
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="D14" s="5">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="E14" s="5">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="4">
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D15" s="5">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="E15" s="5">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="4">
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="D16" s="5">
-        <v>16000</v>
+        <v>20000</v>
       </c>
       <c r="E16" s="5">
-        <v>16000</v>
+        <v>20000</v>
       </c>
       <c r="F16" s="6"/>
       <c r="G16" s="4">
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
-        <v>46261</v>
+        <v>46263</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D17" s="5">
-        <v>20000</v>
+        <v>1200</v>
       </c>
       <c r="E17" s="5">
-        <v>20000</v>
+        <v>1200</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="4">
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
-        <v>46261</v>
+        <v>46263</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D18" s="5">
-        <v>20000</v>
+        <v>3000</v>
       </c>
       <c r="E18" s="5">
-        <v>20000</v>
+        <v>3000</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="4">
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <v>46261</v>
+        <v>46263</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="D19" s="5">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="E19" s="5">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="4">
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <v>46261</v>
+        <v>46263</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="D20" s="5">
-        <v>24000</v>
+        <v>8000</v>
       </c>
       <c r="E20" s="5">
-        <v>24000</v>
+        <v>8000</v>
       </c>
       <c r="F20" s="6"/>
       <c r="G20" s="4">
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D21" s="3">
-        <v>100</v>
-      </c>
-      <c r="E21" s="3">
-        <v>100</v>
+        <v>10</v>
+      </c>
+      <c r="D21" s="5">
+        <v>8000</v>
+      </c>
+      <c r="E21" s="5">
+        <v>8000</v>
       </c>
       <c r="F21" s="6"/>
       <c r="G21" s="4">
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="D22" s="5">
-        <v>3000</v>
+        <v>12000</v>
       </c>
       <c r="E22" s="5">
-        <v>3000</v>
+        <v>12000</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="4">
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D23" s="5">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="E23" s="5">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="4">
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>68</v>
+        <v>7</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>69</v>
+        <v>8</v>
       </c>
       <c r="D24" s="5">
-        <v>8000</v>
+        <v>20000</v>
       </c>
       <c r="E24" s="5">
-        <v>8000</v>
+        <v>20000</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="4">
         <v>0</v>
       </c>
       <c r="H24" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="D25" s="5">
-        <v>8000</v>
+        <v>40000</v>
       </c>
       <c r="E25" s="5">
-        <v>8000</v>
+        <v>40000</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="4">
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>46262</v>
+        <v>46264</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>52</v>
@@ -1353,317 +1299,317 @@
       <c r="C26" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D26" s="5">
-        <v>1200</v>
-      </c>
-      <c r="E26" s="5">
-        <v>1200</v>
+      <c r="D26" s="3">
+        <v>100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>100</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="4">
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>46262</v>
+        <v>46264</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="D27" s="5">
-        <v>8000</v>
+        <v>1600</v>
       </c>
       <c r="E27" s="5">
-        <v>8000</v>
+        <v>1600</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="4">
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>46262</v>
+        <v>46264</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D28" s="5">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="E28" s="5">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="4">
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
-        <v>46262</v>
+        <v>46264</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D29" s="5">
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="E29" s="5">
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="F29" s="6"/>
       <c r="G29" s="4">
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
-        <v>46262</v>
+        <v>46264</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>91</v>
+        <v>32</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>92</v>
+        <v>33</v>
       </c>
       <c r="D30" s="5">
-        <v>12000</v>
+        <v>7300</v>
       </c>
       <c r="E30" s="5">
-        <v>12000</v>
+        <v>7300</v>
       </c>
       <c r="F30" s="6"/>
       <c r="G30" s="4">
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <v>46262</v>
+        <v>46264</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D31" s="5">
-        <v>30000</v>
+        <v>7500</v>
       </c>
       <c r="E31" s="5">
-        <v>30000</v>
+        <v>7500</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="4">
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>46262</v>
+        <v>46264</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="D32" s="5">
-        <v>40000</v>
+        <v>10000</v>
       </c>
       <c r="E32" s="5">
-        <v>40000</v>
+        <v>10000</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="4">
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D33" s="3">
-        <v>100</v>
-      </c>
-      <c r="E33" s="3">
-        <v>100</v>
+        <v>63</v>
+      </c>
+      <c r="D33" s="5">
+        <v>10000</v>
+      </c>
+      <c r="E33" s="5">
+        <v>10000</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="4">
         <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="D34" s="5">
-        <v>1600</v>
+        <v>20000</v>
       </c>
       <c r="E34" s="5">
-        <v>1600</v>
+        <v>20000</v>
       </c>
       <c r="F34" s="6"/>
       <c r="G34" s="4">
         <v>0</v>
       </c>
       <c r="H34" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D35" s="5">
-        <v>4000</v>
+        <v>20000</v>
       </c>
       <c r="E35" s="5">
-        <v>4000</v>
+        <v>20000</v>
       </c>
       <c r="F35" s="6"/>
       <c r="G35" s="4">
         <v>0</v>
       </c>
       <c r="H35" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="D36" s="5">
-        <v>7300</v>
+        <v>40000</v>
       </c>
       <c r="E36" s="5">
-        <v>7300</v>
+        <v>40000</v>
       </c>
       <c r="F36" s="6"/>
       <c r="G36" s="4">
         <v>0</v>
       </c>
       <c r="H36" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="D37" s="5">
-        <v>7500</v>
+        <v>3000</v>
       </c>
       <c r="E37" s="5">
-        <v>7500</v>
+        <v>3000</v>
       </c>
       <c r="F37" s="6"/>
       <c r="G37" s="4">
         <v>0</v>
       </c>
       <c r="H37" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="D38" s="5">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="E38" s="5">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="F38" s="6"/>
       <c r="G38" s="4">
         <v>0</v>
       </c>
       <c r="H38" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="D39" s="5">
         <v>8000</v>
@@ -1676,365 +1622,367 @@
         <v>0</v>
       </c>
       <c r="H39" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>14</v>
+        <v>78</v>
       </c>
       <c r="D40" s="5">
-        <v>15000</v>
-      </c>
-      <c r="E40" s="3">
-        <v>0</v>
+        <v>10000</v>
+      </c>
+      <c r="E40" s="5">
+        <v>10000</v>
       </c>
       <c r="F40" s="6"/>
       <c r="G40" s="4">
         <v>0</v>
       </c>
       <c r="H40" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D41" s="5">
-        <v>20000</v>
+        <v>12000</v>
       </c>
       <c r="E41" s="5">
-        <v>20000</v>
+        <v>12000</v>
       </c>
       <c r="F41" s="6"/>
       <c r="G41" s="4">
         <v>0</v>
       </c>
       <c r="H41" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>7</v>
+        <v>81</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="D42" s="5">
-        <v>20000</v>
+        <v>14000</v>
       </c>
       <c r="E42" s="5">
-        <v>20000</v>
+        <v>14000</v>
       </c>
       <c r="F42" s="6"/>
       <c r="G42" s="4">
         <v>0</v>
       </c>
       <c r="H42" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="D43" s="5">
-        <v>20000</v>
+        <v>24000</v>
       </c>
       <c r="E43" s="5">
-        <v>20000</v>
+        <v>24000</v>
       </c>
       <c r="F43" s="6"/>
       <c r="G43" s="4">
         <v>0</v>
       </c>
       <c r="H43" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D44" s="5">
-        <v>30000</v>
-      </c>
-      <c r="E44" s="5">
-        <v>30000</v>
+        <v>15000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0</v>
       </c>
       <c r="F44" s="6"/>
       <c r="G44" s="4">
         <v>0</v>
       </c>
       <c r="H44" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>93</v>
+        <v>7</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>94</v>
+        <v>8</v>
       </c>
       <c r="D45" s="5">
-        <v>3000</v>
+        <v>20000</v>
       </c>
       <c r="E45" s="5">
-        <v>3000</v>
+        <v>20000</v>
       </c>
       <c r="F45" s="6"/>
       <c r="G45" s="4">
         <v>0</v>
       </c>
       <c r="H45" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="D46" s="5">
-        <v>8000</v>
+        <v>40000</v>
       </c>
       <c r="E46" s="5">
-        <v>8000</v>
+        <v>40000</v>
       </c>
       <c r="F46" s="6"/>
-      <c r="G46" s="6"/>
+      <c r="G46" s="4">
+        <v>0</v>
+      </c>
       <c r="H46" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D47" s="5">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="E47" s="5">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="F47" s="6"/>
       <c r="G47" s="4">
         <v>0</v>
       </c>
       <c r="H47" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>46264</v>
+        <v>46261</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>98</v>
+        <v>23</v>
       </c>
       <c r="D48" s="5">
-        <v>24000</v>
+        <v>50000</v>
       </c>
       <c r="E48" s="5">
-        <v>24000</v>
+        <v>50000</v>
       </c>
       <c r="F48" s="6"/>
       <c r="G48" s="4">
         <v>0</v>
       </c>
       <c r="H48" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>46264</v>
+        <v>46261</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>82</v>
+        <v>24</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>83</v>
+        <v>25</v>
       </c>
       <c r="D49" s="5">
-        <v>15000</v>
+        <v>50000</v>
       </c>
       <c r="E49" s="5">
-        <v>15000</v>
+        <v>50000</v>
       </c>
       <c r="F49" s="6"/>
       <c r="G49" s="4">
         <v>0</v>
       </c>
       <c r="H49" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D50" s="5">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="E50" s="5">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="F50" s="6"/>
       <c r="G50" s="4">
         <v>0</v>
       </c>
       <c r="H50" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <v>46264</v>
+        <v>46263</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="D51" s="5">
-        <v>40000</v>
+        <v>6000</v>
       </c>
       <c r="E51" s="5">
-        <v>40000</v>
+        <v>6000</v>
       </c>
       <c r="F51" s="6"/>
       <c r="G51" s="4">
         <v>0</v>
       </c>
       <c r="H51" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <v>46264</v>
+        <v>46261</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="D52" s="5">
-        <v>40000</v>
+        <v>8600</v>
       </c>
       <c r="E52" s="5">
-        <v>40000</v>
+        <v>8600</v>
       </c>
       <c r="F52" s="6"/>
       <c r="G52" s="4">
         <v>0</v>
       </c>
       <c r="H52" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
-        <v>46265</v>
+        <v>46260</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D53" s="5">
-        <v>10000</v>
+        <v>63104</v>
       </c>
       <c r="E53" s="5">
-        <v>10000</v>
+        <v>63104</v>
       </c>
       <c r="F53" s="6"/>
       <c r="G53" s="4">
         <v>0</v>
       </c>
       <c r="H53" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
-        <v>46265</v>
+        <v>46262</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D54" s="5">
-        <v>40000</v>
+        <v>35000</v>
       </c>
       <c r="E54" s="5">
-        <v>40000</v>
+        <v>35000</v>
       </c>
       <c r="F54" s="6"/>
       <c r="G54" s="4">
         <v>0</v>
       </c>
       <c r="H54" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
@@ -2042,215 +1990,23 @@
         <v>46265</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="D55" s="5">
-        <v>40000</v>
+        <v>32000</v>
       </c>
       <c r="E55" s="5">
-        <v>40000</v>
+        <v>32000</v>
       </c>
       <c r="F55" s="6"/>
       <c r="G55" s="4">
         <v>0</v>
       </c>
       <c r="H55" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A56" s="2">
-        <v>46260</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D56" s="5">
-        <v>50000</v>
-      </c>
-      <c r="E56" s="5">
-        <v>50000</v>
-      </c>
-      <c r="F56" s="6"/>
-      <c r="G56" s="4">
-        <v>0</v>
-      </c>
-      <c r="H56" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A57" s="2">
-        <v>46260</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C57" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="D57" s="5">
-        <v>50000</v>
-      </c>
-      <c r="E57" s="5">
-        <v>50000</v>
-      </c>
-      <c r="F57" s="6"/>
-      <c r="G57" s="4">
-        <v>0</v>
-      </c>
-      <c r="H57" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A58" s="2">
-        <v>46263</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D58" s="5">
-        <v>25000</v>
-      </c>
-      <c r="E58" s="5">
-        <v>25000</v>
-      </c>
-      <c r="F58" s="6"/>
-      <c r="G58" s="4">
-        <v>0</v>
-      </c>
-      <c r="H58" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A59" s="2">
-        <v>46263</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D59" s="5">
-        <v>6000</v>
-      </c>
-      <c r="E59" s="5">
-        <v>6000</v>
-      </c>
-      <c r="F59" s="6"/>
-      <c r="G59" s="4">
-        <v>0</v>
-      </c>
-      <c r="H59" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A60" s="2">
-        <v>46260</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D60" s="5">
-        <v>8600</v>
-      </c>
-      <c r="E60" s="5">
-        <v>8600</v>
-      </c>
-      <c r="F60" s="6"/>
-      <c r="G60" s="4">
-        <v>0</v>
-      </c>
-      <c r="H60" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A61" s="2">
-        <v>46260</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D61" s="5">
-        <v>63104</v>
-      </c>
-      <c r="E61" s="5">
-        <v>63104</v>
-      </c>
-      <c r="F61" s="6"/>
-      <c r="G61" s="4">
-        <v>0</v>
-      </c>
-      <c r="H61" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A62" s="2">
-        <v>46262</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D62" s="5">
-        <v>35000</v>
-      </c>
-      <c r="E62" s="5">
-        <v>35000</v>
-      </c>
-      <c r="F62" s="6"/>
-      <c r="G62" s="4">
-        <v>0</v>
-      </c>
-      <c r="H62" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A63" s="2">
-        <v>46265</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D63" s="5">
-        <v>32000</v>
-      </c>
-      <c r="E63" s="5">
-        <v>32000</v>
-      </c>
-      <c r="F63" s="6"/>
-      <c r="G63" s="4">
-        <v>0</v>
-      </c>
-      <c r="H63" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/data/Plan.xlsx
+++ b/data/Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raman/Documents/GitHub/production-board/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C9A64DD-341C-7E47-B710-0C962E1273F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25DA7C15-1155-5D42-BF85-5C6ED6F8D7CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16560" xr2:uid="{7C08584A-5D47-2049-B143-911B93E5D6E0}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="30">
   <si>
     <t>Date</t>
   </si>
@@ -126,6 +126,12 @@
   </si>
   <si>
     <t>Oil &amp; Acne Control Face Wash</t>
+  </si>
+  <si>
+    <t>BA63</t>
+  </si>
+  <si>
+    <t>Bare Anatomy Advanced Hair Growth Serum</t>
   </si>
 </sst>
 </file>
@@ -522,7 +528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C578346-EE80-DF41-8099-4E3028D96EBE}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="57.1640625" customWidth="1"/>
@@ -791,6 +797,30 @@
         <v>7</v>
       </c>
     </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>46265</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="5">
+        <v>28800</v>
+      </c>
+      <c r="E12" s="5">
+        <v>28800</v>
+      </c>
+      <c r="F12" s="6"/>
+      <c r="G12" s="4">
+        <v>0</v>
+      </c>
+      <c r="H12" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Plan.xlsx
+++ b/data/Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raman/Documents/GitHub/production-board/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25DA7C15-1155-5D42-BF85-5C6ED6F8D7CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F00CC15-00BE-6F4A-9F5A-E7A103848F0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16560" xr2:uid="{7C08584A-5D47-2049-B143-911B93E5D6E0}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Date</t>
   </si>
@@ -63,82 +63,13 @@
   </si>
   <si>
     <t>Fill rate</t>
-  </si>
-  <si>
-    <t>Inhouse</t>
-  </si>
-  <si>
-    <t>BA4</t>
-  </si>
-  <si>
-    <t>EXPERT | Damage Repair Shampoo (250 ML)</t>
-  </si>
-  <si>
-    <t>USTTCAP24</t>
-  </si>
-  <si>
-    <t>Exfoliating Body Wash-236ml</t>
-  </si>
-  <si>
-    <t>CAP53</t>
-  </si>
-  <si>
-    <t>Anti-Frizz Leave-In Conditioner</t>
-  </si>
-  <si>
-    <t>CAP166</t>
-  </si>
-  <si>
-    <t>Under Arm Roll On- Fragrance Free - 75ml</t>
-  </si>
-  <si>
-    <t>CAP154</t>
-  </si>
-  <si>
-    <t>Exfoliating face wash 75 ml</t>
-  </si>
-  <si>
-    <t>BA124</t>
-  </si>
-  <si>
-    <t>Rosemary &amp; Rice Water Hair Growth Spray- 100ml</t>
-  </si>
-  <si>
-    <t>BA74</t>
-  </si>
-  <si>
-    <t>BA Expert Anti Dandruff Shampoo 100 ml</t>
-  </si>
-  <si>
-    <t>UKTTCAP49</t>
-  </si>
-  <si>
-    <t>Roll on FF 40 ml - TikTok UK</t>
-  </si>
-  <si>
-    <t>BA76</t>
-  </si>
-  <si>
-    <t>Rosemary &amp; Rice Water Hair Growth Spray-200ml</t>
-  </si>
-  <si>
-    <t>CAP82</t>
-  </si>
-  <si>
-    <t>Oil &amp; Acne Control Face Wash</t>
-  </si>
-  <si>
-    <t>BA63</t>
-  </si>
-  <si>
-    <t>Bare Anatomy Advanced Hair Growth Serum</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -151,18 +82,6 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -186,14 +105,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -528,13 +442,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C578346-EE80-DF41-8099-4E3028D96EBE}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="57.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -555,270 +469,6 @@
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="2">
-        <v>46265</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="5">
-        <v>5000</v>
-      </c>
-      <c r="E2" s="5">
-        <v>5000</v>
-      </c>
-      <c r="F2" s="6"/>
-      <c r="G2" s="4">
-        <v>0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="2">
-        <v>46265</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="5">
-        <v>5000</v>
-      </c>
-      <c r="E3" s="5">
-        <v>5000</v>
-      </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="4">
-        <v>0</v>
-      </c>
-      <c r="H3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="2">
-        <v>46265</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="5">
-        <v>7500</v>
-      </c>
-      <c r="E4" s="5">
-        <v>7500</v>
-      </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="4">
-        <v>0</v>
-      </c>
-      <c r="H4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="2">
-        <v>46265</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="5">
-        <v>15000</v>
-      </c>
-      <c r="E5" s="5">
-        <v>15000</v>
-      </c>
-      <c r="F5" s="6"/>
-      <c r="G5" s="4">
-        <v>0</v>
-      </c>
-      <c r="H5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="2">
-        <v>46265</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="5">
-        <v>12000</v>
-      </c>
-      <c r="E6" s="5">
-        <v>12000</v>
-      </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="4">
-        <v>0</v>
-      </c>
-      <c r="H6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="2">
-        <v>46265</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="5">
-        <v>12000</v>
-      </c>
-      <c r="E7" s="5">
-        <v>12000</v>
-      </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="4">
-        <v>0</v>
-      </c>
-      <c r="H7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="2">
-        <v>46265</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="5">
-        <v>20000</v>
-      </c>
-      <c r="E8" s="5">
-        <v>20000</v>
-      </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="4">
-        <v>0</v>
-      </c>
-      <c r="H8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="2">
-        <v>46265</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="5">
-        <v>15000</v>
-      </c>
-      <c r="E9" s="5">
-        <v>15000</v>
-      </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="4">
-        <v>0</v>
-      </c>
-      <c r="H9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="2">
-        <v>46265</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="5">
-        <v>20000</v>
-      </c>
-      <c r="E10" s="5">
-        <v>20000</v>
-      </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="4">
-        <v>0</v>
-      </c>
-      <c r="H10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="2">
-        <v>46265</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="5">
-        <v>40000</v>
-      </c>
-      <c r="E11" s="5">
-        <v>40000</v>
-      </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="4">
-        <v>0</v>
-      </c>
-      <c r="H11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="2">
-        <v>46265</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="5">
-        <v>28800</v>
-      </c>
-      <c r="E12" s="5">
-        <v>28800</v>
-      </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="4">
-        <v>0</v>
-      </c>
-      <c r="H12" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/Plan.xlsx
+++ b/data/Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raman/Documents/GitHub/production-board/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F00CC15-00BE-6F4A-9F5A-E7A103848F0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F815F554-1D8A-6940-A2B5-C19077A1C5E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16560" xr2:uid="{7C08584A-5D47-2049-B143-911B93E5D6E0}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="145">
   <si>
     <t>Date</t>
   </si>
@@ -63,13 +63,427 @@
   </si>
   <si>
     <t>Fill rate</t>
+  </si>
+  <si>
+    <t>BA9</t>
+  </si>
+  <si>
+    <t>EXPERT | Ultra Smoothing Hair Mask (250 gms)</t>
+  </si>
+  <si>
+    <t>CAP1</t>
+  </si>
+  <si>
+    <t>Acne Control Body Wash (236 ml)</t>
+  </si>
+  <si>
+    <t>CAP70</t>
+  </si>
+  <si>
+    <t>Underarm Roll On - 40 ml / White jasmine (Rectangular Monocarton)-399</t>
+  </si>
+  <si>
+    <t>CAP82</t>
+  </si>
+  <si>
+    <t>Oil &amp; Acne Control Face Wash</t>
+  </si>
+  <si>
+    <t>USTTCAP126</t>
+  </si>
+  <si>
+    <t>Chemist at Play Underarm Roll On Aqua 75ml (CAP126) USTT</t>
+  </si>
+  <si>
+    <t>CAP106</t>
+  </si>
+  <si>
+    <t>Brightening Face Serum(10% VitaminC)30ml</t>
+  </si>
+  <si>
+    <t>USTTBA93</t>
+  </si>
+  <si>
+    <t>EXPERT | Ultra Smoothing Serum (100 ML) - TikTok US</t>
+  </si>
+  <si>
+    <t>BA22</t>
+  </si>
+  <si>
+    <t>BA Expert | Anti Hairfall Shampoo 250 ml</t>
+  </si>
+  <si>
+    <t>BA55</t>
+  </si>
+  <si>
+    <t>Rosemary and Coconut Milk Hydrating Conditioner</t>
+  </si>
+  <si>
+    <t>BA104</t>
+  </si>
+  <si>
+    <t>Anti-Dandruff Conditioner 100 gm</t>
+  </si>
+  <si>
+    <t>SS43</t>
+  </si>
+  <si>
+    <t>5% Niacinamide Sunscreen Body Lotion 200 ml</t>
+  </si>
+  <si>
+    <t>BA10</t>
+  </si>
+  <si>
+    <t>EXPERT | Ultra Smoothing Shampoo (250 ML)</t>
+  </si>
+  <si>
+    <t>USTTCAP16</t>
+  </si>
+  <si>
+    <t>Brightening body wash 236 ml - Tik Tok US</t>
+  </si>
+  <si>
+    <t>CAP24</t>
+  </si>
+  <si>
+    <t>Exfoliating Body Wash (236 ml)</t>
+  </si>
+  <si>
+    <t>USTTBA76</t>
+  </si>
+  <si>
+    <t>Rosemary &amp; Rice Water Hair Spray-200ml - TikTok US</t>
+  </si>
+  <si>
+    <t>BA121</t>
+  </si>
+  <si>
+    <t>NxS Flaxseed &amp; Rice Water Hair Gel 300ml</t>
+  </si>
+  <si>
+    <t>USTTCAP70</t>
+  </si>
+  <si>
+    <t> Roll On -  White jasmine 40 ml- Tik Tok US</t>
+  </si>
+  <si>
+    <t>BA87</t>
+  </si>
+  <si>
+    <t>Advanced Anti-Grey Hair Serum 50ml</t>
+  </si>
+  <si>
+    <t>BA98</t>
+  </si>
+  <si>
+    <t>Anti-Dandruff Conditioner -175gm</t>
+  </si>
+  <si>
+    <t>BA60</t>
+  </si>
+  <si>
+    <t>Rosemary and Coconut Milk Hydrating Shampoo 200ML</t>
+  </si>
+  <si>
+    <t>CAP137</t>
+  </si>
+  <si>
+    <t>Oil &amp; Acne Control Face Wash 100ml - Flipkart</t>
+  </si>
+  <si>
+    <t>BA73</t>
+  </si>
+  <si>
+    <t>BA Expert Anti Hairfall Shampoo 100 ml</t>
+  </si>
+  <si>
+    <t>BA24</t>
+  </si>
+  <si>
+    <t>Anti Dandruff Shampoo</t>
+  </si>
+  <si>
+    <t>BA76</t>
+  </si>
+  <si>
+    <t>Rosemary &amp; Rice Water Hair Growth Spray-200ml</t>
+  </si>
+  <si>
+    <t>USTTBA9</t>
+  </si>
+  <si>
+    <t>EXPERT | Ultra Smoothing Hair Mask (250 gms) - TikTok US</t>
+  </si>
+  <si>
+    <t>BA100</t>
+  </si>
+  <si>
+    <t>Anti-Dandruff Shampoo 450ml</t>
+  </si>
+  <si>
+    <t>USTTBA50</t>
+  </si>
+  <si>
+    <t>Curl Intensifying Leave in Conditioner USTT</t>
+  </si>
+  <si>
+    <t>CAP173</t>
+  </si>
+  <si>
+    <t>Gentle Exfoliating Face Wash 75ml- Pack of 2</t>
+  </si>
+  <si>
+    <t>BA50</t>
+  </si>
+  <si>
+    <t>Curl Intensifying Leave in Conditioner 140 ml</t>
+  </si>
+  <si>
+    <t>USTTCAP62</t>
+  </si>
+  <si>
+    <t>AHA Body Lotion 236ml - Tik Tok US</t>
+  </si>
+  <si>
+    <t>CAP83</t>
+  </si>
+  <si>
+    <t>Brightening Boost Face Wash</t>
+  </si>
+  <si>
+    <t>CAP153</t>
+  </si>
+  <si>
+    <t>Exfoliating face wash 100 ml</t>
+  </si>
+  <si>
+    <t>USTTCAP24</t>
+  </si>
+  <si>
+    <t>Exfoliating Body Wash-236ml</t>
+  </si>
+  <si>
+    <t>CAP165</t>
+  </si>
+  <si>
+    <t>Epsom Body Wash - 236ml</t>
+  </si>
+  <si>
+    <t>CAP132</t>
+  </si>
+  <si>
+    <t>2% Salicylic Acid Serum 10ml</t>
+  </si>
+  <si>
+    <t>CAP145</t>
+  </si>
+  <si>
+    <t>Oil &amp; Acne Control Face Wash - Flipkart pack of 3</t>
+  </si>
+  <si>
+    <t>CAP144</t>
+  </si>
+  <si>
+    <t>Oil &amp; Acne Control Face Wash - Flipkart pack of 2</t>
+  </si>
+  <si>
+    <t>BA105</t>
+  </si>
+  <si>
+    <t>Ultra smoothing shampoo 100 ml</t>
+  </si>
+  <si>
+    <t>BA118</t>
+  </si>
+  <si>
+    <t>Fenugreek &amp; Curry Leaves Hair Strengthening Spray - 200ml</t>
+  </si>
+  <si>
+    <t>USTTBA10</t>
+  </si>
+  <si>
+    <t>EXPERT | Ultra Smoothing Shampoo (250 ML) -  TikTok US</t>
+  </si>
+  <si>
+    <t>CAP107</t>
+  </si>
+  <si>
+    <t>Brightening face serum (10% Vitamin C) 10ml</t>
+  </si>
+  <si>
+    <t>CAP105</t>
+  </si>
+  <si>
+    <t>Gentle Exfoliating Face Scrub 100ML</t>
+  </si>
+  <si>
+    <t>CAP134</t>
+  </si>
+  <si>
+    <t>Deep Cleansing Body Wash 236ml</t>
+  </si>
+  <si>
+    <t>BA66</t>
+  </si>
+  <si>
+    <t>Rosemary hair growth oil 100ml</t>
+  </si>
+  <si>
+    <t>BA103</t>
+  </si>
+  <si>
+    <t>Anti-Hairfall Conditioner 100 gm</t>
+  </si>
+  <si>
+    <t>BA88</t>
+  </si>
+  <si>
+    <t>Gentle Cleansing Shampoo- 750ml</t>
+  </si>
+  <si>
+    <t>CAP17</t>
+  </si>
+  <si>
+    <t>Brightening Body Wash (473 ml)</t>
+  </si>
+  <si>
+    <t>CAP16</t>
+  </si>
+  <si>
+    <t>Brightening Body Wash (236 ml)</t>
+  </si>
+  <si>
+    <t>BA97</t>
+  </si>
+  <si>
+    <t>Anti-Hairfall Conditioner - 175gm</t>
+  </si>
+  <si>
+    <t>BA51</t>
+  </si>
+  <si>
+    <t>BA Gentle Cleansing Shampoo</t>
+  </si>
+  <si>
+    <t>CAP65</t>
+  </si>
+  <si>
+    <t>Neck, Knee, Elbow Brightening Roll On</t>
+  </si>
+  <si>
+    <t>BA82</t>
+  </si>
+  <si>
+    <t>Ultra Smoothing Shampoo- 750ml</t>
+  </si>
+  <si>
+    <t>CAP25</t>
+  </si>
+  <si>
+    <t>Exfoliating Body Wash (473 ml)</t>
+  </si>
+  <si>
+    <t>CAP48</t>
+  </si>
+  <si>
+    <t>Roll On: Aqua 40 ml (Rectangular Monocarton)-399</t>
+  </si>
+  <si>
+    <t>CAP62</t>
+  </si>
+  <si>
+    <t>AHA Body Lotion 236 ml</t>
+  </si>
+  <si>
+    <t>CAP50</t>
+  </si>
+  <si>
+    <t>Under Arm Roll On - 40 ml / Peach (Rectangular Monocarton)-399</t>
+  </si>
+  <si>
+    <t>CAP49</t>
+  </si>
+  <si>
+    <t>Roll On: Fragrance Free (40 ml) (Rectangular)-399</t>
+  </si>
+  <si>
+    <t>BA74</t>
+  </si>
+  <si>
+    <t>BA Expert Anti Dandruff Shampoo 100 ml</t>
+  </si>
+  <si>
+    <t>CAP135</t>
+  </si>
+  <si>
+    <t>Odour Control Body Wash 236ml</t>
+  </si>
+  <si>
+    <t>CO358</t>
+  </si>
+  <si>
+    <t>Combo- Anti-Dandruff Shampoo (100ml) + Anti-Dandruff Conditioner (100g)</t>
+  </si>
+  <si>
+    <t>CAP139</t>
+  </si>
+  <si>
+    <t>Cherry Lip Balm 4.5gm</t>
+  </si>
+  <si>
+    <t>CAP138</t>
+  </si>
+  <si>
+    <t>Natural Lip Balm 4.5gm</t>
+  </si>
+  <si>
+    <t>BA110</t>
+  </si>
+  <si>
+    <t>Instant Cover-Up Hair Powder Black-4gm</t>
+  </si>
+  <si>
+    <t>BA111</t>
+  </si>
+  <si>
+    <t>Instant Cover-Up Hair Powder Brown-4gm</t>
+  </si>
+  <si>
+    <t>BA77</t>
+  </si>
+  <si>
+    <t>Scalp Massager</t>
+  </si>
+  <si>
+    <t>CAP157</t>
+  </si>
+  <si>
+    <t>Age Defence Night Cream-30gm</t>
+  </si>
+  <si>
+    <t>SS42</t>
+  </si>
+  <si>
+    <t>3% Niacinamide Featherlight Fluid Sunscreen 45g</t>
+  </si>
+  <si>
+    <t>BA107</t>
+  </si>
+  <si>
+    <t>Advanced Hair Growth Serum Roll-On</t>
+  </si>
+  <si>
+    <t>Inhouse</t>
+  </si>
+  <si>
+    <t>Outsource</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -82,6 +496,18 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -105,9 +531,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -442,13 +873,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C578346-EE80-DF41-8099-4E3028D96EBE}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="57.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -469,6 +900,2478 @@
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="4">
+        <v>3200</v>
+      </c>
+      <c r="E2" s="4">
+        <v>3200</v>
+      </c>
+      <c r="F2" s="5"/>
+      <c r="G2" s="6">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="4">
+        <v>4000</v>
+      </c>
+      <c r="E3" s="4">
+        <v>4000</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="6">
+        <v>0</v>
+      </c>
+      <c r="H3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="4">
+        <v>5000</v>
+      </c>
+      <c r="E4" s="4">
+        <v>5000</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="6">
+        <v>0</v>
+      </c>
+      <c r="H4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="4">
+        <v>5000</v>
+      </c>
+      <c r="E5" s="4">
+        <v>5000</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="6">
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="4">
+        <v>6000</v>
+      </c>
+      <c r="E6" s="4">
+        <v>6000</v>
+      </c>
+      <c r="F6" s="5"/>
+      <c r="G6" s="6">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="4">
+        <v>6000</v>
+      </c>
+      <c r="E7" s="4">
+        <v>6000</v>
+      </c>
+      <c r="F7" s="5"/>
+      <c r="G7" s="6">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="4">
+        <v>6390</v>
+      </c>
+      <c r="E8" s="4">
+        <v>6000</v>
+      </c>
+      <c r="F8" s="5"/>
+      <c r="G8" s="6">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="4">
+        <v>10000</v>
+      </c>
+      <c r="E9" s="4">
+        <v>10000</v>
+      </c>
+      <c r="F9" s="5"/>
+      <c r="G9" s="6">
+        <v>0</v>
+      </c>
+      <c r="H9" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="4">
+        <v>13000</v>
+      </c>
+      <c r="E10" s="4">
+        <v>13000</v>
+      </c>
+      <c r="F10" s="5"/>
+      <c r="G10" s="6">
+        <v>0</v>
+      </c>
+      <c r="H10" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="4">
+        <v>20000</v>
+      </c>
+      <c r="E11" s="4">
+        <v>20000</v>
+      </c>
+      <c r="F11" s="5"/>
+      <c r="G11" s="6">
+        <v>0</v>
+      </c>
+      <c r="H11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="4">
+        <v>20000</v>
+      </c>
+      <c r="E12" s="4">
+        <v>20000</v>
+      </c>
+      <c r="F12" s="5"/>
+      <c r="G12" s="6">
+        <v>0</v>
+      </c>
+      <c r="H12" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="4">
+        <v>20000</v>
+      </c>
+      <c r="E13" s="4">
+        <v>20000</v>
+      </c>
+      <c r="F13" s="5"/>
+      <c r="G13" s="6">
+        <v>0</v>
+      </c>
+      <c r="H13" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="4">
+        <v>21000</v>
+      </c>
+      <c r="E14" s="4">
+        <v>21000</v>
+      </c>
+      <c r="F14" s="5"/>
+      <c r="G14" s="6">
+        <v>0</v>
+      </c>
+      <c r="H14" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="4">
+        <v>34160</v>
+      </c>
+      <c r="E15" s="4">
+        <v>34160</v>
+      </c>
+      <c r="F15" s="5"/>
+      <c r="G15" s="6">
+        <v>0</v>
+      </c>
+      <c r="H15" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="4">
+        <v>40000</v>
+      </c>
+      <c r="E16" s="4">
+        <v>40000</v>
+      </c>
+      <c r="F16" s="5"/>
+      <c r="G16" s="6">
+        <v>0</v>
+      </c>
+      <c r="H16" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1600</v>
+      </c>
+      <c r="E17" s="4">
+        <v>1600</v>
+      </c>
+      <c r="F17" s="5"/>
+      <c r="G17" s="6">
+        <v>0</v>
+      </c>
+      <c r="H17" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="4">
+        <v>5000</v>
+      </c>
+      <c r="E18" s="4">
+        <v>5000</v>
+      </c>
+      <c r="F18" s="5"/>
+      <c r="G18" s="6">
+        <v>0</v>
+      </c>
+      <c r="H18" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="4">
+        <v>4700</v>
+      </c>
+      <c r="E19" s="4">
+        <v>4700</v>
+      </c>
+      <c r="F19" s="5"/>
+      <c r="G19" s="6">
+        <v>0</v>
+      </c>
+      <c r="H19" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="4">
+        <v>10000</v>
+      </c>
+      <c r="E20" s="4">
+        <v>10000</v>
+      </c>
+      <c r="F20" s="5"/>
+      <c r="G20" s="6">
+        <v>0</v>
+      </c>
+      <c r="H20" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="4">
+        <v>10000</v>
+      </c>
+      <c r="E21" s="4">
+        <v>10000</v>
+      </c>
+      <c r="F21" s="5"/>
+      <c r="G21" s="6">
+        <v>0</v>
+      </c>
+      <c r="H21" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="4">
+        <v>11000</v>
+      </c>
+      <c r="E22" s="4">
+        <v>11000</v>
+      </c>
+      <c r="F22" s="5"/>
+      <c r="G22" s="6">
+        <v>0</v>
+      </c>
+      <c r="H22" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D23" s="4">
+        <v>20000</v>
+      </c>
+      <c r="E23" s="4">
+        <v>20000</v>
+      </c>
+      <c r="F23" s="5"/>
+      <c r="G23" s="6">
+        <v>0</v>
+      </c>
+      <c r="H23" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" s="4">
+        <v>20000</v>
+      </c>
+      <c r="E24" s="4">
+        <v>20000</v>
+      </c>
+      <c r="F24" s="5"/>
+      <c r="G24" s="6">
+        <v>0</v>
+      </c>
+      <c r="H24" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25" s="4">
+        <v>28000</v>
+      </c>
+      <c r="E25" s="4">
+        <v>28000</v>
+      </c>
+      <c r="F25" s="5"/>
+      <c r="G25" s="6">
+        <v>0</v>
+      </c>
+      <c r="H25" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26" s="4">
+        <v>30000</v>
+      </c>
+      <c r="E26" s="4">
+        <v>30000</v>
+      </c>
+      <c r="F26" s="5"/>
+      <c r="G26" s="6">
+        <v>0</v>
+      </c>
+      <c r="H26" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D27" s="4">
+        <v>40000</v>
+      </c>
+      <c r="E27" s="4">
+        <v>40000</v>
+      </c>
+      <c r="F27" s="5"/>
+      <c r="G27" s="6">
+        <v>0</v>
+      </c>
+      <c r="H27" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" s="2">
+        <v>46268</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D28" s="4">
+        <v>47328</v>
+      </c>
+      <c r="E28" s="4">
+        <v>47328</v>
+      </c>
+      <c r="F28" s="5"/>
+      <c r="G28" s="6">
+        <v>0</v>
+      </c>
+      <c r="H28" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" s="4">
+        <v>5000</v>
+      </c>
+      <c r="E29" s="4">
+        <v>5000</v>
+      </c>
+      <c r="F29" s="5"/>
+      <c r="G29" s="6">
+        <v>0</v>
+      </c>
+      <c r="H29" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D30" s="4">
+        <v>5000</v>
+      </c>
+      <c r="E30" s="4">
+        <v>5000</v>
+      </c>
+      <c r="F30" s="5"/>
+      <c r="G30" s="6">
+        <v>0</v>
+      </c>
+      <c r="H30" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D31" s="4">
+        <v>6500</v>
+      </c>
+      <c r="E31" s="4">
+        <v>6500</v>
+      </c>
+      <c r="F31" s="5"/>
+      <c r="G31" s="6">
+        <v>0</v>
+      </c>
+      <c r="H31" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D32" s="4">
+        <v>8000</v>
+      </c>
+      <c r="E32" s="4">
+        <v>8000</v>
+      </c>
+      <c r="F32" s="5"/>
+      <c r="G32" s="6">
+        <v>0</v>
+      </c>
+      <c r="H32" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D33" s="4">
+        <v>8000</v>
+      </c>
+      <c r="E33" s="4">
+        <v>8000</v>
+      </c>
+      <c r="F33" s="5"/>
+      <c r="G33" s="6">
+        <v>0</v>
+      </c>
+      <c r="H33" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34" s="4">
+        <v>10000</v>
+      </c>
+      <c r="E34" s="4">
+        <v>10000</v>
+      </c>
+      <c r="F34" s="5"/>
+      <c r="G34" s="6">
+        <v>0</v>
+      </c>
+      <c r="H34" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35" s="4">
+        <v>10000</v>
+      </c>
+      <c r="E35" s="4">
+        <v>10000</v>
+      </c>
+      <c r="F35" s="5"/>
+      <c r="G35" s="6">
+        <v>0</v>
+      </c>
+      <c r="H35" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D36" s="4">
+        <v>20000</v>
+      </c>
+      <c r="E36" s="4">
+        <v>20000</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="6">
+        <v>0</v>
+      </c>
+      <c r="H36" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D37" s="4">
+        <v>40000</v>
+      </c>
+      <c r="E37" s="4">
+        <v>40000</v>
+      </c>
+      <c r="F37" s="5"/>
+      <c r="G37" s="6">
+        <v>0</v>
+      </c>
+      <c r="H37" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D38" s="4">
+        <v>1800</v>
+      </c>
+      <c r="E38" s="4">
+        <v>1800</v>
+      </c>
+      <c r="F38" s="5"/>
+      <c r="G38" s="6">
+        <v>0</v>
+      </c>
+      <c r="H38" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D39" s="4">
+        <v>3000</v>
+      </c>
+      <c r="E39" s="4">
+        <v>3000</v>
+      </c>
+      <c r="F39" s="5"/>
+      <c r="G39" s="6">
+        <v>0</v>
+      </c>
+      <c r="H39" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D40" s="4">
+        <v>2000</v>
+      </c>
+      <c r="E40" s="4">
+        <v>2000</v>
+      </c>
+      <c r="F40" s="5"/>
+      <c r="G40" s="6">
+        <v>0</v>
+      </c>
+      <c r="H40" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D41" s="4">
+        <v>5000</v>
+      </c>
+      <c r="E41" s="4">
+        <v>5000</v>
+      </c>
+      <c r="F41" s="5"/>
+      <c r="G41" s="6">
+        <v>0</v>
+      </c>
+      <c r="H41" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A42" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D42" s="4">
+        <v>10000</v>
+      </c>
+      <c r="E42" s="4">
+        <v>10000</v>
+      </c>
+      <c r="F42" s="5"/>
+      <c r="G42" s="6">
+        <v>0</v>
+      </c>
+      <c r="H42" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A43" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D43" s="4">
+        <v>7000</v>
+      </c>
+      <c r="E43" s="4">
+        <v>7000</v>
+      </c>
+      <c r="F43" s="5"/>
+      <c r="G43" s="6">
+        <v>0</v>
+      </c>
+      <c r="H43" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A44" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D44" s="4">
+        <v>15000</v>
+      </c>
+      <c r="E44" s="4">
+        <v>15000</v>
+      </c>
+      <c r="F44" s="5"/>
+      <c r="G44" s="6">
+        <v>0</v>
+      </c>
+      <c r="H44" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A45" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D45" s="4">
+        <v>16000</v>
+      </c>
+      <c r="E45" s="4">
+        <v>16000</v>
+      </c>
+      <c r="F45" s="5"/>
+      <c r="G45" s="6">
+        <v>0</v>
+      </c>
+      <c r="H45" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A46" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D46" s="4">
+        <v>20000</v>
+      </c>
+      <c r="E46" s="4">
+        <v>20000</v>
+      </c>
+      <c r="F46" s="5"/>
+      <c r="G46" s="6">
+        <v>0</v>
+      </c>
+      <c r="H46" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A47" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D47" s="4">
+        <v>20000</v>
+      </c>
+      <c r="E47" s="4">
+        <v>20000</v>
+      </c>
+      <c r="F47" s="5"/>
+      <c r="G47" s="6">
+        <v>0</v>
+      </c>
+      <c r="H47" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A48" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D48" s="4">
+        <v>20000</v>
+      </c>
+      <c r="E48" s="4">
+        <v>20000</v>
+      </c>
+      <c r="F48" s="5"/>
+      <c r="G48" s="6">
+        <v>0</v>
+      </c>
+      <c r="H48" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A49" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D49" s="4">
+        <v>30000</v>
+      </c>
+      <c r="E49" s="4">
+        <v>30000</v>
+      </c>
+      <c r="F49" s="5"/>
+      <c r="G49" s="6">
+        <v>0</v>
+      </c>
+      <c r="H49" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A50" s="2">
+        <v>46271</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D50" s="4">
+        <v>6000</v>
+      </c>
+      <c r="E50" s="4">
+        <v>6000</v>
+      </c>
+      <c r="F50" s="5"/>
+      <c r="G50" s="6">
+        <v>0</v>
+      </c>
+      <c r="H50" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A51" s="2">
+        <v>46271</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D51" s="4">
+        <v>10000</v>
+      </c>
+      <c r="E51" s="4">
+        <v>10000</v>
+      </c>
+      <c r="F51" s="5"/>
+      <c r="G51" s="6">
+        <v>0</v>
+      </c>
+      <c r="H51" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A52" s="2">
+        <v>46271</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D52" s="4">
+        <v>20000</v>
+      </c>
+      <c r="E52" s="4">
+        <v>20000</v>
+      </c>
+      <c r="F52" s="5"/>
+      <c r="G52" s="6">
+        <v>0</v>
+      </c>
+      <c r="H52" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A53" s="2">
+        <v>46271</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D53" s="4">
+        <v>20000</v>
+      </c>
+      <c r="E53" s="4">
+        <v>20000</v>
+      </c>
+      <c r="F53" s="5"/>
+      <c r="G53" s="6">
+        <v>0</v>
+      </c>
+      <c r="H53" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A54" s="2">
+        <v>46271</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D54" s="4">
+        <v>20000</v>
+      </c>
+      <c r="E54" s="4">
+        <v>20000</v>
+      </c>
+      <c r="F54" s="5"/>
+      <c r="G54" s="6">
+        <v>0</v>
+      </c>
+      <c r="H54" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A55" s="2">
+        <v>46271</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D55" s="4">
+        <v>20000</v>
+      </c>
+      <c r="E55" s="4">
+        <v>20000</v>
+      </c>
+      <c r="F55" s="5"/>
+      <c r="G55" s="6">
+        <v>0</v>
+      </c>
+      <c r="H55" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A56" s="2">
+        <v>46271</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D56" s="4">
+        <v>20000</v>
+      </c>
+      <c r="E56" s="4">
+        <v>20000</v>
+      </c>
+      <c r="F56" s="5"/>
+      <c r="G56" s="6">
+        <v>0</v>
+      </c>
+      <c r="H56" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A57" s="2">
+        <v>46271</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D57" s="4">
+        <v>40000</v>
+      </c>
+      <c r="E57" s="4">
+        <v>40000</v>
+      </c>
+      <c r="F57" s="5"/>
+      <c r="G57" s="6">
+        <v>0</v>
+      </c>
+      <c r="H57" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A58" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D58" s="4">
+        <v>1000</v>
+      </c>
+      <c r="E58" s="4">
+        <v>1000</v>
+      </c>
+      <c r="F58" s="5"/>
+      <c r="G58" s="6">
+        <v>0</v>
+      </c>
+      <c r="H58" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A59" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D59" s="4">
+        <v>2000</v>
+      </c>
+      <c r="E59" s="4">
+        <v>2000</v>
+      </c>
+      <c r="F59" s="5"/>
+      <c r="G59" s="6">
+        <v>0</v>
+      </c>
+      <c r="H59" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A60" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D60" s="4">
+        <v>8000</v>
+      </c>
+      <c r="E60" s="4">
+        <v>8000</v>
+      </c>
+      <c r="F60" s="5"/>
+      <c r="G60" s="6">
+        <v>0</v>
+      </c>
+      <c r="H60" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A61" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D61" s="4">
+        <v>11000</v>
+      </c>
+      <c r="E61" s="4">
+        <v>11000</v>
+      </c>
+      <c r="F61" s="5"/>
+      <c r="G61" s="6">
+        <v>0</v>
+      </c>
+      <c r="H61" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A62" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D62" s="4">
+        <v>16000</v>
+      </c>
+      <c r="E62" s="4">
+        <v>16000</v>
+      </c>
+      <c r="F62" s="5"/>
+      <c r="G62" s="6">
+        <v>0</v>
+      </c>
+      <c r="H62" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A63" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D63" s="4">
+        <v>20000</v>
+      </c>
+      <c r="E63" s="4">
+        <v>20000</v>
+      </c>
+      <c r="F63" s="5"/>
+      <c r="G63" s="6">
+        <v>0</v>
+      </c>
+      <c r="H63" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A64" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D64" s="4">
+        <v>20000</v>
+      </c>
+      <c r="E64" s="4">
+        <v>20000</v>
+      </c>
+      <c r="F64" s="5"/>
+      <c r="G64" s="6">
+        <v>0</v>
+      </c>
+      <c r="H64" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A65" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D65" s="4">
+        <v>24000</v>
+      </c>
+      <c r="E65" s="4">
+        <v>24000</v>
+      </c>
+      <c r="F65" s="5"/>
+      <c r="G65" s="6">
+        <v>0</v>
+      </c>
+      <c r="H65" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A66" s="2">
+        <v>46272</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D66" s="4">
+        <v>40000</v>
+      </c>
+      <c r="E66" s="4">
+        <v>40000</v>
+      </c>
+      <c r="F66" s="5"/>
+      <c r="G66" s="6">
+        <v>0</v>
+      </c>
+      <c r="H66" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A67" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D67" s="4">
+        <v>10000</v>
+      </c>
+      <c r="E67" s="4">
+        <v>10000</v>
+      </c>
+      <c r="F67" s="5"/>
+      <c r="G67" s="6">
+        <v>0</v>
+      </c>
+      <c r="H67" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A68" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D68" s="4">
+        <v>3000</v>
+      </c>
+      <c r="E68" s="4">
+        <v>3000</v>
+      </c>
+      <c r="F68" s="5"/>
+      <c r="G68" s="6">
+        <v>0</v>
+      </c>
+      <c r="H68" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A69" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D69" s="4">
+        <v>10000</v>
+      </c>
+      <c r="E69" s="4">
+        <v>10000</v>
+      </c>
+      <c r="F69" s="5"/>
+      <c r="G69" s="6">
+        <v>0</v>
+      </c>
+      <c r="H69" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A70" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D70" s="4">
+        <v>16000</v>
+      </c>
+      <c r="E70" s="4">
+        <v>16000</v>
+      </c>
+      <c r="F70" s="5"/>
+      <c r="G70" s="6">
+        <v>0</v>
+      </c>
+      <c r="H70" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A71" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D71" s="4">
+        <v>20000</v>
+      </c>
+      <c r="E71" s="4">
+        <v>20000</v>
+      </c>
+      <c r="F71" s="5"/>
+      <c r="G71" s="6">
+        <v>0</v>
+      </c>
+      <c r="H71" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A72" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D72" s="4">
+        <v>10000</v>
+      </c>
+      <c r="E72" s="4">
+        <v>10000</v>
+      </c>
+      <c r="F72" s="5"/>
+      <c r="G72" s="6">
+        <v>0</v>
+      </c>
+      <c r="H72" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A73" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D73" s="4">
+        <v>40000</v>
+      </c>
+      <c r="E73" s="4">
+        <v>40000</v>
+      </c>
+      <c r="F73" s="5"/>
+      <c r="G73" s="6">
+        <v>0</v>
+      </c>
+      <c r="H73" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A74" s="2">
+        <v>46273</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D74" s="4">
+        <v>48000</v>
+      </c>
+      <c r="E74" s="4">
+        <v>48000</v>
+      </c>
+      <c r="F74" s="5"/>
+      <c r="G74" s="6">
+        <v>0</v>
+      </c>
+      <c r="H74" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A75" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D75" s="4">
+        <v>10000</v>
+      </c>
+      <c r="E75" s="4">
+        <v>10000</v>
+      </c>
+      <c r="F75" s="5"/>
+      <c r="G75" s="6">
+        <v>0</v>
+      </c>
+      <c r="H75" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A76" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D76" s="4">
+        <v>10000</v>
+      </c>
+      <c r="E76" s="4">
+        <v>10000</v>
+      </c>
+      <c r="F76" s="5"/>
+      <c r="G76" s="6">
+        <v>0</v>
+      </c>
+      <c r="H76" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A77" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D77" s="4">
+        <v>16000</v>
+      </c>
+      <c r="E77" s="4">
+        <v>16000</v>
+      </c>
+      <c r="F77" s="5"/>
+      <c r="G77" s="6">
+        <v>0</v>
+      </c>
+      <c r="H77" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A78" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D78" s="4">
+        <v>20000</v>
+      </c>
+      <c r="E78" s="4">
+        <v>20000</v>
+      </c>
+      <c r="F78" s="5"/>
+      <c r="G78" s="6">
+        <v>0</v>
+      </c>
+      <c r="H78" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A79" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D79" s="4">
+        <v>20000</v>
+      </c>
+      <c r="E79" s="4">
+        <v>20000</v>
+      </c>
+      <c r="F79" s="5"/>
+      <c r="G79" s="6">
+        <v>0</v>
+      </c>
+      <c r="H79" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A80" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D80" s="4">
+        <v>24000</v>
+      </c>
+      <c r="E80" s="4">
+        <v>24000</v>
+      </c>
+      <c r="F80" s="5"/>
+      <c r="G80" s="6">
+        <v>0</v>
+      </c>
+      <c r="H80" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A81" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D81" s="4">
+        <v>24000</v>
+      </c>
+      <c r="E81" s="4">
+        <v>24000</v>
+      </c>
+      <c r="F81" s="5"/>
+      <c r="G81" s="6">
+        <v>0</v>
+      </c>
+      <c r="H81" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A82" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D82" s="4">
+        <v>40000</v>
+      </c>
+      <c r="E82" s="4">
+        <v>40000</v>
+      </c>
+      <c r="F82" s="5"/>
+      <c r="G82" s="6">
+        <v>0</v>
+      </c>
+      <c r="H82" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A83" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D83" s="4">
+        <v>10000</v>
+      </c>
+      <c r="E83" s="4">
+        <v>10000</v>
+      </c>
+      <c r="F83" s="5"/>
+      <c r="G83" s="6">
+        <v>0</v>
+      </c>
+      <c r="H83" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A84" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D84" s="4">
+        <v>10000</v>
+      </c>
+      <c r="E84" s="4">
+        <v>10000</v>
+      </c>
+      <c r="F84" s="5"/>
+      <c r="G84" s="6">
+        <v>0</v>
+      </c>
+      <c r="H84" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A85" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D85" s="4">
+        <v>20000</v>
+      </c>
+      <c r="E85" s="4">
+        <v>20000</v>
+      </c>
+      <c r="F85" s="5"/>
+      <c r="G85" s="6">
+        <v>0</v>
+      </c>
+      <c r="H85" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A86" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D86" s="4">
+        <v>24000</v>
+      </c>
+      <c r="E86" s="4">
+        <v>24000</v>
+      </c>
+      <c r="F86" s="5"/>
+      <c r="G86" s="6">
+        <v>0</v>
+      </c>
+      <c r="H86" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A87" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D87" s="4">
+        <v>18000</v>
+      </c>
+      <c r="E87" s="4">
+        <v>18000</v>
+      </c>
+      <c r="F87" s="5"/>
+      <c r="G87" s="6">
+        <v>0</v>
+      </c>
+      <c r="H87" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A88" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D88" s="4">
+        <v>40000</v>
+      </c>
+      <c r="E88" s="4">
+        <v>40000</v>
+      </c>
+      <c r="F88" s="5"/>
+      <c r="G88" s="6">
+        <v>0</v>
+      </c>
+      <c r="H88" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A89" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D89" s="4">
+        <v>40000</v>
+      </c>
+      <c r="E89" s="4">
+        <v>40000</v>
+      </c>
+      <c r="F89" s="5"/>
+      <c r="G89" s="6">
+        <v>0</v>
+      </c>
+      <c r="H89" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A90" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D90" s="4">
+        <v>8000</v>
+      </c>
+      <c r="E90" s="4">
+        <v>8000</v>
+      </c>
+      <c r="F90" s="5"/>
+      <c r="G90" s="6">
+        <v>0</v>
+      </c>
+      <c r="H90" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A91" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D91" s="4">
+        <v>8000</v>
+      </c>
+      <c r="E91" s="4">
+        <v>8000</v>
+      </c>
+      <c r="F91" s="5"/>
+      <c r="G91" s="6">
+        <v>0</v>
+      </c>
+      <c r="H91" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A92" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D92" s="4">
+        <v>10000</v>
+      </c>
+      <c r="E92" s="4">
+        <v>10000</v>
+      </c>
+      <c r="F92" s="5"/>
+      <c r="G92" s="6">
+        <v>0</v>
+      </c>
+      <c r="H92" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A93" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D93" s="4">
+        <v>20000</v>
+      </c>
+      <c r="E93" s="4">
+        <v>20000</v>
+      </c>
+      <c r="F93" s="5"/>
+      <c r="G93" s="6">
+        <v>0</v>
+      </c>
+      <c r="H93" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A94" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D94" s="4">
+        <v>20000</v>
+      </c>
+      <c r="E94" s="4">
+        <v>20000</v>
+      </c>
+      <c r="F94" s="5"/>
+      <c r="G94" s="6">
+        <v>0</v>
+      </c>
+      <c r="H94" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A95" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D95" s="4">
+        <v>40000</v>
+      </c>
+      <c r="E95" s="4">
+        <v>40000</v>
+      </c>
+      <c r="F95" s="5"/>
+      <c r="G95" s="6">
+        <v>0</v>
+      </c>
+      <c r="H95" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A96" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D96" s="4">
+        <v>40000</v>
+      </c>
+      <c r="E96" s="4">
+        <v>40000</v>
+      </c>
+      <c r="F96" s="5"/>
+      <c r="G96" s="6">
+        <v>0</v>
+      </c>
+      <c r="H96" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A97" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D97" s="4">
+        <v>28000</v>
+      </c>
+      <c r="E97" s="4">
+        <v>28000</v>
+      </c>
+      <c r="F97" s="5"/>
+      <c r="G97" s="6">
+        <v>0</v>
+      </c>
+      <c r="H97" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A98" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D98" s="4">
+        <v>12000</v>
+      </c>
+      <c r="E98" s="4">
+        <v>12000</v>
+      </c>
+      <c r="F98" s="5"/>
+      <c r="G98" s="6">
+        <v>0</v>
+      </c>
+      <c r="H98" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A99" s="2">
+        <v>46292</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D99" s="4">
+        <v>25000</v>
+      </c>
+      <c r="E99" s="4">
+        <v>25000</v>
+      </c>
+      <c r="F99" s="5"/>
+      <c r="G99" s="6">
+        <v>0</v>
+      </c>
+      <c r="H99" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A100" s="2">
+        <v>46292</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D100" s="4">
+        <v>25000</v>
+      </c>
+      <c r="E100" s="4">
+        <v>25000</v>
+      </c>
+      <c r="F100" s="5"/>
+      <c r="G100" s="6">
+        <v>0</v>
+      </c>
+      <c r="H100" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A101" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D101" s="4">
+        <v>15000</v>
+      </c>
+      <c r="E101" s="4">
+        <v>15000</v>
+      </c>
+      <c r="F101" s="5"/>
+      <c r="G101" s="6">
+        <v>0</v>
+      </c>
+      <c r="H101" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A102" s="2">
+        <v>46269</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D102" s="4">
+        <v>10000</v>
+      </c>
+      <c r="E102" s="4">
+        <v>10000</v>
+      </c>
+      <c r="F102" s="5"/>
+      <c r="G102" s="6">
+        <v>0</v>
+      </c>
+      <c r="H102" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A103" s="2">
+        <v>46270</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D103" s="4">
+        <v>12000</v>
+      </c>
+      <c r="E103" s="4">
+        <v>12000</v>
+      </c>
+      <c r="F103" s="5"/>
+      <c r="G103" s="6">
+        <v>0</v>
+      </c>
+      <c r="H103" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A104" s="2">
+        <v>46267</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D104" s="4">
+        <v>28000</v>
+      </c>
+      <c r="E104" s="4">
+        <v>28000</v>
+      </c>
+      <c r="F104" s="5"/>
+      <c r="G104" s="6">
+        <v>0</v>
+      </c>
+      <c r="H104" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/data/Plan.xlsx
+++ b/data/Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raman/Documents/GitHub/production-board/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F815F554-1D8A-6940-A2B5-C19077A1C5E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{815C59EC-68F3-8544-B2DA-E685F2918E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16560" xr2:uid="{7C08584A-5D47-2049-B143-911B93E5D6E0}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$104</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -3184,7 +3184,7 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>127</v>
@@ -3375,6 +3375,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H104" xr:uid="{5C578346-EE80-DF41-8099-4E3028D96EBE}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/Plan.xlsx
+++ b/data/Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raman/Documents/GitHub/production-board/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{815C59EC-68F3-8544-B2DA-E685F2918E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07FC677B-2B4E-FD48-AC2E-D99E4D537386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16560" xr2:uid="{7C08584A-5D47-2049-B143-911B93E5D6E0}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="149">
   <si>
     <t>Date</t>
   </si>
@@ -477,6 +477,18 @@
   </si>
   <si>
     <t>Outsource</t>
+  </si>
+  <si>
+    <t>CO539</t>
+  </si>
+  <si>
+    <t>CO538</t>
+  </si>
+  <si>
+    <t>4 step hairfall control Kit</t>
+  </si>
+  <si>
+    <t>Rosemary Hair growth and repair kit pack of 5</t>
   </si>
 </sst>
 </file>
@@ -531,7 +543,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -539,6 +551,7 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -873,7 +886,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C578346-EE80-DF41-8099-4E3028D96EBE}">
-  <dimension ref="A1:H104"/>
+  <dimension ref="A1:H106"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="57.1640625" customWidth="1"/>
@@ -3374,6 +3387,52 @@
         <v>144</v>
       </c>
     </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A105" s="7">
+        <v>46272</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D105" s="4">
+        <v>10000</v>
+      </c>
+      <c r="E105" s="4">
+        <v>10000</v>
+      </c>
+      <c r="G105" s="6">
+        <v>0</v>
+      </c>
+      <c r="H105" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A106" s="7">
+        <v>46272</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D106" s="4">
+        <v>10000</v>
+      </c>
+      <c r="E106" s="4">
+        <v>10000</v>
+      </c>
+      <c r="G106" s="6">
+        <v>0</v>
+      </c>
+      <c r="H106" t="s">
+        <v>144</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H104" xr:uid="{5C578346-EE80-DF41-8099-4E3028D96EBE}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Plan.xlsx
+++ b/data/Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raman/Documents/GitHub/production-board/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07FC677B-2B4E-FD48-AC2E-D99E4D537386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E0960FF-2CCD-CC40-B392-DF8454BF1BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16560" xr2:uid="{7C08584A-5D47-2049-B143-911B93E5D6E0}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="139">
   <si>
     <t>Date</t>
   </si>
@@ -77,30 +77,12 @@
     <t>Acne Control Body Wash (236 ml)</t>
   </si>
   <si>
-    <t>CAP70</t>
-  </si>
-  <si>
-    <t>Underarm Roll On - 40 ml / White jasmine (Rectangular Monocarton)-399</t>
-  </si>
-  <si>
     <t>CAP82</t>
   </si>
   <si>
     <t>Oil &amp; Acne Control Face Wash</t>
   </si>
   <si>
-    <t>USTTCAP126</t>
-  </si>
-  <si>
-    <t>Chemist at Play Underarm Roll On Aqua 75ml (CAP126) USTT</t>
-  </si>
-  <si>
-    <t>CAP106</t>
-  </si>
-  <si>
-    <t>Brightening Face Serum(10% VitaminC)30ml</t>
-  </si>
-  <si>
     <t>USTTBA93</t>
   </si>
   <si>
@@ -113,18 +95,6 @@
     <t>BA Expert | Anti Hairfall Shampoo 250 ml</t>
   </si>
   <si>
-    <t>BA55</t>
-  </si>
-  <si>
-    <t>Rosemary and Coconut Milk Hydrating Conditioner</t>
-  </si>
-  <si>
-    <t>BA104</t>
-  </si>
-  <si>
-    <t>Anti-Dandruff Conditioner 100 gm</t>
-  </si>
-  <si>
     <t>SS43</t>
   </si>
   <si>
@@ -425,12 +395,6 @@
     <t>Combo- Anti-Dandruff Shampoo (100ml) + Anti-Dandruff Conditioner (100g)</t>
   </si>
   <si>
-    <t>CAP139</t>
-  </si>
-  <si>
-    <t>Cherry Lip Balm 4.5gm</t>
-  </si>
-  <si>
     <t>CAP138</t>
   </si>
   <si>
@@ -489,6 +453,12 @@
   </si>
   <si>
     <t>Rosemary Hair growth and repair kit pack of 5</t>
+  </si>
+  <si>
+    <t>CO357</t>
+  </si>
+  <si>
+    <t>Combo- Anti-Hairfall Shampoo (100ml) + Anti-Hairfall Conditioner (100g)</t>
   </si>
 </sst>
 </file>
@@ -523,12 +493,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -543,7 +519,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -551,7 +527,11 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="16" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -886,7 +866,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C578346-EE80-DF41-8099-4E3028D96EBE}">
-  <dimension ref="A1:H106"/>
+  <dimension ref="A1:H98"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="57.1640625" customWidth="1"/>
@@ -917,362 +897,358 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>7</v>
+        <v>117</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>8</v>
+        <v>118</v>
       </c>
       <c r="D2" s="4">
-        <v>3200</v>
+        <v>12000</v>
       </c>
       <c r="E2" s="4">
-        <v>3200</v>
+        <v>12000</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="6">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <v>46267</v>
+        <v>46292</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>9</v>
+        <v>119</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="D3" s="4">
-        <v>4000</v>
+        <v>25000</v>
       </c>
       <c r="E3" s="4">
-        <v>4000</v>
+        <v>25000</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="6">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>46267</v>
+        <v>46292</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>11</v>
+        <v>121</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>12</v>
+        <v>122</v>
       </c>
       <c r="D4" s="4">
-        <v>5000</v>
+        <v>25000</v>
       </c>
       <c r="E4" s="4">
-        <v>5000</v>
+        <v>25000</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="6">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>46267</v>
+        <v>46275</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>13</v>
+        <v>123</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="D5" s="4">
-        <v>5000</v>
+        <v>15000</v>
       </c>
       <c r="E5" s="4">
-        <v>5000</v>
+        <v>15000</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="6">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>15</v>
+        <v>125</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>16</v>
+        <v>126</v>
       </c>
       <c r="D6" s="4">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="E6" s="4">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>46267</v>
+        <v>46270</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>18</v>
+        <v>128</v>
       </c>
       <c r="D7" s="4">
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="E7" s="4">
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="6">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>19</v>
+        <v>129</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="D8" s="4">
-        <v>6390</v>
+        <v>28000</v>
       </c>
       <c r="E8" s="4">
-        <v>6000</v>
+        <v>28000</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="6">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="2">
-        <v>46267</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="4">
-        <v>10000</v>
-      </c>
-      <c r="E9" s="4">
-        <v>10000</v>
-      </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="6">
-        <v>0</v>
-      </c>
-      <c r="H9" t="s">
-        <v>143</v>
+      <c r="A9" s="11">
+        <v>46272</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D9" s="8">
+        <v>10000</v>
+      </c>
+      <c r="E9" s="8">
+        <v>10000</v>
+      </c>
+      <c r="F9" s="10"/>
+      <c r="G9" s="9">
+        <v>0</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="2">
-        <v>46267</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="4">
-        <v>13000</v>
-      </c>
-      <c r="E10" s="4">
-        <v>13000</v>
-      </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="6">
-        <v>0</v>
-      </c>
-      <c r="H10" t="s">
-        <v>143</v>
+      <c r="A10" s="11">
+        <v>46272</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D10" s="8">
+        <v>10000</v>
+      </c>
+      <c r="E10" s="8">
+        <v>10000</v>
+      </c>
+      <c r="F10" s="10"/>
+      <c r="G10" s="9">
+        <v>0</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D11" s="4">
-        <v>20000</v>
+        <v>1600</v>
       </c>
       <c r="E11" s="4">
-        <v>20000</v>
+        <v>1600</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="6">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="D12" s="4">
-        <v>20000</v>
+        <v>4700</v>
       </c>
       <c r="E12" s="4">
-        <v>20000</v>
+        <v>4700</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="6">
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D13" s="4">
-        <v>20000</v>
+        <v>4000</v>
       </c>
       <c r="E13" s="4">
-        <v>20000</v>
+        <v>4000</v>
       </c>
       <c r="F13" s="5"/>
-      <c r="G13" s="6">
-        <v>0</v>
-      </c>
+      <c r="G13" s="5"/>
       <c r="H13" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="D14" s="4">
-        <v>21000</v>
+        <v>8000</v>
       </c>
       <c r="E14" s="4">
-        <v>21000</v>
+        <v>8000</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="6">
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D15" s="4">
-        <v>34160</v>
+        <v>8708</v>
       </c>
       <c r="E15" s="4">
-        <v>34160</v>
+        <v>8708</v>
       </c>
       <c r="F15" s="5"/>
-      <c r="G15" s="6">
-        <v>0</v>
-      </c>
+      <c r="G15" s="5"/>
       <c r="H15" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D16" s="4">
-        <v>40000</v>
+        <v>10000</v>
       </c>
       <c r="E16" s="4">
-        <v>40000</v>
+        <v>10000</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="6">
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
@@ -1280,23 +1256,23 @@
         <v>46268</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D17" s="4">
-        <v>1600</v>
+        <v>20000</v>
       </c>
       <c r="E17" s="4">
-        <v>1600</v>
+        <v>20000</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="6">
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -1304,23 +1280,23 @@
         <v>46268</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D18" s="4">
-        <v>5000</v>
+        <v>20000</v>
       </c>
       <c r="E18" s="4">
-        <v>5000</v>
+        <v>20000</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="6">
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -1328,23 +1304,23 @@
         <v>46268</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D19" s="4">
-        <v>4700</v>
+        <v>28000</v>
       </c>
       <c r="E19" s="4">
-        <v>4700</v>
+        <v>28000</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="6">
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
@@ -1358,17 +1334,17 @@
         <v>42</v>
       </c>
       <c r="D20" s="4">
-        <v>10000</v>
+        <v>30000</v>
       </c>
       <c r="E20" s="4">
-        <v>10000</v>
+        <v>30000</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="6">
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
@@ -1376,23 +1352,23 @@
         <v>46268</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="D21" s="4">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="E21" s="4">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="6">
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
@@ -1400,76 +1376,76 @@
         <v>46268</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D22" s="4">
-        <v>11000</v>
+        <v>47328</v>
       </c>
       <c r="E22" s="4">
-        <v>11000</v>
+        <v>47328</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="6">
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D23" s="4">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="E23" s="4">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="6">
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="D24" s="4">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="E24" s="4">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="6">
         <v>0</v>
       </c>
       <c r="H24" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>49</v>
@@ -1478,22 +1454,22 @@
         <v>50</v>
       </c>
       <c r="D25" s="4">
-        <v>28000</v>
+        <v>5000</v>
       </c>
       <c r="E25" s="4">
-        <v>28000</v>
+        <v>5000</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="6">
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>51</v>
@@ -1502,22 +1478,22 @@
         <v>52</v>
       </c>
       <c r="D26" s="4">
-        <v>30000</v>
+        <v>6500</v>
       </c>
       <c r="E26" s="4">
-        <v>30000</v>
+        <v>6500</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="6">
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>53</v>
@@ -1526,22 +1502,22 @@
         <v>54</v>
       </c>
       <c r="D27" s="4">
-        <v>40000</v>
+        <v>8000</v>
       </c>
       <c r="E27" s="4">
-        <v>40000</v>
+        <v>8000</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="6">
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>55</v>
@@ -1550,17 +1526,17 @@
         <v>56</v>
       </c>
       <c r="D28" s="4">
-        <v>47328</v>
+        <v>8000</v>
       </c>
       <c r="E28" s="4">
-        <v>47328</v>
+        <v>8000</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="6">
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
@@ -1574,17 +1550,17 @@
         <v>58</v>
       </c>
       <c r="D29" s="4">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="E29" s="4">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="6">
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
@@ -1598,17 +1574,17 @@
         <v>60</v>
       </c>
       <c r="D30" s="4">
-        <v>5000</v>
-      </c>
-      <c r="E30" s="4">
-        <v>5000</v>
+        <v>10000</v>
+      </c>
+      <c r="E30" s="3">
+        <v>0</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="6">
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
@@ -1616,23 +1592,23 @@
         <v>46269</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="D31" s="4">
-        <v>6500</v>
+        <v>11000</v>
       </c>
       <c r="E31" s="4">
-        <v>6500</v>
+        <v>11000</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="6">
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
@@ -1640,23 +1616,23 @@
         <v>46269</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D32" s="4">
-        <v>8000</v>
+        <v>20000</v>
       </c>
       <c r="E32" s="4">
-        <v>8000</v>
+        <v>20000</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="6">
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
@@ -1664,119 +1640,119 @@
         <v>46269</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="D33" s="4">
-        <v>8000</v>
+        <v>40000</v>
       </c>
       <c r="E33" s="4">
-        <v>8000</v>
+        <v>40000</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="6">
         <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D34" s="4">
-        <v>10000</v>
+        <v>1800</v>
       </c>
       <c r="E34" s="4">
-        <v>10000</v>
+        <v>1800</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="6">
         <v>0</v>
       </c>
       <c r="H34" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D35" s="4">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="E35" s="4">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="6">
         <v>0</v>
       </c>
       <c r="H35" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D36" s="4">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="E36" s="4">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="6">
         <v>0</v>
       </c>
       <c r="H36" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="D37" s="4">
-        <v>40000</v>
+        <v>5000</v>
       </c>
       <c r="E37" s="4">
-        <v>40000</v>
+        <v>5000</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="6">
         <v>0</v>
       </c>
       <c r="H37" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
@@ -1784,23 +1760,23 @@
         <v>46270</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D38" s="4">
-        <v>1800</v>
+        <v>10000</v>
       </c>
       <c r="E38" s="4">
-        <v>1800</v>
+        <v>10000</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="6">
         <v>0</v>
       </c>
       <c r="H38" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
@@ -1808,23 +1784,23 @@
         <v>46270</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D39" s="4">
-        <v>3000</v>
+        <v>7000</v>
       </c>
       <c r="E39" s="4">
-        <v>3000</v>
+        <v>7000</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="6">
         <v>0</v>
       </c>
       <c r="H39" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
@@ -1832,23 +1808,23 @@
         <v>46270</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D40" s="4">
-        <v>2000</v>
+        <v>15000</v>
       </c>
       <c r="E40" s="4">
-        <v>2000</v>
+        <v>15000</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="6">
         <v>0</v>
       </c>
       <c r="H40" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
@@ -1856,23 +1832,23 @@
         <v>46270</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="D41" s="4">
-        <v>5000</v>
+        <v>16000</v>
       </c>
       <c r="E41" s="4">
-        <v>5000</v>
+        <v>16000</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="6">
         <v>0</v>
       </c>
       <c r="H41" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
@@ -1880,23 +1856,23 @@
         <v>46270</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D42" s="4">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="E42" s="4">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="F42" s="5"/>
       <c r="G42" s="6">
         <v>0</v>
       </c>
       <c r="H42" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
@@ -1904,23 +1880,23 @@
         <v>46270</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="D43" s="4">
-        <v>7000</v>
+        <v>20000</v>
       </c>
       <c r="E43" s="4">
-        <v>7000</v>
+        <v>20000</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="6">
         <v>0</v>
       </c>
       <c r="H43" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
@@ -1928,23 +1904,23 @@
         <v>46270</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D44" s="4">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="E44" s="4">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="6">
         <v>0</v>
       </c>
       <c r="H44" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
@@ -1952,82 +1928,82 @@
         <v>46270</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="D45" s="4">
-        <v>16000</v>
+        <v>30000</v>
       </c>
       <c r="E45" s="4">
-        <v>16000</v>
+        <v>30000</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="6">
         <v>0</v>
       </c>
       <c r="H45" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D46" s="4">
-        <v>20000</v>
+        <v>6000</v>
       </c>
       <c r="E46" s="4">
-        <v>20000</v>
+        <v>6000</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="6">
         <v>0</v>
       </c>
       <c r="H46" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="D47" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E47" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="6">
         <v>0</v>
       </c>
       <c r="H47" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D48" s="4">
         <v>20000</v>
@@ -2040,31 +2016,31 @@
         <v>0</v>
       </c>
       <c r="H48" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="D49" s="4">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="E49" s="4">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="6">
         <v>0</v>
       </c>
       <c r="H49" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
@@ -2072,23 +2048,23 @@
         <v>46271</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>91</v>
+        <v>13</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>92</v>
+        <v>14</v>
       </c>
       <c r="D50" s="4">
-        <v>6000</v>
+        <v>20000</v>
       </c>
       <c r="E50" s="4">
-        <v>6000</v>
+        <v>20000</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="6">
         <v>0</v>
       </c>
       <c r="H50" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
@@ -2096,23 +2072,23 @@
         <v>46271</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="D51" s="4">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="E51" s="4">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="6">
         <v>0</v>
       </c>
       <c r="H51" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
@@ -2120,10 +2096,10 @@
         <v>46271</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>87</v>
+        <v>21</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="D52" s="4">
         <v>20000</v>
@@ -2136,7 +2112,7 @@
         <v>0</v>
       </c>
       <c r="H52" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
@@ -2144,119 +2120,119 @@
         <v>46271</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="D53" s="4">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="E53" s="4">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="6">
         <v>0</v>
       </c>
       <c r="H53" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="D54" s="4">
-        <v>20000</v>
+        <v>1000</v>
       </c>
       <c r="E54" s="4">
-        <v>20000</v>
+        <v>1000</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="6">
         <v>0</v>
       </c>
       <c r="H54" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D55" s="4">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="E55" s="4">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="6">
         <v>0</v>
       </c>
       <c r="H55" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="D56" s="4">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="E56" s="4">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="6">
         <v>0</v>
       </c>
       <c r="H56" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="D57" s="4">
-        <v>40000</v>
+        <v>11000</v>
       </c>
       <c r="E57" s="4">
-        <v>40000</v>
+        <v>11000</v>
       </c>
       <c r="F57" s="5"/>
       <c r="G57" s="6">
         <v>0</v>
       </c>
       <c r="H57" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
@@ -2264,23 +2240,23 @@
         <v>46272</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D58" s="4">
-        <v>1000</v>
+        <v>16000</v>
       </c>
       <c r="E58" s="4">
-        <v>1000</v>
+        <v>16000</v>
       </c>
       <c r="F58" s="5"/>
       <c r="G58" s="6">
         <v>0</v>
       </c>
       <c r="H58" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
@@ -2288,23 +2264,23 @@
         <v>46272</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="D59" s="4">
-        <v>2000</v>
+        <v>20000</v>
       </c>
       <c r="E59" s="4">
-        <v>2000</v>
+        <v>20000</v>
       </c>
       <c r="F59" s="5"/>
       <c r="G59" s="6">
         <v>0</v>
       </c>
       <c r="H59" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
@@ -2312,23 +2288,23 @@
         <v>46272</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>101</v>
+        <v>21</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>102</v>
+        <v>22</v>
       </c>
       <c r="D60" s="4">
-        <v>8000</v>
+        <v>20000</v>
       </c>
       <c r="E60" s="4">
-        <v>8000</v>
+        <v>20000</v>
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="6">
         <v>0</v>
       </c>
       <c r="H60" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
@@ -2336,23 +2312,23 @@
         <v>46272</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D61" s="4">
-        <v>11000</v>
+        <v>24000</v>
       </c>
       <c r="E61" s="4">
-        <v>11000</v>
+        <v>24000</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="6">
         <v>0</v>
       </c>
       <c r="H61" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
@@ -2360,119 +2336,119 @@
         <v>46272</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>106</v>
+        <v>44</v>
       </c>
       <c r="D62" s="4">
-        <v>16000</v>
+        <v>40000</v>
       </c>
       <c r="E62" s="4">
-        <v>16000</v>
+        <v>40000</v>
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="6">
         <v>0</v>
       </c>
       <c r="H62" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="D63" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E63" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F63" s="5"/>
       <c r="G63" s="6">
         <v>0</v>
       </c>
       <c r="H63" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>31</v>
+        <v>99</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="D64" s="4">
-        <v>20000</v>
+        <v>3000</v>
       </c>
       <c r="E64" s="4">
-        <v>20000</v>
+        <v>3000</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="6">
         <v>0</v>
       </c>
       <c r="H64" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>108</v>
+        <v>20</v>
       </c>
       <c r="D65" s="4">
-        <v>24000</v>
+        <v>10000</v>
       </c>
       <c r="E65" s="4">
-        <v>24000</v>
+        <v>10000</v>
       </c>
       <c r="F65" s="5"/>
       <c r="G65" s="6">
         <v>0</v>
       </c>
       <c r="H65" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D66" s="4">
-        <v>40000</v>
+        <v>16000</v>
       </c>
       <c r="E66" s="4">
-        <v>40000</v>
+        <v>16000</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="6">
         <v>0</v>
       </c>
       <c r="H66" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
@@ -2480,23 +2456,23 @@
         <v>46273</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>87</v>
+        <v>11</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>88</v>
+        <v>12</v>
       </c>
       <c r="D67" s="4">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="E67" s="4">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="6">
         <v>0</v>
       </c>
       <c r="H67" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
@@ -2504,23 +2480,23 @@
         <v>46273</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D68" s="4">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="E68" s="4">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="6">
         <v>0</v>
       </c>
       <c r="H68" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
@@ -2528,23 +2504,23 @@
         <v>46273</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D69" s="4">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="E69" s="4">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="6">
         <v>0</v>
       </c>
       <c r="H69" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
@@ -2552,58 +2528,58 @@
         <v>46273</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="D70" s="4">
-        <v>16000</v>
+        <v>48000</v>
       </c>
       <c r="E70" s="4">
-        <v>16000</v>
+        <v>48000</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" s="6">
         <v>0</v>
       </c>
       <c r="H70" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>13</v>
+        <v>101</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D71" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E71" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F71" s="5"/>
       <c r="G71" s="6">
         <v>0</v>
       </c>
       <c r="H71" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>111</v>
+        <v>59</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="D72" s="4">
         <v>10000</v>
@@ -2616,55 +2592,55 @@
         <v>0</v>
       </c>
       <c r="H72" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="D73" s="4">
-        <v>40000</v>
+        <v>16000</v>
       </c>
       <c r="E73" s="4">
-        <v>40000</v>
+        <v>16000</v>
       </c>
       <c r="F73" s="5"/>
       <c r="G73" s="6">
         <v>0</v>
       </c>
       <c r="H73" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>114</v>
+        <v>12</v>
       </c>
       <c r="D74" s="4">
-        <v>48000</v>
+        <v>20000</v>
       </c>
       <c r="E74" s="4">
-        <v>48000</v>
+        <v>20000</v>
       </c>
       <c r="F74" s="5"/>
       <c r="G74" s="6">
         <v>0</v>
       </c>
       <c r="H74" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
@@ -2672,23 +2648,23 @@
         <v>46274</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>111</v>
+        <v>23</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>112</v>
+        <v>24</v>
       </c>
       <c r="D75" s="4">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="E75" s="4">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="F75" s="5"/>
       <c r="G75" s="6">
         <v>0</v>
       </c>
       <c r="H75" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
@@ -2696,23 +2672,23 @@
         <v>46274</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="D76" s="4">
-        <v>10000</v>
+        <v>24000</v>
       </c>
       <c r="E76" s="4">
-        <v>10000</v>
+        <v>24000</v>
       </c>
       <c r="F76" s="5"/>
       <c r="G76" s="6">
         <v>0</v>
       </c>
       <c r="H76" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
@@ -2720,23 +2696,23 @@
         <v>46274</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="D77" s="4">
-        <v>16000</v>
+        <v>24000</v>
       </c>
       <c r="E77" s="4">
-        <v>16000</v>
+        <v>24000</v>
       </c>
       <c r="F77" s="5"/>
       <c r="G77" s="6">
         <v>0</v>
       </c>
       <c r="H77" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
@@ -2744,119 +2720,119 @@
         <v>46274</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D78" s="4">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="E78" s="4">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="F78" s="5"/>
       <c r="G78" s="6">
         <v>0</v>
       </c>
       <c r="H78" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>34</v>
+        <v>78</v>
       </c>
       <c r="D79" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E79" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F79" s="5"/>
       <c r="G79" s="6">
         <v>0</v>
       </c>
       <c r="H79" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>113</v>
+        <v>59</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>114</v>
+        <v>60</v>
       </c>
       <c r="D80" s="4">
-        <v>24000</v>
+        <v>10000</v>
       </c>
       <c r="E80" s="4">
-        <v>24000</v>
+        <v>10000</v>
       </c>
       <c r="F80" s="5"/>
       <c r="G80" s="6">
         <v>0</v>
       </c>
       <c r="H80" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>117</v>
+        <v>37</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>118</v>
+        <v>38</v>
       </c>
       <c r="D81" s="4">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="E81" s="4">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="F81" s="5"/>
       <c r="G81" s="6">
         <v>0</v>
       </c>
       <c r="H81" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>35</v>
+        <v>109</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="D82" s="4">
-        <v>40000</v>
+        <v>24000</v>
       </c>
       <c r="E82" s="4">
-        <v>40000</v>
+        <v>24000</v>
       </c>
       <c r="F82" s="5"/>
       <c r="G82" s="6">
         <v>0</v>
       </c>
       <c r="H82" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
@@ -2864,23 +2840,23 @@
         <v>46275</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="D83" s="4">
-        <v>10000</v>
+        <v>18000</v>
       </c>
       <c r="E83" s="4">
-        <v>10000</v>
+        <v>18000</v>
       </c>
       <c r="F83" s="5"/>
       <c r="G83" s="6">
         <v>0</v>
       </c>
       <c r="H83" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
@@ -2888,23 +2864,23 @@
         <v>46275</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="D84" s="4">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="E84" s="4">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="F84" s="5"/>
       <c r="G84" s="6">
         <v>0</v>
       </c>
       <c r="H84" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
@@ -2912,119 +2888,119 @@
         <v>46275</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="D85" s="4">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="E85" s="4">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="F85" s="5"/>
       <c r="G85" s="6">
         <v>0</v>
       </c>
       <c r="H85" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D86" s="4">
-        <v>24000</v>
+        <v>8000</v>
       </c>
       <c r="E86" s="4">
-        <v>24000</v>
+        <v>8000</v>
       </c>
       <c r="F86" s="5"/>
       <c r="G86" s="6">
         <v>0</v>
       </c>
       <c r="H86" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>121</v>
+        <v>9</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>122</v>
+        <v>10</v>
       </c>
       <c r="D87" s="4">
-        <v>18000</v>
+        <v>8000</v>
       </c>
       <c r="E87" s="4">
-        <v>18000</v>
+        <v>8000</v>
       </c>
       <c r="F87" s="5"/>
       <c r="G87" s="6">
         <v>0</v>
       </c>
       <c r="H87" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>35</v>
+        <v>115</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>36</v>
+        <v>116</v>
       </c>
       <c r="D88" s="4">
-        <v>40000</v>
+        <v>10000</v>
       </c>
       <c r="E88" s="4">
-        <v>40000</v>
+        <v>10000</v>
       </c>
       <c r="F88" s="5"/>
       <c r="G88" s="6">
         <v>0</v>
       </c>
       <c r="H88" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>34</v>
+        <v>78</v>
       </c>
       <c r="D89" s="4">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="E89" s="4">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="F89" s="5"/>
       <c r="G89" s="6">
         <v>0</v>
       </c>
       <c r="H89" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
@@ -3032,23 +3008,23 @@
         <v>46276</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>124</v>
+        <v>80</v>
       </c>
       <c r="D90" s="4">
-        <v>8000</v>
+        <v>20000</v>
       </c>
       <c r="E90" s="4">
-        <v>8000</v>
+        <v>20000</v>
       </c>
       <c r="F90" s="5"/>
       <c r="G90" s="6">
         <v>0</v>
       </c>
       <c r="H90" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
@@ -3056,23 +3032,23 @@
         <v>46276</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D91" s="4">
-        <v>8000</v>
+        <v>40000</v>
       </c>
       <c r="E91" s="4">
-        <v>8000</v>
+        <v>40000</v>
       </c>
       <c r="F91" s="5"/>
       <c r="G91" s="6">
         <v>0</v>
       </c>
       <c r="H91" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
@@ -3080,361 +3056,171 @@
         <v>46276</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>125</v>
+        <v>43</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>126</v>
+        <v>44</v>
       </c>
       <c r="D92" s="4">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="E92" s="4">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="F92" s="5"/>
       <c r="G92" s="6">
         <v>0</v>
       </c>
       <c r="H92" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="D93" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E93" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F93" s="5"/>
       <c r="G93" s="6">
         <v>0</v>
       </c>
       <c r="H93" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>89</v>
+        <v>137</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="D94" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E94" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F94" s="5"/>
       <c r="G94" s="6">
         <v>0</v>
       </c>
       <c r="H94" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D95" s="4">
-        <v>40000</v>
+        <v>18000</v>
       </c>
       <c r="E95" s="4">
-        <v>40000</v>
+        <v>18000</v>
       </c>
       <c r="F95" s="5"/>
       <c r="G95" s="6">
         <v>0</v>
       </c>
       <c r="H95" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="D96" s="4">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="E96" s="4">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="F96" s="5"/>
       <c r="G96" s="6">
         <v>0</v>
       </c>
       <c r="H96" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
-        <v>46267</v>
+        <v>46277</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>127</v>
+        <v>23</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>128</v>
+        <v>24</v>
       </c>
       <c r="D97" s="4">
-        <v>28000</v>
+        <v>30000</v>
       </c>
       <c r="E97" s="4">
-        <v>28000</v>
+        <v>30000</v>
       </c>
       <c r="F97" s="5"/>
       <c r="G97" s="6">
         <v>0</v>
       </c>
       <c r="H97" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
-        <v>46269</v>
+        <v>46277</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>129</v>
+        <v>43</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>130</v>
+        <v>44</v>
       </c>
       <c r="D98" s="4">
-        <v>12000</v>
+        <v>40000</v>
       </c>
       <c r="E98" s="4">
-        <v>12000</v>
+        <v>40000</v>
       </c>
       <c r="F98" s="5"/>
       <c r="G98" s="6">
         <v>0</v>
       </c>
       <c r="H98" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A99" s="2">
-        <v>46292</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D99" s="4">
-        <v>25000</v>
-      </c>
-      <c r="E99" s="4">
-        <v>25000</v>
-      </c>
-      <c r="F99" s="5"/>
-      <c r="G99" s="6">
-        <v>0</v>
-      </c>
-      <c r="H99" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A100" s="2">
-        <v>46292</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="D100" s="4">
-        <v>25000</v>
-      </c>
-      <c r="E100" s="4">
-        <v>25000</v>
-      </c>
-      <c r="F100" s="5"/>
-      <c r="G100" s="6">
-        <v>0</v>
-      </c>
-      <c r="H100" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A101" s="2">
-        <v>46275</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="D101" s="4">
-        <v>15000</v>
-      </c>
-      <c r="E101" s="4">
-        <v>15000</v>
-      </c>
-      <c r="F101" s="5"/>
-      <c r="G101" s="6">
-        <v>0</v>
-      </c>
-      <c r="H101" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A102" s="2">
-        <v>46269</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D102" s="4">
-        <v>10000</v>
-      </c>
-      <c r="E102" s="4">
-        <v>10000</v>
-      </c>
-      <c r="F102" s="5"/>
-      <c r="G102" s="6">
-        <v>0</v>
-      </c>
-      <c r="H102" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A103" s="2">
-        <v>46270</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D103" s="4">
-        <v>12000</v>
-      </c>
-      <c r="E103" s="4">
-        <v>12000</v>
-      </c>
-      <c r="F103" s="5"/>
-      <c r="G103" s="6">
-        <v>0</v>
-      </c>
-      <c r="H103" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A104" s="2">
-        <v>46267</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="D104" s="4">
-        <v>28000</v>
-      </c>
-      <c r="E104" s="4">
-        <v>28000</v>
-      </c>
-      <c r="F104" s="5"/>
-      <c r="G104" s="6">
-        <v>0</v>
-      </c>
-      <c r="H104" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A105" s="7">
-        <v>46272</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D105" s="4">
-        <v>10000</v>
-      </c>
-      <c r="E105" s="4">
-        <v>10000</v>
-      </c>
-      <c r="G105" s="6">
-        <v>0</v>
-      </c>
-      <c r="H105" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A106" s="7">
-        <v>46272</v>
-      </c>
-      <c r="B106" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D106" s="4">
-        <v>10000</v>
-      </c>
-      <c r="E106" s="4">
-        <v>10000</v>
-      </c>
-      <c r="G106" s="6">
-        <v>0</v>
-      </c>
-      <c r="H106" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H104" xr:uid="{5C578346-EE80-DF41-8099-4E3028D96EBE}"/>
+  <autoFilter ref="A1:H8" xr:uid="{5C578346-EE80-DF41-8099-4E3028D96EBE}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/Plan.xlsx
+++ b/data/Plan.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raman/Documents/GitHub/production-board/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E0960FF-2CCD-CC40-B392-DF8454BF1BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6A898D2-5D2C-214E-92EA-8214D49805D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16560" xr2:uid="{7C08584A-5D47-2049-B143-911B93E5D6E0}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="135">
   <si>
     <t>Date</t>
   </si>
@@ -65,12 +65,6 @@
     <t>Fill rate</t>
   </si>
   <si>
-    <t>BA9</t>
-  </si>
-  <si>
-    <t>EXPERT | Ultra Smoothing Hair Mask (250 gms)</t>
-  </si>
-  <si>
     <t>CAP1</t>
   </si>
   <si>
@@ -89,18 +83,6 @@
     <t>EXPERT | Ultra Smoothing Serum (100 ML) - TikTok US</t>
   </si>
   <si>
-    <t>BA22</t>
-  </si>
-  <si>
-    <t>BA Expert | Anti Hairfall Shampoo 250 ml</t>
-  </si>
-  <si>
-    <t>SS43</t>
-  </si>
-  <si>
-    <t>5% Niacinamide Sunscreen Body Lotion 200 ml</t>
-  </si>
-  <si>
     <t>BA10</t>
   </si>
   <si>
@@ -459,6 +441,12 @@
   </si>
   <si>
     <t>Combo- Anti-Hairfall Shampoo (100ml) + Anti-Hairfall Conditioner (100g)</t>
+  </si>
+  <si>
+    <t>BA124</t>
+  </si>
+  <si>
+    <t>Rosemary &amp; Rice Water Hair Growth Spray- 100ml</t>
   </si>
 </sst>
 </file>
@@ -866,7 +854,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C578346-EE80-DF41-8099-4E3028D96EBE}">
-  <dimension ref="A1:H98"/>
+  <dimension ref="A1:H93"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="57.1640625" customWidth="1"/>
@@ -900,10 +888,10 @@
         <v>46269</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D2" s="4">
         <v>12000</v>
@@ -916,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -924,10 +912,10 @@
         <v>46292</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D3" s="4">
         <v>25000</v>
@@ -940,7 +928,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -948,10 +936,10 @@
         <v>46292</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D4" s="4">
         <v>25000</v>
@@ -964,7 +952,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -972,10 +960,10 @@
         <v>46275</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D5" s="4">
         <v>15000</v>
@@ -988,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -996,10 +984,10 @@
         <v>46269</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D6" s="4">
         <v>10000</v>
@@ -1012,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -1020,10 +1008,10 @@
         <v>46270</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D7" s="4">
         <v>12000</v>
@@ -1036,18 +1024,18 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D8" s="4">
         <v>28000</v>
@@ -1060,7 +1048,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -1068,10 +1056,10 @@
         <v>46272</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D9" s="8">
         <v>10000</v>
@@ -1084,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -1092,10 +1080,10 @@
         <v>46272</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D10" s="8">
         <v>10000</v>
@@ -1108,291 +1096,295 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D11" s="4">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="E11" s="4">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="6">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D12" s="4">
-        <v>4700</v>
+        <v>1800</v>
       </c>
       <c r="E12" s="4">
-        <v>4700</v>
+        <v>1800</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="6">
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D13" s="4">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="E13" s="4">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
+      <c r="G13" s="6">
+        <v>0</v>
+      </c>
       <c r="H13" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D14" s="4">
-        <v>8000</v>
+        <v>3300</v>
       </c>
       <c r="E14" s="4">
-        <v>8000</v>
+        <v>3300</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="6">
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="D15" s="4">
-        <v>8708</v>
+        <v>3000</v>
       </c>
       <c r="E15" s="4">
-        <v>8708</v>
+        <v>3000</v>
       </c>
       <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
+      <c r="G15" s="6">
+        <v>0</v>
+      </c>
       <c r="H15" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D16" s="4">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="E16" s="4">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="6">
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D17" s="4">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="E17" s="4">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="6">
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D18" s="4">
-        <v>20000</v>
+        <v>6500</v>
       </c>
       <c r="E18" s="4">
-        <v>20000</v>
+        <v>6500</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="6">
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="D19" s="4">
-        <v>28000</v>
+        <v>7000</v>
       </c>
       <c r="E19" s="4">
-        <v>28000</v>
+        <v>7000</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="6">
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D20" s="4">
-        <v>30000</v>
+        <v>8000</v>
       </c>
       <c r="E20" s="4">
-        <v>30000</v>
+        <v>8000</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="6">
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D21" s="4">
-        <v>40000</v>
+        <v>8000</v>
       </c>
       <c r="E21" s="4">
-        <v>40000</v>
+        <v>8000</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="6">
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>45</v>
+        <v>133</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>46</v>
+        <v>134</v>
       </c>
       <c r="D22" s="4">
-        <v>47328</v>
+        <v>8000</v>
       </c>
       <c r="E22" s="4">
-        <v>47328</v>
+        <v>8000</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="6">
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
@@ -1400,23 +1392,23 @@
         <v>46269</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D23" s="4">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="E23" s="4">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="6">
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
@@ -1424,23 +1416,23 @@
         <v>46269</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="D24" s="4">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="E24" s="4">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="6">
         <v>0</v>
       </c>
       <c r="H24" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
@@ -1448,23 +1440,23 @@
         <v>46269</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="D25" s="4">
-        <v>5000</v>
+        <v>11000</v>
       </c>
       <c r="E25" s="4">
-        <v>5000</v>
+        <v>11000</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="6">
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
@@ -1472,23 +1464,23 @@
         <v>46269</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D26" s="4">
-        <v>6500</v>
+        <v>15000</v>
       </c>
       <c r="E26" s="4">
-        <v>6500</v>
+        <v>15000</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="6">
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -1496,23 +1488,23 @@
         <v>46269</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="D27" s="4">
-        <v>8000</v>
+        <v>20000</v>
       </c>
       <c r="E27" s="4">
-        <v>8000</v>
+        <v>20000</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="6">
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
@@ -1520,23 +1512,23 @@
         <v>46269</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="D28" s="4">
-        <v>8000</v>
+        <v>30000</v>
       </c>
       <c r="E28" s="4">
-        <v>8000</v>
+        <v>30000</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="6">
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
@@ -1544,119 +1536,119 @@
         <v>46269</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="D29" s="4">
-        <v>10000</v>
+        <v>39456</v>
       </c>
       <c r="E29" s="4">
-        <v>10000</v>
+        <v>39456</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="6">
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D30" s="4">
-        <v>10000</v>
-      </c>
-      <c r="E30" s="3">
-        <v>0</v>
+        <v>1800</v>
+      </c>
+      <c r="E30" s="4">
+        <v>1800</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="6">
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="D31" s="4">
-        <v>11000</v>
+        <v>2000</v>
       </c>
       <c r="E31" s="4">
-        <v>11000</v>
+        <v>2000</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="6">
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="D32" s="4">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="E32" s="4">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="6">
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="D33" s="4">
-        <v>40000</v>
+        <v>5000</v>
       </c>
       <c r="E33" s="4">
-        <v>40000</v>
+        <v>5000</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="6">
         <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
@@ -1664,23 +1656,23 @@
         <v>46270</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D34" s="4">
-        <v>1800</v>
+        <v>10000</v>
       </c>
       <c r="E34" s="4">
-        <v>1800</v>
+        <v>10000</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="6">
         <v>0</v>
       </c>
       <c r="H34" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
@@ -1688,23 +1680,23 @@
         <v>46270</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D35" s="4">
-        <v>3000</v>
+        <v>15000</v>
       </c>
       <c r="E35" s="4">
-        <v>3000</v>
+        <v>15000</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="6">
         <v>0</v>
       </c>
       <c r="H35" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
@@ -1712,23 +1704,23 @@
         <v>46270</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D36" s="4">
-        <v>2000</v>
+        <v>16000</v>
       </c>
       <c r="E36" s="4">
-        <v>2000</v>
+        <v>16000</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="6">
         <v>0</v>
       </c>
       <c r="H36" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
@@ -1736,23 +1728,23 @@
         <v>46270</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D37" s="4">
-        <v>5000</v>
+        <v>20000</v>
       </c>
       <c r="E37" s="4">
-        <v>5000</v>
+        <v>20000</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="6">
         <v>0</v>
       </c>
       <c r="H37" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
@@ -1760,23 +1752,23 @@
         <v>46270</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="D38" s="4">
-        <v>10000</v>
+        <v>25000</v>
       </c>
       <c r="E38" s="4">
-        <v>10000</v>
+        <v>25000</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="6">
         <v>0</v>
       </c>
       <c r="H38" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
@@ -1790,17 +1782,17 @@
         <v>74</v>
       </c>
       <c r="D39" s="4">
-        <v>7000</v>
+        <v>20000</v>
       </c>
       <c r="E39" s="4">
-        <v>7000</v>
+        <v>20000</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="6">
         <v>0</v>
       </c>
       <c r="H39" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
@@ -1808,52 +1800,52 @@
         <v>46270</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="D40" s="4">
-        <v>15000</v>
+        <v>30000</v>
       </c>
       <c r="E40" s="4">
-        <v>15000</v>
+        <v>30000</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="6">
         <v>0</v>
       </c>
       <c r="H40" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D41" s="4">
-        <v>16000</v>
+        <v>8000</v>
       </c>
       <c r="E41" s="4">
-        <v>16000</v>
+        <v>8000</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="6">
         <v>0</v>
       </c>
       <c r="H41" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>77</v>
@@ -1862,28 +1854,28 @@
         <v>78</v>
       </c>
       <c r="D42" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E42" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F42" s="5"/>
       <c r="G42" s="6">
         <v>0</v>
       </c>
       <c r="H42" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="D43" s="4">
         <v>20000</v>
@@ -1896,18 +1888,18 @@
         <v>0</v>
       </c>
       <c r="H43" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="D44" s="4">
         <v>20000</v>
@@ -1920,31 +1912,31 @@
         <v>0</v>
       </c>
       <c r="H44" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="D45" s="4">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="E45" s="4">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="6">
         <v>0</v>
       </c>
       <c r="H45" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
@@ -1952,23 +1944,23 @@
         <v>46271</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="D46" s="4">
-        <v>6000</v>
+        <v>20000</v>
       </c>
       <c r="E46" s="4">
-        <v>6000</v>
+        <v>20000</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="6">
         <v>0</v>
       </c>
       <c r="H46" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
@@ -1976,167 +1968,167 @@
         <v>46271</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>83</v>
+        <v>19</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="D47" s="4">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="E47" s="4">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="6">
         <v>0</v>
       </c>
       <c r="H47" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D48" s="4">
-        <v>20000</v>
+        <v>1000</v>
       </c>
       <c r="E48" s="4">
-        <v>20000</v>
+        <v>1000</v>
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="6">
         <v>0</v>
       </c>
       <c r="H48" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D49" s="4">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="E49" s="4">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="6">
         <v>0</v>
       </c>
       <c r="H49" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="D50" s="4">
-        <v>20000</v>
+        <v>6000</v>
       </c>
       <c r="E50" s="4">
-        <v>20000</v>
+        <v>6000</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="6">
         <v>0</v>
       </c>
       <c r="H50" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="D51" s="4">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="E51" s="4">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="6">
         <v>0</v>
       </c>
       <c r="H51" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="D52" s="4">
-        <v>20000</v>
+        <v>11000</v>
       </c>
       <c r="E52" s="4">
-        <v>20000</v>
+        <v>11000</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="6">
         <v>0</v>
       </c>
       <c r="H52" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>25</v>
+        <v>89</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="D53" s="4">
-        <v>40000</v>
+        <v>16000</v>
       </c>
       <c r="E53" s="4">
-        <v>40000</v>
+        <v>16000</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="6">
         <v>0</v>
       </c>
       <c r="H53" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
@@ -2144,23 +2136,23 @@
         <v>46272</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="D54" s="4">
-        <v>1000</v>
+        <v>20000</v>
       </c>
       <c r="E54" s="4">
-        <v>1000</v>
+        <v>20000</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="6">
         <v>0</v>
       </c>
       <c r="H54" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
@@ -2168,23 +2160,23 @@
         <v>46272</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>89</v>
+        <v>11</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="D55" s="4">
-        <v>2000</v>
+        <v>20000</v>
       </c>
       <c r="E55" s="4">
-        <v>2000</v>
+        <v>20000</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="6">
         <v>0</v>
       </c>
       <c r="H55" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
@@ -2192,23 +2184,23 @@
         <v>46272</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>91</v>
+        <v>15</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="D56" s="4">
-        <v>8000</v>
+        <v>20000</v>
       </c>
       <c r="E56" s="4">
-        <v>8000</v>
+        <v>20000</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="6">
         <v>0</v>
       </c>
       <c r="H56" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
@@ -2216,23 +2208,23 @@
         <v>46272</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D57" s="4">
-        <v>11000</v>
+        <v>24000</v>
       </c>
       <c r="E57" s="4">
-        <v>11000</v>
+        <v>24000</v>
       </c>
       <c r="F57" s="5"/>
       <c r="G57" s="6">
         <v>0</v>
       </c>
       <c r="H57" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
@@ -2240,119 +2232,119 @@
         <v>46272</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>95</v>
+        <v>37</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="D58" s="4">
-        <v>16000</v>
+        <v>40000</v>
       </c>
       <c r="E58" s="4">
-        <v>16000</v>
+        <v>40000</v>
       </c>
       <c r="F58" s="5"/>
       <c r="G58" s="6">
         <v>0</v>
       </c>
       <c r="H58" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="D59" s="4">
-        <v>20000</v>
+        <v>3000</v>
       </c>
       <c r="E59" s="4">
-        <v>20000</v>
+        <v>3000</v>
       </c>
       <c r="F59" s="5"/>
       <c r="G59" s="6">
         <v>0</v>
       </c>
       <c r="H59" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D60" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E60" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="6">
         <v>0</v>
       </c>
       <c r="H60" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>97</v>
+        <v>49</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="D61" s="4">
-        <v>24000</v>
+        <v>16000</v>
       </c>
       <c r="E61" s="4">
-        <v>24000</v>
+        <v>16000</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="6">
         <v>0</v>
       </c>
       <c r="H61" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="D62" s="4">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="E62" s="4">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="6">
         <v>0</v>
       </c>
       <c r="H62" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
@@ -2360,10 +2352,10 @@
         <v>46273</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="D63" s="4">
         <v>10000</v>
@@ -2376,7 +2368,7 @@
         <v>0</v>
       </c>
       <c r="H63" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
@@ -2384,23 +2376,23 @@
         <v>46273</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="D64" s="4">
-        <v>3000</v>
+        <v>40000</v>
       </c>
       <c r="E64" s="4">
-        <v>3000</v>
+        <v>40000</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="6">
         <v>0</v>
       </c>
       <c r="H64" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
@@ -2408,143 +2400,143 @@
         <v>46273</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>19</v>
+        <v>97</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="D65" s="4">
-        <v>10000</v>
+        <v>48000</v>
       </c>
       <c r="E65" s="4">
-        <v>10000</v>
+        <v>48000</v>
       </c>
       <c r="F65" s="5"/>
       <c r="G65" s="6">
         <v>0</v>
       </c>
       <c r="H65" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="D66" s="4">
-        <v>16000</v>
+        <v>10000</v>
       </c>
       <c r="E66" s="4">
-        <v>16000</v>
+        <v>10000</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="6">
         <v>0</v>
       </c>
       <c r="H66" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="D67" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E67" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="6">
         <v>0</v>
       </c>
       <c r="H67" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D68" s="4">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="E68" s="4">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="6">
         <v>0</v>
       </c>
       <c r="H68" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="D69" s="4">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="E69" s="4">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="6">
         <v>0</v>
       </c>
       <c r="H69" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>103</v>
+        <v>17</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>104</v>
+        <v>18</v>
       </c>
       <c r="D70" s="4">
-        <v>48000</v>
+        <v>20000</v>
       </c>
       <c r="E70" s="4">
-        <v>48000</v>
+        <v>20000</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" s="6">
         <v>0</v>
       </c>
       <c r="H70" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
@@ -2552,23 +2544,23 @@
         <v>46274</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D71" s="4">
-        <v>10000</v>
+        <v>24000</v>
       </c>
       <c r="E71" s="4">
-        <v>10000</v>
+        <v>24000</v>
       </c>
       <c r="F71" s="5"/>
       <c r="G71" s="6">
         <v>0</v>
       </c>
       <c r="H71" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
@@ -2576,23 +2568,23 @@
         <v>46274</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="D72" s="4">
-        <v>10000</v>
+        <v>24000</v>
       </c>
       <c r="E72" s="4">
-        <v>10000</v>
+        <v>24000</v>
       </c>
       <c r="F72" s="5"/>
       <c r="G72" s="6">
         <v>0</v>
       </c>
       <c r="H72" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
@@ -2600,106 +2592,106 @@
         <v>46274</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>106</v>
+        <v>20</v>
       </c>
       <c r="D73" s="4">
-        <v>16000</v>
+        <v>40000</v>
       </c>
       <c r="E73" s="4">
-        <v>16000</v>
+        <v>40000</v>
       </c>
       <c r="F73" s="5"/>
       <c r="G73" s="6">
         <v>0</v>
       </c>
       <c r="H73" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="D74" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E74" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F74" s="5"/>
       <c r="G74" s="6">
         <v>0</v>
       </c>
       <c r="H74" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="D75" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E75" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F75" s="5"/>
       <c r="G75" s="6">
         <v>0</v>
       </c>
       <c r="H75" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>103</v>
+        <v>31</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>104</v>
+        <v>32</v>
       </c>
       <c r="D76" s="4">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="E76" s="4">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="F76" s="5"/>
       <c r="G76" s="6">
         <v>0</v>
       </c>
       <c r="H76" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D77" s="4">
         <v>24000</v>
@@ -2712,31 +2704,31 @@
         <v>0</v>
       </c>
       <c r="H77" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>26</v>
+        <v>106</v>
       </c>
       <c r="D78" s="4">
-        <v>40000</v>
+        <v>18000</v>
       </c>
       <c r="E78" s="4">
-        <v>40000</v>
+        <v>18000</v>
       </c>
       <c r="F78" s="5"/>
       <c r="G78" s="6">
         <v>0</v>
       </c>
       <c r="H78" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
@@ -2744,23 +2736,23 @@
         <v>46275</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="D79" s="4">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="E79" s="4">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="F79" s="5"/>
       <c r="G79" s="6">
         <v>0</v>
       </c>
       <c r="H79" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
@@ -2768,143 +2760,143 @@
         <v>46275</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="D80" s="4">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="E80" s="4">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="F80" s="5"/>
       <c r="G80" s="6">
         <v>0</v>
       </c>
       <c r="H80" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>37</v>
+        <v>107</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="D81" s="4">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="E81" s="4">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="F81" s="5"/>
       <c r="G81" s="6">
         <v>0</v>
       </c>
       <c r="H81" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>109</v>
+        <v>7</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>110</v>
+        <v>8</v>
       </c>
       <c r="D82" s="4">
-        <v>24000</v>
+        <v>8000</v>
       </c>
       <c r="E82" s="4">
-        <v>24000</v>
+        <v>8000</v>
       </c>
       <c r="F82" s="5"/>
       <c r="G82" s="6">
         <v>0</v>
       </c>
       <c r="H82" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D83" s="4">
-        <v>18000</v>
+        <v>10000</v>
       </c>
       <c r="E83" s="4">
-        <v>18000</v>
+        <v>10000</v>
       </c>
       <c r="F83" s="5"/>
       <c r="G83" s="6">
         <v>0</v>
       </c>
       <c r="H83" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="D84" s="4">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="E84" s="4">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="F84" s="5"/>
       <c r="G84" s="6">
         <v>0</v>
       </c>
       <c r="H84" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="D85" s="4">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="E85" s="4">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="F85" s="5"/>
       <c r="G85" s="6">
         <v>0</v>
       </c>
       <c r="H85" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
@@ -2912,23 +2904,23 @@
         <v>46276</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>114</v>
+        <v>18</v>
       </c>
       <c r="D86" s="4">
-        <v>8000</v>
+        <v>40000</v>
       </c>
       <c r="E86" s="4">
-        <v>8000</v>
+        <v>40000</v>
       </c>
       <c r="F86" s="5"/>
       <c r="G86" s="6">
         <v>0</v>
       </c>
       <c r="H86" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
@@ -2936,34 +2928,34 @@
         <v>46276</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="D87" s="4">
-        <v>8000</v>
+        <v>40000</v>
       </c>
       <c r="E87" s="4">
-        <v>8000</v>
+        <v>40000</v>
       </c>
       <c r="F87" s="5"/>
       <c r="G87" s="6">
         <v>0</v>
       </c>
       <c r="H87" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>116</v>
+        <v>56</v>
       </c>
       <c r="D88" s="4">
         <v>10000</v>
@@ -2976,103 +2968,103 @@
         <v>0</v>
       </c>
       <c r="H88" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="D89" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E89" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F89" s="5"/>
       <c r="G89" s="6">
         <v>0</v>
       </c>
       <c r="H89" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="D90" s="4">
-        <v>20000</v>
+        <v>18000</v>
       </c>
       <c r="E90" s="4">
-        <v>20000</v>
+        <v>18000</v>
       </c>
       <c r="F90" s="5"/>
       <c r="G90" s="6">
         <v>0</v>
       </c>
       <c r="H90" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="D91" s="4">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="E91" s="4">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="F91" s="5"/>
       <c r="G91" s="6">
         <v>0</v>
       </c>
       <c r="H91" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="D92" s="4">
-        <v>40000</v>
+        <v>30000</v>
       </c>
       <c r="E92" s="4">
-        <v>40000</v>
+        <v>30000</v>
       </c>
       <c r="F92" s="5"/>
       <c r="G92" s="6">
         <v>0</v>
       </c>
       <c r="H92" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
@@ -3080,143 +3072,23 @@
         <v>46277</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="D93" s="4">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="E93" s="4">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="F93" s="5"/>
       <c r="G93" s="6">
         <v>0</v>
       </c>
       <c r="H93" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A94" s="2">
-        <v>46277</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D94" s="4">
-        <v>10000</v>
-      </c>
-      <c r="E94" s="4">
-        <v>10000</v>
-      </c>
-      <c r="F94" s="5"/>
-      <c r="G94" s="6">
-        <v>0</v>
-      </c>
-      <c r="H94" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A95" s="2">
-        <v>46277</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D95" s="4">
-        <v>18000</v>
-      </c>
-      <c r="E95" s="4">
-        <v>18000</v>
-      </c>
-      <c r="F95" s="5"/>
-      <c r="G95" s="6">
-        <v>0</v>
-      </c>
-      <c r="H95" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A96" s="2">
-        <v>46277</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D96" s="4">
-        <v>20000</v>
-      </c>
-      <c r="E96" s="4">
-        <v>20000</v>
-      </c>
-      <c r="F96" s="5"/>
-      <c r="G96" s="6">
-        <v>0</v>
-      </c>
-      <c r="H96" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A97" s="2">
-        <v>46277</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D97" s="4">
-        <v>30000</v>
-      </c>
-      <c r="E97" s="4">
-        <v>30000</v>
-      </c>
-      <c r="F97" s="5"/>
-      <c r="G97" s="6">
-        <v>0</v>
-      </c>
-      <c r="H97" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A98" s="2">
-        <v>46277</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D98" s="4">
-        <v>40000</v>
-      </c>
-      <c r="E98" s="4">
-        <v>40000</v>
-      </c>
-      <c r="F98" s="5"/>
-      <c r="G98" s="6">
-        <v>0</v>
-      </c>
-      <c r="H98" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/data/Plan.xlsx
+++ b/data/Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raman/Documents/GitHub/production-board/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6A898D2-5D2C-214E-92EA-8214D49805D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6713A39A-0E91-F14B-8913-FA2C331726F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16560" xr2:uid="{7C08584A-5D47-2049-B143-911B93E5D6E0}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="104">
   <si>
     <t>Date</t>
   </si>
@@ -65,12 +65,6 @@
     <t>Fill rate</t>
   </si>
   <si>
-    <t>CAP1</t>
-  </si>
-  <si>
-    <t>Acne Control Body Wash (236 ml)</t>
-  </si>
-  <si>
     <t>CAP82</t>
   </si>
   <si>
@@ -89,12 +83,6 @@
     <t>EXPERT | Ultra Smoothing Shampoo (250 ML)</t>
   </si>
   <si>
-    <t>USTTCAP16</t>
-  </si>
-  <si>
-    <t>Brightening body wash 236 ml - Tik Tok US</t>
-  </si>
-  <si>
     <t>CAP24</t>
   </si>
   <si>
@@ -107,36 +95,12 @@
     <t>Rosemary &amp; Rice Water Hair Spray-200ml - TikTok US</t>
   </si>
   <si>
-    <t>BA121</t>
-  </si>
-  <si>
-    <t>NxS Flaxseed &amp; Rice Water Hair Gel 300ml</t>
-  </si>
-  <si>
     <t>USTTCAP70</t>
   </si>
   <si>
     <t> Roll On -  White jasmine 40 ml- Tik Tok US</t>
   </si>
   <si>
-    <t>BA87</t>
-  </si>
-  <si>
-    <t>Advanced Anti-Grey Hair Serum 50ml</t>
-  </si>
-  <si>
-    <t>BA98</t>
-  </si>
-  <si>
-    <t>Anti-Dandruff Conditioner -175gm</t>
-  </si>
-  <si>
-    <t>BA60</t>
-  </si>
-  <si>
-    <t>Rosemary and Coconut Milk Hydrating Shampoo 200ML</t>
-  </si>
-  <si>
     <t>CAP137</t>
   </si>
   <si>
@@ -161,48 +125,18 @@
     <t>Rosemary &amp; Rice Water Hair Growth Spray-200ml</t>
   </si>
   <si>
-    <t>USTTBA9</t>
-  </si>
-  <si>
-    <t>EXPERT | Ultra Smoothing Hair Mask (250 gms) - TikTok US</t>
-  </si>
-  <si>
-    <t>BA100</t>
-  </si>
-  <si>
-    <t>Anti-Dandruff Shampoo 450ml</t>
-  </si>
-  <si>
     <t>USTTBA50</t>
   </si>
   <si>
     <t>Curl Intensifying Leave in Conditioner USTT</t>
   </si>
   <si>
-    <t>CAP173</t>
-  </si>
-  <si>
-    <t>Gentle Exfoliating Face Wash 75ml- Pack of 2</t>
-  </si>
-  <si>
-    <t>BA50</t>
-  </si>
-  <si>
-    <t>Curl Intensifying Leave in Conditioner 140 ml</t>
-  </si>
-  <si>
     <t>USTTCAP62</t>
   </si>
   <si>
     <t>AHA Body Lotion 236ml - Tik Tok US</t>
   </si>
   <si>
-    <t>CAP83</t>
-  </si>
-  <si>
-    <t>Brightening Boost Face Wash</t>
-  </si>
-  <si>
     <t>CAP153</t>
   </si>
   <si>
@@ -221,12 +155,6 @@
     <t>Epsom Body Wash - 236ml</t>
   </si>
   <si>
-    <t>CAP132</t>
-  </si>
-  <si>
-    <t>2% Salicylic Acid Serum 10ml</t>
-  </si>
-  <si>
     <t>CAP145</t>
   </si>
   <si>
@@ -239,18 +167,6 @@
     <t>Oil &amp; Acne Control Face Wash - Flipkart pack of 2</t>
   </si>
   <si>
-    <t>BA105</t>
-  </si>
-  <si>
-    <t>Ultra smoothing shampoo 100 ml</t>
-  </si>
-  <si>
-    <t>BA118</t>
-  </si>
-  <si>
-    <t>Fenugreek &amp; Curry Leaves Hair Strengthening Spray - 200ml</t>
-  </si>
-  <si>
     <t>USTTBA10</t>
   </si>
   <si>
@@ -263,12 +179,6 @@
     <t>Brightening face serum (10% Vitamin C) 10ml</t>
   </si>
   <si>
-    <t>CAP105</t>
-  </si>
-  <si>
-    <t>Gentle Exfoliating Face Scrub 100ML</t>
-  </si>
-  <si>
     <t>CAP134</t>
   </si>
   <si>
@@ -281,12 +191,6 @@
     <t>Rosemary hair growth oil 100ml</t>
   </si>
   <si>
-    <t>BA103</t>
-  </si>
-  <si>
-    <t>Anti-Hairfall Conditioner 100 gm</t>
-  </si>
-  <si>
     <t>BA88</t>
   </si>
   <si>
@@ -371,60 +275,9 @@
     <t>Odour Control Body Wash 236ml</t>
   </si>
   <si>
-    <t>CO358</t>
-  </si>
-  <si>
-    <t>Combo- Anti-Dandruff Shampoo (100ml) + Anti-Dandruff Conditioner (100g)</t>
-  </si>
-  <si>
-    <t>CAP138</t>
-  </si>
-  <si>
-    <t>Natural Lip Balm 4.5gm</t>
-  </si>
-  <si>
-    <t>BA110</t>
-  </si>
-  <si>
-    <t>Instant Cover-Up Hair Powder Black-4gm</t>
-  </si>
-  <si>
-    <t>BA111</t>
-  </si>
-  <si>
-    <t>Instant Cover-Up Hair Powder Brown-4gm</t>
-  </si>
-  <si>
-    <t>BA77</t>
-  </si>
-  <si>
-    <t>Scalp Massager</t>
-  </si>
-  <si>
-    <t>CAP157</t>
-  </si>
-  <si>
-    <t>Age Defence Night Cream-30gm</t>
-  </si>
-  <si>
-    <t>SS42</t>
-  </si>
-  <si>
-    <t>3% Niacinamide Featherlight Fluid Sunscreen 45g</t>
-  </si>
-  <si>
-    <t>BA107</t>
-  </si>
-  <si>
-    <t>Advanced Hair Growth Serum Roll-On</t>
-  </si>
-  <si>
     <t>Inhouse</t>
   </si>
   <si>
-    <t>Outsource</t>
-  </si>
-  <si>
     <t>CO539</t>
   </si>
   <si>
@@ -443,10 +296,64 @@
     <t>Combo- Anti-Hairfall Shampoo (100ml) + Anti-Hairfall Conditioner (100g)</t>
   </si>
   <si>
-    <t>BA124</t>
-  </si>
-  <si>
-    <t>Rosemary &amp; Rice Water Hair Growth Spray- 100ml</t>
+    <t>BA93</t>
+  </si>
+  <si>
+    <t>EXPERT | Ultra Smoothing Serum (100 ML)</t>
+  </si>
+  <si>
+    <t>TRA4</t>
+  </si>
+  <si>
+    <t>Tierra Shampoo- 5L</t>
+  </si>
+  <si>
+    <t>TRA3</t>
+  </si>
+  <si>
+    <t>Tierra body lotion- 5L</t>
+  </si>
+  <si>
+    <t>CAP146</t>
+  </si>
+  <si>
+    <t>Clarifying Face Serum - 10ml</t>
+  </si>
+  <si>
+    <t>BA72</t>
+  </si>
+  <si>
+    <t>Bare Anatomy Nature x Science Argan Oil &amp; Vitamin E Anti Frizz Serum 75 ml</t>
+  </si>
+  <si>
+    <t>CAP154</t>
+  </si>
+  <si>
+    <t>Exfoliating face wash 75 ml</t>
+  </si>
+  <si>
+    <t>CO529</t>
+  </si>
+  <si>
+    <t>Exfoliation and Odour Control Kit</t>
+  </si>
+  <si>
+    <t>CAP141</t>
+  </si>
+  <si>
+    <t>Bright Boost SPF Lotion 236 ml</t>
+  </si>
+  <si>
+    <t>CAP81</t>
+  </si>
+  <si>
+    <t>Hydrating Face Wash (Tube)-100ML</t>
+  </si>
+  <si>
+    <t>CAP152</t>
+  </si>
+  <si>
+    <t>Under Eye Cream 15 gm</t>
   </si>
 </sst>
 </file>
@@ -854,7 +761,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C578346-EE80-DF41-8099-4E3028D96EBE}">
-  <dimension ref="A1:H93"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="57.1640625" customWidth="1"/>
@@ -884,1070 +791,1070 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="2">
-        <v>46269</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D2" s="4">
-        <v>12000</v>
-      </c>
-      <c r="E2" s="4">
-        <v>12000</v>
-      </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="6">
-        <v>0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>126</v>
+      <c r="A2" s="11">
+        <v>46272</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" s="8">
+        <v>10000</v>
+      </c>
+      <c r="E2" s="8">
+        <v>10000</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="9">
+        <v>0</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="2">
-        <v>46292</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D3" s="4">
-        <v>25000</v>
-      </c>
-      <c r="E3" s="4">
-        <v>25000</v>
-      </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="6">
-        <v>0</v>
-      </c>
-      <c r="H3" t="s">
-        <v>126</v>
+      <c r="A3" s="11">
+        <v>46272</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D3" s="8">
+        <v>10000</v>
+      </c>
+      <c r="E3" s="8">
+        <v>10000</v>
+      </c>
+      <c r="F3" s="10"/>
+      <c r="G3" s="9">
+        <v>0</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>46292</v>
+        <v>46272</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>115</v>
+        <v>49</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>116</v>
+        <v>50</v>
       </c>
       <c r="D4" s="4">
-        <v>25000</v>
+        <v>1000</v>
       </c>
       <c r="E4" s="4">
-        <v>25000</v>
+        <v>1000</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="6">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>126</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>46275</v>
+        <v>46272</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>117</v>
+        <v>47</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>118</v>
+        <v>48</v>
       </c>
       <c r="D5" s="4">
-        <v>15000</v>
+        <v>1000</v>
       </c>
       <c r="E5" s="4">
-        <v>15000</v>
+        <v>1000</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="6">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>126</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="D6" s="4">
-        <v>10000</v>
+        <v>1500</v>
       </c>
       <c r="E6" s="4">
-        <v>10000</v>
+        <v>1500</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>126</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>46270</v>
+        <v>46272</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>121</v>
+        <v>51</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="D7" s="4">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="E7" s="4">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="6">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>126</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>123</v>
+        <v>37</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>124</v>
+        <v>38</v>
       </c>
       <c r="D8" s="4">
-        <v>28000</v>
+        <v>2000</v>
       </c>
       <c r="E8" s="4">
-        <v>28000</v>
+        <v>2000</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="6">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>126</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="11">
+      <c r="A9" s="2">
         <v>46272</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="D9" s="8">
-        <v>10000</v>
-      </c>
-      <c r="E9" s="8">
-        <v>10000</v>
-      </c>
-      <c r="F9" s="10"/>
-      <c r="G9" s="9">
-        <v>0</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>125</v>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="4">
+        <v>4000</v>
+      </c>
+      <c r="E9" s="4">
+        <v>4000</v>
+      </c>
+      <c r="F9" s="5"/>
+      <c r="G9" s="6">
+        <v>0</v>
+      </c>
+      <c r="H9" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="11">
+      <c r="A10" s="2">
         <v>46272</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="D10" s="8">
-        <v>10000</v>
-      </c>
-      <c r="E10" s="8">
-        <v>10000</v>
-      </c>
-      <c r="F10" s="10"/>
-      <c r="G10" s="9">
-        <v>0</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>125</v>
+      <c r="B10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="4">
+        <v>5000</v>
+      </c>
+      <c r="E10" s="4">
+        <v>5000</v>
+      </c>
+      <c r="F10" s="5"/>
+      <c r="G10" s="6">
+        <v>0</v>
+      </c>
+      <c r="H10" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="D11" s="4">
-        <v>1500</v>
+        <v>5000</v>
       </c>
       <c r="E11" s="4">
-        <v>1500</v>
+        <v>5000</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="6">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D12" s="4">
-        <v>1800</v>
+        <v>5000</v>
       </c>
       <c r="E12" s="4">
-        <v>1800</v>
+        <v>5000</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="6">
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="D13" s="4">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="E13" s="4">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="6">
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D14" s="4">
-        <v>3300</v>
+        <v>8000</v>
       </c>
       <c r="E14" s="4">
-        <v>3300</v>
+        <v>8000</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="6">
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D15" s="4">
-        <v>3000</v>
+        <v>11000</v>
       </c>
       <c r="E15" s="4">
-        <v>3000</v>
+        <v>11000</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="6">
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="D16" s="4">
-        <v>5000</v>
+        <v>18000</v>
       </c>
       <c r="E16" s="4">
-        <v>5000</v>
+        <v>18000</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="6">
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="D17" s="4">
-        <v>5000</v>
+        <v>20000</v>
       </c>
       <c r="E17" s="4">
-        <v>5000</v>
+        <v>20000</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="6">
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D18" s="4">
-        <v>6500</v>
+        <v>24000</v>
       </c>
       <c r="E18" s="4">
-        <v>6500</v>
+        <v>24000</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="6">
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D19" s="4">
-        <v>7000</v>
+        <v>24000</v>
       </c>
       <c r="E19" s="4">
-        <v>7000</v>
+        <v>24000</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="6">
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="D20" s="4">
-        <v>8000</v>
+        <v>25000</v>
       </c>
       <c r="E20" s="4">
-        <v>8000</v>
+        <v>25000</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="6">
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>47</v>
+        <v>86</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D21" s="4">
-        <v>8000</v>
-      </c>
-      <c r="E21" s="4">
-        <v>8000</v>
+        <v>87</v>
+      </c>
+      <c r="D21" s="3">
+        <v>50</v>
+      </c>
+      <c r="E21" s="3">
+        <v>50</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="6">
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>133</v>
+        <v>88</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="D22" s="4">
-        <v>8000</v>
-      </c>
-      <c r="E22" s="4">
-        <v>8000</v>
+        <v>89</v>
+      </c>
+      <c r="D22" s="3">
+        <v>50</v>
+      </c>
+      <c r="E22" s="3">
+        <v>50</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="6">
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D23" s="4">
-        <v>10000</v>
+        <v>1800</v>
       </c>
       <c r="E23" s="4">
-        <v>10000</v>
+        <v>1800</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="6">
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="D24" s="4">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="E24" s="4">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="6">
         <v>0</v>
       </c>
       <c r="H24" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="D25" s="4">
-        <v>11000</v>
+        <v>6000</v>
       </c>
       <c r="E25" s="4">
-        <v>11000</v>
+        <v>6000</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="6">
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D26" s="4">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="E26" s="4">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="6">
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="D27" s="4">
-        <v>20000</v>
+        <v>16000</v>
       </c>
       <c r="E27" s="4">
-        <v>20000</v>
+        <v>16000</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="6">
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D28" s="4">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="E28" s="4">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="6">
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D29" s="4">
-        <v>39456</v>
+        <v>20000</v>
       </c>
       <c r="E29" s="4">
-        <v>39456</v>
+        <v>20000</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="6">
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
-        <v>46270</v>
+        <v>46273</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="D30" s="4">
-        <v>1800</v>
+        <v>20000</v>
       </c>
       <c r="E30" s="4">
-        <v>1800</v>
+        <v>20000</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="6">
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <v>46270</v>
+        <v>46273</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D31" s="4">
-        <v>2000</v>
+        <v>24000</v>
       </c>
       <c r="E31" s="4">
-        <v>2000</v>
+        <v>24000</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="6">
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>46270</v>
+        <v>46273</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D32" s="4">
-        <v>5000</v>
+        <v>40000</v>
       </c>
       <c r="E32" s="4">
-        <v>5000</v>
+        <v>40000</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="6">
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>46270</v>
+        <v>46274</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="D33" s="4">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="E33" s="4">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="6">
         <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>46270</v>
+        <v>46274</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D34" s="4">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="E34" s="4">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="6">
         <v>0</v>
       </c>
       <c r="H34" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>46270</v>
+        <v>46274</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="D35" s="4">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="E35" s="4">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="6">
         <v>0</v>
       </c>
       <c r="H35" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>46270</v>
+        <v>46274</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D36" s="4">
-        <v>16000</v>
+        <v>10000</v>
       </c>
       <c r="E36" s="4">
-        <v>16000</v>
+        <v>10000</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="6">
         <v>0</v>
       </c>
       <c r="H36" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>46270</v>
+        <v>46274</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D37" s="4">
-        <v>20000</v>
+        <v>16000</v>
       </c>
       <c r="E37" s="4">
-        <v>20000</v>
+        <v>16000</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="6">
         <v>0</v>
       </c>
       <c r="H37" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <v>46270</v>
+        <v>46274</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="D38" s="4">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="E38" s="4">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="6">
         <v>0</v>
       </c>
       <c r="H38" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
-        <v>46270</v>
+        <v>46274</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="D39" s="4">
-        <v>20000</v>
+        <v>24000</v>
       </c>
       <c r="E39" s="4">
-        <v>20000</v>
+        <v>24000</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="6">
         <v>0</v>
       </c>
       <c r="H39" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
-        <v>46270</v>
+        <v>46274</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D40" s="4">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="E40" s="4">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="6">
         <v>0</v>
       </c>
       <c r="H40" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
-        <v>46271</v>
+        <v>46274</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="D41" s="4">
-        <v>8000</v>
+        <v>48000</v>
       </c>
       <c r="E41" s="4">
-        <v>8000</v>
+        <v>48000</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="6">
         <v>0</v>
       </c>
       <c r="H41" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>46271</v>
+        <v>46275</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="D42" s="4">
-        <v>10000</v>
-      </c>
-      <c r="E42" s="4">
-        <v>10000</v>
+        <v>3520</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
       </c>
       <c r="F42" s="5"/>
       <c r="G42" s="6">
         <v>0</v>
       </c>
       <c r="H42" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>46271</v>
+        <v>46275</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="D43" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E43" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="6">
         <v>0</v>
       </c>
       <c r="H43" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>46271</v>
+        <v>46275</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D44" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E44" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="6">
         <v>0</v>
       </c>
       <c r="H44" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
-        <v>46271</v>
+        <v>46275</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D45" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E45" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="6">
         <v>0</v>
       </c>
       <c r="H45" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <v>46271</v>
+        <v>46275</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D46" s="4">
         <v>20000</v>
@@ -1960,84 +1867,84 @@
         <v>0</v>
       </c>
       <c r="H46" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <v>46271</v>
+        <v>46275</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D47" s="4">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="E47" s="4">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="6">
         <v>0</v>
       </c>
       <c r="H47" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>46272</v>
+        <v>46275</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D48" s="4">
-        <v>1000</v>
+        <v>24000</v>
       </c>
       <c r="E48" s="4">
-        <v>1000</v>
+        <v>24000</v>
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="6">
         <v>0</v>
       </c>
       <c r="H48" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>46272</v>
+        <v>46275</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="D49" s="4">
-        <v>2000</v>
+        <v>40000</v>
       </c>
       <c r="E49" s="4">
-        <v>2000</v>
+        <v>40000</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="6">
         <v>0</v>
       </c>
       <c r="H49" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <v>46272</v>
+        <v>46276</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>75</v>
@@ -2046,292 +1953,292 @@
         <v>76</v>
       </c>
       <c r="D50" s="4">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="E50" s="4">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="6">
         <v>0</v>
       </c>
       <c r="H50" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <v>46272</v>
+        <v>46276</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="D51" s="4">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="E51" s="4">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="6">
         <v>0</v>
       </c>
       <c r="H51" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <v>46272</v>
+        <v>46276</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D52" s="4">
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="E52" s="4">
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="6">
         <v>0</v>
       </c>
       <c r="H52" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
-        <v>46272</v>
+        <v>46276</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="D53" s="4">
-        <v>16000</v>
+        <v>20000</v>
       </c>
       <c r="E53" s="4">
-        <v>16000</v>
+        <v>20000</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="6">
         <v>0</v>
       </c>
       <c r="H53" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
-        <v>46272</v>
+        <v>46276</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>71</v>
+        <v>13</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="D54" s="4">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="E54" s="4">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="6">
         <v>0</v>
       </c>
       <c r="H54" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
-        <v>46272</v>
+        <v>46276</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D55" s="4">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="E55" s="4">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="6">
         <v>0</v>
       </c>
       <c r="H55" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
-        <v>46272</v>
+        <v>46277</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="D56" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E56" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="6">
         <v>0</v>
       </c>
       <c r="H56" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
-        <v>46272</v>
+        <v>46277</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="D57" s="4">
-        <v>24000</v>
+        <v>8000</v>
       </c>
       <c r="E57" s="4">
-        <v>24000</v>
+        <v>8000</v>
       </c>
       <c r="F57" s="5"/>
       <c r="G57" s="6">
         <v>0</v>
       </c>
       <c r="H57" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
-        <v>46272</v>
+        <v>46277</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="D58" s="4">
-        <v>40000</v>
+        <v>10000</v>
       </c>
       <c r="E58" s="4">
-        <v>40000</v>
+        <v>10000</v>
       </c>
       <c r="F58" s="5"/>
       <c r="G58" s="6">
         <v>0</v>
       </c>
       <c r="H58" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
-        <v>46273</v>
+        <v>46277</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="D59" s="4">
-        <v>3000</v>
+        <v>12000</v>
       </c>
       <c r="E59" s="4">
-        <v>3000</v>
+        <v>12000</v>
       </c>
       <c r="F59" s="5"/>
       <c r="G59" s="6">
         <v>0</v>
       </c>
       <c r="H59" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
-        <v>46273</v>
+        <v>46277</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D60" s="4">
-        <v>10000</v>
+        <v>18000</v>
       </c>
       <c r="E60" s="4">
-        <v>10000</v>
+        <v>18000</v>
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="6">
         <v>0</v>
       </c>
       <c r="H60" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
-        <v>46273</v>
+        <v>46277</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D61" s="4">
-        <v>16000</v>
+        <v>20000</v>
       </c>
       <c r="E61" s="4">
-        <v>16000</v>
+        <v>20000</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="6">
         <v>0</v>
       </c>
       <c r="H61" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
-        <v>46273</v>
+        <v>46277</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D62" s="4">
         <v>20000</v>
@@ -2344,42 +2251,42 @@
         <v>0</v>
       </c>
       <c r="H62" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
-        <v>46273</v>
+        <v>46277</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>95</v>
+        <v>13</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="D63" s="4">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="E63" s="4">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="F63" s="5"/>
       <c r="G63" s="6">
         <v>0</v>
       </c>
       <c r="H63" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
-        <v>46273</v>
+        <v>46277</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="D64" s="4">
         <v>40000</v>
@@ -2392,707 +2299,107 @@
         <v>0</v>
       </c>
       <c r="H64" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
-        <v>46273</v>
+        <v>46278</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D65" s="4">
-        <v>48000</v>
+        <v>2500</v>
       </c>
       <c r="E65" s="4">
-        <v>48000</v>
+        <v>2500</v>
       </c>
       <c r="F65" s="5"/>
       <c r="G65" s="6">
         <v>0</v>
       </c>
       <c r="H65" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
-        <v>46274</v>
+        <v>46278</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D66" s="4">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="E66" s="4">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="6">
         <v>0</v>
       </c>
       <c r="H66" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
-        <v>46274</v>
+        <v>46278</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="D67" s="4">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="E67" s="4">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="6">
         <v>0</v>
       </c>
       <c r="H67" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
-        <v>46274</v>
+        <v>46278</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="D68" s="4">
-        <v>16000</v>
+        <v>40000</v>
       </c>
       <c r="E68" s="4">
-        <v>16000</v>
+        <v>40000</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="6">
         <v>0</v>
       </c>
       <c r="H68" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A69" s="2">
-        <v>46274</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D69" s="4">
-        <v>20000</v>
-      </c>
-      <c r="E69" s="4">
-        <v>20000</v>
-      </c>
-      <c r="F69" s="5"/>
-      <c r="G69" s="6">
-        <v>0</v>
-      </c>
-      <c r="H69" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A70" s="2">
-        <v>46274</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D70" s="4">
-        <v>20000</v>
-      </c>
-      <c r="E70" s="4">
-        <v>20000</v>
-      </c>
-      <c r="F70" s="5"/>
-      <c r="G70" s="6">
-        <v>0</v>
-      </c>
-      <c r="H70" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A71" s="2">
-        <v>46274</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D71" s="4">
-        <v>24000</v>
-      </c>
-      <c r="E71" s="4">
-        <v>24000</v>
-      </c>
-      <c r="F71" s="5"/>
-      <c r="G71" s="6">
-        <v>0</v>
-      </c>
-      <c r="H71" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A72" s="2">
-        <v>46274</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D72" s="4">
-        <v>24000</v>
-      </c>
-      <c r="E72" s="4">
-        <v>24000</v>
-      </c>
-      <c r="F72" s="5"/>
-      <c r="G72" s="6">
-        <v>0</v>
-      </c>
-      <c r="H72" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A73" s="2">
-        <v>46274</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D73" s="4">
-        <v>40000</v>
-      </c>
-      <c r="E73" s="4">
-        <v>40000</v>
-      </c>
-      <c r="F73" s="5"/>
-      <c r="G73" s="6">
-        <v>0</v>
-      </c>
-      <c r="H73" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A74" s="2">
-        <v>46275</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D74" s="4">
-        <v>10000</v>
-      </c>
-      <c r="E74" s="4">
-        <v>10000</v>
-      </c>
-      <c r="F74" s="5"/>
-      <c r="G74" s="6">
-        <v>0</v>
-      </c>
-      <c r="H74" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A75" s="2">
-        <v>46275</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D75" s="4">
-        <v>10000</v>
-      </c>
-      <c r="E75" s="4">
-        <v>10000</v>
-      </c>
-      <c r="F75" s="5"/>
-      <c r="G75" s="6">
-        <v>0</v>
-      </c>
-      <c r="H75" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A76" s="2">
-        <v>46275</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D76" s="4">
-        <v>20000</v>
-      </c>
-      <c r="E76" s="4">
-        <v>20000</v>
-      </c>
-      <c r="F76" s="5"/>
-      <c r="G76" s="6">
-        <v>0</v>
-      </c>
-      <c r="H76" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A77" s="2">
-        <v>46275</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="D77" s="4">
-        <v>24000</v>
-      </c>
-      <c r="E77" s="4">
-        <v>24000</v>
-      </c>
-      <c r="F77" s="5"/>
-      <c r="G77" s="6">
-        <v>0</v>
-      </c>
-      <c r="H77" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A78" s="2">
-        <v>46275</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D78" s="4">
-        <v>18000</v>
-      </c>
-      <c r="E78" s="4">
-        <v>18000</v>
-      </c>
-      <c r="F78" s="5"/>
-      <c r="G78" s="6">
-        <v>0</v>
-      </c>
-      <c r="H78" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A79" s="2">
-        <v>46275</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D79" s="4">
-        <v>40000</v>
-      </c>
-      <c r="E79" s="4">
-        <v>40000</v>
-      </c>
-      <c r="F79" s="5"/>
-      <c r="G79" s="6">
-        <v>0</v>
-      </c>
-      <c r="H79" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A80" s="2">
-        <v>46275</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D80" s="4">
-        <v>40000</v>
-      </c>
-      <c r="E80" s="4">
-        <v>40000</v>
-      </c>
-      <c r="F80" s="5"/>
-      <c r="G80" s="6">
-        <v>0</v>
-      </c>
-      <c r="H80" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A81" s="2">
-        <v>46276</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D81" s="4">
-        <v>8000</v>
-      </c>
-      <c r="E81" s="4">
-        <v>8000</v>
-      </c>
-      <c r="F81" s="5"/>
-      <c r="G81" s="6">
-        <v>0</v>
-      </c>
-      <c r="H81" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A82" s="2">
-        <v>46276</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D82" s="4">
-        <v>8000</v>
-      </c>
-      <c r="E82" s="4">
-        <v>8000</v>
-      </c>
-      <c r="F82" s="5"/>
-      <c r="G82" s="6">
-        <v>0</v>
-      </c>
-      <c r="H82" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A83" s="2">
-        <v>46276</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D83" s="4">
-        <v>10000</v>
-      </c>
-      <c r="E83" s="4">
-        <v>10000</v>
-      </c>
-      <c r="F83" s="5"/>
-      <c r="G83" s="6">
-        <v>0</v>
-      </c>
-      <c r="H83" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A84" s="2">
-        <v>46276</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D84" s="4">
-        <v>20000</v>
-      </c>
-      <c r="E84" s="4">
-        <v>20000</v>
-      </c>
-      <c r="F84" s="5"/>
-      <c r="G84" s="6">
-        <v>0</v>
-      </c>
-      <c r="H84" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A85" s="2">
-        <v>46276</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D85" s="4">
-        <v>20000</v>
-      </c>
-      <c r="E85" s="4">
-        <v>20000</v>
-      </c>
-      <c r="F85" s="5"/>
-      <c r="G85" s="6">
-        <v>0</v>
-      </c>
-      <c r="H85" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A86" s="2">
-        <v>46276</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D86" s="4">
-        <v>40000</v>
-      </c>
-      <c r="E86" s="4">
-        <v>40000</v>
-      </c>
-      <c r="F86" s="5"/>
-      <c r="G86" s="6">
-        <v>0</v>
-      </c>
-      <c r="H86" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A87" s="2">
-        <v>46276</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D87" s="4">
-        <v>40000</v>
-      </c>
-      <c r="E87" s="4">
-        <v>40000</v>
-      </c>
-      <c r="F87" s="5"/>
-      <c r="G87" s="6">
-        <v>0</v>
-      </c>
-      <c r="H87" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A88" s="2">
-        <v>46277</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D88" s="4">
-        <v>10000</v>
-      </c>
-      <c r="E88" s="4">
-        <v>10000</v>
-      </c>
-      <c r="F88" s="5"/>
-      <c r="G88" s="6">
-        <v>0</v>
-      </c>
-      <c r="H88" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A89" s="2">
-        <v>46277</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D89" s="4">
-        <v>10000</v>
-      </c>
-      <c r="E89" s="4">
-        <v>10000</v>
-      </c>
-      <c r="F89" s="5"/>
-      <c r="G89" s="6">
-        <v>0</v>
-      </c>
-      <c r="H89" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A90" s="2">
-        <v>46277</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D90" s="4">
-        <v>18000</v>
-      </c>
-      <c r="E90" s="4">
-        <v>18000</v>
-      </c>
-      <c r="F90" s="5"/>
-      <c r="G90" s="6">
-        <v>0</v>
-      </c>
-      <c r="H90" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A91" s="2">
-        <v>46277</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D91" s="4">
-        <v>20000</v>
-      </c>
-      <c r="E91" s="4">
-        <v>20000</v>
-      </c>
-      <c r="F91" s="5"/>
-      <c r="G91" s="6">
-        <v>0</v>
-      </c>
-      <c r="H91" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A92" s="2">
-        <v>46277</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D92" s="4">
-        <v>30000</v>
-      </c>
-      <c r="E92" s="4">
-        <v>30000</v>
-      </c>
-      <c r="F92" s="5"/>
-      <c r="G92" s="6">
-        <v>0</v>
-      </c>
-      <c r="H92" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A93" s="2">
-        <v>46277</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D93" s="4">
-        <v>40000</v>
-      </c>
-      <c r="E93" s="4">
-        <v>40000</v>
-      </c>
-      <c r="F93" s="5"/>
-      <c r="G93" s="6">
-        <v>0</v>
-      </c>
-      <c r="H93" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H8" xr:uid="{5C578346-EE80-DF41-8099-4E3028D96EBE}"/>
+  <autoFilter ref="A1:H1" xr:uid="{5C578346-EE80-DF41-8099-4E3028D96EBE}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/Plan.xlsx
+++ b/data/Plan.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raman/Documents/GitHub/production-board/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6713A39A-0E91-F14B-8913-FA2C331726F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6D1F6F6-F461-AB44-94E1-F059352A8222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16560" xr2:uid="{7C08584A-5D47-2049-B143-911B93E5D6E0}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{7C08584A-5D47-2049-B143-911B93E5D6E0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$72</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="123">
   <si>
     <t>Date</t>
   </si>
@@ -95,12 +95,6 @@
     <t>Rosemary &amp; Rice Water Hair Spray-200ml - TikTok US</t>
   </si>
   <si>
-    <t>USTTCAP70</t>
-  </si>
-  <si>
-    <t> Roll On -  White jasmine 40 ml- Tik Tok US</t>
-  </si>
-  <si>
     <t>CAP137</t>
   </si>
   <si>
@@ -143,30 +137,12 @@
     <t>Exfoliating face wash 100 ml</t>
   </si>
   <si>
-    <t>USTTCAP24</t>
-  </si>
-  <si>
-    <t>Exfoliating Body Wash-236ml</t>
-  </si>
-  <si>
     <t>CAP165</t>
   </si>
   <si>
     <t>Epsom Body Wash - 236ml</t>
   </si>
   <si>
-    <t>CAP145</t>
-  </si>
-  <si>
-    <t>Oil &amp; Acne Control Face Wash - Flipkart pack of 3</t>
-  </si>
-  <si>
-    <t>CAP144</t>
-  </si>
-  <si>
-    <t>Oil &amp; Acne Control Face Wash - Flipkart pack of 2</t>
-  </si>
-  <si>
     <t>USTTBA10</t>
   </si>
   <si>
@@ -185,24 +161,6 @@
     <t>Deep Cleansing Body Wash 236ml</t>
   </si>
   <si>
-    <t>BA66</t>
-  </si>
-  <si>
-    <t>Rosemary hair growth oil 100ml</t>
-  </si>
-  <si>
-    <t>BA88</t>
-  </si>
-  <si>
-    <t>Gentle Cleansing Shampoo- 750ml</t>
-  </si>
-  <si>
-    <t>CAP17</t>
-  </si>
-  <si>
-    <t>Brightening Body Wash (473 ml)</t>
-  </si>
-  <si>
     <t>CAP16</t>
   </si>
   <si>
@@ -251,12 +209,6 @@
     <t>AHA Body Lotion 236 ml</t>
   </si>
   <si>
-    <t>CAP50</t>
-  </si>
-  <si>
-    <t>Under Arm Roll On - 40 ml / Peach (Rectangular Monocarton)-399</t>
-  </si>
-  <si>
     <t>CAP49</t>
   </si>
   <si>
@@ -296,24 +248,6 @@
     <t>Combo- Anti-Hairfall Shampoo (100ml) + Anti-Hairfall Conditioner (100g)</t>
   </si>
   <si>
-    <t>BA93</t>
-  </si>
-  <si>
-    <t>EXPERT | Ultra Smoothing Serum (100 ML)</t>
-  </si>
-  <si>
-    <t>TRA4</t>
-  </si>
-  <si>
-    <t>Tierra Shampoo- 5L</t>
-  </si>
-  <si>
-    <t>TRA3</t>
-  </si>
-  <si>
-    <t>Tierra body lotion- 5L</t>
-  </si>
-  <si>
     <t>CAP146</t>
   </si>
   <si>
@@ -354,6 +288,129 @@
   </si>
   <si>
     <t>Under Eye Cream 15 gm</t>
+  </si>
+  <si>
+    <t>CAP53</t>
+  </si>
+  <si>
+    <t>Anti-Frizz Leave-In Conditioner</t>
+  </si>
+  <si>
+    <t>BA26</t>
+  </si>
+  <si>
+    <t>EXPERT | Scalp Scrub (250 gms)</t>
+  </si>
+  <si>
+    <t>BA119</t>
+  </si>
+  <si>
+    <t>Anti hairfall shampoo 750 ml</t>
+  </si>
+  <si>
+    <t>CAP105</t>
+  </si>
+  <si>
+    <t>Gentle Exfoliating Face Scrub 100ML</t>
+  </si>
+  <si>
+    <t>BA22</t>
+  </si>
+  <si>
+    <t>BA Expert | Anti Hairfall Shampoo 250 ml</t>
+  </si>
+  <si>
+    <t>CAP106</t>
+  </si>
+  <si>
+    <t>Brightening Face Serum(10% VitaminC)30ml</t>
+  </si>
+  <si>
+    <t>CAP132</t>
+  </si>
+  <si>
+    <t>2% Salicylic Acid Serum 10ml</t>
+  </si>
+  <si>
+    <t>BA112</t>
+  </si>
+  <si>
+    <t>Anti Hairfall Shampoo - 450ml</t>
+  </si>
+  <si>
+    <t>BA50</t>
+  </si>
+  <si>
+    <t>Curl Intensifying Leave in Conditioner 140 ml</t>
+  </si>
+  <si>
+    <t>HO8</t>
+  </si>
+  <si>
+    <t>HORECA Neroli Amber Body Wash 5L</t>
+  </si>
+  <si>
+    <t>HO12</t>
+  </si>
+  <si>
+    <t>Horeca hand wash 5L</t>
+  </si>
+  <si>
+    <t>CAP139</t>
+  </si>
+  <si>
+    <t>Cherry Lip Balm 4.5gm</t>
+  </si>
+  <si>
+    <t>CAP138</t>
+  </si>
+  <si>
+    <t>Natural Lip Balm 4.5gm</t>
+  </si>
+  <si>
+    <t>BA65</t>
+  </si>
+  <si>
+    <t>Derma Roller</t>
+  </si>
+  <si>
+    <t>BA110</t>
+  </si>
+  <si>
+    <t>Instant Cover-Up Hair Powder Black-4gm</t>
+  </si>
+  <si>
+    <t>BA111</t>
+  </si>
+  <si>
+    <t>Instant Cover-Up Hair Powder Brown-4gm</t>
+  </si>
+  <si>
+    <t>CAP157</t>
+  </si>
+  <si>
+    <t>Age Defence Night Cream-30gm</t>
+  </si>
+  <si>
+    <t>UKTTBA107</t>
+  </si>
+  <si>
+    <t>Hair Growth Serum Roll On 25 ml</t>
+  </si>
+  <si>
+    <t>Outsouce</t>
+  </si>
+  <si>
+    <t>EXPERT | Ultra Smoothing Hair Mask (250 gms)</t>
+  </si>
+  <si>
+    <t>EXPERT | Ultra Smoothing Hair Mask (250 gms) US TT</t>
+  </si>
+  <si>
+    <t>BA9</t>
+  </si>
+  <si>
+    <t>USTTBA9</t>
   </si>
 </sst>
 </file>
@@ -414,7 +471,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -427,6 +484,7 @@
     <xf numFmtId="9" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="16" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -761,7 +819,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C578346-EE80-DF41-8099-4E3028D96EBE}">
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="57.1640625" customWidth="1"/>
@@ -792,13 +850,13 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="11">
-        <v>46272</v>
+        <v>46275</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="D2" s="8">
         <v>10000</v>
@@ -811,18 +869,18 @@
         <v>0</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="11">
-        <v>46272</v>
+        <v>46275</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="D3" s="8">
         <v>10000</v>
@@ -835,762 +893,762 @@
         <v>0</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="D4" s="4">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="E4" s="4">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="6">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D5" s="4">
-        <v>1000</v>
+        <v>3199</v>
       </c>
       <c r="E5" s="4">
-        <v>1000</v>
+        <v>3199</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="6">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="D6" s="4">
-        <v>1500</v>
+        <v>5000</v>
       </c>
       <c r="E6" s="4">
-        <v>1500</v>
+        <v>5000</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D7" s="4">
-        <v>2000</v>
+        <v>7400</v>
       </c>
       <c r="E7" s="4">
-        <v>2000</v>
+        <v>7400</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="6">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D8" s="4">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="E8" s="4">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="6">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="D9" s="4">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="E9" s="4">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="6">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="D10" s="4">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="E10" s="4">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="6">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>84</v>
+        <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="D11" s="4">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="E11" s="4">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="6">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D12" s="4">
-        <v>5000</v>
+        <v>16000</v>
       </c>
       <c r="E12" s="4">
-        <v>5000</v>
+        <v>16000</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="6">
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="D13" s="4">
-        <v>5000</v>
+        <v>14000</v>
       </c>
       <c r="E13" s="4">
-        <v>5000</v>
+        <v>14000</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="6">
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D14" s="4">
-        <v>8000</v>
+        <v>20000</v>
       </c>
       <c r="E14" s="4">
-        <v>8000</v>
+        <v>20000</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="6">
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="D15" s="4">
-        <v>11000</v>
+        <v>20000</v>
       </c>
       <c r="E15" s="4">
-        <v>11000</v>
+        <v>20000</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="6">
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="D16" s="4">
-        <v>18000</v>
+        <v>40000</v>
       </c>
       <c r="E16" s="4">
-        <v>18000</v>
+        <v>40000</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="6">
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="D17" s="4">
-        <v>20000</v>
+        <v>1800</v>
       </c>
       <c r="E17" s="4">
-        <v>20000</v>
+        <v>1800</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="6">
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D18" s="4">
-        <v>24000</v>
+        <v>3000</v>
       </c>
       <c r="E18" s="4">
-        <v>24000</v>
+        <v>3000</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="6">
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="D19" s="4">
-        <v>24000</v>
+        <v>5000</v>
       </c>
       <c r="E19" s="4">
-        <v>24000</v>
+        <v>5000</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="6">
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="D20" s="4">
-        <v>25000</v>
+        <v>5000</v>
       </c>
       <c r="E20" s="4">
-        <v>25000</v>
+        <v>5000</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="6">
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D21" s="3">
-        <v>50</v>
-      </c>
-      <c r="E21" s="3">
-        <v>50</v>
+        <v>24</v>
+      </c>
+      <c r="D21" s="4">
+        <v>10000</v>
+      </c>
+      <c r="E21" s="4">
+        <v>10000</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="6">
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>88</v>
+        <v>11</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D22" s="3">
-        <v>50</v>
-      </c>
-      <c r="E22" s="3">
-        <v>50</v>
+        <v>12</v>
+      </c>
+      <c r="D22" s="4">
+        <v>10000</v>
+      </c>
+      <c r="E22" s="4">
+        <v>10000</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="6">
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D23" s="4">
-        <v>1800</v>
+        <v>16000</v>
       </c>
       <c r="E23" s="4">
-        <v>1800</v>
+        <v>16000</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="6">
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="D24" s="4">
-        <v>5000</v>
+        <v>20000</v>
       </c>
       <c r="E24" s="4">
-        <v>5000</v>
+        <v>20000</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="6">
         <v>0</v>
       </c>
       <c r="H24" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="D25" s="4">
-        <v>6000</v>
+        <v>20000</v>
       </c>
       <c r="E25" s="4">
-        <v>6000</v>
+        <v>20000</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="6">
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D26" s="4">
-        <v>10000</v>
+        <v>24000</v>
       </c>
       <c r="E26" s="4">
-        <v>10000</v>
+        <v>24000</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="6">
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="D27" s="4">
-        <v>16000</v>
+        <v>24000</v>
       </c>
       <c r="E27" s="4">
-        <v>16000</v>
+        <v>24000</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="6">
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="D28" s="4">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="E28" s="4">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="6">
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="D29" s="4">
-        <v>20000</v>
-      </c>
-      <c r="E29" s="4">
-        <v>20000</v>
+        <v>3520</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="6">
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D30" s="4">
-        <v>20000</v>
+        <v>1800</v>
       </c>
       <c r="E30" s="4">
-        <v>20000</v>
+        <v>1800</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="6">
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D31" s="4">
-        <v>24000</v>
+        <v>2500</v>
       </c>
       <c r="E31" s="4">
-        <v>24000</v>
+        <v>2500</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="6">
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="D32" s="4">
-        <v>40000</v>
+        <v>3000</v>
       </c>
       <c r="E32" s="4">
-        <v>40000</v>
+        <v>3000</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="6">
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D33" s="4">
-        <v>3000</v>
+        <v>6500</v>
       </c>
       <c r="E33" s="4">
-        <v>3000</v>
+        <v>6500</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="6">
         <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="D34" s="4">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="E34" s="4">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="6">
         <v>0</v>
       </c>
       <c r="H34" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D35" s="4">
         <v>10000</v>
@@ -1603,66 +1661,66 @@
         <v>0</v>
       </c>
       <c r="H35" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="D36" s="4">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="E36" s="4">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="6">
         <v>0</v>
       </c>
       <c r="H36" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="D37" s="4">
-        <v>16000</v>
+        <v>20000</v>
       </c>
       <c r="E37" s="4">
-        <v>16000</v>
+        <v>20000</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="6">
         <v>0</v>
       </c>
       <c r="H37" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>9</v>
+        <v>90</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="D38" s="4">
         <v>20000</v>
@@ -1675,114 +1733,114 @@
         <v>0</v>
       </c>
       <c r="H38" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>94</v>
+        <v>15</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="D39" s="4">
-        <v>24000</v>
+        <v>40000</v>
       </c>
       <c r="E39" s="4">
-        <v>24000</v>
+        <v>40000</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="6">
         <v>0</v>
       </c>
       <c r="H39" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="D40" s="4">
-        <v>40000</v>
+        <v>48000</v>
       </c>
       <c r="E40" s="4">
-        <v>40000</v>
+        <v>48000</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="6">
         <v>0</v>
       </c>
       <c r="H40" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D41" s="4">
-        <v>48000</v>
+        <v>8000</v>
       </c>
       <c r="E41" s="4">
-        <v>48000</v>
+        <v>8000</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="6">
         <v>0</v>
       </c>
       <c r="H41" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="D42" s="4">
-        <v>3520</v>
-      </c>
-      <c r="E42" s="3">
-        <v>0</v>
+        <v>8000</v>
+      </c>
+      <c r="E42" s="4">
+        <v>8000</v>
       </c>
       <c r="F42" s="5"/>
       <c r="G42" s="6">
         <v>0</v>
       </c>
       <c r="H42" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="D43" s="4">
         <v>10000</v>
@@ -1795,18 +1853,18 @@
         <v>0</v>
       </c>
       <c r="H43" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="D44" s="4">
         <v>10000</v>
@@ -1819,42 +1877,42 @@
         <v>0</v>
       </c>
       <c r="H44" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="D45" s="4">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="E45" s="4">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="6">
         <v>0</v>
       </c>
       <c r="H45" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>7</v>
+        <v>90</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="D46" s="4">
         <v>20000</v>
@@ -1867,114 +1925,114 @@
         <v>0</v>
       </c>
       <c r="H46" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D47" s="4">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="E47" s="4">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="6">
         <v>0</v>
       </c>
       <c r="H47" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="D48" s="4">
-        <v>24000</v>
+        <v>40000</v>
       </c>
       <c r="E48" s="4">
-        <v>24000</v>
+        <v>40000</v>
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="6">
         <v>0</v>
       </c>
       <c r="H48" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>16</v>
+        <v>93</v>
       </c>
       <c r="D49" s="4">
-        <v>40000</v>
+        <v>7000</v>
       </c>
       <c r="E49" s="4">
-        <v>40000</v>
+        <v>7000</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="6">
         <v>0</v>
       </c>
       <c r="H49" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="D50" s="4">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="E50" s="4">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="6">
         <v>0</v>
       </c>
       <c r="H50" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="D51" s="4">
         <v>10000</v>
@@ -1987,12 +2045,12 @@
         <v>0</v>
       </c>
       <c r="H51" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>82</v>
@@ -2001,28 +2059,28 @@
         <v>83</v>
       </c>
       <c r="D52" s="4">
-        <v>10000</v>
+        <v>13000</v>
       </c>
       <c r="E52" s="4">
-        <v>10000</v>
+        <v>13000</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="6">
         <v>0</v>
       </c>
       <c r="H52" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D53" s="4">
         <v>20000</v>
@@ -2035,55 +2093,55 @@
         <v>0</v>
       </c>
       <c r="H53" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="D54" s="4">
-        <v>40000</v>
+        <v>24000</v>
       </c>
       <c r="E54" s="4">
-        <v>40000</v>
+        <v>24000</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="6">
         <v>0</v>
       </c>
       <c r="H54" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="D55" s="4">
-        <v>40000</v>
+        <v>28000</v>
       </c>
       <c r="E55" s="4">
-        <v>40000</v>
+        <v>28000</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="6">
         <v>0</v>
       </c>
       <c r="H55" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
@@ -2091,215 +2149,215 @@
         <v>46277</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="D56" s="4">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="E56" s="4">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="6">
         <v>0</v>
       </c>
       <c r="H56" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D57" s="4">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="E57" s="4">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="F57" s="5"/>
       <c r="G57" s="6">
         <v>0</v>
       </c>
       <c r="H57" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="D58" s="4">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="E58" s="4">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="F58" s="5"/>
       <c r="G58" s="6">
         <v>0</v>
       </c>
       <c r="H58" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>28</v>
+        <v>99</v>
       </c>
       <c r="D59" s="4">
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="E59" s="4">
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="F59" s="5"/>
       <c r="G59" s="6">
         <v>0</v>
       </c>
       <c r="H59" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D60" s="4">
-        <v>18000</v>
+        <v>7000</v>
       </c>
       <c r="E60" s="4">
-        <v>18000</v>
+        <v>7000</v>
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="6">
         <v>0</v>
       </c>
       <c r="H60" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="D61" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E61" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="6">
         <v>0</v>
       </c>
       <c r="H61" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D62" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E62" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="6">
         <v>0</v>
       </c>
       <c r="H62" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D63" s="4">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="E63" s="4">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="F63" s="5"/>
       <c r="G63" s="6">
         <v>0</v>
       </c>
       <c r="H63" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D64" s="4">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="E64" s="4">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="6">
         <v>0</v>
       </c>
       <c r="H64" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
@@ -2307,23 +2365,23 @@
         <v>46278</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
       <c r="D65" s="4">
-        <v>2500</v>
+        <v>30000</v>
       </c>
       <c r="E65" s="4">
-        <v>2500</v>
+        <v>30000</v>
       </c>
       <c r="F65" s="5"/>
       <c r="G65" s="6">
         <v>0</v>
       </c>
       <c r="H65" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
@@ -2331,75 +2389,480 @@
         <v>46278</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>102</v>
+        <v>13</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="D66" s="4">
-        <v>15000</v>
+        <v>40000</v>
       </c>
       <c r="E66" s="4">
-        <v>15000</v>
+        <v>40000</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="6">
         <v>0</v>
       </c>
       <c r="H66" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D67" s="4">
-        <v>20000</v>
-      </c>
-      <c r="E67" s="4">
-        <v>20000</v>
+        <v>101</v>
+      </c>
+      <c r="D67" s="3">
+        <v>50</v>
+      </c>
+      <c r="E67" s="3">
+        <v>50</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="6">
         <v>0</v>
       </c>
       <c r="H67" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>15</v>
+        <v>102</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D68" s="4">
-        <v>40000</v>
-      </c>
-      <c r="E68" s="4">
-        <v>40000</v>
+        <v>103</v>
+      </c>
+      <c r="D68" s="3">
+        <v>50</v>
+      </c>
+      <c r="E68" s="3">
+        <v>50</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="6">
         <v>0</v>
       </c>
       <c r="H68" t="s">
-        <v>77</v>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A69" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D69" s="4">
+        <v>10000</v>
+      </c>
+      <c r="E69" s="4">
+        <v>10000</v>
+      </c>
+      <c r="F69" s="5"/>
+      <c r="G69" s="6">
+        <v>0</v>
+      </c>
+      <c r="H69" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A70" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D70" s="4">
+        <v>11000</v>
+      </c>
+      <c r="E70" s="4">
+        <v>11000</v>
+      </c>
+      <c r="F70" s="5"/>
+      <c r="G70" s="6">
+        <v>0</v>
+      </c>
+      <c r="H70" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A71" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D71" s="4">
+        <v>40000</v>
+      </c>
+      <c r="E71" s="4">
+        <v>40000</v>
+      </c>
+      <c r="F71" s="5"/>
+      <c r="G71" s="6">
+        <v>0</v>
+      </c>
+      <c r="H71" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A72" s="2">
+        <v>46279</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D72" s="4">
+        <v>40000</v>
+      </c>
+      <c r="E72" s="4">
+        <v>40000</v>
+      </c>
+      <c r="F72" s="5"/>
+      <c r="G72" s="6">
+        <v>0</v>
+      </c>
+      <c r="H72" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A73" s="2">
+        <v>46289</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D73" s="4">
+        <v>30000</v>
+      </c>
+      <c r="E73" s="4">
+        <v>30000</v>
+      </c>
+      <c r="F73" s="5"/>
+      <c r="G73" s="6">
+        <v>0</v>
+      </c>
+      <c r="H73" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A74" s="2">
+        <v>46289</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D74" s="4">
+        <v>25000</v>
+      </c>
+      <c r="E74" s="4">
+        <v>25000</v>
+      </c>
+      <c r="F74" s="5"/>
+      <c r="G74" s="6">
+        <v>0</v>
+      </c>
+      <c r="H74" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A75" s="2">
+        <v>46277</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D75" s="4">
+        <v>4000</v>
+      </c>
+      <c r="E75" s="4">
+        <v>4000</v>
+      </c>
+      <c r="F75" s="5"/>
+      <c r="G75" s="6">
+        <v>0</v>
+      </c>
+      <c r="H75" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A76" s="2">
+        <v>46292</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D76" s="4">
+        <v>25000</v>
+      </c>
+      <c r="E76" s="4">
+        <v>25000</v>
+      </c>
+      <c r="F76" s="5"/>
+      <c r="G76" s="6">
+        <v>0</v>
+      </c>
+      <c r="H76" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A77" s="2">
+        <v>46292</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D77" s="4">
+        <v>25000</v>
+      </c>
+      <c r="E77" s="4">
+        <v>25000</v>
+      </c>
+      <c r="F77" s="5"/>
+      <c r="G77" s="6">
+        <v>0</v>
+      </c>
+      <c r="H77" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A78" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D78" s="4">
+        <v>9800</v>
+      </c>
+      <c r="E78" s="4">
+        <v>9800</v>
+      </c>
+      <c r="F78" s="5"/>
+      <c r="G78" s="6">
+        <v>0</v>
+      </c>
+      <c r="H78" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A79" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D79" s="4">
+        <v>20000</v>
+      </c>
+      <c r="E79" s="4">
+        <v>20000</v>
+      </c>
+      <c r="F79" s="5"/>
+      <c r="G79" s="6">
+        <v>0</v>
+      </c>
+      <c r="H79" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A80" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D80" s="4">
+        <v>7000</v>
+      </c>
+      <c r="E80" s="4">
+        <v>7000</v>
+      </c>
+      <c r="F80" s="5"/>
+      <c r="G80" s="6">
+        <v>0</v>
+      </c>
+      <c r="H80" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A81" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D81" s="4">
+        <v>7000</v>
+      </c>
+      <c r="E81" s="4">
+        <v>7000</v>
+      </c>
+      <c r="F81" s="5"/>
+      <c r="G81" s="6">
+        <v>0</v>
+      </c>
+      <c r="H81" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A82" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D82" s="4">
+        <v>7900</v>
+      </c>
+      <c r="E82" s="4">
+        <v>7900</v>
+      </c>
+      <c r="F82" s="5"/>
+      <c r="G82" s="6">
+        <v>0</v>
+      </c>
+      <c r="H82" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A83" s="12">
+        <v>46276</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D83" s="4">
+        <v>50000</v>
+      </c>
+      <c r="E83" s="4">
+        <v>50000</v>
+      </c>
+      <c r="G83" s="6">
+        <v>0</v>
+      </c>
+      <c r="H83" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A84" s="12">
+        <v>46277</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D84" s="4">
+        <v>50000</v>
+      </c>
+      <c r="E84" s="4">
+        <v>50000</v>
+      </c>
+      <c r="G84" s="6">
+        <v>0</v>
+      </c>
+      <c r="H84" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A85" s="12">
+        <v>46281</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D85" s="4">
+        <v>22000</v>
+      </c>
+      <c r="E85" s="4">
+        <v>22000</v>
+      </c>
+      <c r="G85" s="6">
+        <v>0</v>
+      </c>
+      <c r="H85" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1" xr:uid="{5C578346-EE80-DF41-8099-4E3028D96EBE}"/>
+  <autoFilter ref="A1:H72" xr:uid="{5C578346-EE80-DF41-8099-4E3028D96EBE}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/Plan.xlsx
+++ b/data/Plan.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raman/Documents/GitHub/production-board/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6D1F6F6-F461-AB44-94E1-F059352A8222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95CC446A-898A-2648-891A-6223B23B5F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{7C08584A-5D47-2049-B143-911B93E5D6E0}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16560" xr2:uid="{7C08584A-5D47-2049-B143-911B93E5D6E0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$60</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="115">
   <si>
     <t>Date</t>
   </si>
@@ -125,12 +125,6 @@
     <t>Curl Intensifying Leave in Conditioner USTT</t>
   </si>
   <si>
-    <t>USTTCAP62</t>
-  </si>
-  <si>
-    <t>AHA Body Lotion 236ml - Tik Tok US</t>
-  </si>
-  <si>
     <t>CAP153</t>
   </si>
   <si>
@@ -143,48 +137,18 @@
     <t>Epsom Body Wash - 236ml</t>
   </si>
   <si>
-    <t>USTTBA10</t>
-  </si>
-  <si>
-    <t>EXPERT | Ultra Smoothing Shampoo (250 ML) -  TikTok US</t>
-  </si>
-  <si>
     <t>CAP107</t>
   </si>
   <si>
     <t>Brightening face serum (10% Vitamin C) 10ml</t>
   </si>
   <si>
-    <t>CAP134</t>
-  </si>
-  <si>
-    <t>Deep Cleansing Body Wash 236ml</t>
-  </si>
-  <si>
-    <t>CAP16</t>
-  </si>
-  <si>
-    <t>Brightening Body Wash (236 ml)</t>
-  </si>
-  <si>
     <t>BA97</t>
   </si>
   <si>
     <t>Anti-Hairfall Conditioner - 175gm</t>
   </si>
   <si>
-    <t>BA51</t>
-  </si>
-  <si>
-    <t>BA Gentle Cleansing Shampoo</t>
-  </si>
-  <si>
-    <t>CAP65</t>
-  </si>
-  <si>
-    <t>Neck, Knee, Elbow Brightening Roll On</t>
-  </si>
-  <si>
     <t>BA82</t>
   </si>
   <si>
@@ -411,6 +375,18 @@
   </si>
   <si>
     <t>USTTBA9</t>
+  </si>
+  <si>
+    <t>UKTTBA76</t>
+  </si>
+  <si>
+    <t>Hair Growth Spray- TikTok UK</t>
+  </si>
+  <si>
+    <t>CAP177</t>
+  </si>
+  <si>
+    <t>Odour Control Underarm Mist - Aqua</t>
   </si>
 </sst>
 </file>
@@ -819,7 +795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C578346-EE80-DF41-8099-4E3028D96EBE}">
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="57.1640625" customWidth="1"/>
@@ -853,10 +829,10 @@
         <v>46275</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D2" s="8">
         <v>10000</v>
@@ -869,7 +845,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -877,10 +853,10 @@
         <v>46275</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D3" s="8">
         <v>10000</v>
@@ -893,114 +869,114 @@
         <v>0</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D4" s="4">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="E4" s="4">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="6">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D5" s="4">
-        <v>3199</v>
+        <v>2200</v>
       </c>
       <c r="E5" s="4">
-        <v>3199</v>
+        <v>2200</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="6">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D6" s="4">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="E6" s="4">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D7" s="4">
-        <v>7400</v>
+        <v>3000</v>
       </c>
       <c r="E7" s="4">
-        <v>7400</v>
+        <v>3000</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="6">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="D8" s="4">
         <v>5000</v>
@@ -1013,42 +989,42 @@
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D9" s="4">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="E9" s="4">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="6">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="D10" s="4">
         <v>10000</v>
@@ -1061,132 +1037,132 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="D11" s="4">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="E11" s="4">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="6">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D12" s="4">
-        <v>16000</v>
+        <v>20000</v>
       </c>
       <c r="E12" s="4">
-        <v>16000</v>
+        <v>20000</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="6">
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="D13" s="4">
-        <v>14000</v>
+        <v>20000</v>
       </c>
       <c r="E13" s="4">
-        <v>14000</v>
+        <v>20000</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="6">
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D14" s="4">
-        <v>20000</v>
+        <v>24000</v>
       </c>
       <c r="E14" s="4">
-        <v>20000</v>
+        <v>24000</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="6">
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D15" s="4">
-        <v>20000</v>
+        <v>24000</v>
       </c>
       <c r="E15" s="4">
-        <v>20000</v>
+        <v>24000</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="6">
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>15</v>
@@ -1205,18 +1181,18 @@
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="D17" s="4">
         <v>1800</v>
@@ -1229,90 +1205,90 @@
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="D18" s="4">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="E18" s="4">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="6">
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D19" s="4">
-        <v>5000</v>
+        <v>6500</v>
       </c>
       <c r="E19" s="4">
-        <v>5000</v>
+        <v>6500</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="6">
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="D20" s="4">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="E20" s="4">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="6">
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D21" s="4">
         <v>10000</v>
@@ -1325,66 +1301,66 @@
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="D22" s="4">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="E22" s="4">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="6">
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="D23" s="4">
-        <v>16000</v>
+        <v>20000</v>
       </c>
       <c r="E23" s="4">
-        <v>16000</v>
+        <v>20000</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="6">
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="D24" s="4">
         <v>20000</v>
@@ -1397,612 +1373,612 @@
         <v>0</v>
       </c>
       <c r="H24" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>29</v>
+        <v>111</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="D25" s="4">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="E25" s="4">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="6">
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D26" s="4">
-        <v>24000</v>
+        <v>48000</v>
       </c>
       <c r="E26" s="4">
-        <v>24000</v>
+        <v>48000</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="6">
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D27" s="4">
-        <v>24000</v>
+        <v>4500</v>
       </c>
       <c r="E27" s="4">
-        <v>24000</v>
+        <v>4500</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="6">
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D28" s="4">
-        <v>40000</v>
+        <v>8000</v>
       </c>
       <c r="E28" s="4">
-        <v>40000</v>
+        <v>8000</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="6">
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D29" s="4">
-        <v>3520</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
+        <v>8000</v>
+      </c>
+      <c r="E29" s="4">
+        <v>8000</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="6">
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D30" s="4">
-        <v>1800</v>
+        <v>10000</v>
       </c>
       <c r="E30" s="4">
-        <v>1800</v>
+        <v>10000</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="6">
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="D31" s="4">
-        <v>2500</v>
+        <v>10000</v>
       </c>
       <c r="E31" s="4">
-        <v>2500</v>
+        <v>10000</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="6">
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="D32" s="4">
-        <v>3000</v>
+        <v>20000</v>
       </c>
       <c r="E32" s="4">
-        <v>3000</v>
+        <v>20000</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="6">
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D33" s="4">
-        <v>6500</v>
+        <v>20000</v>
       </c>
       <c r="E33" s="4">
-        <v>6500</v>
+        <v>20000</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="6">
         <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D34" s="4">
-        <v>10000</v>
+        <v>30000</v>
       </c>
       <c r="E34" s="4">
-        <v>10000</v>
+        <v>30000</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="6">
         <v>0</v>
       </c>
       <c r="H34" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D35" s="4">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="E35" s="4">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="6">
         <v>0</v>
       </c>
       <c r="H35" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D36" s="4">
-        <v>20000</v>
+        <v>7000</v>
       </c>
       <c r="E36" s="4">
-        <v>20000</v>
+        <v>7000</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="6">
         <v>0</v>
       </c>
       <c r="H36" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="D37" s="4">
-        <v>20000</v>
+        <v>9000</v>
       </c>
       <c r="E37" s="4">
-        <v>20000</v>
+        <v>9000</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="6">
         <v>0</v>
       </c>
       <c r="H37" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>91</v>
+        <v>24</v>
       </c>
       <c r="D38" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E38" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="6">
         <v>0</v>
       </c>
       <c r="H38" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="D39" s="4">
-        <v>40000</v>
+        <v>10000</v>
       </c>
       <c r="E39" s="4">
-        <v>40000</v>
+        <v>10000</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="6">
         <v>0</v>
       </c>
       <c r="H39" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="D40" s="4">
-        <v>48000</v>
+        <v>13000</v>
       </c>
       <c r="E40" s="4">
-        <v>48000</v>
+        <v>13000</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="6">
         <v>0</v>
       </c>
       <c r="H40" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="D41" s="4">
-        <v>8000</v>
+        <v>20000</v>
       </c>
       <c r="E41" s="4">
-        <v>8000</v>
+        <v>20000</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="6">
         <v>0</v>
       </c>
       <c r="H41" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="D42" s="4">
-        <v>8000</v>
+        <v>24000</v>
       </c>
       <c r="E42" s="4">
-        <v>8000</v>
+        <v>24000</v>
       </c>
       <c r="F42" s="5"/>
       <c r="G42" s="6">
         <v>0</v>
       </c>
       <c r="H42" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="D43" s="4">
-        <v>10000</v>
+        <v>28000</v>
       </c>
       <c r="E43" s="4">
-        <v>10000</v>
+        <v>28000</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="6">
         <v>0</v>
       </c>
       <c r="H43" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="D44" s="4">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="E44" s="4">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="6">
         <v>0</v>
       </c>
       <c r="H44" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="D45" s="4">
-        <v>20000</v>
+        <v>4000</v>
       </c>
       <c r="E45" s="4">
-        <v>20000</v>
+        <v>4000</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="6">
         <v>0</v>
       </c>
       <c r="H45" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D46" s="4">
-        <v>20000</v>
+        <v>6000</v>
       </c>
       <c r="E46" s="4">
-        <v>20000</v>
+        <v>6000</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="6">
         <v>0</v>
       </c>
       <c r="H46" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>7</v>
+        <v>86</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>8</v>
+        <v>87</v>
       </c>
       <c r="D47" s="4">
-        <v>30000</v>
+        <v>6000</v>
       </c>
       <c r="E47" s="4">
-        <v>30000</v>
+        <v>6000</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="6">
         <v>0</v>
       </c>
       <c r="H47" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D48" s="4">
-        <v>40000</v>
+        <v>7000</v>
       </c>
       <c r="E48" s="4">
-        <v>40000</v>
+        <v>7000</v>
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="6">
         <v>0</v>
       </c>
       <c r="H48" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>92</v>
+        <v>54</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="D49" s="4">
-        <v>7000</v>
+        <v>10000</v>
       </c>
       <c r="E49" s="4">
-        <v>7000</v>
+        <v>10000</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="6">
         <v>0</v>
       </c>
       <c r="H49" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>23</v>
@@ -2021,848 +1997,560 @@
         <v>0</v>
       </c>
       <c r="H50" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="D51" s="4">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="E51" s="4">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="6">
         <v>0</v>
       </c>
       <c r="H51" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="D52" s="4">
-        <v>13000</v>
+        <v>20000</v>
       </c>
       <c r="E52" s="4">
-        <v>13000</v>
+        <v>20000</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="6">
         <v>0</v>
       </c>
       <c r="H52" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D53" s="4">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="E53" s="4">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="6">
         <v>0</v>
       </c>
       <c r="H53" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="D54" s="4">
-        <v>24000</v>
+        <v>40000</v>
       </c>
       <c r="E54" s="4">
-        <v>24000</v>
+        <v>40000</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="6">
         <v>0</v>
       </c>
       <c r="H54" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D55" s="4">
-        <v>28000</v>
-      </c>
-      <c r="E55" s="4">
-        <v>28000</v>
+        <v>89</v>
+      </c>
+      <c r="D55" s="3">
+        <v>50</v>
+      </c>
+      <c r="E55" s="3">
+        <v>50</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="6">
         <v>0</v>
       </c>
       <c r="H55" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D56" s="4">
-        <v>40000</v>
-      </c>
-      <c r="E56" s="4">
-        <v>40000</v>
+        <v>91</v>
+      </c>
+      <c r="D56" s="3">
+        <v>50</v>
+      </c>
+      <c r="E56" s="3">
+        <v>50</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="6">
         <v>0</v>
       </c>
       <c r="H56" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>94</v>
+        <v>23</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>95</v>
+        <v>24</v>
       </c>
       <c r="D57" s="4">
-        <v>4000</v>
+        <v>10000</v>
       </c>
       <c r="E57" s="4">
-        <v>4000</v>
+        <v>10000</v>
       </c>
       <c r="F57" s="5"/>
       <c r="G57" s="6">
         <v>0</v>
       </c>
       <c r="H57" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="D58" s="4">
-        <v>6000</v>
+        <v>11000</v>
       </c>
       <c r="E58" s="4">
-        <v>6000</v>
+        <v>11000</v>
       </c>
       <c r="F58" s="5"/>
       <c r="G58" s="6">
         <v>0</v>
       </c>
       <c r="H58" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>98</v>
+        <v>15</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>99</v>
+        <v>16</v>
       </c>
       <c r="D59" s="4">
-        <v>6000</v>
+        <v>40000</v>
       </c>
       <c r="E59" s="4">
-        <v>6000</v>
+        <v>40000</v>
       </c>
       <c r="F59" s="5"/>
       <c r="G59" s="6">
         <v>0</v>
       </c>
       <c r="H59" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D60" s="4">
-        <v>7000</v>
+        <v>40000</v>
       </c>
       <c r="E60" s="4">
-        <v>7000</v>
+        <v>40000</v>
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="6">
         <v>0</v>
       </c>
       <c r="H60" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
-        <v>46278</v>
+        <v>46289</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="D61" s="4">
-        <v>10000</v>
+        <v>30000</v>
       </c>
       <c r="E61" s="4">
-        <v>10000</v>
+        <v>30000</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="6">
         <v>0</v>
       </c>
       <c r="H61" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
-        <v>46278</v>
+        <v>46289</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>23</v>
+        <v>94</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="D62" s="4">
-        <v>10000</v>
+        <v>25000</v>
       </c>
       <c r="E62" s="4">
-        <v>10000</v>
+        <v>25000</v>
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="6">
         <v>0</v>
       </c>
       <c r="H62" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
-        <v>46278</v>
+        <v>46277</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="D63" s="4">
-        <v>20000</v>
+        <v>4000</v>
       </c>
       <c r="E63" s="4">
-        <v>20000</v>
+        <v>4000</v>
       </c>
       <c r="F63" s="5"/>
       <c r="G63" s="6">
         <v>0</v>
       </c>
       <c r="H63" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
-        <v>46278</v>
+        <v>46292</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="D64" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="E64" s="4">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="6">
         <v>0</v>
       </c>
       <c r="H64" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
-        <v>46278</v>
+        <v>46292</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>16</v>
+        <v>101</v>
       </c>
       <c r="D65" s="4">
-        <v>30000</v>
+        <v>25000</v>
       </c>
       <c r="E65" s="4">
-        <v>30000</v>
+        <v>25000</v>
       </c>
       <c r="F65" s="5"/>
       <c r="G65" s="6">
         <v>0</v>
       </c>
       <c r="H65" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
-        <v>46278</v>
+        <v>46274</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="D66" s="4">
-        <v>40000</v>
+        <v>9800</v>
       </c>
       <c r="E66" s="4">
-        <v>40000</v>
+        <v>9800</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="6">
         <v>0</v>
       </c>
       <c r="H66" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
-        <v>46279</v>
+        <v>46275</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D67" s="3">
-        <v>50</v>
-      </c>
-      <c r="E67" s="3">
-        <v>50</v>
+        <v>105</v>
+      </c>
+      <c r="D67" s="4">
+        <v>20000</v>
+      </c>
+      <c r="E67" s="4">
+        <v>20000</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="6">
         <v>0</v>
       </c>
       <c r="H67" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D68" s="3">
-        <v>50</v>
-      </c>
-      <c r="E68" s="3">
-        <v>50</v>
+        <v>97</v>
+      </c>
+      <c r="D68" s="4">
+        <v>7000</v>
+      </c>
+      <c r="E68" s="4">
+        <v>7000</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="6">
         <v>0</v>
       </c>
       <c r="H68" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
-        <v>46279</v>
+        <v>46282</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>24</v>
+        <v>97</v>
       </c>
       <c r="D69" s="4">
-        <v>10000</v>
+        <v>7000</v>
       </c>
       <c r="E69" s="4">
-        <v>10000</v>
+        <v>7000</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="6">
         <v>0</v>
       </c>
       <c r="H69" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
-        <v>46279</v>
+        <v>46287</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="D70" s="4">
-        <v>11000</v>
+        <v>7900</v>
       </c>
       <c r="E70" s="4">
-        <v>11000</v>
+        <v>7900</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" s="6">
         <v>0</v>
       </c>
       <c r="H70" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A71" s="2">
-        <v>46279</v>
+      <c r="A71" s="12">
+        <v>46276</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>16</v>
+        <v>108</v>
       </c>
       <c r="D71" s="4">
-        <v>40000</v>
+        <v>50000</v>
       </c>
       <c r="E71" s="4">
-        <v>40000</v>
-      </c>
-      <c r="F71" s="5"/>
+        <v>50000</v>
+      </c>
       <c r="G71" s="6">
         <v>0</v>
       </c>
       <c r="H71" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A72" s="2">
-        <v>46279</v>
+      <c r="A72" s="12">
+        <v>46277</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>13</v>
+        <v>109</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>14</v>
+        <v>107</v>
       </c>
       <c r="D72" s="4">
-        <v>40000</v>
+        <v>50000</v>
       </c>
       <c r="E72" s="4">
-        <v>40000</v>
-      </c>
-      <c r="F72" s="5"/>
+        <v>50000</v>
+      </c>
       <c r="G72" s="6">
         <v>0</v>
       </c>
       <c r="H72" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A73" s="2">
-        <v>46289</v>
+      <c r="A73" s="12">
+        <v>46281</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D73" s="4">
-        <v>30000</v>
+        <v>22000</v>
       </c>
       <c r="E73" s="4">
-        <v>30000</v>
-      </c>
-      <c r="F73" s="5"/>
+        <v>22000</v>
+      </c>
       <c r="G73" s="6">
         <v>0</v>
       </c>
       <c r="H73" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A74" s="2">
-        <v>46289</v>
-      </c>
-      <c r="B74" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C74" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D74" s="4">
-        <v>25000</v>
-      </c>
-      <c r="E74" s="4">
-        <v>25000</v>
-      </c>
-      <c r="F74" s="5"/>
-      <c r="G74" s="6">
-        <v>0</v>
-      </c>
-      <c r="H74" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A75" s="2">
-        <v>46277</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D75" s="4">
-        <v>4000</v>
-      </c>
-      <c r="E75" s="4">
-        <v>4000</v>
-      </c>
-      <c r="F75" s="5"/>
-      <c r="G75" s="6">
-        <v>0</v>
-      </c>
-      <c r="H75" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A76" s="2">
-        <v>46292</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D76" s="4">
-        <v>25000</v>
-      </c>
-      <c r="E76" s="4">
-        <v>25000</v>
-      </c>
-      <c r="F76" s="5"/>
-      <c r="G76" s="6">
-        <v>0</v>
-      </c>
-      <c r="H76" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A77" s="2">
-        <v>46292</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D77" s="4">
-        <v>25000</v>
-      </c>
-      <c r="E77" s="4">
-        <v>25000</v>
-      </c>
-      <c r="F77" s="5"/>
-      <c r="G77" s="6">
-        <v>0</v>
-      </c>
-      <c r="H77" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A78" s="2">
-        <v>46274</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D78" s="4">
-        <v>9800</v>
-      </c>
-      <c r="E78" s="4">
-        <v>9800</v>
-      </c>
-      <c r="F78" s="5"/>
-      <c r="G78" s="6">
-        <v>0</v>
-      </c>
-      <c r="H78" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A79" s="2">
-        <v>46275</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D79" s="4">
-        <v>20000</v>
-      </c>
-      <c r="E79" s="4">
-        <v>20000</v>
-      </c>
-      <c r="F79" s="5"/>
-      <c r="G79" s="6">
-        <v>0</v>
-      </c>
-      <c r="H79" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A80" s="2">
-        <v>46280</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D80" s="4">
-        <v>7000</v>
-      </c>
-      <c r="E80" s="4">
-        <v>7000</v>
-      </c>
-      <c r="F80" s="5"/>
-      <c r="G80" s="6">
-        <v>0</v>
-      </c>
-      <c r="H80" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A81" s="2">
-        <v>46282</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D81" s="4">
-        <v>7000</v>
-      </c>
-      <c r="E81" s="4">
-        <v>7000</v>
-      </c>
-      <c r="F81" s="5"/>
-      <c r="G81" s="6">
-        <v>0</v>
-      </c>
-      <c r="H81" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A82" s="2">
-        <v>46287</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D82" s="4">
-        <v>7900</v>
-      </c>
-      <c r="E82" s="4">
-        <v>7900</v>
-      </c>
-      <c r="F82" s="5"/>
-      <c r="G82" s="6">
-        <v>0</v>
-      </c>
-      <c r="H82" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A83" s="12">
-        <v>46276</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D83" s="4">
-        <v>50000</v>
-      </c>
-      <c r="E83" s="4">
-        <v>50000</v>
-      </c>
-      <c r="G83" s="6">
-        <v>0</v>
-      </c>
-      <c r="H83" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A84" s="12">
-        <v>46277</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D84" s="4">
-        <v>50000</v>
-      </c>
-      <c r="E84" s="4">
-        <v>50000</v>
-      </c>
-      <c r="G84" s="6">
-        <v>0</v>
-      </c>
-      <c r="H84" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A85" s="12">
-        <v>46281</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D85" s="4">
-        <v>22000</v>
-      </c>
-      <c r="E85" s="4">
-        <v>22000</v>
-      </c>
-      <c r="G85" s="6">
-        <v>0</v>
-      </c>
-      <c r="H85" t="s">
-        <v>118</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H72" xr:uid="{5C578346-EE80-DF41-8099-4E3028D96EBE}"/>
+  <autoFilter ref="A1:H60" xr:uid="{5C578346-EE80-DF41-8099-4E3028D96EBE}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/Plan.xlsx
+++ b/data/Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raman/Documents/GitHub/production-board/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95CC446A-898A-2648-891A-6223B23B5F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23BA6EC1-B0CE-3C48-900B-F27A1B15699F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16560" xr2:uid="{7C08584A-5D47-2049-B143-911B93E5D6E0}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="135">
   <si>
     <t>Date</t>
   </si>
@@ -77,12 +77,6 @@
     <t>EXPERT | Ultra Smoothing Serum (100 ML) - TikTok US</t>
   </si>
   <si>
-    <t>BA10</t>
-  </si>
-  <si>
-    <t>EXPERT | Ultra Smoothing Shampoo (250 ML)</t>
-  </si>
-  <si>
     <t>CAP24</t>
   </si>
   <si>
@@ -125,12 +119,6 @@
     <t>Curl Intensifying Leave in Conditioner USTT</t>
   </si>
   <si>
-    <t>CAP153</t>
-  </si>
-  <si>
-    <t>Exfoliating face wash 100 ml</t>
-  </si>
-  <si>
     <t>CAP165</t>
   </si>
   <si>
@@ -149,12 +137,6 @@
     <t>Anti-Hairfall Conditioner - 175gm</t>
   </si>
   <si>
-    <t>BA82</t>
-  </si>
-  <si>
-    <t>Ultra Smoothing Shampoo- 750ml</t>
-  </si>
-  <si>
     <t>CAP25</t>
   </si>
   <si>
@@ -173,12 +155,6 @@
     <t>AHA Body Lotion 236 ml</t>
   </si>
   <si>
-    <t>CAP49</t>
-  </si>
-  <si>
-    <t>Roll On: Fragrance Free (40 ml) (Rectangular)-399</t>
-  </si>
-  <si>
     <t>BA74</t>
   </si>
   <si>
@@ -218,12 +194,6 @@
     <t>Clarifying Face Serum - 10ml</t>
   </si>
   <si>
-    <t>BA72</t>
-  </si>
-  <si>
-    <t>Bare Anatomy Nature x Science Argan Oil &amp; Vitamin E Anti Frizz Serum 75 ml</t>
-  </si>
-  <si>
     <t>CAP154</t>
   </si>
   <si>
@@ -242,30 +212,12 @@
     <t>Bright Boost SPF Lotion 236 ml</t>
   </si>
   <si>
-    <t>CAP81</t>
-  </si>
-  <si>
-    <t>Hydrating Face Wash (Tube)-100ML</t>
-  </si>
-  <si>
-    <t>CAP152</t>
-  </si>
-  <si>
-    <t>Under Eye Cream 15 gm</t>
-  </si>
-  <si>
     <t>CAP53</t>
   </si>
   <si>
     <t>Anti-Frizz Leave-In Conditioner</t>
   </si>
   <si>
-    <t>BA26</t>
-  </si>
-  <si>
-    <t>EXPERT | Scalp Scrub (250 gms)</t>
-  </si>
-  <si>
     <t>BA119</t>
   </si>
   <si>
@@ -350,12 +302,6 @@
     <t>Instant Cover-Up Hair Powder Brown-4gm</t>
   </si>
   <si>
-    <t>CAP157</t>
-  </si>
-  <si>
-    <t>Age Defence Night Cream-30gm</t>
-  </si>
-  <si>
     <t>UKTTBA107</t>
   </si>
   <si>
@@ -387,6 +333,120 @@
   </si>
   <si>
     <t>Odour Control Underarm Mist - Aqua</t>
+  </si>
+  <si>
+    <t>USTTCAP25</t>
+  </si>
+  <si>
+    <t>Exfoliating Body Wash-473ml</t>
+  </si>
+  <si>
+    <t>CAP89</t>
+  </si>
+  <si>
+    <t>Hydrating Foot Cream</t>
+  </si>
+  <si>
+    <t>USTTCAP50</t>
+  </si>
+  <si>
+    <t>Under Arm Roll on - Peach Fragrence</t>
+  </si>
+  <si>
+    <t>CAP70</t>
+  </si>
+  <si>
+    <t>Underarm Roll On - 40 ml / White jasmine (Rectangular Monocarton)-399</t>
+  </si>
+  <si>
+    <t>USTTCAP24</t>
+  </si>
+  <si>
+    <t>Exfoliating Body Wash-236ml</t>
+  </si>
+  <si>
+    <t>CAP162</t>
+  </si>
+  <si>
+    <t>Intensely Hydrating Face Serum 10ml</t>
+  </si>
+  <si>
+    <t>CAP129</t>
+  </si>
+  <si>
+    <t>2% Salicylic Acid Serum 30ml</t>
+  </si>
+  <si>
+    <t>BA47</t>
+  </si>
+  <si>
+    <t>Curl Defining Hair Gel 140 ml</t>
+  </si>
+  <si>
+    <t>USTTCAP62</t>
+  </si>
+  <si>
+    <t>AHA Body Lotion 236ml - Tik Tok US</t>
+  </si>
+  <si>
+    <t>CAP119</t>
+  </si>
+  <si>
+    <t>AHA Body Lotion - 473 ml</t>
+  </si>
+  <si>
+    <t>UKTTCAP2</t>
+  </si>
+  <si>
+    <t>Acne Body Wash 473 ml- TikTok UK</t>
+  </si>
+  <si>
+    <t>BA91</t>
+  </si>
+  <si>
+    <t>Oil Control Shampoo 236ml</t>
+  </si>
+  <si>
+    <t>CAP151</t>
+  </si>
+  <si>
+    <t>AHA lotion 100 ml</t>
+  </si>
+  <si>
+    <t>USTTCAP16</t>
+  </si>
+  <si>
+    <t>Brightening body wash 236 ml - Tik Tok US</t>
+  </si>
+  <si>
+    <t>HO11</t>
+  </si>
+  <si>
+    <t>Horeca Shampoo 5L</t>
+  </si>
+  <si>
+    <t>CAP16</t>
+  </si>
+  <si>
+    <t>Brightening Body Wash (236 ml)</t>
+  </si>
+  <si>
+    <t>USTTCAP17</t>
+  </si>
+  <si>
+    <t>Brightening Body Wash-473ml</t>
+  </si>
+  <si>
+    <t>UKTTCAP1</t>
+  </si>
+  <si>
+    <t>Acne Body Wash 236 ml-TikTok UK</t>
+  </si>
+  <si>
+    <t>BA27</t>
+  </si>
+  <si>
+    <t>EXPERT | Heat Protection Spray</t>
   </si>
 </sst>
 </file>
@@ -795,7 +855,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C578346-EE80-DF41-8099-4E3028D96EBE}">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H89"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="57.1640625" customWidth="1"/>
@@ -829,10 +889,10 @@
         <v>46275</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D2" s="8">
         <v>10000</v>
@@ -845,7 +905,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -853,10 +913,10 @@
         <v>46275</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D3" s="8">
         <v>10000</v>
@@ -869,66 +929,66 @@
         <v>0</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="D4" s="4">
-        <v>1800</v>
+        <v>1200</v>
       </c>
       <c r="E4" s="4">
-        <v>1800</v>
+        <v>1200</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="6">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="D5" s="4">
-        <v>2200</v>
-      </c>
-      <c r="E5" s="4">
-        <v>2200</v>
+        <v>1800</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="6">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="D6" s="4">
         <v>3000</v>
@@ -941,138 +1001,138 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D7" s="4">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="E7" s="4">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="6">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D8" s="4">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="E8" s="4">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="6">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="D9" s="4">
-        <v>10000</v>
+        <v>6500</v>
       </c>
       <c r="E9" s="4">
-        <v>10000</v>
+        <v>6500</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="6">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="D10" s="4">
-        <v>10000</v>
+        <v>7000</v>
       </c>
       <c r="E10" s="4">
-        <v>10000</v>
+        <v>7000</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="6">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D11" s="4">
-        <v>16000</v>
+        <v>10000</v>
       </c>
       <c r="E11" s="4">
-        <v>16000</v>
+        <v>10000</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="6">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D12" s="4">
         <v>20000</v>
@@ -1085,103 +1145,103 @@
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="D13" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E13" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="6">
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="D14" s="4">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="E14" s="4">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="6">
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>43</v>
+        <v>93</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="D15" s="4">
-        <v>24000</v>
+        <v>25000</v>
       </c>
       <c r="E15" s="4">
-        <v>24000</v>
+        <v>25000</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="6">
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D16" s="4">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="E16" s="4">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="6">
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
@@ -1189,82 +1249,82 @@
         <v>46275</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D17" s="4">
-        <v>1800</v>
+        <v>48000</v>
       </c>
       <c r="E17" s="4">
-        <v>1800</v>
+        <v>48000</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="6">
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="D18" s="4">
-        <v>2500</v>
+        <v>8000</v>
       </c>
       <c r="E18" s="4">
-        <v>2500</v>
+        <v>8000</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="6">
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="D19" s="4">
-        <v>6500</v>
+        <v>8000</v>
       </c>
       <c r="E19" s="4">
-        <v>6500</v>
+        <v>8000</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="6">
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D20" s="4">
         <v>10000</v>
@@ -1277,42 +1337,42 @@
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>7</v>
+        <v>93</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>8</v>
+        <v>94</v>
       </c>
       <c r="D21" s="4">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="E21" s="4">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="6">
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="D22" s="4">
         <v>20000</v>
@@ -1325,42 +1385,42 @@
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="D23" s="4">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="E23" s="4">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="6">
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>78</v>
+        <v>7</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>79</v>
+        <v>8</v>
       </c>
       <c r="D24" s="4">
         <v>20000</v>
@@ -1373,162 +1433,162 @@
         <v>0</v>
       </c>
       <c r="H24" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>112</v>
+        <v>16</v>
       </c>
       <c r="D25" s="4">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="E25" s="4">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="6">
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="D26" s="4">
-        <v>48000</v>
+        <v>20000</v>
       </c>
       <c r="E26" s="4">
-        <v>48000</v>
+        <v>20000</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="6">
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="D27" s="4">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="E27" s="4">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="6">
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="D28" s="4">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="E28" s="4">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="6">
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D29" s="4">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="E29" s="4">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="6">
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>23</v>
+        <v>101</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="D30" s="4">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="E30" s="4">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="6">
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D31" s="4">
         <v>10000</v>
@@ -1541,103 +1601,103 @@
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="D32" s="4">
-        <v>20000</v>
+        <v>13000</v>
       </c>
       <c r="E32" s="4">
-        <v>20000</v>
+        <v>13000</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="6">
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="D33" s="4">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="E33" s="4">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="6">
         <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="D34" s="4">
-        <v>30000</v>
+        <v>24000</v>
       </c>
       <c r="E34" s="4">
-        <v>30000</v>
+        <v>24000</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="6">
         <v>0</v>
       </c>
       <c r="H34" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="D35" s="4">
-        <v>40000</v>
+        <v>28000</v>
       </c>
       <c r="E35" s="4">
-        <v>40000</v>
+        <v>28000</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="6">
         <v>0</v>
       </c>
       <c r="H35" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
@@ -1645,58 +1705,58 @@
         <v>46277</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="D36" s="4">
-        <v>7000</v>
+        <v>40000</v>
       </c>
       <c r="E36" s="4">
-        <v>7000</v>
+        <v>40000</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="6">
         <v>0</v>
       </c>
       <c r="H36" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>114</v>
+        <v>69</v>
       </c>
       <c r="D37" s="4">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="E37" s="4">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="6">
         <v>0</v>
       </c>
       <c r="H37" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="D38" s="4">
         <v>10000</v>
@@ -1709,18 +1769,18 @@
         <v>0</v>
       </c>
       <c r="H38" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D39" s="4">
         <v>10000</v>
@@ -1733,127 +1793,127 @@
         <v>0</v>
       </c>
       <c r="H39" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D40" s="4">
-        <v>13000</v>
+        <v>15000</v>
       </c>
       <c r="E40" s="4">
-        <v>13000</v>
+        <v>15000</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="6">
         <v>0</v>
       </c>
       <c r="H40" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="D41" s="4">
-        <v>20000</v>
+        <v>48000</v>
       </c>
       <c r="E41" s="4">
-        <v>20000</v>
+        <v>48000</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="6">
         <v>0</v>
       </c>
       <c r="H41" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="D42" s="4">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="E42" s="4">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="F42" s="5"/>
       <c r="G42" s="6">
         <v>0</v>
       </c>
       <c r="H42" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D43" s="4">
-        <v>28000</v>
+        <v>30000</v>
       </c>
       <c r="E43" s="4">
-        <v>28000</v>
+        <v>30000</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="6">
         <v>0</v>
       </c>
       <c r="H43" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="D44" s="4">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="E44" s="4">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="6">
         <v>0</v>
       </c>
       <c r="H44" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
@@ -1861,239 +1921,239 @@
         <v>46278</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>82</v>
+        <v>11</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
       <c r="D45" s="4">
-        <v>4000</v>
+        <v>20000</v>
       </c>
       <c r="E45" s="4">
-        <v>4000</v>
+        <v>20000</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="6">
         <v>0</v>
       </c>
       <c r="H45" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D46" s="4">
-        <v>6000</v>
-      </c>
-      <c r="E46" s="4">
-        <v>6000</v>
+        <v>73</v>
+      </c>
+      <c r="D46" s="3">
+        <v>50</v>
+      </c>
+      <c r="E46" s="3">
+        <v>50</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="6">
         <v>0</v>
       </c>
       <c r="H46" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D47" s="4">
-        <v>6000</v>
-      </c>
-      <c r="E47" s="4">
-        <v>6000</v>
+        <v>75</v>
+      </c>
+      <c r="D47" s="3">
+        <v>50</v>
+      </c>
+      <c r="E47" s="3">
+        <v>50</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="6">
         <v>0</v>
       </c>
       <c r="H47" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>25</v>
+        <v>107</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>26</v>
+        <v>108</v>
       </c>
       <c r="D48" s="4">
-        <v>7000</v>
+        <v>4000</v>
       </c>
       <c r="E48" s="4">
-        <v>7000</v>
+        <v>4000</v>
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="6">
         <v>0</v>
       </c>
       <c r="H48" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="D49" s="4">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="E49" s="4">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="6">
         <v>0</v>
       </c>
       <c r="H49" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="D50" s="4">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="E50" s="4">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="6">
         <v>0</v>
       </c>
       <c r="H50" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>18</v>
+        <v>112</v>
       </c>
       <c r="D51" s="4">
-        <v>20000</v>
+        <v>6000</v>
       </c>
       <c r="E51" s="4">
-        <v>20000</v>
+        <v>6000</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="6">
         <v>0</v>
       </c>
       <c r="H51" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D52" s="4">
-        <v>20000</v>
+        <v>7000</v>
       </c>
       <c r="E52" s="4">
-        <v>20000</v>
+        <v>7000</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="6">
         <v>0</v>
       </c>
       <c r="H52" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>15</v>
+        <v>113</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>16</v>
+        <v>114</v>
       </c>
       <c r="D53" s="4">
-        <v>30000</v>
+        <v>8000</v>
       </c>
       <c r="E53" s="4">
-        <v>30000</v>
+        <v>8000</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="6">
         <v>0</v>
       </c>
       <c r="H53" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D54" s="4">
-        <v>40000</v>
+        <v>10000</v>
       </c>
       <c r="E54" s="4">
-        <v>40000</v>
+        <v>10000</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="6">
         <v>0</v>
       </c>
       <c r="H54" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
@@ -2101,23 +2161,23 @@
         <v>46279</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D55" s="3">
-        <v>50</v>
-      </c>
-      <c r="E55" s="3">
-        <v>50</v>
+        <v>18</v>
+      </c>
+      <c r="D55" s="4">
+        <v>18000</v>
+      </c>
+      <c r="E55" s="4">
+        <v>18000</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="6">
         <v>0</v>
       </c>
       <c r="H55" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
@@ -2125,23 +2185,23 @@
         <v>46279</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D56" s="3">
-        <v>50</v>
-      </c>
-      <c r="E56" s="3">
-        <v>50</v>
+        <v>30</v>
+      </c>
+      <c r="D56" s="4">
+        <v>11000</v>
+      </c>
+      <c r="E56" s="4">
+        <v>11000</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="6">
         <v>0</v>
       </c>
       <c r="H56" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
@@ -2149,23 +2209,23 @@
         <v>46279</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D57" s="4">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="E57" s="4">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="F57" s="5"/>
       <c r="G57" s="6">
         <v>0</v>
       </c>
       <c r="H57" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
@@ -2173,380 +2233,764 @@
         <v>46279</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D58" s="4">
-        <v>11000</v>
+        <v>40000</v>
       </c>
       <c r="E58" s="4">
-        <v>11000</v>
+        <v>40000</v>
       </c>
       <c r="F58" s="5"/>
       <c r="G58" s="6">
         <v>0</v>
       </c>
       <c r="H58" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>15</v>
+        <v>115</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>16</v>
+        <v>116</v>
       </c>
       <c r="D59" s="4">
-        <v>40000</v>
+        <v>2000</v>
       </c>
       <c r="E59" s="4">
-        <v>40000</v>
+        <v>2000</v>
       </c>
       <c r="F59" s="5"/>
       <c r="G59" s="6">
         <v>0</v>
       </c>
       <c r="H59" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>13</v>
+        <v>117</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>14</v>
+        <v>118</v>
       </c>
       <c r="D60" s="4">
-        <v>40000</v>
+        <v>2500</v>
       </c>
       <c r="E60" s="4">
-        <v>40000</v>
+        <v>2500</v>
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="6">
         <v>0</v>
       </c>
       <c r="H60" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
-        <v>46289</v>
+        <v>46280</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="D61" s="4">
-        <v>30000</v>
+        <v>8000</v>
       </c>
       <c r="E61" s="4">
-        <v>30000</v>
+        <v>8000</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="6">
         <v>0</v>
       </c>
       <c r="H61" t="s">
-        <v>106</v>
+        <v>41</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
-        <v>46289</v>
+        <v>46280</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="D62" s="4">
-        <v>25000</v>
+        <v>10000</v>
       </c>
       <c r="E62" s="4">
-        <v>25000</v>
+        <v>10000</v>
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="6">
         <v>0</v>
       </c>
       <c r="H62" t="s">
-        <v>106</v>
+        <v>41</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
-        <v>46277</v>
+        <v>46280</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>96</v>
+        <v>21</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="D63" s="4">
-        <v>4000</v>
+        <v>10000</v>
       </c>
       <c r="E63" s="4">
-        <v>4000</v>
+        <v>10000</v>
       </c>
       <c r="F63" s="5"/>
       <c r="G63" s="6">
         <v>0</v>
       </c>
       <c r="H63" t="s">
-        <v>106</v>
+        <v>41</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
-        <v>46292</v>
+        <v>46280</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>98</v>
+        <v>11</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>99</v>
+        <v>12</v>
       </c>
       <c r="D64" s="4">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="E64" s="4">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="6">
         <v>0</v>
       </c>
       <c r="H64" t="s">
-        <v>106</v>
+        <v>41</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
-        <v>46292</v>
+        <v>46280</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="D65" s="4">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="E65" s="4">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="F65" s="5"/>
       <c r="G65" s="6">
         <v>0</v>
       </c>
       <c r="H65" t="s">
-        <v>106</v>
+        <v>41</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
-        <v>46274</v>
+        <v>46280</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>102</v>
+        <v>13</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="D66" s="4">
-        <v>9800</v>
+        <v>40000</v>
       </c>
       <c r="E66" s="4">
-        <v>9800</v>
+        <v>40000</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="6">
         <v>0</v>
       </c>
       <c r="H66" t="s">
-        <v>106</v>
+        <v>41</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
-        <v>46275</v>
+        <v>46281</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="D67" s="4">
-        <v>20000</v>
-      </c>
-      <c r="E67" s="4">
-        <v>20000</v>
+        <v>73</v>
+      </c>
+      <c r="D67" s="3">
+        <v>50</v>
+      </c>
+      <c r="E67" s="3">
+        <v>50</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="6">
         <v>0</v>
       </c>
       <c r="H67" t="s">
-        <v>106</v>
+        <v>41</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D68" s="4">
-        <v>7000</v>
-      </c>
-      <c r="E68" s="4">
-        <v>7000</v>
+        <v>126</v>
+      </c>
+      <c r="D68" s="3">
+        <v>50</v>
+      </c>
+      <c r="E68" s="3">
+        <v>50</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="6">
         <v>0</v>
       </c>
       <c r="H68" t="s">
-        <v>106</v>
+        <v>41</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D69" s="4">
-        <v>7000</v>
-      </c>
-      <c r="E69" s="4">
-        <v>7000</v>
+        <v>75</v>
+      </c>
+      <c r="D69" s="3">
+        <v>50</v>
+      </c>
+      <c r="E69" s="3">
+        <v>50</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="6">
         <v>0</v>
       </c>
       <c r="H69" t="s">
-        <v>106</v>
+        <v>41</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
-        <v>46287</v>
+        <v>46281</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>96</v>
+        <v>37</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>97</v>
+        <v>38</v>
       </c>
       <c r="D70" s="4">
-        <v>7900</v>
+        <v>20000</v>
       </c>
       <c r="E70" s="4">
-        <v>7900</v>
+        <v>20000</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" s="6">
         <v>0</v>
       </c>
       <c r="H70" t="s">
-        <v>106</v>
+        <v>41</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A71" s="12">
+      <c r="A71" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D71" s="4">
+        <v>40000</v>
+      </c>
+      <c r="E71" s="4">
+        <v>40000</v>
+      </c>
+      <c r="F71" s="5"/>
+      <c r="G71" s="6">
+        <v>0</v>
+      </c>
+      <c r="H71" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A72" s="2">
+        <v>46281</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D72" s="4">
+        <v>40000</v>
+      </c>
+      <c r="E72" s="4">
+        <v>40000</v>
+      </c>
+      <c r="F72" s="5"/>
+      <c r="G72" s="6">
+        <v>0</v>
+      </c>
+      <c r="H72" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A73" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D73" s="4">
+        <v>10000</v>
+      </c>
+      <c r="E73" s="4">
+        <v>10000</v>
+      </c>
+      <c r="F73" s="5"/>
+      <c r="G73" s="6">
+        <v>0</v>
+      </c>
+      <c r="H73" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A74" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D74" s="4">
+        <v>8000</v>
+      </c>
+      <c r="E74" s="4">
+        <v>8000</v>
+      </c>
+      <c r="F74" s="5"/>
+      <c r="G74" s="6">
+        <v>0</v>
+      </c>
+      <c r="H74" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A75" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D75" s="4">
+        <v>8000</v>
+      </c>
+      <c r="E75" s="4">
+        <v>8000</v>
+      </c>
+      <c r="F75" s="5"/>
+      <c r="G75" s="6">
+        <v>0</v>
+      </c>
+      <c r="H75" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A76" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D76" s="4">
+        <v>13000</v>
+      </c>
+      <c r="E76" s="4">
+        <v>13000</v>
+      </c>
+      <c r="F76" s="5"/>
+      <c r="G76" s="6">
+        <v>0</v>
+      </c>
+      <c r="H76" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A77" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D77" s="4">
+        <v>20000</v>
+      </c>
+      <c r="E77" s="4">
+        <v>20000</v>
+      </c>
+      <c r="F77" s="5"/>
+      <c r="G77" s="6">
+        <v>0</v>
+      </c>
+      <c r="H77" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A78" s="2">
+        <v>46289</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D78" s="4">
+        <v>30000</v>
+      </c>
+      <c r="E78" s="4">
+        <v>30000</v>
+      </c>
+      <c r="F78" s="5"/>
+      <c r="G78" s="6">
+        <v>0</v>
+      </c>
+      <c r="H78" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A79" s="2">
+        <v>46289</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D79" s="4">
+        <v>25000</v>
+      </c>
+      <c r="E79" s="4">
+        <v>25000</v>
+      </c>
+      <c r="F79" s="5"/>
+      <c r="G79" s="6">
+        <v>0</v>
+      </c>
+      <c r="H79" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A80" s="2">
+        <v>46277</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D80" s="4">
+        <v>4000</v>
+      </c>
+      <c r="E80" s="4">
+        <v>4000</v>
+      </c>
+      <c r="F80" s="5"/>
+      <c r="G80" s="6">
+        <v>0</v>
+      </c>
+      <c r="H80" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A81" s="2">
+        <v>46292</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D81" s="4">
+        <v>25000</v>
+      </c>
+      <c r="E81" s="4">
+        <v>25000</v>
+      </c>
+      <c r="F81" s="5"/>
+      <c r="G81" s="6">
+        <v>0</v>
+      </c>
+      <c r="H81" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A82" s="2">
+        <v>46292</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D82" s="4">
+        <v>25000</v>
+      </c>
+      <c r="E82" s="4">
+        <v>25000</v>
+      </c>
+      <c r="F82" s="5"/>
+      <c r="G82" s="6">
+        <v>0</v>
+      </c>
+      <c r="H82" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A83" s="2">
+        <v>46275</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D83" s="4">
+        <v>20000</v>
+      </c>
+      <c r="E83" s="4">
+        <v>20000</v>
+      </c>
+      <c r="F83" s="5"/>
+      <c r="G83" s="6">
+        <v>0</v>
+      </c>
+      <c r="H83" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A84" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D84" s="4">
+        <v>7000</v>
+      </c>
+      <c r="E84" s="4">
+        <v>7000</v>
+      </c>
+      <c r="F84" s="5"/>
+      <c r="G84" s="6">
+        <v>0</v>
+      </c>
+      <c r="H84" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A85" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D85" s="4">
+        <v>7000</v>
+      </c>
+      <c r="E85" s="4">
+        <v>7000</v>
+      </c>
+      <c r="F85" s="5"/>
+      <c r="G85" s="6">
+        <v>0</v>
+      </c>
+      <c r="H85" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A86" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D86" s="4">
+        <v>7900</v>
+      </c>
+      <c r="E86" s="4">
+        <v>7900</v>
+      </c>
+      <c r="F86" s="5"/>
+      <c r="G86" s="6">
+        <v>0</v>
+      </c>
+      <c r="H86" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A87" s="12">
         <v>46276</v>
       </c>
-      <c r="B71" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D71" s="4">
+      <c r="B87" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D87" s="4">
         <v>50000</v>
       </c>
-      <c r="E71" s="4">
+      <c r="E87" s="4">
         <v>50000</v>
       </c>
-      <c r="G71" s="6">
-        <v>0</v>
-      </c>
-      <c r="H71" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A72" s="12">
+      <c r="G87" s="6">
+        <v>0</v>
+      </c>
+      <c r="H87" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A88" s="12">
         <v>46277</v>
       </c>
-      <c r="B72" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D72" s="4">
+      <c r="B88" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D88" s="4">
         <v>50000</v>
       </c>
-      <c r="E72" s="4">
+      <c r="E88" s="4">
         <v>50000</v>
       </c>
-      <c r="G72" s="6">
-        <v>0</v>
-      </c>
-      <c r="H72" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A73" s="12">
+      <c r="G88" s="6">
+        <v>0</v>
+      </c>
+      <c r="H88" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A89" s="12">
         <v>46281</v>
       </c>
-      <c r="B73" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D73" s="4">
+      <c r="B89" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D89" s="4">
         <v>22000</v>
       </c>
-      <c r="E73" s="4">
+      <c r="E89" s="4">
         <v>22000</v>
       </c>
-      <c r="G73" s="6">
-        <v>0</v>
-      </c>
-      <c r="H73" t="s">
-        <v>106</v>
+      <c r="G89" s="6">
+        <v>0</v>
+      </c>
+      <c r="H89" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/data/Plan.xlsx
+++ b/data/Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raman/Documents/GitHub/production-board/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23BA6EC1-B0CE-3C48-900B-F27A1B15699F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ECF7705-8372-764C-A499-607EBF3F4F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16560" xr2:uid="{7C08584A-5D47-2049-B143-911B93E5D6E0}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="145">
   <si>
     <t>Date</t>
   </si>
@@ -101,12 +101,6 @@
     <t>BA Expert Anti Hairfall Shampoo 100 ml</t>
   </si>
   <si>
-    <t>BA24</t>
-  </si>
-  <si>
-    <t>Anti Dandruff Shampoo</t>
-  </si>
-  <si>
     <t>BA76</t>
   </si>
   <si>
@@ -119,12 +113,6 @@
     <t>Curl Intensifying Leave in Conditioner USTT</t>
   </si>
   <si>
-    <t>CAP165</t>
-  </si>
-  <si>
-    <t>Epsom Body Wash - 236ml</t>
-  </si>
-  <si>
     <t>CAP107</t>
   </si>
   <si>
@@ -149,12 +137,6 @@
     <t>Roll On: Aqua 40 ml (Rectangular Monocarton)-399</t>
   </si>
   <si>
-    <t>CAP62</t>
-  </si>
-  <si>
-    <t>AHA Body Lotion 236 ml</t>
-  </si>
-  <si>
     <t>BA74</t>
   </si>
   <si>
@@ -188,12 +170,6 @@
     <t>Combo- Anti-Hairfall Shampoo (100ml) + Anti-Hairfall Conditioner (100g)</t>
   </si>
   <si>
-    <t>CAP146</t>
-  </si>
-  <si>
-    <t>Clarifying Face Serum - 10ml</t>
-  </si>
-  <si>
     <t>CAP154</t>
   </si>
   <si>
@@ -218,12 +194,6 @@
     <t>Anti-Frizz Leave-In Conditioner</t>
   </si>
   <si>
-    <t>BA119</t>
-  </si>
-  <si>
-    <t>Anti hairfall shampoo 750 ml</t>
-  </si>
-  <si>
     <t>CAP105</t>
   </si>
   <si>
@@ -302,12 +272,6 @@
     <t>Instant Cover-Up Hair Powder Brown-4gm</t>
   </si>
   <si>
-    <t>UKTTBA107</t>
-  </si>
-  <si>
-    <t>Hair Growth Serum Roll On 25 ml</t>
-  </si>
-  <si>
     <t>Outsouce</t>
   </si>
   <si>
@@ -447,13 +411,79 @@
   </si>
   <si>
     <t>EXPERT | Heat Protection Spray</t>
+  </si>
+  <si>
+    <t>BA113</t>
+  </si>
+  <si>
+    <t>Anti Hairfall Shampoo - 500ml</t>
+  </si>
+  <si>
+    <t>BA98</t>
+  </si>
+  <si>
+    <t>Anti-Dandruff Conditioner -175gm</t>
+  </si>
+  <si>
+    <t>BA121</t>
+  </si>
+  <si>
+    <t>NxS Flaxseed &amp; Rice Water Hair Gel 300ml</t>
+  </si>
+  <si>
+    <t>BA86</t>
+  </si>
+  <si>
+    <t>Bare Anatomy Sleek Stick</t>
+  </si>
+  <si>
+    <t>BA66</t>
+  </si>
+  <si>
+    <t>Rosemary hair growth oil 100ml</t>
+  </si>
+  <si>
+    <t>BA55</t>
+  </si>
+  <si>
+    <t>Rosemary and Coconut Milk Hydrating Conditioner</t>
+  </si>
+  <si>
+    <t>CAP172</t>
+  </si>
+  <si>
+    <t>Exfoliating Face Scrub - 75ml</t>
+  </si>
+  <si>
+    <t>BA108</t>
+  </si>
+  <si>
+    <t>Neem &amp; Lemon Dandruff Control Scalp Spray - 200ml</t>
+  </si>
+  <si>
+    <t>CAP160</t>
+  </si>
+  <si>
+    <t>Oil Control Face Moisturiser - 100gm</t>
+  </si>
+  <si>
+    <t>CAP17</t>
+  </si>
+  <si>
+    <t>Brightening Body Wash (473 ml)</t>
+  </si>
+  <si>
+    <t>BA109</t>
+  </si>
+  <si>
+    <t>Advanced Anti Dandruff Serum - 50ml</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -479,6 +509,11 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Lora"/>
     </font>
   </fonts>
   <fills count="3">
@@ -507,7 +542,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -521,6 +556,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="16" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -855,7 +891,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C578346-EE80-DF41-8099-4E3028D96EBE}">
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="57.1640625" customWidth="1"/>
@@ -886,13 +922,13 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="11">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D2" s="8">
         <v>10000</v>
@@ -905,367 +941,369 @@
         <v>0</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="11">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D3" s="8">
-        <v>10000</v>
+        <f>10000-2244</f>
+        <v>7756</v>
       </c>
       <c r="E3" s="8">
-        <v>10000</v>
+        <f>10000-2244</f>
+        <v>7756</v>
       </c>
       <c r="F3" s="10"/>
       <c r="G3" s="9">
         <v>0</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D4" s="4">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="E4" s="4">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="6">
         <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="D5" s="4">
-        <v>1800</v>
-      </c>
-      <c r="E5" s="3">
-        <v>0</v>
+        <v>2000</v>
+      </c>
+      <c r="E5" s="4">
+        <v>2000</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="6">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="D6" s="4">
-        <v>3000</v>
+        <v>4500</v>
       </c>
       <c r="E6" s="4">
-        <v>3000</v>
+        <v>4500</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="6">
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="D7" s="4">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="E7" s="4">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="F7" s="5"/>
       <c r="G7" s="6">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="D8" s="4">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="E8" s="4">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="6">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>59</v>
+        <v>98</v>
       </c>
       <c r="D9" s="4">
-        <v>6500</v>
+        <v>2000</v>
       </c>
       <c r="E9" s="4">
-        <v>6500</v>
+        <v>2000</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="6">
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="D10" s="4">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="E10" s="4">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="6">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="D11" s="4">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="E11" s="4">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="6">
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D12" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E12" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="6">
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="D13" s="4">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="E13" s="4">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="6">
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="D14" s="4">
-        <v>20000</v>
+        <v>14000</v>
       </c>
       <c r="E14" s="4">
-        <v>20000</v>
+        <v>14000</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="6">
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="D15" s="4">
-        <v>25000</v>
+        <v>10000</v>
       </c>
       <c r="E15" s="4">
-        <v>25000</v>
+        <v>10000</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="6">
         <v>0</v>
       </c>
       <c r="H15" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D16" s="4">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="E16" s="4">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="6">
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="D17" s="4">
-        <v>48000</v>
+        <v>20000</v>
       </c>
       <c r="E17" s="4">
-        <v>48000</v>
+        <v>20000</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="6">
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -1273,23 +1311,23 @@
         <v>46276</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="D18" s="4">
-        <v>8000</v>
+        <v>24000</v>
       </c>
       <c r="E18" s="4">
-        <v>8000</v>
+        <v>24000</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="6">
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -1297,191 +1335,191 @@
         <v>46276</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D19" s="4">
-        <v>8000</v>
+        <v>30000</v>
       </c>
       <c r="E19" s="4">
-        <v>8000</v>
+        <v>30000</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="6">
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="D20" s="4">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="E20" s="4">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="6">
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D21" s="4">
-        <v>15000</v>
+        <v>9000</v>
       </c>
       <c r="E21" s="4">
-        <v>15000</v>
+        <v>9000</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="6">
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>27</v>
+        <v>89</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="D22" s="4">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="E22" s="4">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="6">
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="D23" s="4">
-        <v>30000</v>
+        <v>10000</v>
       </c>
       <c r="E23" s="4">
-        <v>30000</v>
+        <v>10000</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="6">
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="D24" s="4">
-        <v>20000</v>
+        <v>13000</v>
       </c>
       <c r="E24" s="4">
-        <v>20000</v>
+        <v>13000</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="6">
         <v>0</v>
       </c>
       <c r="H24" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D25" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E25" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="6">
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="D26" s="4">
-        <v>20000</v>
+        <v>24000</v>
       </c>
       <c r="E26" s="4">
-        <v>20000</v>
+        <v>24000</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="6">
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
@@ -1489,23 +1527,23 @@
         <v>46277</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>97</v>
+        <v>31</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="D27" s="4">
-        <v>5000</v>
+        <v>28000</v>
       </c>
       <c r="E27" s="4">
-        <v>5000</v>
+        <v>28000</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="6">
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
@@ -1513,82 +1551,82 @@
         <v>46277</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="D28" s="4">
-        <v>5000</v>
+        <v>40000</v>
       </c>
       <c r="E28" s="4">
-        <v>5000</v>
+        <v>40000</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="6">
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
-        <v>46277</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>95</v>
+        <v>46278</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>123</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="D29" s="4">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="E29" s="4">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="6">
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="D30" s="4">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="E30" s="4">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="6">
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="D31" s="4">
         <v>10000</v>
@@ -1601,127 +1639,127 @@
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="D32" s="4">
-        <v>13000</v>
+        <v>10000</v>
       </c>
       <c r="E32" s="4">
-        <v>13000</v>
+        <v>10000</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="6">
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="D33" s="4">
-        <v>15000</v>
+        <v>48000</v>
       </c>
       <c r="E33" s="4">
-        <v>15000</v>
+        <v>48000</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="6">
         <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="D34" s="4">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="E34" s="4">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="6">
         <v>0</v>
       </c>
       <c r="H34" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="D35" s="4">
-        <v>28000</v>
+        <v>30000</v>
       </c>
       <c r="E35" s="4">
-        <v>28000</v>
+        <v>30000</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="6">
         <v>0</v>
       </c>
       <c r="H35" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="D36" s="4">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="E36" s="4">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="6">
         <v>0</v>
       </c>
       <c r="H36" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
@@ -1729,215 +1767,215 @@
         <v>46278</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="D37" s="4">
-        <v>6000</v>
+        <v>20000</v>
       </c>
       <c r="E37" s="4">
-        <v>6000</v>
+        <v>20000</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="6">
         <v>0</v>
       </c>
       <c r="H37" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="D38" s="4">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="E38" s="4">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="6">
         <v>0</v>
       </c>
       <c r="H38" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="D39" s="4">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="E39" s="4">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="6">
         <v>0</v>
       </c>
       <c r="H39" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="D40" s="4">
-        <v>15000</v>
+        <v>6000</v>
       </c>
       <c r="E40" s="4">
-        <v>15000</v>
+        <v>6000</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="6">
         <v>0</v>
       </c>
       <c r="H40" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>104</v>
+        <v>22</v>
       </c>
       <c r="D41" s="4">
-        <v>48000</v>
+        <v>7000</v>
       </c>
       <c r="E41" s="4">
-        <v>48000</v>
+        <v>7000</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="6">
         <v>0</v>
       </c>
       <c r="H41" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>17</v>
+        <v>101</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>18</v>
+        <v>102</v>
       </c>
       <c r="D42" s="4">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="E42" s="4">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="F42" s="5"/>
       <c r="G42" s="6">
         <v>0</v>
       </c>
       <c r="H42" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D43" s="4">
-        <v>30000</v>
+        <v>10000</v>
       </c>
       <c r="E43" s="4">
-        <v>30000</v>
+        <v>10000</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="6">
         <v>0</v>
       </c>
       <c r="H43" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>105</v>
+        <v>17</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>106</v>
+        <v>18</v>
       </c>
       <c r="D44" s="4">
-        <v>20000</v>
+        <v>18000</v>
       </c>
       <c r="E44" s="4">
-        <v>20000</v>
+        <v>18000</v>
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="6">
         <v>0</v>
       </c>
       <c r="H44" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>11</v>
+        <v>125</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>12</v>
+        <v>126</v>
       </c>
       <c r="D45" s="4">
-        <v>20000</v>
+        <v>11000</v>
       </c>
       <c r="E45" s="4">
-        <v>20000</v>
+        <v>11000</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="6">
         <v>0</v>
       </c>
       <c r="H45" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
@@ -1945,23 +1983,23 @@
         <v>46279</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D46" s="3">
-        <v>50</v>
-      </c>
-      <c r="E46" s="3">
-        <v>50</v>
+        <v>30</v>
+      </c>
+      <c r="D46" s="4">
+        <v>24000</v>
+      </c>
+      <c r="E46" s="4">
+        <v>24000</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="6">
         <v>0</v>
       </c>
       <c r="H46" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
@@ -1969,23 +2007,23 @@
         <v>46279</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D47" s="3">
-        <v>50</v>
-      </c>
-      <c r="E47" s="3">
-        <v>50</v>
+        <v>14</v>
+      </c>
+      <c r="D47" s="4">
+        <v>40000</v>
+      </c>
+      <c r="E47" s="4">
+        <v>40000</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="6">
         <v>0</v>
       </c>
       <c r="H47" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
@@ -1993,154 +2031,154 @@
         <v>46279</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>107</v>
+        <v>11</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>108</v>
+        <v>12</v>
       </c>
       <c r="D48" s="4">
-        <v>4000</v>
+        <v>40000</v>
       </c>
       <c r="E48" s="4">
-        <v>4000</v>
+        <v>40000</v>
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="6">
         <v>0</v>
       </c>
       <c r="H48" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="D49" s="4">
-        <v>6000</v>
+        <v>1600</v>
       </c>
       <c r="E49" s="4">
-        <v>6000</v>
+        <v>1600</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="6">
         <v>0</v>
       </c>
       <c r="H49" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="D50" s="4">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="E50" s="4">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="6">
         <v>0</v>
       </c>
       <c r="H50" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D51" s="4">
-        <v>6000</v>
+        <v>2500</v>
       </c>
       <c r="E51" s="4">
-        <v>6000</v>
+        <v>2500</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="6">
         <v>0</v>
       </c>
       <c r="H51" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>23</v>
+        <v>129</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>24</v>
+        <v>130</v>
       </c>
       <c r="D52" s="4">
-        <v>7000</v>
+        <v>4000</v>
       </c>
       <c r="E52" s="4">
-        <v>7000</v>
+        <v>4000</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="6">
         <v>0</v>
       </c>
       <c r="H52" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D53" s="4">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="E53" s="4">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="6">
         <v>0</v>
       </c>
       <c r="H53" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>22</v>
+        <v>132</v>
       </c>
       <c r="D54" s="4">
         <v>10000</v>
@@ -2153,42 +2191,42 @@
         <v>0</v>
       </c>
       <c r="H54" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D55" s="4">
-        <v>18000</v>
+        <v>10000</v>
       </c>
       <c r="E55" s="4">
-        <v>18000</v>
+        <v>10000</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="6">
         <v>0</v>
       </c>
       <c r="H55" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D56" s="4">
         <v>11000</v>
@@ -2201,36 +2239,36 @@
         <v>0</v>
       </c>
       <c r="H56" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="D57" s="4">
-        <v>40000</v>
+        <v>48000</v>
       </c>
       <c r="E57" s="4">
-        <v>40000</v>
+        <v>48000</v>
       </c>
       <c r="F57" s="5"/>
       <c r="G57" s="6">
         <v>0</v>
       </c>
       <c r="H57" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>11</v>
@@ -2239,17 +2277,17 @@
         <v>12</v>
       </c>
       <c r="D58" s="4">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="E58" s="4">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="F58" s="5"/>
       <c r="G58" s="6">
         <v>0</v>
       </c>
       <c r="H58" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
@@ -2257,23 +2295,23 @@
         <v>46280</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D59" s="4">
-        <v>2000</v>
+        <v>20000</v>
       </c>
       <c r="E59" s="4">
-        <v>2000</v>
+        <v>20000</v>
       </c>
       <c r="F59" s="5"/>
       <c r="G59" s="6">
         <v>0</v>
       </c>
       <c r="H59" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
@@ -2281,130 +2319,130 @@
         <v>46280</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>117</v>
+        <v>13</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>118</v>
+        <v>14</v>
       </c>
       <c r="D60" s="4">
-        <v>2500</v>
+        <v>40000</v>
       </c>
       <c r="E60" s="4">
-        <v>2500</v>
+        <v>40000</v>
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="6">
         <v>0</v>
       </c>
       <c r="H60" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>119</v>
+        <v>62</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D61" s="4">
-        <v>8000</v>
-      </c>
-      <c r="E61" s="4">
-        <v>8000</v>
+        <v>63</v>
+      </c>
+      <c r="D61" s="3">
+        <v>50</v>
+      </c>
+      <c r="E61" s="3">
+        <v>50</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="6">
         <v>0</v>
       </c>
       <c r="H61" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>121</v>
+        <v>64</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D62" s="4">
-        <v>10000</v>
-      </c>
-      <c r="E62" s="4">
-        <v>10000</v>
+        <v>65</v>
+      </c>
+      <c r="D62" s="3">
+        <v>50</v>
+      </c>
+      <c r="E62" s="3">
+        <v>50</v>
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="6">
         <v>0</v>
       </c>
       <c r="H62" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D63" s="4">
-        <v>10000</v>
+        <v>5500</v>
       </c>
       <c r="E63" s="4">
-        <v>10000</v>
+        <v>5500</v>
       </c>
       <c r="F63" s="5"/>
       <c r="G63" s="6">
         <v>0</v>
       </c>
       <c r="H63" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="D64" s="4">
-        <v>20000</v>
+        <v>7000</v>
       </c>
       <c r="E64" s="4">
-        <v>20000</v>
+        <v>7000</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="6">
         <v>0</v>
       </c>
       <c r="H64" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>123</v>
+        <v>23</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>124</v>
+        <v>24</v>
       </c>
       <c r="D65" s="4">
         <v>20000</v>
@@ -2417,31 +2455,31 @@
         <v>0</v>
       </c>
       <c r="H65" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D66" s="4">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="E66" s="4">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="6">
         <v>0</v>
       </c>
       <c r="H66" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
@@ -2449,23 +2487,23 @@
         <v>46281</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D67" s="3">
-        <v>50</v>
-      </c>
-      <c r="E67" s="3">
-        <v>50</v>
+        <v>14</v>
+      </c>
+      <c r="D67" s="4">
+        <v>40000</v>
+      </c>
+      <c r="E67" s="4">
+        <v>40000</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="6">
         <v>0</v>
       </c>
       <c r="H67" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
@@ -2473,119 +2511,119 @@
         <v>46281</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D68" s="3">
-        <v>50</v>
-      </c>
-      <c r="E68" s="3">
-        <v>50</v>
+        <v>116</v>
+      </c>
+      <c r="D68" s="4">
+        <v>40000</v>
+      </c>
+      <c r="E68" s="4">
+        <v>40000</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="6">
         <v>0</v>
       </c>
       <c r="H68" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D69" s="3">
-        <v>50</v>
-      </c>
-      <c r="E69" s="3">
-        <v>50</v>
+        <v>134</v>
+      </c>
+      <c r="D69" s="4">
+        <v>6000</v>
+      </c>
+      <c r="E69" s="4">
+        <v>6000</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="6">
         <v>0</v>
       </c>
       <c r="H69" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>37</v>
+        <v>117</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>38</v>
+        <v>118</v>
       </c>
       <c r="D70" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E70" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" s="6">
         <v>0</v>
       </c>
       <c r="H70" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>13</v>
+        <v>119</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>14</v>
+        <v>120</v>
       </c>
       <c r="D71" s="4">
-        <v>40000</v>
+        <v>8000</v>
       </c>
       <c r="E71" s="4">
-        <v>40000</v>
+        <v>8000</v>
       </c>
       <c r="F71" s="5"/>
       <c r="G71" s="6">
         <v>0</v>
       </c>
       <c r="H71" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>127</v>
+        <v>31</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="D72" s="4">
-        <v>40000</v>
+        <v>8000</v>
       </c>
       <c r="E72" s="4">
-        <v>40000</v>
+        <v>8000</v>
       </c>
       <c r="F72" s="5"/>
       <c r="G72" s="6">
         <v>0</v>
       </c>
       <c r="H72" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
@@ -2593,47 +2631,47 @@
         <v>46282</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D73" s="4">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="E73" s="4">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="F73" s="5"/>
       <c r="G73" s="6">
         <v>0</v>
       </c>
       <c r="H73" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <v>46282</v>
       </c>
-      <c r="B74" s="3" t="s">
-        <v>131</v>
+      <c r="B74" s="13" t="s">
+        <v>135</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D74" s="4">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="E74" s="4">
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="F74" s="5"/>
       <c r="G74" s="6">
         <v>0</v>
       </c>
       <c r="H74" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
@@ -2641,23 +2679,23 @@
         <v>46282</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>38</v>
+        <v>122</v>
       </c>
       <c r="D75" s="4">
-        <v>8000</v>
+        <v>13000</v>
       </c>
       <c r="E75" s="4">
-        <v>8000</v>
+        <v>13000</v>
       </c>
       <c r="F75" s="5"/>
       <c r="G75" s="6">
         <v>0</v>
       </c>
       <c r="H75" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
@@ -2665,23 +2703,23 @@
         <v>46282</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="D76" s="4">
-        <v>13000</v>
+        <v>20000</v>
       </c>
       <c r="E76" s="4">
-        <v>13000</v>
+        <v>20000</v>
       </c>
       <c r="F76" s="5"/>
       <c r="G76" s="6">
         <v>0</v>
       </c>
       <c r="H76" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
@@ -2689,10 +2727,10 @@
         <v>46282</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>127</v>
+        <v>17</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>128</v>
+        <v>18</v>
       </c>
       <c r="D77" s="4">
         <v>20000</v>
@@ -2705,292 +2743,652 @@
         <v>0</v>
       </c>
       <c r="H77" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
-        <v>46289</v>
+        <v>46282</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>76</v>
+        <v>137</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="D78" s="4">
-        <v>30000</v>
+        <v>15000</v>
       </c>
       <c r="E78" s="4">
-        <v>30000</v>
+        <v>15000</v>
       </c>
       <c r="F78" s="5"/>
       <c r="G78" s="6">
         <v>0</v>
       </c>
       <c r="H78" t="s">
-        <v>88</v>
+        <v>35</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
-        <v>46289</v>
+        <v>46282</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="D79" s="4">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="E79" s="4">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="F79" s="5"/>
       <c r="G79" s="6">
         <v>0</v>
       </c>
       <c r="H79" t="s">
-        <v>88</v>
+        <v>35</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
-        <v>46277</v>
+        <v>46283</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D80" s="4">
-        <v>4000</v>
-      </c>
-      <c r="E80" s="4">
-        <v>4000</v>
+        <v>114</v>
+      </c>
+      <c r="D80" s="3">
+        <v>50</v>
+      </c>
+      <c r="E80" s="3">
+        <v>50</v>
       </c>
       <c r="F80" s="5"/>
       <c r="G80" s="6">
         <v>0</v>
       </c>
       <c r="H80" t="s">
-        <v>88</v>
+        <v>35</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
-        <v>46292</v>
+        <v>46283</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>82</v>
+        <v>139</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="D81" s="4">
-        <v>25000</v>
+        <v>2500</v>
       </c>
       <c r="E81" s="4">
-        <v>25000</v>
+        <v>2500</v>
       </c>
       <c r="F81" s="5"/>
       <c r="G81" s="6">
         <v>0</v>
       </c>
       <c r="H81" t="s">
-        <v>88</v>
+        <v>35</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
-        <v>46292</v>
+        <v>46283</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="D82" s="4">
-        <v>25000</v>
+        <v>8000</v>
       </c>
       <c r="E82" s="4">
-        <v>25000</v>
+        <v>8000</v>
       </c>
       <c r="F82" s="5"/>
       <c r="G82" s="6">
         <v>0</v>
       </c>
       <c r="H82" t="s">
-        <v>88</v>
+        <v>35</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
-        <v>46275</v>
+        <v>46283</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>86</v>
+        <v>141</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="D83" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="E83" s="4">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F83" s="5"/>
       <c r="G83" s="6">
         <v>0</v>
       </c>
       <c r="H83" t="s">
-        <v>88</v>
+        <v>35</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
-        <v>46280</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>80</v>
+        <v>46283</v>
+      </c>
+      <c r="B84" s="13" t="s">
+        <v>143</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>81</v>
+        <v>144</v>
       </c>
       <c r="D84" s="4">
-        <v>7000</v>
+        <v>10000</v>
       </c>
       <c r="E84" s="4">
-        <v>7000</v>
+        <v>10000</v>
       </c>
       <c r="F84" s="5"/>
       <c r="G84" s="6">
         <v>0</v>
       </c>
       <c r="H84" t="s">
-        <v>88</v>
+        <v>35</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>80</v>
+        <v>19</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="D85" s="4">
-        <v>7000</v>
+        <v>10000</v>
       </c>
       <c r="E85" s="4">
-        <v>7000</v>
+        <v>10000</v>
       </c>
       <c r="F85" s="5"/>
       <c r="G85" s="6">
         <v>0</v>
       </c>
       <c r="H85" t="s">
-        <v>88</v>
+        <v>35</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
-        <v>46287</v>
+        <v>46283</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="D86" s="4">
-        <v>7900</v>
+        <v>20000</v>
       </c>
       <c r="E86" s="4">
-        <v>7900</v>
+        <v>20000</v>
       </c>
       <c r="F86" s="5"/>
       <c r="G86" s="6">
         <v>0</v>
       </c>
       <c r="H86" t="s">
-        <v>88</v>
+        <v>35</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A87" s="12">
+      <c r="A87" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D87" s="4">
+        <v>20000</v>
+      </c>
+      <c r="E87" s="4">
+        <v>20000</v>
+      </c>
+      <c r="F87" s="5"/>
+      <c r="G87" s="6">
+        <v>0</v>
+      </c>
+      <c r="H87" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A88" s="2">
+        <v>46283</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D88" s="4">
+        <v>40000</v>
+      </c>
+      <c r="E88" s="4">
+        <v>40000</v>
+      </c>
+      <c r="F88" s="5"/>
+      <c r="G88" s="6">
+        <v>0</v>
+      </c>
+      <c r="H88" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A89" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D89" s="4">
+        <v>20000</v>
+      </c>
+      <c r="E89" s="4">
+        <v>20000</v>
+      </c>
+      <c r="F89" s="5"/>
+      <c r="G89" s="6">
+        <v>0</v>
+      </c>
+      <c r="H89" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A90" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D90" s="4">
+        <v>11000</v>
+      </c>
+      <c r="E90" s="4">
+        <v>11000</v>
+      </c>
+      <c r="F90" s="5"/>
+      <c r="G90" s="6">
+        <v>0</v>
+      </c>
+      <c r="H90" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A91" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D91" s="4">
+        <v>20000</v>
+      </c>
+      <c r="E91" s="4">
+        <v>20000</v>
+      </c>
+      <c r="F91" s="5"/>
+      <c r="G91" s="6">
+        <v>0</v>
+      </c>
+      <c r="H91" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A92" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D92" s="4">
+        <v>10000</v>
+      </c>
+      <c r="E92" s="4">
+        <v>10000</v>
+      </c>
+      <c r="F92" s="5"/>
+      <c r="G92" s="6">
+        <v>0</v>
+      </c>
+      <c r="H92" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A93" s="2">
+        <v>46284</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D93" s="4">
+        <v>40000</v>
+      </c>
+      <c r="E93" s="4">
+        <v>40000</v>
+      </c>
+      <c r="F93" s="5"/>
+      <c r="G93" s="6">
+        <v>0</v>
+      </c>
+      <c r="H93" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A94" s="2">
+        <v>46289</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D94" s="4">
+        <v>30000</v>
+      </c>
+      <c r="E94" s="4">
+        <v>30000</v>
+      </c>
+      <c r="F94" s="5"/>
+      <c r="G94" s="6">
+        <v>0</v>
+      </c>
+      <c r="H94" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A95" s="2">
+        <v>46289</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D95" s="4">
+        <v>25000</v>
+      </c>
+      <c r="E95" s="4">
+        <v>25000</v>
+      </c>
+      <c r="F95" s="5"/>
+      <c r="G95" s="6">
+        <v>0</v>
+      </c>
+      <c r="H95" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A96" s="2">
+        <v>46277</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D96" s="4">
+        <v>4000</v>
+      </c>
+      <c r="E96" s="4">
+        <v>4000</v>
+      </c>
+      <c r="F96" s="5"/>
+      <c r="G96" s="6">
+        <v>0</v>
+      </c>
+      <c r="H96" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A97" s="2">
+        <v>46292</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D97" s="4">
+        <v>25000</v>
+      </c>
+      <c r="E97" s="4">
+        <v>25000</v>
+      </c>
+      <c r="F97" s="5"/>
+      <c r="G97" s="6">
+        <v>0</v>
+      </c>
+      <c r="H97" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A98" s="2">
+        <v>46292</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D98" s="4">
+        <v>25000</v>
+      </c>
+      <c r="E98" s="4">
+        <v>25000</v>
+      </c>
+      <c r="F98" s="5"/>
+      <c r="G98" s="6">
+        <v>0</v>
+      </c>
+      <c r="H98" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A99" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D99" s="4">
+        <v>7000</v>
+      </c>
+      <c r="E99" s="4">
+        <v>7000</v>
+      </c>
+      <c r="F99" s="5"/>
+      <c r="G99" s="6">
+        <v>0</v>
+      </c>
+      <c r="H99" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A100" s="2">
+        <v>46282</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D100" s="4">
+        <v>7000</v>
+      </c>
+      <c r="E100" s="4">
+        <v>7000</v>
+      </c>
+      <c r="F100" s="5"/>
+      <c r="G100" s="6">
+        <v>0</v>
+      </c>
+      <c r="H100" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A101" s="2">
+        <v>46287</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D101" s="4">
+        <v>7900</v>
+      </c>
+      <c r="E101" s="4">
+        <v>7900</v>
+      </c>
+      <c r="F101" s="5"/>
+      <c r="G101" s="6">
+        <v>0</v>
+      </c>
+      <c r="H101" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A102" s="12">
         <v>46276</v>
       </c>
-      <c r="B87" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D87" s="4">
+      <c r="B102" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D102" s="4">
         <v>50000</v>
       </c>
-      <c r="E87" s="4">
+      <c r="E102" s="4">
         <v>50000</v>
       </c>
-      <c r="G87" s="6">
-        <v>0</v>
-      </c>
-      <c r="H87" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A88" s="12">
+      <c r="G102" s="6">
+        <v>0</v>
+      </c>
+      <c r="H102" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A103" s="12">
         <v>46277</v>
       </c>
-      <c r="B88" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D88" s="4">
+      <c r="B103" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D103" s="4">
         <v>50000</v>
       </c>
-      <c r="E88" s="4">
+      <c r="E103" s="4">
         <v>50000</v>
       </c>
-      <c r="G88" s="6">
-        <v>0</v>
-      </c>
-      <c r="H88" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A89" s="12">
+      <c r="G103" s="6">
+        <v>0</v>
+      </c>
+      <c r="H103" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A104" s="12">
         <v>46281</v>
       </c>
-      <c r="B89" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D89" s="4">
+      <c r="B104" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D104" s="4">
         <v>22000</v>
       </c>
-      <c r="E89" s="4">
+      <c r="E104" s="4">
         <v>22000</v>
       </c>
-      <c r="G89" s="6">
-        <v>0</v>
-      </c>
-      <c r="H89" t="s">
-        <v>88</v>
+      <c r="G104" s="6">
+        <v>0</v>
+      </c>
+      <c r="H104" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
